--- a/artfynd/A 26476-2025 artfynd.xlsx
+++ b/artfynd/A 26476-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2210,6 +2210,754 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125619776</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78684</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stor-Gravberget, Stor-Gravberget, Borgsjö, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>521964</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6936664</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125619796</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92448</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stor-Gravberget, Stor-Gravberget, Borgsjö, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>521959</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6936665</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125599631</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78684</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>521971</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6936621</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125620054</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92448</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stor-Gravberget, Stor-Gravberget, Borgsjö, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>521953</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6936546</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125621452</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91326</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sundsvallstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>521972</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6936608</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125619751</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92448</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stor-Gravberget, Stor-Gravberget, Borgsjö, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>522009</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6936700</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125619969</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stor-Gravberget, Stor-Gravberget, Borgsjö, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>522066</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6936575</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Rebecka Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26476-2025 artfynd.xlsx
+++ b/artfynd/A 26476-2025 artfynd.xlsx
@@ -4483,10 +4483,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125646878</v>
+        <v>125632396</v>
       </c>
       <c r="B35" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4495,25 +4495,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4523,13 +4523,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>522019</v>
+        <v>522109</v>
       </c>
       <c r="R35" t="n">
-        <v>6936608</v>
+        <v>6936384</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4553,12 +4553,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4573,22 +4583,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125601355</v>
+        <v>125632387</v>
       </c>
       <c r="B36" t="n">
-        <v>98290</v>
+        <v>98269</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4597,25 +4607,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4625,13 +4635,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>522217</v>
+        <v>522191</v>
       </c>
       <c r="R36" t="n">
-        <v>6936540</v>
+        <v>6936398</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4658,9 +4668,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4675,22 +4695,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125632396</v>
+        <v>125632422</v>
       </c>
       <c r="B37" t="n">
-        <v>98269</v>
+        <v>92448</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4699,25 +4719,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4727,10 +4747,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>522109</v>
+        <v>522263</v>
       </c>
       <c r="R37" t="n">
-        <v>6936384</v>
+        <v>6936447</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -4762,7 +4782,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4772,7 +4792,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4799,10 +4819,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125632387</v>
+        <v>125632324</v>
       </c>
       <c r="B38" t="n">
-        <v>98269</v>
+        <v>92448</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4811,25 +4831,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4839,10 +4859,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>522191</v>
+        <v>522198</v>
       </c>
       <c r="R38" t="n">
-        <v>6936398</v>
+        <v>6936634</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4874,7 +4894,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4884,7 +4904,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4911,10 +4931,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125632422</v>
+        <v>125632323</v>
       </c>
       <c r="B39" t="n">
-        <v>92448</v>
+        <v>78947</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4923,25 +4943,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4951,10 +4971,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>522263</v>
+        <v>522189</v>
       </c>
       <c r="R39" t="n">
-        <v>6936447</v>
+        <v>6936648</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -4986,7 +5006,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4996,7 +5016,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5023,10 +5043,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125632324</v>
+        <v>125632346</v>
       </c>
       <c r="B40" t="n">
-        <v>92448</v>
+        <v>80028</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5035,25 +5055,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5063,10 +5083,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>522198</v>
+        <v>522239</v>
       </c>
       <c r="R40" t="n">
-        <v>6936634</v>
+        <v>6936527</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5098,7 +5118,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5108,7 +5128,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5135,10 +5155,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125632323</v>
+        <v>125646878</v>
       </c>
       <c r="B41" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5151,21 +5171,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5175,13 +5195,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>522189</v>
+        <v>522019</v>
       </c>
       <c r="R41" t="n">
-        <v>6936648</v>
+        <v>6936608</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5205,22 +5225,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>12:51</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>12:51</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5235,22 +5245,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125632346</v>
+        <v>125601355</v>
       </c>
       <c r="B42" t="n">
-        <v>80028</v>
+        <v>98290</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5259,25 +5269,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5287,13 +5297,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>522239</v>
+        <v>522217</v>
       </c>
       <c r="R42" t="n">
-        <v>6936527</v>
+        <v>6936540</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5320,19 +5330,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:38</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5347,12 +5347,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -6031,7 +6031,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125632385</v>
+        <v>125633218</v>
       </c>
       <c r="B49" t="n">
         <v>98269</v>
@@ -6067,17 +6067,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>MD1:Ånge, SE-VN, SE, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>522197</v>
+        <v>522221</v>
       </c>
       <c r="R49" t="n">
-        <v>6936406</v>
+        <v>6936591</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6143,7 +6143,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125632394</v>
+        <v>125635540</v>
       </c>
       <c r="B50" t="n">
         <v>98269</v>
@@ -6179,17 +6179,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>522136</v>
+        <v>522055</v>
       </c>
       <c r="R50" t="n">
-        <v>6936370</v>
+        <v>6936516</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6213,22 +6213,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6243,22 +6233,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125633218</v>
+        <v>125646875</v>
       </c>
       <c r="B51" t="n">
-        <v>98269</v>
+        <v>78684</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6267,41 +6257,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>MD1:Ånge, SE-VN, SE, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>522221</v>
+        <v>522035</v>
       </c>
       <c r="R51" t="n">
-        <v>6936591</v>
+        <v>6936550</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6325,22 +6315,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>13:16</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>13:16</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6355,22 +6335,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125635540</v>
+        <v>125601877</v>
       </c>
       <c r="B52" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6379,41 +6359,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>522055</v>
+        <v>522217</v>
       </c>
       <c r="R52" t="n">
-        <v>6936516</v>
+        <v>6936540</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6437,12 +6417,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6457,22 +6437,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125601877</v>
+        <v>125632385</v>
       </c>
       <c r="B53" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6481,25 +6461,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6509,13 +6489,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>522217</v>
+        <v>522197</v>
       </c>
       <c r="R53" t="n">
-        <v>6936540</v>
+        <v>6936406</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6542,9 +6522,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6559,22 +6549,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125646875</v>
+        <v>125632394</v>
       </c>
       <c r="B54" t="n">
-        <v>78684</v>
+        <v>98269</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6583,25 +6573,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6611,13 +6601,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>522035</v>
+        <v>522136</v>
       </c>
       <c r="R54" t="n">
-        <v>6936550</v>
+        <v>6936370</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6641,12 +6631,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6661,22 +6661,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125636925</v>
+        <v>125632410</v>
       </c>
       <c r="B55" t="n">
-        <v>98269</v>
+        <v>92448</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6685,41 +6685,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>522220</v>
+        <v>522063</v>
       </c>
       <c r="R55" t="n">
-        <v>6936601</v>
+        <v>6936423</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6743,12 +6743,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6763,22 +6773,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125632410</v>
+        <v>125636925</v>
       </c>
       <c r="B56" t="n">
-        <v>92448</v>
+        <v>98269</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6787,41 +6797,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>522063</v>
+        <v>522220</v>
       </c>
       <c r="R56" t="n">
-        <v>6936423</v>
+        <v>6936601</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6845,22 +6855,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6875,22 +6875,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125646883</v>
+        <v>125601077</v>
       </c>
       <c r="B57" t="n">
-        <v>98269</v>
+        <v>80029</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6899,25 +6899,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6927,13 +6927,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>522097</v>
+        <v>522217</v>
       </c>
       <c r="R57" t="n">
-        <v>6936427</v>
+        <v>6936540</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6957,12 +6957,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6973,23 +6973,38 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125646888</v>
+        <v>125646883</v>
       </c>
       <c r="B58" t="n">
         <v>98269</v>
@@ -7029,10 +7044,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>522159</v>
+        <v>522097</v>
       </c>
       <c r="R58" t="n">
-        <v>6936405</v>
+        <v>6936427</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7091,10 +7106,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125601077</v>
+        <v>125646888</v>
       </c>
       <c r="B59" t="n">
-        <v>80029</v>
+        <v>98269</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7103,25 +7118,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7131,13 +7146,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>522217</v>
+        <v>522159</v>
       </c>
       <c r="R59" t="n">
-        <v>6936540</v>
+        <v>6936405</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7161,12 +7176,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7177,31 +7192,16 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7870,10 +7870,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125632390</v>
+        <v>125632353</v>
       </c>
       <c r="B66" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7882,25 +7882,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7910,10 +7910,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>522187</v>
+        <v>522241</v>
       </c>
       <c r="R66" t="n">
-        <v>6936377</v>
+        <v>6936509</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -7945,7 +7945,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7982,10 +7982,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125632383</v>
+        <v>125632360</v>
       </c>
       <c r="B67" t="n">
-        <v>91166</v>
+        <v>57632</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7998,21 +7998,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8022,10 +8022,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>522219</v>
+        <v>522247</v>
       </c>
       <c r="R67" t="n">
-        <v>6936411</v>
+        <v>6936482</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -8057,7 +8057,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8067,7 +8067,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>födosök död stående tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8094,10 +8099,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125600959</v>
+        <v>125632390</v>
       </c>
       <c r="B68" t="n">
-        <v>80028</v>
+        <v>91166</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8110,21 +8115,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8134,13 +8139,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>522217</v>
+        <v>522187</v>
       </c>
       <c r="R68" t="n">
-        <v>6936540</v>
+        <v>6936377</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8167,11 +8172,21 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8180,41 +8195,26 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125646893</v>
+        <v>125632383</v>
       </c>
       <c r="B69" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8223,25 +8223,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8251,13 +8251,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>522204</v>
+        <v>522219</v>
       </c>
       <c r="R69" t="n">
-        <v>6936495</v>
+        <v>6936411</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8281,12 +8281,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8301,19 +8311,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125646891</v>
+        <v>125646893</v>
       </c>
       <c r="B70" t="n">
         <v>98269</v>
@@ -8353,10 +8363,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>522159</v>
+        <v>522204</v>
       </c>
       <c r="R70" t="n">
-        <v>6936408</v>
+        <v>6936495</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8415,7 +8425,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125632353</v>
+        <v>125646891</v>
       </c>
       <c r="B71" t="n">
         <v>98269</v>
@@ -8455,13 +8465,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>522241</v>
+        <v>522159</v>
       </c>
       <c r="R71" t="n">
-        <v>6936509</v>
+        <v>6936408</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8485,22 +8495,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8515,22 +8515,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125632360</v>
+        <v>125600959</v>
       </c>
       <c r="B72" t="n">
-        <v>57632</v>
+        <v>80028</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8543,21 +8543,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8567,13 +8567,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>522247</v>
+        <v>522217</v>
       </c>
       <c r="R72" t="n">
-        <v>6936482</v>
+        <v>6936540</v>
       </c>
       <c r="S72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8600,26 +8600,11 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>födosök död stående tall</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -8628,16 +8613,31 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -9428,10 +9428,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125637290</v>
+        <v>125633219</v>
       </c>
       <c r="B80" t="n">
-        <v>78683</v>
+        <v>98269</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9440,41 +9440,41 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>MD0:Ånge, SE-VN, SE, Mpd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>522366</v>
+        <v>522237</v>
       </c>
       <c r="R80" t="n">
-        <v>6936463</v>
+        <v>6936437</v>
       </c>
       <c r="S80" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9498,12 +9498,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9518,22 +9528,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125633219</v>
+        <v>125637290</v>
       </c>
       <c r="B81" t="n">
-        <v>98269</v>
+        <v>78683</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9542,41 +9552,41 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>MD0:Ånge, SE-VN, SE, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>522237</v>
+        <v>522366</v>
       </c>
       <c r="R81" t="n">
-        <v>6936437</v>
+        <v>6936463</v>
       </c>
       <c r="S81" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9600,22 +9610,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>14:21</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>14:21</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9630,12 +9630,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -16575,10 +16575,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125632349</v>
+        <v>125637200</v>
       </c>
       <c r="B146" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16587,41 +16587,41 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>522259</v>
+        <v>522362</v>
       </c>
       <c r="R146" t="n">
-        <v>6936489</v>
+        <v>6936466</v>
       </c>
       <c r="S146" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -16645,22 +16645,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16675,22 +16665,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125632350</v>
+        <v>125637287</v>
       </c>
       <c r="B147" t="n">
-        <v>80028</v>
+        <v>79565</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16703,37 +16693,37 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>522254</v>
+        <v>522356</v>
       </c>
       <c r="R147" t="n">
-        <v>6936496</v>
+        <v>6936466</v>
       </c>
       <c r="S147" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16757,22 +16747,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>13:47</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>13:47</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16787,22 +16767,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125637200</v>
+        <v>125646874</v>
       </c>
       <c r="B148" t="n">
-        <v>78947</v>
+        <v>80056</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16811,41 +16791,41 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>522362</v>
+        <v>522022</v>
       </c>
       <c r="R148" t="n">
-        <v>6936466</v>
+        <v>6936611</v>
       </c>
       <c r="S148" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16901,10 +16881,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125637287</v>
+        <v>125646884</v>
       </c>
       <c r="B149" t="n">
-        <v>79565</v>
+        <v>98269</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16913,41 +16893,41 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>522356</v>
+        <v>522100</v>
       </c>
       <c r="R149" t="n">
-        <v>6936466</v>
+        <v>6936419</v>
       </c>
       <c r="S149" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17003,10 +16983,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125646874</v>
+        <v>125601890</v>
       </c>
       <c r="B150" t="n">
-        <v>80056</v>
+        <v>91617</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17015,25 +16995,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6461</v>
+        <v>1209</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17043,13 +17023,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>522022</v>
+        <v>522217</v>
       </c>
       <c r="R150" t="n">
-        <v>6936611</v>
+        <v>6936540</v>
       </c>
       <c r="S150" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17073,12 +17053,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17093,19 +17073,19 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125646884</v>
+        <v>125632349</v>
       </c>
       <c r="B151" t="n">
         <v>98269</v>
@@ -17145,13 +17125,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>522100</v>
+        <v>522259</v>
       </c>
       <c r="R151" t="n">
-        <v>6936419</v>
+        <v>6936489</v>
       </c>
       <c r="S151" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17175,12 +17155,22 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17195,22 +17185,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125601890</v>
+        <v>125632350</v>
       </c>
       <c r="B152" t="n">
-        <v>91617</v>
+        <v>80028</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17219,25 +17209,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -17247,13 +17237,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>522217</v>
+        <v>522254</v>
       </c>
       <c r="R152" t="n">
-        <v>6936540</v>
+        <v>6936496</v>
       </c>
       <c r="S152" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17280,9 +17270,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17297,12 +17297,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>

--- a/artfynd/A 26476-2025 artfynd.xlsx
+++ b/artfynd/A 26476-2025 artfynd.xlsx
@@ -6673,10 +6673,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125632410</v>
+        <v>125636925</v>
       </c>
       <c r="B55" t="n">
-        <v>92448</v>
+        <v>98269</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6685,41 +6685,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>522063</v>
+        <v>522220</v>
       </c>
       <c r="R55" t="n">
-        <v>6936423</v>
+        <v>6936601</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6743,22 +6743,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6773,22 +6763,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125636925</v>
+        <v>125632410</v>
       </c>
       <c r="B56" t="n">
-        <v>98269</v>
+        <v>92448</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6797,41 +6787,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>522220</v>
+        <v>522063</v>
       </c>
       <c r="R56" t="n">
-        <v>6936601</v>
+        <v>6936423</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6855,12 +6845,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6875,22 +6875,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125601077</v>
+        <v>125646883</v>
       </c>
       <c r="B57" t="n">
-        <v>80029</v>
+        <v>98269</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6899,25 +6899,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6927,13 +6927,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>522217</v>
+        <v>522097</v>
       </c>
       <c r="R57" t="n">
-        <v>6936540</v>
+        <v>6936427</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6957,12 +6957,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6973,38 +6973,23 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125646883</v>
+        <v>125646888</v>
       </c>
       <c r="B58" t="n">
         <v>98269</v>
@@ -7044,10 +7029,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>522097</v>
+        <v>522159</v>
       </c>
       <c r="R58" t="n">
-        <v>6936427</v>
+        <v>6936405</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7106,10 +7091,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125646888</v>
+        <v>125601077</v>
       </c>
       <c r="B59" t="n">
-        <v>98269</v>
+        <v>80029</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7118,25 +7103,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7146,13 +7131,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>522159</v>
+        <v>522217</v>
       </c>
       <c r="R59" t="n">
-        <v>6936405</v>
+        <v>6936540</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7176,12 +7161,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7192,16 +7177,31 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7870,10 +7870,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125632353</v>
+        <v>125632390</v>
       </c>
       <c r="B66" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7882,25 +7882,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7910,10 +7910,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>522241</v>
+        <v>522187</v>
       </c>
       <c r="R66" t="n">
-        <v>6936509</v>
+        <v>6936377</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -7945,7 +7945,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7982,10 +7982,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125632360</v>
+        <v>125632383</v>
       </c>
       <c r="B67" t="n">
-        <v>57632</v>
+        <v>91166</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7998,21 +7998,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8022,10 +8022,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>522247</v>
+        <v>522219</v>
       </c>
       <c r="R67" t="n">
-        <v>6936482</v>
+        <v>6936411</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -8057,7 +8057,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8067,12 +8067,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>födosök död stående tall</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8099,10 +8094,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125632390</v>
+        <v>125600959</v>
       </c>
       <c r="B68" t="n">
-        <v>91166</v>
+        <v>80028</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8115,21 +8110,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8139,13 +8134,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>522187</v>
+        <v>522217</v>
       </c>
       <c r="R68" t="n">
-        <v>6936377</v>
+        <v>6936540</v>
       </c>
       <c r="S68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8172,21 +8167,11 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>14:52</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>14:52</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8195,26 +8180,41 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125632383</v>
+        <v>125646893</v>
       </c>
       <c r="B69" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8223,25 +8223,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8251,13 +8251,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>522219</v>
+        <v>522204</v>
       </c>
       <c r="R69" t="n">
-        <v>6936411</v>
+        <v>6936495</v>
       </c>
       <c r="S69" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8281,22 +8281,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8311,19 +8301,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125646893</v>
+        <v>125646891</v>
       </c>
       <c r="B70" t="n">
         <v>98269</v>
@@ -8363,10 +8353,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>522204</v>
+        <v>522159</v>
       </c>
       <c r="R70" t="n">
-        <v>6936495</v>
+        <v>6936408</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8425,7 +8415,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125646891</v>
+        <v>125632353</v>
       </c>
       <c r="B71" t="n">
         <v>98269</v>
@@ -8465,13 +8455,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>522159</v>
+        <v>522241</v>
       </c>
       <c r="R71" t="n">
-        <v>6936408</v>
+        <v>6936509</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8495,12 +8485,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8515,22 +8515,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125600959</v>
+        <v>125632360</v>
       </c>
       <c r="B72" t="n">
-        <v>80028</v>
+        <v>57632</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8543,21 +8543,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8567,13 +8567,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>522217</v>
+        <v>522247</v>
       </c>
       <c r="R72" t="n">
-        <v>6936540</v>
+        <v>6936482</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8600,11 +8600,26 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>födosök död stående tall</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -8613,31 +8628,16 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -9851,10 +9851,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125632344</v>
+        <v>125646872</v>
       </c>
       <c r="B84" t="n">
-        <v>98269</v>
+        <v>91131</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9863,25 +9863,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9891,13 +9891,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>522268</v>
+        <v>522064</v>
       </c>
       <c r="R84" t="n">
-        <v>6936556</v>
+        <v>6936505</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9921,22 +9921,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9951,22 +9941,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125632326</v>
+        <v>125646902</v>
       </c>
       <c r="B85" t="n">
-        <v>78947</v>
+        <v>4869</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9975,25 +9965,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>101675</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10003,13 +9993,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>522213</v>
+        <v>522019</v>
       </c>
       <c r="R85" t="n">
-        <v>6936615</v>
+        <v>6936608</v>
       </c>
       <c r="S85" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10033,22 +10023,17 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>13:02</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>13:02</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Kläckhål på asp</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10063,22 +10048,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125632347</v>
+        <v>125632381</v>
       </c>
       <c r="B86" t="n">
-        <v>78683</v>
+        <v>98269</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10087,25 +10072,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10115,10 +10100,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>522239</v>
+        <v>522240</v>
       </c>
       <c r="R86" t="n">
-        <v>6936527</v>
+        <v>6936412</v>
       </c>
       <c r="S86" t="n">
         <v>4</v>
@@ -10150,7 +10135,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10160,7 +10145,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10187,7 +10172,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125632381</v>
+        <v>125632417</v>
       </c>
       <c r="B87" t="n">
         <v>98269</v>
@@ -10227,10 +10212,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>522240</v>
+        <v>522163</v>
       </c>
       <c r="R87" t="n">
-        <v>6936412</v>
+        <v>6936406</v>
       </c>
       <c r="S87" t="n">
         <v>4</v>
@@ -10262,7 +10247,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10272,7 +10257,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10299,7 +10284,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125632417</v>
+        <v>125632344</v>
       </c>
       <c r="B88" t="n">
         <v>98269</v>
@@ -10339,10 +10324,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>522163</v>
+        <v>522268</v>
       </c>
       <c r="R88" t="n">
-        <v>6936406</v>
+        <v>6936556</v>
       </c>
       <c r="S88" t="n">
         <v>4</v>
@@ -10374,7 +10359,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10384,7 +10369,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10411,10 +10396,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125634580</v>
+        <v>125632326</v>
       </c>
       <c r="B89" t="n">
-        <v>98290</v>
+        <v>78947</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10423,41 +10408,41 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>522044</v>
+        <v>522213</v>
       </c>
       <c r="R89" t="n">
-        <v>6936401</v>
+        <v>6936615</v>
       </c>
       <c r="S89" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10481,12 +10466,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10501,22 +10496,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125646872</v>
+        <v>125632347</v>
       </c>
       <c r="B90" t="n">
-        <v>91131</v>
+        <v>78683</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10525,25 +10520,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10553,13 +10548,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>522064</v>
+        <v>522239</v>
       </c>
       <c r="R90" t="n">
-        <v>6936505</v>
+        <v>6936527</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10583,12 +10578,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10603,22 +10608,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125646902</v>
+        <v>125634580</v>
       </c>
       <c r="B91" t="n">
-        <v>4869</v>
+        <v>98290</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10631,37 +10636,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>101675</v>
+        <v>221952</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>522019</v>
+        <v>522044</v>
       </c>
       <c r="R91" t="n">
-        <v>6936608</v>
+        <v>6936401</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10691,11 +10696,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Kläckhål på asp</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11822,10 +11822,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125636837</v>
+        <v>125636088</v>
       </c>
       <c r="B102" t="n">
-        <v>98269</v>
+        <v>92448</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11834,25 +11834,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11862,10 +11862,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>522164</v>
+        <v>522049</v>
       </c>
       <c r="R102" t="n">
-        <v>6936587</v>
+        <v>6936650</v>
       </c>
       <c r="S102" t="n">
         <v>20</v>
@@ -11924,10 +11924,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125636088</v>
+        <v>125635476</v>
       </c>
       <c r="B103" t="n">
-        <v>92448</v>
+        <v>80028</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11936,25 +11936,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>522049</v>
+        <v>522057</v>
       </c>
       <c r="R103" t="n">
-        <v>6936650</v>
+        <v>6936487</v>
       </c>
       <c r="S103" t="n">
         <v>20</v>
@@ -12000,6 +12000,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12026,10 +12031,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125635476</v>
+        <v>125646901</v>
       </c>
       <c r="B104" t="n">
-        <v>80028</v>
+        <v>92448</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12038,41 +12043,41 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>522057</v>
+        <v>522030</v>
       </c>
       <c r="R104" t="n">
-        <v>6936487</v>
+        <v>6936634</v>
       </c>
       <c r="S104" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12102,11 +12107,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12133,10 +12133,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125646901</v>
+        <v>125646899</v>
       </c>
       <c r="B105" t="n">
-        <v>92448</v>
+        <v>91326</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12145,25 +12145,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12173,10 +12173,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>522030</v>
+        <v>522143</v>
       </c>
       <c r="R105" t="n">
-        <v>6936634</v>
+        <v>6936554</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -12235,10 +12235,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125646899</v>
+        <v>125636837</v>
       </c>
       <c r="B106" t="n">
-        <v>91326</v>
+        <v>98269</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12251,37 +12251,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>522143</v>
+        <v>522164</v>
       </c>
       <c r="R106" t="n">
-        <v>6936554</v>
+        <v>6936587</v>
       </c>
       <c r="S106" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12337,10 +12337,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125632366</v>
+        <v>125635192</v>
       </c>
       <c r="B107" t="n">
-        <v>98290</v>
+        <v>92448</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12353,37 +12353,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221952</v>
+        <v>4364</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>522249</v>
+        <v>522003</v>
       </c>
       <c r="R107" t="n">
-        <v>6936460</v>
+        <v>6936451</v>
       </c>
       <c r="S107" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12407,22 +12407,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12437,22 +12427,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125632359</v>
+        <v>125632366</v>
       </c>
       <c r="B108" t="n">
-        <v>98269</v>
+        <v>98290</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12461,25 +12451,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12489,10 +12479,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>522236</v>
+        <v>522249</v>
       </c>
       <c r="R108" t="n">
-        <v>6936482</v>
+        <v>6936460</v>
       </c>
       <c r="S108" t="n">
         <v>4</v>
@@ -12524,7 +12514,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12534,7 +12524,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12561,10 +12551,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125632330</v>
+        <v>125632359</v>
       </c>
       <c r="B109" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12573,41 +12563,41 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>522172</v>
+        <v>522236</v>
       </c>
       <c r="R109" t="n">
-        <v>6936483</v>
+        <v>6936482</v>
       </c>
       <c r="S109" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12631,12 +12621,22 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12651,22 +12651,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125635192</v>
+        <v>125632330</v>
       </c>
       <c r="B110" t="n">
-        <v>92448</v>
+        <v>78947</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12675,25 +12675,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12703,10 +12703,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>522003</v>
+        <v>522172</v>
       </c>
       <c r="R110" t="n">
-        <v>6936451</v>
+        <v>6936483</v>
       </c>
       <c r="S110" t="n">
         <v>20</v>
@@ -12765,7 +12765,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125638972</v>
+        <v>125646886</v>
       </c>
       <c r="B111" t="n">
         <v>98269</v>
@@ -12801,17 +12801,17 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>522318</v>
+        <v>522109</v>
       </c>
       <c r="R111" t="n">
-        <v>6936398</v>
+        <v>6936414</v>
       </c>
       <c r="S111" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125646886</v>
+        <v>125638972</v>
       </c>
       <c r="B112" t="n">
         <v>98269</v>
@@ -12903,17 +12903,17 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>522109</v>
+        <v>522318</v>
       </c>
       <c r="R112" t="n">
-        <v>6936414</v>
+        <v>6936398</v>
       </c>
       <c r="S112" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12969,10 +12969,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125632401</v>
+        <v>125646887</v>
       </c>
       <c r="B113" t="n">
-        <v>100451</v>
+        <v>98269</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12981,25 +12981,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13009,13 +13009,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>522046</v>
+        <v>522185</v>
       </c>
       <c r="R113" t="n">
-        <v>6936397</v>
+        <v>6936414</v>
       </c>
       <c r="S113" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13039,22 +13039,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>15:09</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>15:09</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13069,22 +13059,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125632408</v>
+        <v>125632401</v>
       </c>
       <c r="B114" t="n">
-        <v>98303</v>
+        <v>100451</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13097,21 +13087,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219874</v>
+        <v>222498</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13121,10 +13111,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>522057</v>
+        <v>522046</v>
       </c>
       <c r="R114" t="n">
-        <v>6936411</v>
+        <v>6936397</v>
       </c>
       <c r="S114" t="n">
         <v>4</v>
@@ -13156,7 +13146,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13166,7 +13156,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13193,10 +13183,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125632407</v>
+        <v>125632408</v>
       </c>
       <c r="B115" t="n">
-        <v>91166</v>
+        <v>98303</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13205,25 +13195,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1202</v>
+        <v>219874</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13233,10 +13223,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>522052</v>
+        <v>522057</v>
       </c>
       <c r="R115" t="n">
-        <v>6936413</v>
+        <v>6936411</v>
       </c>
       <c r="S115" t="n">
         <v>4</v>
@@ -13305,10 +13295,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125632345</v>
+        <v>125632407</v>
       </c>
       <c r="B116" t="n">
-        <v>78947</v>
+        <v>91166</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13321,21 +13311,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13345,10 +13335,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>522244</v>
+        <v>522052</v>
       </c>
       <c r="R116" t="n">
-        <v>6936537</v>
+        <v>6936413</v>
       </c>
       <c r="S116" t="n">
         <v>4</v>
@@ -13380,7 +13370,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13390,7 +13380,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13417,10 +13407,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125646887</v>
+        <v>125632345</v>
       </c>
       <c r="B117" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13429,25 +13419,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13457,13 +13447,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>522185</v>
+        <v>522244</v>
       </c>
       <c r="R117" t="n">
-        <v>6936414</v>
+        <v>6936537</v>
       </c>
       <c r="S117" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13487,12 +13477,22 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13507,12 +13507,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -15475,10 +15475,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125632399</v>
+        <v>125632341</v>
       </c>
       <c r="B136" t="n">
-        <v>56836</v>
+        <v>92448</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15491,21 +15491,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15515,10 +15515,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>522053</v>
+        <v>522236</v>
       </c>
       <c r="R136" t="n">
-        <v>6936400</v>
+        <v>6936562</v>
       </c>
       <c r="S136" t="n">
         <v>4</v>
@@ -15550,7 +15550,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15560,12 +15560,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>15:07</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>spillning</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15592,10 +15587,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125632411</v>
+        <v>125632336</v>
       </c>
       <c r="B137" t="n">
-        <v>98269</v>
+        <v>78683</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15604,25 +15599,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15632,10 +15627,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>522063</v>
+        <v>522224</v>
       </c>
       <c r="R137" t="n">
-        <v>6936424</v>
+        <v>6936572</v>
       </c>
       <c r="S137" t="n">
         <v>4</v>
@@ -15667,7 +15662,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15677,7 +15672,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15704,10 +15699,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125632414</v>
+        <v>125632399</v>
       </c>
       <c r="B138" t="n">
-        <v>91166</v>
+        <v>56836</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15716,25 +15711,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15744,10 +15739,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>522109</v>
+        <v>522053</v>
       </c>
       <c r="R138" t="n">
-        <v>6936426</v>
+        <v>6936400</v>
       </c>
       <c r="S138" t="n">
         <v>4</v>
@@ -15779,7 +15774,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15789,7 +15784,12 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15816,10 +15816,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125632376</v>
+        <v>125632411</v>
       </c>
       <c r="B139" t="n">
-        <v>56836</v>
+        <v>98269</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15828,25 +15828,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15856,10 +15856,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>522237</v>
+        <v>522063</v>
       </c>
       <c r="R139" t="n">
-        <v>6936423</v>
+        <v>6936424</v>
       </c>
       <c r="S139" t="n">
         <v>4</v>
@@ -15891,7 +15891,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15901,7 +15901,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15928,10 +15928,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125632398</v>
+        <v>125632414</v>
       </c>
       <c r="B140" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15940,25 +15940,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15968,10 +15968,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>522059</v>
+        <v>522109</v>
       </c>
       <c r="R140" t="n">
-        <v>6936399</v>
+        <v>6936426</v>
       </c>
       <c r="S140" t="n">
         <v>4</v>
@@ -16003,7 +16003,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -16013,7 +16013,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16040,10 +16040,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125632341</v>
+        <v>125632376</v>
       </c>
       <c r="B141" t="n">
-        <v>92448</v>
+        <v>56836</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16056,21 +16056,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -16080,10 +16080,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>522236</v>
+        <v>522237</v>
       </c>
       <c r="R141" t="n">
-        <v>6936562</v>
+        <v>6936423</v>
       </c>
       <c r="S141" t="n">
         <v>4</v>
@@ -16115,7 +16115,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16152,10 +16152,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125632336</v>
+        <v>125632398</v>
       </c>
       <c r="B142" t="n">
-        <v>78683</v>
+        <v>98269</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16164,25 +16164,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -16192,10 +16192,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>522224</v>
+        <v>522059</v>
       </c>
       <c r="R142" t="n">
-        <v>6936572</v>
+        <v>6936399</v>
       </c>
       <c r="S142" t="n">
         <v>4</v>
@@ -16227,7 +16227,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -16237,7 +16237,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD142" t="b">

--- a/artfynd/A 26476-2025 artfynd.xlsx
+++ b/artfynd/A 26476-2025 artfynd.xlsx
@@ -2925,32 +2925,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125601310</v>
+        <v>125602968</v>
       </c>
       <c r="B21" t="n">
-        <v>98324</v>
+        <v>98345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3022,7 +3022,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125632569</v>
+        <v>125601310</v>
       </c>
       <c r="B22" t="n">
         <v>98324</v>
@@ -3053,17 +3053,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>522108</v>
+        <v>522217</v>
       </c>
       <c r="R22" t="n">
-        <v>6936467</v>
+        <v>6936540</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3087,12 +3087,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3107,19 +3107,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125632421</v>
+        <v>125632569</v>
       </c>
       <c r="B23" t="n">
         <v>98324</v>
@@ -3150,17 +3150,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>522260</v>
+        <v>522108</v>
       </c>
       <c r="R23" t="n">
-        <v>6936447</v>
+        <v>6936467</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3184,22 +3184,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3214,44 +3204,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125646875</v>
+        <v>125632421</v>
       </c>
       <c r="B24" t="n">
-        <v>78726</v>
+        <v>98324</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3261,13 +3251,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>522035</v>
+        <v>522260</v>
       </c>
       <c r="R24" t="n">
-        <v>6936550</v>
+        <v>6936447</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3291,12 +3281,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3311,22 +3311,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125632425</v>
+        <v>125646875</v>
       </c>
       <c r="B25" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3334,21 +3334,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3358,13 +3358,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>522345</v>
+        <v>522035</v>
       </c>
       <c r="R25" t="n">
-        <v>6936464</v>
+        <v>6936550</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3388,22 +3388,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3418,22 +3408,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125646874</v>
+        <v>125646902</v>
       </c>
       <c r="B26" t="n">
-        <v>80098</v>
+        <v>4869</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3441,21 +3431,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6461</v>
+        <v>101675</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3465,10 +3455,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>522022</v>
+        <v>522019</v>
       </c>
       <c r="R26" t="n">
-        <v>6936611</v>
+        <v>6936608</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3501,6 +3491,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Kläckhål på asp</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3527,32 +3522,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125646902</v>
+        <v>125632425</v>
       </c>
       <c r="B27" t="n">
-        <v>4869</v>
+        <v>78967</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101675</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3562,13 +3557,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>522019</v>
+        <v>522345</v>
       </c>
       <c r="R27" t="n">
-        <v>6936608</v>
+        <v>6936464</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3592,17 +3587,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Kläckhål på asp</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3617,22 +3617,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125602968</v>
+        <v>125646874</v>
       </c>
       <c r="B28" t="n">
-        <v>98345</v>
+        <v>80098</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,21 +3640,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3664,13 +3664,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>522217</v>
+        <v>522022</v>
       </c>
       <c r="R28" t="n">
-        <v>6936540</v>
+        <v>6936611</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3714,12 +3714,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -8055,32 +8055,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125632370</v>
+        <v>125632357</v>
       </c>
       <c r="B71" t="n">
-        <v>98324</v>
+        <v>91220</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8090,10 +8090,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>522243</v>
+        <v>522221</v>
       </c>
       <c r="R71" t="n">
-        <v>6936456</v>
+        <v>6936489</v>
       </c>
       <c r="S71" t="n">
         <v>4</v>
@@ -8125,7 +8125,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8162,32 +8162,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125632381</v>
+        <v>125646872</v>
       </c>
       <c r="B72" t="n">
-        <v>98324</v>
+        <v>91185</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8197,13 +8197,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>522240</v>
+        <v>522064</v>
       </c>
       <c r="R72" t="n">
-        <v>6936412</v>
+        <v>6936505</v>
       </c>
       <c r="S72" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8227,22 +8227,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>14:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>14:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8257,44 +8247,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125632418</v>
+        <v>125632350</v>
       </c>
       <c r="B73" t="n">
-        <v>98324</v>
+        <v>80070</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8304,10 +8294,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>522162</v>
+        <v>522254</v>
       </c>
       <c r="R73" t="n">
-        <v>6936404</v>
+        <v>6936496</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -8339,7 +8329,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8349,7 +8339,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8376,10 +8366,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125632357</v>
+        <v>125646879</v>
       </c>
       <c r="B74" t="n">
-        <v>91220</v>
+        <v>80070</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8387,21 +8377,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8411,13 +8401,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>522221</v>
+        <v>522202</v>
       </c>
       <c r="R74" t="n">
-        <v>6936489</v>
+        <v>6936502</v>
       </c>
       <c r="S74" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8441,22 +8431,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8471,22 +8451,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125646872</v>
+        <v>125632372</v>
       </c>
       <c r="B75" t="n">
-        <v>91185</v>
+        <v>98345</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8494,21 +8474,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8518,13 +8498,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>522064</v>
+        <v>522236</v>
       </c>
       <c r="R75" t="n">
-        <v>6936505</v>
+        <v>6936448</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8548,12 +8528,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8568,44 +8558,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125632350</v>
+        <v>125632370</v>
       </c>
       <c r="B76" t="n">
-        <v>80070</v>
+        <v>98324</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8615,10 +8605,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>522254</v>
+        <v>522243</v>
       </c>
       <c r="R76" t="n">
-        <v>6936496</v>
+        <v>6936456</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -8650,7 +8640,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8660,7 +8650,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8687,32 +8677,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125646879</v>
+        <v>125632381</v>
       </c>
       <c r="B77" t="n">
-        <v>80070</v>
+        <v>98324</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8722,13 +8712,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>522202</v>
+        <v>522240</v>
       </c>
       <c r="R77" t="n">
-        <v>6936502</v>
+        <v>6936412</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8752,12 +8742,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8772,44 +8772,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125632372</v>
+        <v>125632418</v>
       </c>
       <c r="B78" t="n">
-        <v>98345</v>
+        <v>98324</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8819,10 +8819,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>522236</v>
+        <v>522162</v>
       </c>
       <c r="R78" t="n">
-        <v>6936448</v>
+        <v>6936404</v>
       </c>
       <c r="S78" t="n">
         <v>4</v>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9727,48 +9727,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125637200</v>
+        <v>125646882</v>
       </c>
       <c r="B87" t="n">
-        <v>78967</v>
+        <v>98324</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>522362</v>
+        <v>522029</v>
       </c>
       <c r="R87" t="n">
-        <v>6936466</v>
+        <v>6936561</v>
       </c>
       <c r="S87" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9824,48 +9824,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125635192</v>
+        <v>125632417</v>
       </c>
       <c r="B88" t="n">
-        <v>92502</v>
+        <v>98324</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>522003</v>
+        <v>522163</v>
       </c>
       <c r="R88" t="n">
-        <v>6936451</v>
+        <v>6936406</v>
       </c>
       <c r="S88" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9889,12 +9889,22 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9909,60 +9919,60 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125646882</v>
+        <v>125637200</v>
       </c>
       <c r="B89" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>522029</v>
+        <v>522362</v>
       </c>
       <c r="R89" t="n">
-        <v>6936561</v>
+        <v>6936466</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10018,48 +10028,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125632417</v>
+        <v>125635192</v>
       </c>
       <c r="B90" t="n">
-        <v>98324</v>
+        <v>92502</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>522163</v>
+        <v>522003</v>
       </c>
       <c r="R90" t="n">
-        <v>6936406</v>
+        <v>6936451</v>
       </c>
       <c r="S90" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10083,22 +10093,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10113,12 +10113,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -10334,48 +10334,53 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125632409</v>
+        <v>125633268</v>
       </c>
       <c r="B93" t="n">
-        <v>98324</v>
+        <v>57811</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>522062</v>
+        <v>522121</v>
       </c>
       <c r="R93" t="n">
-        <v>6936422</v>
+        <v>6936402</v>
       </c>
       <c r="S93" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10399,22 +10404,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10429,19 +10424,19 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125632415</v>
+        <v>125632409</v>
       </c>
       <c r="B94" t="n">
         <v>98324</v>
@@ -10476,10 +10471,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>522124</v>
+        <v>522062</v>
       </c>
       <c r="R94" t="n">
-        <v>6936410</v>
+        <v>6936422</v>
       </c>
       <c r="S94" t="n">
         <v>4</v>
@@ -10511,7 +10506,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10521,7 +10516,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10548,32 +10543,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125632358</v>
+        <v>125632415</v>
       </c>
       <c r="B95" t="n">
-        <v>98345</v>
+        <v>98324</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10583,10 +10578,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>522231</v>
+        <v>522124</v>
       </c>
       <c r="R95" t="n">
-        <v>6936488</v>
+        <v>6936410</v>
       </c>
       <c r="S95" t="n">
         <v>4</v>
@@ -10618,7 +10613,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10628,7 +10623,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10655,53 +10650,48 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125633268</v>
+        <v>125632358</v>
       </c>
       <c r="B96" t="n">
-        <v>57811</v>
+        <v>98345</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>522121</v>
+        <v>522231</v>
       </c>
       <c r="R96" t="n">
-        <v>6936402</v>
+        <v>6936488</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10725,12 +10715,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10745,12 +10745,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -11481,32 +11481,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125632412</v>
+        <v>125632325</v>
       </c>
       <c r="B104" t="n">
-        <v>98324</v>
+        <v>78725</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11516,13 +11516,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>522101</v>
+        <v>522198</v>
       </c>
       <c r="R104" t="n">
-        <v>6936425</v>
+        <v>6936620</v>
       </c>
       <c r="S104" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11588,32 +11588,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125632379</v>
+        <v>125646880</v>
       </c>
       <c r="B105" t="n">
-        <v>98324</v>
+        <v>80070</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11623,13 +11623,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>522237</v>
+        <v>522225</v>
       </c>
       <c r="R105" t="n">
-        <v>6936415</v>
+        <v>6936564</v>
       </c>
       <c r="S105" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11653,22 +11653,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>14:26</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>14:26</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11683,60 +11673,60 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125632351</v>
+        <v>125635476</v>
       </c>
       <c r="B106" t="n">
-        <v>98324</v>
+        <v>80070</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>522250</v>
+        <v>522057</v>
       </c>
       <c r="R106" t="n">
-        <v>6936497</v>
+        <v>6936487</v>
       </c>
       <c r="S106" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11760,22 +11750,17 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>13:48</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>13:48</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11790,22 +11775,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125632325</v>
+        <v>125632323</v>
       </c>
       <c r="B107" t="n">
-        <v>78725</v>
+        <v>78967</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11813,21 +11798,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11837,13 +11822,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>522198</v>
+        <v>522189</v>
       </c>
       <c r="R107" t="n">
-        <v>6936620</v>
+        <v>6936648</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11872,7 +11857,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11882,7 +11867,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11909,10 +11894,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125646880</v>
+        <v>125632330</v>
       </c>
       <c r="B108" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11920,37 +11905,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>522225</v>
+        <v>522172</v>
       </c>
       <c r="R108" t="n">
-        <v>6936564</v>
+        <v>6936483</v>
       </c>
       <c r="S108" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12006,48 +11991,48 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125635476</v>
+        <v>125632412</v>
       </c>
       <c r="B109" t="n">
-        <v>80070</v>
+        <v>98324</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>522057</v>
+        <v>522101</v>
       </c>
       <c r="R109" t="n">
-        <v>6936487</v>
+        <v>6936425</v>
       </c>
       <c r="S109" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12071,17 +12056,22 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12096,44 +12086,44 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125632323</v>
+        <v>125632379</v>
       </c>
       <c r="B110" t="n">
-        <v>78967</v>
+        <v>98324</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12143,10 +12133,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>522189</v>
+        <v>522237</v>
       </c>
       <c r="R110" t="n">
-        <v>6936648</v>
+        <v>6936415</v>
       </c>
       <c r="S110" t="n">
         <v>4</v>
@@ -12178,7 +12168,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12188,7 +12178,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12215,48 +12205,48 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125632330</v>
+        <v>125632351</v>
       </c>
       <c r="B111" t="n">
-        <v>78967</v>
+        <v>98324</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>522172</v>
+        <v>522250</v>
       </c>
       <c r="R111" t="n">
-        <v>6936483</v>
+        <v>6936497</v>
       </c>
       <c r="S111" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12280,12 +12270,22 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12300,12 +12300,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -13571,10 +13571,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125632360</v>
+        <v>125637290</v>
       </c>
       <c r="B124" t="n">
-        <v>57648</v>
+        <v>78725</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13582,37 +13582,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>522247</v>
+        <v>522366</v>
       </c>
       <c r="R124" t="n">
-        <v>6936482</v>
+        <v>6936463</v>
       </c>
       <c r="S124" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13636,27 +13636,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>14:06</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>födosök död stående tall</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13671,22 +13656,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125637290</v>
+        <v>125632360</v>
       </c>
       <c r="B125" t="n">
-        <v>78725</v>
+        <v>57648</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13694,37 +13679,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>522366</v>
+        <v>522247</v>
       </c>
       <c r="R125" t="n">
-        <v>6936463</v>
+        <v>6936482</v>
       </c>
       <c r="S125" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13748,12 +13733,27 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>födosök död stående tall</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13768,12 +13768,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
@@ -14728,48 +14728,48 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125632407</v>
+        <v>125633219</v>
       </c>
       <c r="B135" t="n">
-        <v>91220</v>
+        <v>98324</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>MD0:Ånge, SE-VN, SE, Mpd</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>522052</v>
+        <v>522237</v>
       </c>
       <c r="R135" t="n">
-        <v>6936413</v>
+        <v>6936437</v>
       </c>
       <c r="S135" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14808,7 +14808,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14835,32 +14835,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125632334</v>
+        <v>125632373</v>
       </c>
       <c r="B136" t="n">
-        <v>80099</v>
+        <v>98324</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14870,10 +14870,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>522239</v>
+        <v>522236</v>
       </c>
       <c r="R136" t="n">
-        <v>6936600</v>
+        <v>6936449</v>
       </c>
       <c r="S136" t="n">
         <v>4</v>
@@ -14905,7 +14905,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14942,7 +14942,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125633219</v>
+        <v>125632352</v>
       </c>
       <c r="B137" t="n">
         <v>98324</v>
@@ -14973,17 +14973,17 @@
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>MD0:Ånge, SE-VN, SE, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>522237</v>
+        <v>522245</v>
       </c>
       <c r="R137" t="n">
-        <v>6936437</v>
+        <v>6936497</v>
       </c>
       <c r="S137" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15049,7 +15049,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125632373</v>
+        <v>125632359</v>
       </c>
       <c r="B138" t="n">
         <v>98324</v>
@@ -15087,7 +15087,7 @@
         <v>522236</v>
       </c>
       <c r="R138" t="n">
-        <v>6936449</v>
+        <v>6936482</v>
       </c>
       <c r="S138" t="n">
         <v>4</v>
@@ -15119,7 +15119,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15156,32 +15156,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125632352</v>
+        <v>125632407</v>
       </c>
       <c r="B139" t="n">
-        <v>98324</v>
+        <v>91220</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15191,10 +15191,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>522245</v>
+        <v>522052</v>
       </c>
       <c r="R139" t="n">
-        <v>6936497</v>
+        <v>6936413</v>
       </c>
       <c r="S139" t="n">
         <v>4</v>
@@ -15226,7 +15226,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15236,7 +15236,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15263,32 +15263,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125632359</v>
+        <v>125632334</v>
       </c>
       <c r="B140" t="n">
-        <v>98324</v>
+        <v>80099</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15298,10 +15298,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>522236</v>
+        <v>522239</v>
       </c>
       <c r="R140" t="n">
-        <v>6936482</v>
+        <v>6936600</v>
       </c>
       <c r="S140" t="n">
         <v>4</v>
@@ -15333,7 +15333,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15343,7 +15343,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD140" t="b">

--- a/artfynd/A 26476-2025 artfynd.xlsx
+++ b/artfynd/A 26476-2025 artfynd.xlsx
@@ -2215,7 +2215,7 @@
         <v>125621452</v>
       </c>
       <c r="B14" t="n">
-        <v>91380</v>
+        <v>91387</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>125620054</v>
       </c>
       <c r="B15" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>125619796</v>
       </c>
       <c r="B18" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>125619751</v>
       </c>
       <c r="B19" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2925,10 +2925,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125602968</v>
+        <v>125646874</v>
       </c>
       <c r="B21" t="n">
-        <v>98345</v>
+        <v>80098</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2960,13 +2960,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>522217</v>
+        <v>522022</v>
       </c>
       <c r="R21" t="n">
-        <v>6936540</v>
+        <v>6936611</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2990,12 +2990,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3010,12 +3010,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3025,7 +3025,7 @@
         <v>125601310</v>
       </c>
       <c r="B22" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>125632569</v>
       </c>
       <c r="B23" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>125632421</v>
       </c>
       <c r="B24" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3323,32 +3323,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125646875</v>
+        <v>125602968</v>
       </c>
       <c r="B25" t="n">
-        <v>78726</v>
+        <v>98352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3358,13 +3358,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>522035</v>
+        <v>522217</v>
       </c>
       <c r="R25" t="n">
-        <v>6936550</v>
+        <v>6936540</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3388,12 +3388,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3408,44 +3408,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125646902</v>
+        <v>125646875</v>
       </c>
       <c r="B26" t="n">
-        <v>4869</v>
+        <v>78726</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>101675</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>522019</v>
+        <v>522035</v>
       </c>
       <c r="R26" t="n">
-        <v>6936608</v>
+        <v>6936550</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3491,11 +3491,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Kläckhål på asp</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3629,10 +3624,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125646874</v>
+        <v>125646902</v>
       </c>
       <c r="B28" t="n">
-        <v>80098</v>
+        <v>4869</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,21 +3635,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6461</v>
+        <v>101675</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3664,10 +3659,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>522022</v>
+        <v>522019</v>
       </c>
       <c r="R28" t="n">
-        <v>6936611</v>
+        <v>6936608</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3700,6 +3695,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Kläckhål på asp</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3726,32 +3726,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125601890</v>
+        <v>125600959</v>
       </c>
       <c r="B29" t="n">
-        <v>91671</v>
+        <v>80070</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3807,6 +3807,21 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3823,32 +3838,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125632332</v>
+        <v>125632349</v>
       </c>
       <c r="B30" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3858,13 +3873,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>522239</v>
+        <v>522259</v>
       </c>
       <c r="R30" t="n">
-        <v>6936598</v>
+        <v>6936489</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3893,7 +3908,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3903,7 +3918,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3930,48 +3945,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125600959</v>
+        <v>125636837</v>
       </c>
       <c r="B31" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>522217</v>
+        <v>522164</v>
       </c>
       <c r="R31" t="n">
-        <v>6936540</v>
+        <v>6936587</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3995,12 +4010,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4011,41 +4026,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125600280</v>
+        <v>125632367</v>
       </c>
       <c r="B32" t="n">
-        <v>92502</v>
+        <v>98352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4053,21 +4053,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4077,13 +4077,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>522217</v>
+        <v>522247</v>
       </c>
       <c r="R32" t="n">
-        <v>6936540</v>
+        <v>6936458</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4110,9 +4110,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4127,60 +4137,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125632349</v>
+        <v>125634580</v>
       </c>
       <c r="B33" t="n">
-        <v>98324</v>
+        <v>98352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>522259</v>
+        <v>522044</v>
       </c>
       <c r="R33" t="n">
-        <v>6936489</v>
+        <v>6936401</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4204,22 +4214,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4234,22 +4234,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125603562</v>
+        <v>125600280</v>
       </c>
       <c r="B34" t="n">
-        <v>80030</v>
+        <v>92509</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4257,21 +4257,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229497</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4343,48 +4343,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125636837</v>
+        <v>125632332</v>
       </c>
       <c r="B35" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>522164</v>
+        <v>522239</v>
       </c>
       <c r="R35" t="n">
-        <v>6936587</v>
+        <v>6936598</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4408,12 +4408,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4428,44 +4438,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125632367</v>
+        <v>125601890</v>
       </c>
       <c r="B36" t="n">
-        <v>98345</v>
+        <v>91678</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4475,13 +4485,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>522247</v>
+        <v>522217</v>
       </c>
       <c r="R36" t="n">
-        <v>6936458</v>
+        <v>6936540</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4508,19 +4518,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>14:16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4535,22 +4535,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125634580</v>
+        <v>125603562</v>
       </c>
       <c r="B37" t="n">
-        <v>98345</v>
+        <v>80030</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4558,37 +4558,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221952</v>
+        <v>229497</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>522044</v>
+        <v>522217</v>
       </c>
       <c r="R37" t="n">
-        <v>6936401</v>
+        <v>6936540</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4632,44 +4632,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125632329</v>
+        <v>125632337</v>
       </c>
       <c r="B38" t="n">
-        <v>80099</v>
+        <v>78967</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4679,10 +4679,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>522215</v>
+        <v>522224</v>
       </c>
       <c r="R38" t="n">
-        <v>6936627</v>
+        <v>6936572</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4751,10 +4751,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125632337</v>
+        <v>125632362</v>
       </c>
       <c r="B39" t="n">
-        <v>78967</v>
+        <v>78725</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4762,21 +4762,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4786,10 +4786,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>522224</v>
+        <v>522249</v>
       </c>
       <c r="R39" t="n">
-        <v>6936572</v>
+        <v>6936486</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4858,32 +4858,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125632362</v>
+        <v>125632338</v>
       </c>
       <c r="B40" t="n">
-        <v>78725</v>
+        <v>92509</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>522249</v>
+        <v>522221</v>
       </c>
       <c r="R40" t="n">
-        <v>6936486</v>
+        <v>6936572</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4965,10 +4965,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125632338</v>
+        <v>125636088</v>
       </c>
       <c r="B41" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4996,17 +4996,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>522221</v>
+        <v>522049</v>
       </c>
       <c r="R41" t="n">
-        <v>6936572</v>
+        <v>6936650</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5030,22 +5030,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5060,22 +5050,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125636088</v>
+        <v>125632329</v>
       </c>
       <c r="B42" t="n">
-        <v>92502</v>
+        <v>80099</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5083,37 +5073,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>522049</v>
+        <v>522215</v>
       </c>
       <c r="R42" t="n">
-        <v>6936650</v>
+        <v>6936627</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5137,12 +5127,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5157,22 +5157,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125646892</v>
+        <v>125632353</v>
       </c>
       <c r="B43" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>522130</v>
+        <v>522241</v>
       </c>
       <c r="R43" t="n">
-        <v>6936481</v>
+        <v>6936509</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5234,12 +5234,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5254,22 +5264,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125646893</v>
+        <v>125646892</v>
       </c>
       <c r="B44" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5301,10 +5311,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>522204</v>
+        <v>522130</v>
       </c>
       <c r="R44" t="n">
-        <v>6936495</v>
+        <v>6936481</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5363,32 +5373,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125632368</v>
+        <v>125646893</v>
       </c>
       <c r="B45" t="n">
-        <v>98345</v>
+        <v>98331</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5398,13 +5408,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>522245</v>
+        <v>522204</v>
       </c>
       <c r="R45" t="n">
-        <v>6936456</v>
+        <v>6936495</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5428,22 +5438,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:17</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:17</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5458,22 +5458,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125632401</v>
+        <v>125632368</v>
       </c>
       <c r="B46" t="n">
-        <v>100506</v>
+        <v>98352</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5481,21 +5481,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>522046</v>
+        <v>522245</v>
       </c>
       <c r="R46" t="n">
-        <v>6936397</v>
+        <v>6936456</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5577,32 +5577,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125632353</v>
+        <v>125632401</v>
       </c>
       <c r="B47" t="n">
-        <v>98324</v>
+        <v>100513</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5612,10 +5612,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>522241</v>
+        <v>522046</v>
       </c>
       <c r="R47" t="n">
-        <v>6936509</v>
+        <v>6936397</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5687,7 +5687,7 @@
         <v>125632416</v>
       </c>
       <c r="B48" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5791,32 +5791,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125632382</v>
+        <v>125600818</v>
       </c>
       <c r="B49" t="n">
-        <v>98324</v>
+        <v>98248</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5826,13 +5826,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>522214</v>
+        <v>522217</v>
       </c>
       <c r="R49" t="n">
-        <v>6936414</v>
+        <v>6936540</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5859,19 +5859,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5886,22 +5876,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125646883</v>
+        <v>125638972</v>
       </c>
       <c r="B50" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5929,17 +5919,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>522097</v>
+        <v>522318</v>
       </c>
       <c r="R50" t="n">
-        <v>6936427</v>
+        <v>6936398</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5995,10 +5985,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125638972</v>
+        <v>125632382</v>
       </c>
       <c r="B51" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6026,17 +6016,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>522318</v>
+        <v>522214</v>
       </c>
       <c r="R51" t="n">
-        <v>6936398</v>
+        <v>6936414</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6060,12 +6050,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6080,44 +6080,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125600818</v>
+        <v>125646883</v>
       </c>
       <c r="B52" t="n">
-        <v>98241</v>
+        <v>98331</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6127,13 +6127,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>522217</v>
+        <v>522097</v>
       </c>
       <c r="R52" t="n">
-        <v>6936540</v>
+        <v>6936427</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6157,12 +6157,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6177,60 +6177,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125637287</v>
+        <v>125632397</v>
       </c>
       <c r="B53" t="n">
-        <v>79585</v>
+        <v>98331</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>522356</v>
+        <v>522077</v>
       </c>
       <c r="R53" t="n">
-        <v>6936466</v>
+        <v>6936379</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6254,12 +6254,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6274,60 +6284,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125632336</v>
+        <v>125636925</v>
       </c>
       <c r="B54" t="n">
-        <v>78725</v>
+        <v>98331</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>522224</v>
+        <v>522220</v>
       </c>
       <c r="R54" t="n">
-        <v>6936572</v>
+        <v>6936601</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6351,22 +6361,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>13:25</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>13:25</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6381,44 +6381,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125637245</v>
+        <v>125632815</v>
       </c>
       <c r="B55" t="n">
-        <v>80070</v>
+        <v>98352</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6428,13 +6428,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>522360</v>
+        <v>522129</v>
       </c>
       <c r="R55" t="n">
-        <v>6936453</v>
+        <v>6936436</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6490,10 +6490,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125632400</v>
+        <v>125637287</v>
       </c>
       <c r="B56" t="n">
-        <v>91220</v>
+        <v>79585</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6501,37 +6501,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>522048</v>
+        <v>522356</v>
       </c>
       <c r="R56" t="n">
-        <v>6936403</v>
+        <v>6936466</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6555,22 +6555,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:08</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:08</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6585,44 +6575,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125632397</v>
+        <v>125632336</v>
       </c>
       <c r="B57" t="n">
-        <v>98324</v>
+        <v>78725</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6632,10 +6622,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>522077</v>
+        <v>522224</v>
       </c>
       <c r="R57" t="n">
-        <v>6936379</v>
+        <v>6936572</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6667,7 +6657,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6677,7 +6667,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6704,48 +6694,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125636925</v>
+        <v>125632400</v>
       </c>
       <c r="B58" t="n">
-        <v>98324</v>
+        <v>91227</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>522220</v>
+        <v>522048</v>
       </c>
       <c r="R58" t="n">
-        <v>6936601</v>
+        <v>6936403</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6769,12 +6759,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6789,44 +6789,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125632815</v>
+        <v>125637245</v>
       </c>
       <c r="B59" t="n">
-        <v>98345</v>
+        <v>80070</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6836,13 +6836,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>522129</v>
+        <v>522360</v>
       </c>
       <c r="R59" t="n">
-        <v>6936436</v>
+        <v>6936453</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6898,32 +6898,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125632410</v>
+        <v>125646891</v>
       </c>
       <c r="B60" t="n">
-        <v>92502</v>
+        <v>98331</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6933,13 +6933,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>522063</v>
+        <v>522159</v>
       </c>
       <c r="R60" t="n">
-        <v>6936423</v>
+        <v>6936408</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6963,22 +6963,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6993,44 +6983,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125632324</v>
+        <v>125632392</v>
       </c>
       <c r="B61" t="n">
-        <v>92502</v>
+        <v>98331</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7040,10 +7030,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>522198</v>
+        <v>522181</v>
       </c>
       <c r="R61" t="n">
-        <v>6936634</v>
+        <v>6936381</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -7075,7 +7065,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7085,7 +7075,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7112,32 +7102,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125632356</v>
+        <v>125632398</v>
       </c>
       <c r="B62" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7147,10 +7137,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>522233</v>
+        <v>522059</v>
       </c>
       <c r="R62" t="n">
-        <v>6936499</v>
+        <v>6936399</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -7182,7 +7172,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7192,7 +7182,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7219,10 +7209,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125646891</v>
+        <v>125632354</v>
       </c>
       <c r="B63" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7254,13 +7244,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>522159</v>
+        <v>522234</v>
       </c>
       <c r="R63" t="n">
-        <v>6936408</v>
+        <v>6936499</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7284,12 +7274,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7304,22 +7304,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125632392</v>
+        <v>125646887</v>
       </c>
       <c r="B64" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7351,13 +7351,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>522181</v>
+        <v>522185</v>
       </c>
       <c r="R64" t="n">
-        <v>6936381</v>
+        <v>6936414</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7381,22 +7381,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7411,44 +7401,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125632398</v>
+        <v>125632356</v>
       </c>
       <c r="B65" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7458,10 +7448,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>522059</v>
+        <v>522233</v>
       </c>
       <c r="R65" t="n">
-        <v>6936399</v>
+        <v>6936499</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7493,7 +7483,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7503,7 +7493,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7530,32 +7520,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125632354</v>
+        <v>125632410</v>
       </c>
       <c r="B66" t="n">
-        <v>98324</v>
+        <v>92509</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7565,10 +7555,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>522234</v>
+        <v>522063</v>
       </c>
       <c r="R66" t="n">
-        <v>6936499</v>
+        <v>6936423</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -7600,7 +7590,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7610,7 +7600,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7637,32 +7627,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125646887</v>
+        <v>125632324</v>
       </c>
       <c r="B67" t="n">
-        <v>98324</v>
+        <v>92509</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7672,13 +7662,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>522185</v>
+        <v>522198</v>
       </c>
       <c r="R67" t="n">
-        <v>6936414</v>
+        <v>6936634</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7702,12 +7692,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7722,12 +7722,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7737,7 +7737,7 @@
         <v>125632422</v>
       </c>
       <c r="B68" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>125632396</v>
       </c>
       <c r="B69" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>125632361</v>
       </c>
       <c r="B70" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>125632357</v>
       </c>
       <c r="B71" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>125646872</v>
       </c>
       <c r="B72" t="n">
-        <v>91185</v>
+        <v>91192</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125632350</v>
+        <v>125646879</v>
       </c>
       <c r="B73" t="n">
         <v>80070</v>
@@ -8294,13 +8294,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>522254</v>
+        <v>522202</v>
       </c>
       <c r="R73" t="n">
-        <v>6936496</v>
+        <v>6936502</v>
       </c>
       <c r="S73" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8324,22 +8324,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>13:47</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>13:47</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8354,19 +8344,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125646879</v>
+        <v>125632350</v>
       </c>
       <c r="B74" t="n">
         <v>80070</v>
@@ -8401,13 +8391,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>522202</v>
+        <v>522254</v>
       </c>
       <c r="R74" t="n">
-        <v>6936502</v>
+        <v>6936496</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8431,12 +8421,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8451,12 +8451,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8466,7 +8466,7 @@
         <v>125632372</v>
       </c>
       <c r="B75" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>125632370</v>
       </c>
       <c r="B76" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>125632381</v>
       </c>
       <c r="B77" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>125632418</v>
       </c>
       <c r="B78" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>125632406</v>
       </c>
       <c r="B79" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>125632377</v>
       </c>
       <c r="B80" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>125632387</v>
       </c>
       <c r="B81" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>125632423</v>
       </c>
       <c r="B82" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>125632365</v>
       </c>
       <c r="B83" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>125632554</v>
       </c>
       <c r="B84" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>125632593</v>
       </c>
       <c r="B85" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>125632420</v>
       </c>
       <c r="B86" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9727,48 +9727,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125646882</v>
+        <v>125637200</v>
       </c>
       <c r="B87" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>522029</v>
+        <v>522362</v>
       </c>
       <c r="R87" t="n">
-        <v>6936561</v>
+        <v>6936466</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9824,48 +9824,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125632417</v>
+        <v>125635192</v>
       </c>
       <c r="B88" t="n">
-        <v>98324</v>
+        <v>92509</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>522163</v>
+        <v>522003</v>
       </c>
       <c r="R88" t="n">
-        <v>6936406</v>
+        <v>6936451</v>
       </c>
       <c r="S88" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9889,22 +9889,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9919,60 +9909,60 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125637200</v>
+        <v>125646882</v>
       </c>
       <c r="B89" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>522362</v>
+        <v>522029</v>
       </c>
       <c r="R89" t="n">
-        <v>6936466</v>
+        <v>6936561</v>
       </c>
       <c r="S89" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10028,48 +10018,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125635192</v>
+        <v>125632417</v>
       </c>
       <c r="B90" t="n">
-        <v>92502</v>
+        <v>98331</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>522003</v>
+        <v>522163</v>
       </c>
       <c r="R90" t="n">
-        <v>6936451</v>
+        <v>6936406</v>
       </c>
       <c r="S90" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10093,12 +10083,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10113,60 +10113,60 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125635666</v>
+        <v>125632341</v>
       </c>
       <c r="B91" t="n">
-        <v>80070</v>
+        <v>92509</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>522038</v>
+        <v>522236</v>
       </c>
       <c r="R91" t="n">
-        <v>6936535</v>
+        <v>6936562</v>
       </c>
       <c r="S91" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10190,17 +10190,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10215,60 +10220,65 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125632341</v>
+        <v>125633268</v>
       </c>
       <c r="B92" t="n">
-        <v>92502</v>
+        <v>57811</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>522236</v>
+        <v>522121</v>
       </c>
       <c r="R92" t="n">
-        <v>6936562</v>
+        <v>6936402</v>
       </c>
       <c r="S92" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10292,22 +10302,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10322,65 +10322,60 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125633268</v>
+        <v>125632409</v>
       </c>
       <c r="B93" t="n">
-        <v>57811</v>
+        <v>98331</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>522121</v>
+        <v>522062</v>
       </c>
       <c r="R93" t="n">
-        <v>6936402</v>
+        <v>6936422</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10404,12 +10399,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10424,22 +10429,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125632409</v>
+        <v>125632415</v>
       </c>
       <c r="B94" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10471,10 +10476,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>522062</v>
+        <v>522124</v>
       </c>
       <c r="R94" t="n">
-        <v>6936422</v>
+        <v>6936410</v>
       </c>
       <c r="S94" t="n">
         <v>4</v>
@@ -10506,7 +10511,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10516,7 +10521,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10543,32 +10548,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125632415</v>
+        <v>125632358</v>
       </c>
       <c r="B95" t="n">
-        <v>98324</v>
+        <v>98352</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10578,10 +10583,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>522124</v>
+        <v>522231</v>
       </c>
       <c r="R95" t="n">
-        <v>6936410</v>
+        <v>6936488</v>
       </c>
       <c r="S95" t="n">
         <v>4</v>
@@ -10613,7 +10618,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10623,7 +10628,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10650,48 +10655,48 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125632358</v>
+        <v>125635666</v>
       </c>
       <c r="B96" t="n">
-        <v>98345</v>
+        <v>80070</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>522231</v>
+        <v>522038</v>
       </c>
       <c r="R96" t="n">
-        <v>6936488</v>
+        <v>6936535</v>
       </c>
       <c r="S96" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10715,22 +10720,17 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10745,44 +10745,44 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125632333</v>
+        <v>125646894</v>
       </c>
       <c r="B97" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10792,13 +10792,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>522235</v>
+        <v>522227</v>
       </c>
       <c r="R97" t="n">
-        <v>6936598</v>
+        <v>6936562</v>
       </c>
       <c r="S97" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10822,22 +10822,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10852,44 +10842,44 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125632348</v>
+        <v>125632344</v>
       </c>
       <c r="B98" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10899,10 +10889,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>522241</v>
+        <v>522268</v>
       </c>
       <c r="R98" t="n">
-        <v>6936518</v>
+        <v>6936556</v>
       </c>
       <c r="S98" t="n">
         <v>4</v>
@@ -10934,7 +10924,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10944,7 +10934,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10971,32 +10961,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125646900</v>
+        <v>125646886</v>
       </c>
       <c r="B99" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11006,10 +10996,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>521975</v>
+        <v>522109</v>
       </c>
       <c r="R99" t="n">
-        <v>6936372</v>
+        <v>6936414</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11042,11 +11032,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11073,32 +11058,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125646894</v>
+        <v>125646900</v>
       </c>
       <c r="B100" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11108,10 +11093,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>522227</v>
+        <v>521975</v>
       </c>
       <c r="R100" t="n">
-        <v>6936562</v>
+        <v>6936372</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11144,6 +11129,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11170,32 +11160,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125632344</v>
+        <v>125632348</v>
       </c>
       <c r="B101" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11205,10 +11195,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>522268</v>
+        <v>522241</v>
       </c>
       <c r="R101" t="n">
-        <v>6936556</v>
+        <v>6936518</v>
       </c>
       <c r="S101" t="n">
         <v>4</v>
@@ -11240,7 +11230,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11250,7 +11240,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11277,32 +11267,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125646886</v>
+        <v>125632333</v>
       </c>
       <c r="B102" t="n">
-        <v>98324</v>
+        <v>80070</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11312,13 +11302,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>522109</v>
+        <v>522235</v>
       </c>
       <c r="R102" t="n">
-        <v>6936414</v>
+        <v>6936598</v>
       </c>
       <c r="S102" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11342,12 +11332,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11362,22 +11362,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125632390</v>
+        <v>125632323</v>
       </c>
       <c r="B103" t="n">
-        <v>91220</v>
+        <v>78967</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11385,21 +11385,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11409,10 +11409,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>522187</v>
+        <v>522189</v>
       </c>
       <c r="R103" t="n">
-        <v>6936377</v>
+        <v>6936648</v>
       </c>
       <c r="S103" t="n">
         <v>4</v>
@@ -11444,7 +11444,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11454,7 +11454,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11481,10 +11481,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125632325</v>
+        <v>125635476</v>
       </c>
       <c r="B104" t="n">
-        <v>78725</v>
+        <v>80070</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11492,37 +11492,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>522198</v>
+        <v>522057</v>
       </c>
       <c r="R104" t="n">
-        <v>6936620</v>
+        <v>6936487</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11546,22 +11546,17 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>12:57</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>12:57</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11576,22 +11571,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125646880</v>
+        <v>125632325</v>
       </c>
       <c r="B105" t="n">
-        <v>80070</v>
+        <v>78725</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11599,21 +11594,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11623,13 +11618,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>522225</v>
+        <v>522198</v>
       </c>
       <c r="R105" t="n">
-        <v>6936564</v>
+        <v>6936620</v>
       </c>
       <c r="S105" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11653,12 +11648,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11673,22 +11678,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125635476</v>
+        <v>125632390</v>
       </c>
       <c r="B106" t="n">
-        <v>80070</v>
+        <v>91227</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11696,37 +11701,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>522057</v>
+        <v>522187</v>
       </c>
       <c r="R106" t="n">
-        <v>6936487</v>
+        <v>6936377</v>
       </c>
       <c r="S106" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11750,17 +11755,22 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11775,19 +11785,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125632323</v>
+        <v>125632330</v>
       </c>
       <c r="B107" t="n">
         <v>78967</v>
@@ -11818,17 +11828,17 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>522189</v>
+        <v>522172</v>
       </c>
       <c r="R107" t="n">
-        <v>6936648</v>
+        <v>6936483</v>
       </c>
       <c r="S107" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11852,22 +11862,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>12:51</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>12:51</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11882,22 +11882,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125632330</v>
+        <v>125646880</v>
       </c>
       <c r="B108" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11905,37 +11905,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>522172</v>
+        <v>522225</v>
       </c>
       <c r="R108" t="n">
-        <v>6936483</v>
+        <v>6936564</v>
       </c>
       <c r="S108" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>125632412</v>
       </c>
       <c r="B109" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>125632379</v>
       </c>
       <c r="B110" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12205,10 +12205,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125632351</v>
+        <v>125632340</v>
       </c>
       <c r="B111" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12240,10 +12240,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>522250</v>
+        <v>522232</v>
       </c>
       <c r="R111" t="n">
-        <v>6936497</v>
+        <v>6936562</v>
       </c>
       <c r="S111" t="n">
         <v>4</v>
@@ -12275,7 +12275,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12312,10 +12312,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125632340</v>
+        <v>125632351</v>
       </c>
       <c r="B112" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12347,10 +12347,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>522232</v>
+        <v>522250</v>
       </c>
       <c r="R112" t="n">
-        <v>6936562</v>
+        <v>6936497</v>
       </c>
       <c r="S112" t="n">
         <v>4</v>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12392,7 +12392,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12422,7 +12422,7 @@
         <v>125646884</v>
       </c>
       <c r="B113" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12516,32 +12516,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125632371</v>
+        <v>125632347</v>
       </c>
       <c r="B114" t="n">
-        <v>98324</v>
+        <v>78725</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12551,10 +12551,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>522243</v>
+        <v>522239</v>
       </c>
       <c r="R114" t="n">
-        <v>6936460</v>
+        <v>6936527</v>
       </c>
       <c r="S114" t="n">
         <v>4</v>
@@ -12586,7 +12586,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12623,32 +12623,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125632385</v>
+        <v>125632346</v>
       </c>
       <c r="B115" t="n">
-        <v>98324</v>
+        <v>80070</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12658,10 +12658,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>522197</v>
+        <v>522239</v>
       </c>
       <c r="R115" t="n">
-        <v>6936406</v>
+        <v>6936527</v>
       </c>
       <c r="S115" t="n">
         <v>4</v>
@@ -12693,7 +12693,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12703,7 +12703,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12730,48 +12730,48 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125635820</v>
+        <v>125632399</v>
       </c>
       <c r="B116" t="n">
-        <v>98324</v>
+        <v>56843</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>522040</v>
+        <v>522053</v>
       </c>
       <c r="R116" t="n">
-        <v>6936582</v>
+        <v>6936400</v>
       </c>
       <c r="S116" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12795,12 +12795,27 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12815,22 +12830,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125632394</v>
+        <v>125632371</v>
       </c>
       <c r="B117" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12862,10 +12877,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>522136</v>
+        <v>522243</v>
       </c>
       <c r="R117" t="n">
-        <v>6936370</v>
+        <v>6936460</v>
       </c>
       <c r="S117" t="n">
         <v>4</v>
@@ -12897,7 +12912,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12907,7 +12922,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12934,32 +12949,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125632347</v>
+        <v>125632385</v>
       </c>
       <c r="B118" t="n">
-        <v>78725</v>
+        <v>98331</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12969,10 +12984,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>522239</v>
+        <v>522197</v>
       </c>
       <c r="R118" t="n">
-        <v>6936527</v>
+        <v>6936406</v>
       </c>
       <c r="S118" t="n">
         <v>4</v>
@@ -13004,7 +13019,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13014,7 +13029,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13041,32 +13056,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125632346</v>
+        <v>125632394</v>
       </c>
       <c r="B119" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13076,10 +13091,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>522239</v>
+        <v>522136</v>
       </c>
       <c r="R119" t="n">
-        <v>6936527</v>
+        <v>6936370</v>
       </c>
       <c r="S119" t="n">
         <v>4</v>
@@ -13111,7 +13126,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13121,7 +13136,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13148,48 +13163,48 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125632399</v>
+        <v>125635820</v>
       </c>
       <c r="B120" t="n">
-        <v>56843</v>
+        <v>98331</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>522053</v>
+        <v>522040</v>
       </c>
       <c r="R120" t="n">
-        <v>6936400</v>
+        <v>6936582</v>
       </c>
       <c r="S120" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13213,27 +13228,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>15:07</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>15:07</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>spillning</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13248,12 +13248,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -13263,7 +13263,7 @@
         <v>125632405</v>
       </c>
       <c r="B121" t="n">
-        <v>91513</v>
+        <v>91520</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13367,10 +13367,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125632383</v>
+        <v>125601877</v>
       </c>
       <c r="B122" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13402,13 +13402,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>522219</v>
+        <v>522217</v>
       </c>
       <c r="R122" t="n">
-        <v>6936411</v>
+        <v>6936540</v>
       </c>
       <c r="S122" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13435,19 +13435,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>14:30</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13462,22 +13452,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125601877</v>
+        <v>125637290</v>
       </c>
       <c r="B123" t="n">
-        <v>91220</v>
+        <v>78725</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13485,37 +13475,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>522217</v>
+        <v>522366</v>
       </c>
       <c r="R123" t="n">
-        <v>6936540</v>
+        <v>6936463</v>
       </c>
       <c r="S123" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13539,12 +13529,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13559,22 +13549,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125637290</v>
+        <v>125632383</v>
       </c>
       <c r="B124" t="n">
-        <v>78725</v>
+        <v>91227</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13582,37 +13572,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>522366</v>
+        <v>522219</v>
       </c>
       <c r="R124" t="n">
-        <v>6936463</v>
+        <v>6936411</v>
       </c>
       <c r="S124" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13636,12 +13626,22 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13656,12 +13656,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -13780,32 +13780,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125632345</v>
+        <v>125632408</v>
       </c>
       <c r="B126" t="n">
-        <v>78967</v>
+        <v>98365</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13815,10 +13815,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>522244</v>
+        <v>522057</v>
       </c>
       <c r="R126" t="n">
-        <v>6936537</v>
+        <v>6936411</v>
       </c>
       <c r="S126" t="n">
         <v>4</v>
@@ -13850,7 +13850,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13860,7 +13860,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13887,32 +13887,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125632326</v>
+        <v>125632395</v>
       </c>
       <c r="B127" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13922,10 +13922,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>522213</v>
+        <v>522113</v>
       </c>
       <c r="R127" t="n">
-        <v>6936615</v>
+        <v>6936367</v>
       </c>
       <c r="S127" t="n">
         <v>4</v>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -13967,7 +13967,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13994,48 +13994,48 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125635162</v>
+        <v>125632388</v>
       </c>
       <c r="B128" t="n">
-        <v>79585</v>
+        <v>98331</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>522010</v>
+        <v>522190</v>
       </c>
       <c r="R128" t="n">
-        <v>6936407</v>
+        <v>6936390</v>
       </c>
       <c r="S128" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14059,12 +14059,22 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14079,22 +14089,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125646878</v>
+        <v>125632326</v>
       </c>
       <c r="B129" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14102,21 +14112,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14126,13 +14136,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>522019</v>
+        <v>522213</v>
       </c>
       <c r="R129" t="n">
-        <v>6936608</v>
+        <v>6936615</v>
       </c>
       <c r="S129" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14156,12 +14166,22 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14176,22 +14196,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125632414</v>
+        <v>125646878</v>
       </c>
       <c r="B130" t="n">
-        <v>91220</v>
+        <v>80070</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14199,21 +14219,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14223,13 +14243,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>522109</v>
+        <v>522019</v>
       </c>
       <c r="R130" t="n">
-        <v>6936426</v>
+        <v>6936608</v>
       </c>
       <c r="S130" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14253,22 +14273,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>15:24</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>15:24</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14283,22 +14293,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125601077</v>
+        <v>125632345</v>
       </c>
       <c r="B131" t="n">
-        <v>80071</v>
+        <v>78967</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14306,21 +14316,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14330,13 +14340,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>522217</v>
+        <v>522244</v>
       </c>
       <c r="R131" t="n">
-        <v>6936540</v>
+        <v>6936537</v>
       </c>
       <c r="S131" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14363,11 +14373,21 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
@@ -14376,63 +14396,48 @@
       </c>
       <c r="AG131" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125632408</v>
+        <v>125632414</v>
       </c>
       <c r="B132" t="n">
-        <v>98358</v>
+        <v>91227</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14442,10 +14447,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>522057</v>
+        <v>522109</v>
       </c>
       <c r="R132" t="n">
-        <v>6936411</v>
+        <v>6936426</v>
       </c>
       <c r="S132" t="n">
         <v>4</v>
@@ -14477,7 +14482,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14487,7 +14492,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14514,32 +14519,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125632395</v>
+        <v>125601077</v>
       </c>
       <c r="B133" t="n">
-        <v>98324</v>
+        <v>80071</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14549,13 +14554,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>522113</v>
+        <v>522217</v>
       </c>
       <c r="R133" t="n">
-        <v>6936367</v>
+        <v>6936540</v>
       </c>
       <c r="S133" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14582,21 +14587,11 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
@@ -14605,64 +14600,79 @@
       </c>
       <c r="AG133" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125632388</v>
+        <v>125635162</v>
       </c>
       <c r="B134" t="n">
-        <v>98324</v>
+        <v>79585</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>522190</v>
+        <v>522010</v>
       </c>
       <c r="R134" t="n">
-        <v>6936390</v>
+        <v>6936407</v>
       </c>
       <c r="S134" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14686,22 +14696,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14716,60 +14716,60 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125633219</v>
+        <v>125632407</v>
       </c>
       <c r="B135" t="n">
-        <v>98324</v>
+        <v>91227</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>MD0:Ånge, SE-VN, SE, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>522237</v>
+        <v>522052</v>
       </c>
       <c r="R135" t="n">
-        <v>6936437</v>
+        <v>6936413</v>
       </c>
       <c r="S135" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14808,7 +14808,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14835,32 +14835,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125632373</v>
+        <v>125632334</v>
       </c>
       <c r="B136" t="n">
-        <v>98324</v>
+        <v>80099</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14870,10 +14870,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>522236</v>
+        <v>522239</v>
       </c>
       <c r="R136" t="n">
-        <v>6936449</v>
+        <v>6936600</v>
       </c>
       <c r="S136" t="n">
         <v>4</v>
@@ -14905,7 +14905,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14942,10 +14942,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125632352</v>
+        <v>125633219</v>
       </c>
       <c r="B137" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14973,17 +14973,17 @@
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>MD0:Ånge, SE-VN, SE, Mpd</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>522245</v>
+        <v>522237</v>
       </c>
       <c r="R137" t="n">
-        <v>6936497</v>
+        <v>6936437</v>
       </c>
       <c r="S137" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15049,10 +15049,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125632359</v>
+        <v>125632373</v>
       </c>
       <c r="B138" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>522236</v>
       </c>
       <c r="R138" t="n">
-        <v>6936482</v>
+        <v>6936449</v>
       </c>
       <c r="S138" t="n">
         <v>4</v>
@@ -15119,7 +15119,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15156,32 +15156,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125632407</v>
+        <v>125632352</v>
       </c>
       <c r="B139" t="n">
-        <v>91220</v>
+        <v>98331</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15191,10 +15191,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>522052</v>
+        <v>522245</v>
       </c>
       <c r="R139" t="n">
-        <v>6936413</v>
+        <v>6936497</v>
       </c>
       <c r="S139" t="n">
         <v>4</v>
@@ -15226,7 +15226,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15236,7 +15236,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15263,32 +15263,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125632334</v>
+        <v>125632359</v>
       </c>
       <c r="B140" t="n">
-        <v>80099</v>
+        <v>98331</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15298,10 +15298,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>522239</v>
+        <v>522236</v>
       </c>
       <c r="R140" t="n">
-        <v>6936600</v>
+        <v>6936482</v>
       </c>
       <c r="S140" t="n">
         <v>4</v>
@@ -15333,7 +15333,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15343,7 +15343,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15370,48 +15370,48 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125636452</v>
+        <v>125646901</v>
       </c>
       <c r="B141" t="n">
-        <v>91380</v>
+        <v>92509</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>522141</v>
+        <v>522030</v>
       </c>
       <c r="R141" t="n">
-        <v>6936548</v>
+        <v>6936634</v>
       </c>
       <c r="S141" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15467,32 +15467,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125646901</v>
+        <v>125632389</v>
       </c>
       <c r="B142" t="n">
-        <v>92502</v>
+        <v>78967</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15502,13 +15502,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>522030</v>
+        <v>522188</v>
       </c>
       <c r="R142" t="n">
-        <v>6936634</v>
+        <v>6936385</v>
       </c>
       <c r="S142" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15532,12 +15532,22 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15552,60 +15562,60 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125632389</v>
+        <v>125636452</v>
       </c>
       <c r="B143" t="n">
-        <v>78967</v>
+        <v>91387</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>522188</v>
+        <v>522141</v>
       </c>
       <c r="R143" t="n">
-        <v>6936385</v>
+        <v>6936548</v>
       </c>
       <c r="S143" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15629,22 +15639,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15659,12 +15659,12 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
@@ -15674,7 +15674,7 @@
         <v>125632375</v>
       </c>
       <c r="B144" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>125633218</v>
       </c>
       <c r="B145" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>125632364</v>
       </c>
       <c r="B146" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15992,32 +15992,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125646888</v>
+        <v>125632366</v>
       </c>
       <c r="B147" t="n">
-        <v>98324</v>
+        <v>98352</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16027,13 +16027,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>522159</v>
+        <v>522249</v>
       </c>
       <c r="R147" t="n">
-        <v>6936405</v>
+        <v>6936460</v>
       </c>
       <c r="S147" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16057,12 +16057,22 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16077,44 +16087,44 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125632419</v>
+        <v>125632384</v>
       </c>
       <c r="B148" t="n">
-        <v>98324</v>
+        <v>98352</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16124,10 +16134,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>522202</v>
+        <v>522207</v>
       </c>
       <c r="R148" t="n">
-        <v>6936414</v>
+        <v>6936406</v>
       </c>
       <c r="S148" t="n">
         <v>4</v>
@@ -16159,7 +16169,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16169,7 +16179,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16196,10 +16206,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125632411</v>
+        <v>125632419</v>
       </c>
       <c r="B149" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16231,10 +16241,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>522063</v>
+        <v>522202</v>
       </c>
       <c r="R149" t="n">
-        <v>6936424</v>
+        <v>6936414</v>
       </c>
       <c r="S149" t="n">
         <v>4</v>
@@ -16266,7 +16276,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16276,7 +16286,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16303,32 +16313,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125632386</v>
+        <v>125646888</v>
       </c>
       <c r="B150" t="n">
-        <v>56843</v>
+        <v>98331</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16338,13 +16348,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>522200</v>
+        <v>522159</v>
       </c>
       <c r="R150" t="n">
-        <v>6936398</v>
+        <v>6936405</v>
       </c>
       <c r="S150" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16368,22 +16378,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16398,44 +16398,44 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125632331</v>
+        <v>125632411</v>
       </c>
       <c r="B151" t="n">
-        <v>92502</v>
+        <v>98331</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16445,10 +16445,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>522221</v>
+        <v>522063</v>
       </c>
       <c r="R151" t="n">
-        <v>6936608</v>
+        <v>6936424</v>
       </c>
       <c r="S151" t="n">
         <v>4</v>
@@ -16480,7 +16480,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16490,7 +16490,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16517,10 +16517,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125632366</v>
+        <v>125632331</v>
       </c>
       <c r="B152" t="n">
-        <v>98345</v>
+        <v>92509</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16528,21 +16528,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>221952</v>
+        <v>4364</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16552,10 +16552,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>522249</v>
+        <v>522221</v>
       </c>
       <c r="R152" t="n">
-        <v>6936460</v>
+        <v>6936608</v>
       </c>
       <c r="S152" t="n">
         <v>4</v>
@@ -16587,7 +16587,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16597,7 +16597,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16624,10 +16624,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125632384</v>
+        <v>125632386</v>
       </c>
       <c r="B153" t="n">
-        <v>98345</v>
+        <v>56843</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16635,21 +16635,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16659,10 +16659,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>522207</v>
+        <v>522200</v>
       </c>
       <c r="R153" t="n">
-        <v>6936406</v>
+        <v>6936398</v>
       </c>
       <c r="S153" t="n">
         <v>4</v>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16704,7 +16704,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16945,32 +16945,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125632376</v>
+        <v>125646899</v>
       </c>
       <c r="B156" t="n">
-        <v>56843</v>
+        <v>91387</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100138</v>
+        <v>1503</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16980,13 +16980,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>522237</v>
+        <v>522143</v>
       </c>
       <c r="R156" t="n">
-        <v>6936423</v>
+        <v>6936554</v>
       </c>
       <c r="S156" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17010,22 +17010,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17040,60 +17030,60 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125635540</v>
+        <v>125632376</v>
       </c>
       <c r="B157" t="n">
-        <v>98324</v>
+        <v>56843</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>522055</v>
+        <v>522237</v>
       </c>
       <c r="R157" t="n">
-        <v>6936516</v>
+        <v>6936423</v>
       </c>
       <c r="S157" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17117,12 +17107,22 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17137,22 +17137,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125632393</v>
+        <v>125635540</v>
       </c>
       <c r="B158" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17180,17 +17180,17 @@
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>522160</v>
+        <v>522055</v>
       </c>
       <c r="R158" t="n">
-        <v>6936368</v>
+        <v>6936516</v>
       </c>
       <c r="S158" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17214,22 +17214,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17244,22 +17234,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125646899</v>
+        <v>125632393</v>
       </c>
       <c r="B159" t="n">
-        <v>91380</v>
+        <v>98331</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17267,21 +17257,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17291,13 +17281,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>522143</v>
+        <v>522160</v>
       </c>
       <c r="R159" t="n">
-        <v>6936554</v>
+        <v>6936368</v>
       </c>
       <c r="S159" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17321,12 +17311,22 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17341,12 +17341,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>

--- a/artfynd/A 26476-2025 artfynd.xlsx
+++ b/artfynd/A 26476-2025 artfynd.xlsx
@@ -2925,32 +2925,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125646874</v>
+        <v>125632425</v>
       </c>
       <c r="B21" t="n">
-        <v>80098</v>
+        <v>78967</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2960,13 +2960,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>522022</v>
+        <v>522345</v>
       </c>
       <c r="R21" t="n">
-        <v>6936611</v>
+        <v>6936464</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2990,12 +2990,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3010,44 +3020,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125601310</v>
+        <v>125646902</v>
       </c>
       <c r="B22" t="n">
-        <v>98331</v>
+        <v>4869</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>101675</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3057,13 +3067,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>522217</v>
+        <v>522019</v>
       </c>
       <c r="R22" t="n">
-        <v>6936540</v>
+        <v>6936608</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3087,12 +3097,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Kläckhål på asp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3107,60 +3122,60 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125632569</v>
+        <v>125646874</v>
       </c>
       <c r="B23" t="n">
-        <v>98331</v>
+        <v>80098</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>522108</v>
+        <v>522022</v>
       </c>
       <c r="R23" t="n">
-        <v>6936467</v>
+        <v>6936611</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3216,7 +3231,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125632421</v>
+        <v>125601310</v>
       </c>
       <c r="B24" t="n">
         <v>98331</v>
@@ -3251,13 +3266,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>522260</v>
+        <v>522217</v>
       </c>
       <c r="R24" t="n">
-        <v>6936447</v>
+        <v>6936540</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3284,19 +3299,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3311,60 +3316,60 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125602968</v>
+        <v>125632569</v>
       </c>
       <c r="B25" t="n">
-        <v>98352</v>
+        <v>98331</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>522217</v>
+        <v>522108</v>
       </c>
       <c r="R25" t="n">
-        <v>6936540</v>
+        <v>6936467</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3388,12 +3393,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3408,44 +3413,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125646875</v>
+        <v>125632421</v>
       </c>
       <c r="B26" t="n">
-        <v>78726</v>
+        <v>98331</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3455,13 +3460,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>522035</v>
+        <v>522260</v>
       </c>
       <c r="R26" t="n">
-        <v>6936550</v>
+        <v>6936447</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3485,12 +3490,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3505,44 +3520,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125632425</v>
+        <v>125602968</v>
       </c>
       <c r="B27" t="n">
-        <v>78967</v>
+        <v>98352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3552,13 +3567,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>522345</v>
+        <v>522217</v>
       </c>
       <c r="R27" t="n">
-        <v>6936464</v>
+        <v>6936540</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3585,19 +3600,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>15:45</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3612,44 +3617,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125646902</v>
+        <v>125646875</v>
       </c>
       <c r="B28" t="n">
-        <v>4869</v>
+        <v>78726</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101675</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3659,10 +3664,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>522019</v>
+        <v>522035</v>
       </c>
       <c r="R28" t="n">
-        <v>6936608</v>
+        <v>6936550</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3695,11 +3700,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Kläckhål på asp</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4644,32 +4644,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125632337</v>
+        <v>125632329</v>
       </c>
       <c r="B38" t="n">
-        <v>78967</v>
+        <v>80099</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4679,10 +4679,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>522224</v>
+        <v>522215</v>
       </c>
       <c r="R38" t="n">
-        <v>6936572</v>
+        <v>6936627</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4751,10 +4751,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125632362</v>
+        <v>125632337</v>
       </c>
       <c r="B39" t="n">
-        <v>78725</v>
+        <v>78967</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4762,21 +4762,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4786,10 +4786,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>522249</v>
+        <v>522224</v>
       </c>
       <c r="R39" t="n">
-        <v>6936486</v>
+        <v>6936572</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4858,32 +4858,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125632338</v>
+        <v>125632362</v>
       </c>
       <c r="B40" t="n">
-        <v>92509</v>
+        <v>78725</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>522221</v>
+        <v>522249</v>
       </c>
       <c r="R40" t="n">
-        <v>6936572</v>
+        <v>6936486</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4965,7 +4965,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125636088</v>
+        <v>125632338</v>
       </c>
       <c r="B41" t="n">
         <v>92509</v>
@@ -4996,17 +4996,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>522049</v>
+        <v>522221</v>
       </c>
       <c r="R41" t="n">
-        <v>6936650</v>
+        <v>6936572</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5030,12 +5030,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5050,22 +5060,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125632329</v>
+        <v>125636088</v>
       </c>
       <c r="B42" t="n">
-        <v>80099</v>
+        <v>92509</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5073,37 +5083,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>522215</v>
+        <v>522049</v>
       </c>
       <c r="R42" t="n">
-        <v>6936627</v>
+        <v>6936650</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5127,22 +5137,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:04</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:04</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5157,12 +5157,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5684,48 +5684,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125632416</v>
+        <v>125638972</v>
       </c>
       <c r="B48" t="n">
-        <v>91245</v>
+        <v>98331</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>522125</v>
+        <v>522318</v>
       </c>
       <c r="R48" t="n">
-        <v>6936430</v>
+        <v>6936398</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5749,22 +5749,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>15:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>15:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5779,44 +5769,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125600818</v>
+        <v>125632382</v>
       </c>
       <c r="B49" t="n">
-        <v>98248</v>
+        <v>98331</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5826,13 +5816,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>522217</v>
+        <v>522214</v>
       </c>
       <c r="R49" t="n">
-        <v>6936540</v>
+        <v>6936414</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5859,9 +5849,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5876,19 +5876,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125638972</v>
+        <v>125646883</v>
       </c>
       <c r="B50" t="n">
         <v>98331</v>
@@ -5919,17 +5919,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>522318</v>
+        <v>522097</v>
       </c>
       <c r="R50" t="n">
-        <v>6936398</v>
+        <v>6936427</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5985,32 +5985,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125632382</v>
+        <v>125632416</v>
       </c>
       <c r="B51" t="n">
-        <v>98331</v>
+        <v>91245</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6020,10 +6020,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>522214</v>
+        <v>522125</v>
       </c>
       <c r="R51" t="n">
-        <v>6936414</v>
+        <v>6936430</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6055,7 +6055,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6092,32 +6092,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125646883</v>
+        <v>125600818</v>
       </c>
       <c r="B52" t="n">
-        <v>98331</v>
+        <v>98248</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6127,13 +6127,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>522097</v>
+        <v>522217</v>
       </c>
       <c r="R52" t="n">
-        <v>6936427</v>
+        <v>6936540</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6157,12 +6157,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6177,12 +6177,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -8463,32 +8463,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125632372</v>
+        <v>125632370</v>
       </c>
       <c r="B75" t="n">
-        <v>98352</v>
+        <v>98331</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8498,10 +8498,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>522236</v>
+        <v>522243</v>
       </c>
       <c r="R75" t="n">
-        <v>6936448</v>
+        <v>6936456</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -8533,7 +8533,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8570,7 +8570,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125632370</v>
+        <v>125632381</v>
       </c>
       <c r="B76" t="n">
         <v>98331</v>
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>522243</v>
+        <v>522240</v>
       </c>
       <c r="R76" t="n">
-        <v>6936456</v>
+        <v>6936412</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8677,7 +8677,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125632381</v>
+        <v>125632418</v>
       </c>
       <c r="B77" t="n">
         <v>98331</v>
@@ -8712,10 +8712,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>522240</v>
+        <v>522162</v>
       </c>
       <c r="R77" t="n">
-        <v>6936412</v>
+        <v>6936404</v>
       </c>
       <c r="S77" t="n">
         <v>4</v>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8784,32 +8784,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125632418</v>
+        <v>125632372</v>
       </c>
       <c r="B78" t="n">
-        <v>98331</v>
+        <v>98352</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8819,10 +8819,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>522162</v>
+        <v>522236</v>
       </c>
       <c r="R78" t="n">
-        <v>6936404</v>
+        <v>6936448</v>
       </c>
       <c r="S78" t="n">
         <v>4</v>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9727,48 +9727,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125637200</v>
+        <v>125646882</v>
       </c>
       <c r="B87" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>522362</v>
+        <v>522029</v>
       </c>
       <c r="R87" t="n">
-        <v>6936466</v>
+        <v>6936561</v>
       </c>
       <c r="S87" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9824,48 +9824,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125635192</v>
+        <v>125632417</v>
       </c>
       <c r="B88" t="n">
-        <v>92509</v>
+        <v>98331</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>522003</v>
+        <v>522163</v>
       </c>
       <c r="R88" t="n">
-        <v>6936451</v>
+        <v>6936406</v>
       </c>
       <c r="S88" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9889,12 +9889,22 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9909,60 +9919,60 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125646882</v>
+        <v>125637200</v>
       </c>
       <c r="B89" t="n">
-        <v>98331</v>
+        <v>78967</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>522029</v>
+        <v>522362</v>
       </c>
       <c r="R89" t="n">
-        <v>6936561</v>
+        <v>6936466</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10018,48 +10028,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125632417</v>
+        <v>125635192</v>
       </c>
       <c r="B90" t="n">
-        <v>98331</v>
+        <v>92509</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>522163</v>
+        <v>522003</v>
       </c>
       <c r="R90" t="n">
-        <v>6936406</v>
+        <v>6936451</v>
       </c>
       <c r="S90" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10083,22 +10093,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10113,12 +10113,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -10232,10 +10232,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125633268</v>
+        <v>125635666</v>
       </c>
       <c r="B92" t="n">
-        <v>57811</v>
+        <v>80070</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10243,42 +10243,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>522121</v>
+        <v>522038</v>
       </c>
       <c r="R92" t="n">
-        <v>6936402</v>
+        <v>6936535</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10308,6 +10303,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10334,48 +10334,53 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125632409</v>
+        <v>125633268</v>
       </c>
       <c r="B93" t="n">
-        <v>98331</v>
+        <v>57811</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>522062</v>
+        <v>522121</v>
       </c>
       <c r="R93" t="n">
-        <v>6936422</v>
+        <v>6936402</v>
       </c>
       <c r="S93" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10399,22 +10404,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10429,19 +10424,19 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125632415</v>
+        <v>125632409</v>
       </c>
       <c r="B94" t="n">
         <v>98331</v>
@@ -10476,10 +10471,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>522124</v>
+        <v>522062</v>
       </c>
       <c r="R94" t="n">
-        <v>6936410</v>
+        <v>6936422</v>
       </c>
       <c r="S94" t="n">
         <v>4</v>
@@ -10511,7 +10506,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10521,7 +10516,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10548,32 +10543,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125632358</v>
+        <v>125632415</v>
       </c>
       <c r="B95" t="n">
-        <v>98352</v>
+        <v>98331</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10583,10 +10578,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>522231</v>
+        <v>522124</v>
       </c>
       <c r="R95" t="n">
-        <v>6936488</v>
+        <v>6936410</v>
       </c>
       <c r="S95" t="n">
         <v>4</v>
@@ -10618,7 +10613,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10628,7 +10623,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10655,48 +10650,48 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125635666</v>
+        <v>125632358</v>
       </c>
       <c r="B96" t="n">
-        <v>80070</v>
+        <v>98352</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>522038</v>
+        <v>522231</v>
       </c>
       <c r="R96" t="n">
-        <v>6936535</v>
+        <v>6936488</v>
       </c>
       <c r="S96" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10720,17 +10715,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10745,44 +10745,44 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125646894</v>
+        <v>125646900</v>
       </c>
       <c r="B97" t="n">
-        <v>98331</v>
+        <v>78967</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10792,10 +10792,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>522227</v>
+        <v>521975</v>
       </c>
       <c r="R97" t="n">
-        <v>6936562</v>
+        <v>6936372</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10828,6 +10828,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10854,32 +10859,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125632344</v>
+        <v>125632348</v>
       </c>
       <c r="B98" t="n">
-        <v>98331</v>
+        <v>78967</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10889,10 +10894,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>522268</v>
+        <v>522241</v>
       </c>
       <c r="R98" t="n">
-        <v>6936556</v>
+        <v>6936518</v>
       </c>
       <c r="S98" t="n">
         <v>4</v>
@@ -10924,7 +10929,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10934,7 +10939,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10961,32 +10966,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125646886</v>
+        <v>125632333</v>
       </c>
       <c r="B99" t="n">
-        <v>98331</v>
+        <v>80070</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10996,13 +11001,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>522109</v>
+        <v>522235</v>
       </c>
       <c r="R99" t="n">
-        <v>6936414</v>
+        <v>6936598</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11026,12 +11031,22 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11046,44 +11061,44 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125646900</v>
+        <v>125646894</v>
       </c>
       <c r="B100" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11093,10 +11108,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>521975</v>
+        <v>522227</v>
       </c>
       <c r="R100" t="n">
-        <v>6936372</v>
+        <v>6936562</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11129,11 +11144,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11160,32 +11170,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125632348</v>
+        <v>125632344</v>
       </c>
       <c r="B101" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11195,10 +11205,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>522241</v>
+        <v>522268</v>
       </c>
       <c r="R101" t="n">
-        <v>6936518</v>
+        <v>6936556</v>
       </c>
       <c r="S101" t="n">
         <v>4</v>
@@ -11230,7 +11240,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11240,7 +11250,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11267,32 +11277,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125632333</v>
+        <v>125646886</v>
       </c>
       <c r="B102" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11302,13 +11312,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>522235</v>
+        <v>522109</v>
       </c>
       <c r="R102" t="n">
-        <v>6936598</v>
+        <v>6936414</v>
       </c>
       <c r="S102" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11332,22 +11342,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11362,12 +11362,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -13260,10 +13260,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125632405</v>
+        <v>125632360</v>
       </c>
       <c r="B121" t="n">
-        <v>91520</v>
+        <v>57648</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13271,21 +13271,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13295,10 +13295,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>522044</v>
+        <v>522247</v>
       </c>
       <c r="R121" t="n">
-        <v>6936401</v>
+        <v>6936482</v>
       </c>
       <c r="S121" t="n">
         <v>4</v>
@@ -13330,7 +13330,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13340,7 +13340,12 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>födosök död stående tall</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13367,10 +13372,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125601877</v>
+        <v>125632405</v>
       </c>
       <c r="B122" t="n">
-        <v>91227</v>
+        <v>91520</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13378,21 +13383,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13402,13 +13407,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>522217</v>
+        <v>522044</v>
       </c>
       <c r="R122" t="n">
-        <v>6936540</v>
+        <v>6936401</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13435,9 +13440,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13452,22 +13467,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125637290</v>
+        <v>125601877</v>
       </c>
       <c r="B123" t="n">
-        <v>78725</v>
+        <v>91227</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13475,37 +13490,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>522366</v>
+        <v>522217</v>
       </c>
       <c r="R123" t="n">
-        <v>6936463</v>
+        <v>6936540</v>
       </c>
       <c r="S123" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13529,12 +13544,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13549,22 +13564,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125632383</v>
+        <v>125637290</v>
       </c>
       <c r="B124" t="n">
-        <v>91227</v>
+        <v>78725</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13572,37 +13587,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>522219</v>
+        <v>522366</v>
       </c>
       <c r="R124" t="n">
-        <v>6936411</v>
+        <v>6936463</v>
       </c>
       <c r="S124" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13626,22 +13641,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13656,22 +13661,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125632360</v>
+        <v>125632383</v>
       </c>
       <c r="B125" t="n">
-        <v>57648</v>
+        <v>91227</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13679,21 +13684,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13703,10 +13708,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>522247</v>
+        <v>522219</v>
       </c>
       <c r="R125" t="n">
-        <v>6936482</v>
+        <v>6936411</v>
       </c>
       <c r="S125" t="n">
         <v>4</v>
@@ -13738,7 +13743,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13748,12 +13753,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>födosök död stående tall</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13780,32 +13780,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125632408</v>
+        <v>125632395</v>
       </c>
       <c r="B126" t="n">
-        <v>98365</v>
+        <v>98331</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13815,10 +13815,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>522057</v>
+        <v>522113</v>
       </c>
       <c r="R126" t="n">
-        <v>6936411</v>
+        <v>6936367</v>
       </c>
       <c r="S126" t="n">
         <v>4</v>
@@ -13850,7 +13850,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13860,7 +13860,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13887,7 +13887,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125632395</v>
+        <v>125632388</v>
       </c>
       <c r="B127" t="n">
         <v>98331</v>
@@ -13922,10 +13922,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>522113</v>
+        <v>522190</v>
       </c>
       <c r="R127" t="n">
-        <v>6936367</v>
+        <v>6936390</v>
       </c>
       <c r="S127" t="n">
         <v>4</v>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -13967,7 +13967,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13994,32 +13994,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125632388</v>
+        <v>125632326</v>
       </c>
       <c r="B128" t="n">
-        <v>98331</v>
+        <v>78967</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14029,10 +14029,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>522190</v>
+        <v>522213</v>
       </c>
       <c r="R128" t="n">
-        <v>6936390</v>
+        <v>6936615</v>
       </c>
       <c r="S128" t="n">
         <v>4</v>
@@ -14064,7 +14064,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14074,7 +14074,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14101,10 +14101,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125632326</v>
+        <v>125646878</v>
       </c>
       <c r="B129" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14112,21 +14112,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14136,13 +14136,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>522213</v>
+        <v>522019</v>
       </c>
       <c r="R129" t="n">
-        <v>6936615</v>
+        <v>6936608</v>
       </c>
       <c r="S129" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14166,22 +14166,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>13:02</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>13:02</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14196,22 +14186,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125646878</v>
+        <v>125632345</v>
       </c>
       <c r="B130" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14219,21 +14209,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14243,13 +14233,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>522019</v>
+        <v>522244</v>
       </c>
       <c r="R130" t="n">
-        <v>6936608</v>
+        <v>6936537</v>
       </c>
       <c r="S130" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14273,12 +14263,22 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14293,22 +14293,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125632345</v>
+        <v>125632414</v>
       </c>
       <c r="B131" t="n">
-        <v>78967</v>
+        <v>91227</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14316,21 +14316,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14340,10 +14340,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>522244</v>
+        <v>522109</v>
       </c>
       <c r="R131" t="n">
-        <v>6936537</v>
+        <v>6936426</v>
       </c>
       <c r="S131" t="n">
         <v>4</v>
@@ -14375,7 +14375,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14412,10 +14412,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125632414</v>
+        <v>125601077</v>
       </c>
       <c r="B132" t="n">
-        <v>91227</v>
+        <v>80071</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14423,21 +14423,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14447,13 +14447,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>522109</v>
+        <v>522217</v>
       </c>
       <c r="R132" t="n">
-        <v>6936426</v>
+        <v>6936540</v>
       </c>
       <c r="S132" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14480,21 +14480,11 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
@@ -14503,26 +14493,41 @@
       </c>
       <c r="AG132" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125601077</v>
+        <v>125635162</v>
       </c>
       <c r="B133" t="n">
-        <v>80071</v>
+        <v>79585</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14530,37 +14535,37 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>522217</v>
+        <v>522010</v>
       </c>
       <c r="R133" t="n">
-        <v>6936540</v>
+        <v>6936407</v>
       </c>
       <c r="S133" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14584,12 +14589,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14600,79 +14605,64 @@
       </c>
       <c r="AG133" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ133" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK133" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO133" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125635162</v>
+        <v>125632408</v>
       </c>
       <c r="B134" t="n">
-        <v>79585</v>
+        <v>98365</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>219874</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>522010</v>
+        <v>522057</v>
       </c>
       <c r="R134" t="n">
-        <v>6936407</v>
+        <v>6936411</v>
       </c>
       <c r="S134" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14696,12 +14686,22 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14716,44 +14716,44 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125632407</v>
+        <v>125632373</v>
       </c>
       <c r="B135" t="n">
-        <v>91227</v>
+        <v>98331</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14763,10 +14763,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>522052</v>
+        <v>522236</v>
       </c>
       <c r="R135" t="n">
-        <v>6936413</v>
+        <v>6936449</v>
       </c>
       <c r="S135" t="n">
         <v>4</v>
@@ -14798,7 +14798,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14808,7 +14808,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14835,32 +14835,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125632334</v>
+        <v>125632352</v>
       </c>
       <c r="B136" t="n">
-        <v>80099</v>
+        <v>98331</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14870,10 +14870,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>522239</v>
+        <v>522245</v>
       </c>
       <c r="R136" t="n">
-        <v>6936600</v>
+        <v>6936497</v>
       </c>
       <c r="S136" t="n">
         <v>4</v>
@@ -14905,7 +14905,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14942,7 +14942,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125633219</v>
+        <v>125632359</v>
       </c>
       <c r="B137" t="n">
         <v>98331</v>
@@ -14973,17 +14973,17 @@
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>MD0:Ånge, SE-VN, SE, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>522237</v>
+        <v>522236</v>
       </c>
       <c r="R137" t="n">
-        <v>6936437</v>
+        <v>6936482</v>
       </c>
       <c r="S137" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15049,7 +15049,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125632373</v>
+        <v>125633219</v>
       </c>
       <c r="B138" t="n">
         <v>98331</v>
@@ -15080,17 +15080,17 @@
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>MD0:Ånge, SE-VN, SE, Mpd</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>522236</v>
+        <v>522237</v>
       </c>
       <c r="R138" t="n">
-        <v>6936449</v>
+        <v>6936437</v>
       </c>
       <c r="S138" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15156,32 +15156,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125632352</v>
+        <v>125632407</v>
       </c>
       <c r="B139" t="n">
-        <v>98331</v>
+        <v>91227</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15191,10 +15191,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>522245</v>
+        <v>522052</v>
       </c>
       <c r="R139" t="n">
-        <v>6936497</v>
+        <v>6936413</v>
       </c>
       <c r="S139" t="n">
         <v>4</v>
@@ -15226,7 +15226,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15236,7 +15236,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15263,32 +15263,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125632359</v>
+        <v>125632334</v>
       </c>
       <c r="B140" t="n">
-        <v>98331</v>
+        <v>80099</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15298,10 +15298,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>522236</v>
+        <v>522239</v>
       </c>
       <c r="R140" t="n">
-        <v>6936482</v>
+        <v>6936600</v>
       </c>
       <c r="S140" t="n">
         <v>4</v>
@@ -15333,7 +15333,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15343,7 +15343,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15370,32 +15370,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125646901</v>
+        <v>125632375</v>
       </c>
       <c r="B141" t="n">
-        <v>92509</v>
+        <v>98331</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15405,13 +15405,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>522030</v>
+        <v>522243</v>
       </c>
       <c r="R141" t="n">
-        <v>6936634</v>
+        <v>6936427</v>
       </c>
       <c r="S141" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15435,12 +15435,22 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15455,60 +15465,60 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125632389</v>
+        <v>125633218</v>
       </c>
       <c r="B142" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>MD1:Ånge, SE-VN, SE, Mpd</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>522188</v>
+        <v>522221</v>
       </c>
       <c r="R142" t="n">
-        <v>6936385</v>
+        <v>6936591</v>
       </c>
       <c r="S142" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15537,7 +15547,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15547,7 +15557,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15574,10 +15584,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125636452</v>
+        <v>125632364</v>
       </c>
       <c r="B143" t="n">
-        <v>91387</v>
+        <v>98331</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15585,37 +15595,37 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>522141</v>
+        <v>522260</v>
       </c>
       <c r="R143" t="n">
-        <v>6936548</v>
+        <v>6936473</v>
       </c>
       <c r="S143" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15639,12 +15649,22 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15659,44 +15679,44 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125632375</v>
+        <v>125646901</v>
       </c>
       <c r="B144" t="n">
-        <v>98331</v>
+        <v>92509</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15706,13 +15726,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>522243</v>
+        <v>522030</v>
       </c>
       <c r="R144" t="n">
-        <v>6936427</v>
+        <v>6936634</v>
       </c>
       <c r="S144" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15736,22 +15756,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15766,60 +15776,60 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125633218</v>
+        <v>125632389</v>
       </c>
       <c r="B145" t="n">
-        <v>98331</v>
+        <v>78967</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>MD1:Ånge, SE-VN, SE, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>522221</v>
+        <v>522188</v>
       </c>
       <c r="R145" t="n">
-        <v>6936591</v>
+        <v>6936385</v>
       </c>
       <c r="S145" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15848,7 +15858,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -15858,7 +15868,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15885,10 +15895,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125632364</v>
+        <v>125636452</v>
       </c>
       <c r="B146" t="n">
-        <v>98331</v>
+        <v>91387</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15896,37 +15906,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>522260</v>
+        <v>522141</v>
       </c>
       <c r="R146" t="n">
-        <v>6936473</v>
+        <v>6936548</v>
       </c>
       <c r="S146" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15950,22 +15960,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15980,12 +15980,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
@@ -16731,48 +16731,48 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125632343</v>
+        <v>125635540</v>
       </c>
       <c r="B154" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>522269</v>
+        <v>522055</v>
       </c>
       <c r="R154" t="n">
-        <v>6936560</v>
+        <v>6936516</v>
       </c>
       <c r="S154" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16796,22 +16796,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>13:32</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>13:32</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16826,44 +16816,44 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125632327</v>
+        <v>125632393</v>
       </c>
       <c r="B155" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16873,10 +16863,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>522218</v>
+        <v>522160</v>
       </c>
       <c r="R155" t="n">
-        <v>6936625</v>
+        <v>6936368</v>
       </c>
       <c r="S155" t="n">
         <v>4</v>
@@ -16908,7 +16898,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -16918,7 +16908,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16945,32 +16935,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125646899</v>
+        <v>125632343</v>
       </c>
       <c r="B156" t="n">
-        <v>91387</v>
+        <v>78967</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16980,13 +16970,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>522143</v>
+        <v>522269</v>
       </c>
       <c r="R156" t="n">
-        <v>6936554</v>
+        <v>6936560</v>
       </c>
       <c r="S156" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17010,12 +17000,22 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17030,44 +17030,44 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125632376</v>
+        <v>125632327</v>
       </c>
       <c r="B157" t="n">
-        <v>56843</v>
+        <v>80070</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17077,10 +17077,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>522237</v>
+        <v>522218</v>
       </c>
       <c r="R157" t="n">
-        <v>6936423</v>
+        <v>6936625</v>
       </c>
       <c r="S157" t="n">
         <v>4</v>
@@ -17112,7 +17112,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17122,7 +17122,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17149,10 +17149,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125635540</v>
+        <v>125646899</v>
       </c>
       <c r="B158" t="n">
-        <v>98331</v>
+        <v>91387</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17160,37 +17160,37 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>522055</v>
+        <v>522143</v>
       </c>
       <c r="R158" t="n">
-        <v>6936516</v>
+        <v>6936554</v>
       </c>
       <c r="S158" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17246,32 +17246,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125632393</v>
+        <v>125632376</v>
       </c>
       <c r="B159" t="n">
-        <v>98331</v>
+        <v>56843</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17281,10 +17281,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>522160</v>
+        <v>522237</v>
       </c>
       <c r="R159" t="n">
-        <v>6936368</v>
+        <v>6936423</v>
       </c>
       <c r="S159" t="n">
         <v>4</v>
@@ -17316,7 +17316,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17326,7 +17326,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD159" t="b">

--- a/artfynd/A 26476-2025 artfynd.xlsx
+++ b/artfynd/A 26476-2025 artfynd.xlsx
@@ -3726,32 +3726,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125600959</v>
+        <v>125632349</v>
       </c>
       <c r="B29" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3761,13 +3761,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>522217</v>
+        <v>522259</v>
       </c>
       <c r="R29" t="n">
-        <v>6936540</v>
+        <v>6936489</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3794,11 +3794,21 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3807,38 +3817,23 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125632349</v>
+        <v>125636837</v>
       </c>
       <c r="B30" t="n">
         <v>98331</v>
@@ -3869,17 +3864,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>522259</v>
+        <v>522164</v>
       </c>
       <c r="R30" t="n">
-        <v>6936489</v>
+        <v>6936587</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3903,22 +3898,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3933,60 +3918,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125636837</v>
+        <v>125603562</v>
       </c>
       <c r="B31" t="n">
-        <v>98331</v>
+        <v>80030</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>522164</v>
+        <v>522217</v>
       </c>
       <c r="R31" t="n">
-        <v>6936587</v>
+        <v>6936540</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4010,12 +3995,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4030,22 +4015,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125632367</v>
+        <v>125600280</v>
       </c>
       <c r="B32" t="n">
-        <v>98352</v>
+        <v>92509</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4053,21 +4038,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4077,13 +4062,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>522247</v>
+        <v>522217</v>
       </c>
       <c r="R32" t="n">
-        <v>6936458</v>
+        <v>6936540</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4110,19 +4095,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4137,60 +4112,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125634580</v>
+        <v>125632332</v>
       </c>
       <c r="B33" t="n">
-        <v>98352</v>
+        <v>78967</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>522044</v>
+        <v>522239</v>
       </c>
       <c r="R33" t="n">
-        <v>6936401</v>
+        <v>6936598</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4214,12 +4189,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4234,44 +4219,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125600280</v>
+        <v>125601890</v>
       </c>
       <c r="B34" t="n">
-        <v>92509</v>
+        <v>91678</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4343,10 +4328,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125632332</v>
+        <v>125600959</v>
       </c>
       <c r="B35" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4354,21 +4339,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4378,13 +4363,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>522239</v>
+        <v>522217</v>
       </c>
       <c r="R35" t="n">
-        <v>6936598</v>
+        <v>6936540</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4411,21 +4396,11 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4434,48 +4409,63 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125601890</v>
+        <v>125632367</v>
       </c>
       <c r="B36" t="n">
-        <v>91678</v>
+        <v>98352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>221952</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4485,13 +4475,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>522217</v>
+        <v>522247</v>
       </c>
       <c r="R36" t="n">
-        <v>6936540</v>
+        <v>6936458</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4518,9 +4508,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4535,22 +4535,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125603562</v>
+        <v>125634580</v>
       </c>
       <c r="B37" t="n">
-        <v>80030</v>
+        <v>98352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4558,37 +4558,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229497</v>
+        <v>221952</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>522217</v>
+        <v>522044</v>
       </c>
       <c r="R37" t="n">
-        <v>6936540</v>
+        <v>6936401</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4632,44 +4632,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125632329</v>
+        <v>125632337</v>
       </c>
       <c r="B38" t="n">
-        <v>80099</v>
+        <v>78967</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4679,10 +4679,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>522215</v>
+        <v>522224</v>
       </c>
       <c r="R38" t="n">
-        <v>6936627</v>
+        <v>6936572</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4751,10 +4751,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125632337</v>
+        <v>125632362</v>
       </c>
       <c r="B39" t="n">
-        <v>78967</v>
+        <v>78725</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4762,21 +4762,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4786,10 +4786,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>522224</v>
+        <v>522249</v>
       </c>
       <c r="R39" t="n">
-        <v>6936572</v>
+        <v>6936486</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4858,32 +4858,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125632362</v>
+        <v>125632338</v>
       </c>
       <c r="B40" t="n">
-        <v>78725</v>
+        <v>92509</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>522249</v>
+        <v>522221</v>
       </c>
       <c r="R40" t="n">
-        <v>6936486</v>
+        <v>6936572</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4965,7 +4965,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125632338</v>
+        <v>125636088</v>
       </c>
       <c r="B41" t="n">
         <v>92509</v>
@@ -4996,17 +4996,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>522221</v>
+        <v>522049</v>
       </c>
       <c r="R41" t="n">
-        <v>6936572</v>
+        <v>6936650</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5030,22 +5030,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5060,22 +5050,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125636088</v>
+        <v>125632329</v>
       </c>
       <c r="B42" t="n">
-        <v>92509</v>
+        <v>80099</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5083,37 +5073,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>522049</v>
+        <v>522215</v>
       </c>
       <c r="R42" t="n">
-        <v>6936650</v>
+        <v>6936627</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5137,12 +5127,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5157,12 +5157,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5684,48 +5684,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125638972</v>
+        <v>125632416</v>
       </c>
       <c r="B48" t="n">
-        <v>98331</v>
+        <v>91245</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>522318</v>
+        <v>522125</v>
       </c>
       <c r="R48" t="n">
-        <v>6936398</v>
+        <v>6936430</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5749,12 +5749,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5769,44 +5779,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125632382</v>
+        <v>125600818</v>
       </c>
       <c r="B49" t="n">
-        <v>98331</v>
+        <v>98248</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5816,13 +5826,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>522214</v>
+        <v>522217</v>
       </c>
       <c r="R49" t="n">
-        <v>6936414</v>
+        <v>6936540</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5849,19 +5859,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5876,19 +5876,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125646883</v>
+        <v>125638972</v>
       </c>
       <c r="B50" t="n">
         <v>98331</v>
@@ -5919,17 +5919,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>522097</v>
+        <v>522318</v>
       </c>
       <c r="R50" t="n">
-        <v>6936427</v>
+        <v>6936398</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5985,32 +5985,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125632416</v>
+        <v>125632382</v>
       </c>
       <c r="B51" t="n">
-        <v>91245</v>
+        <v>98331</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6020,10 +6020,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>522125</v>
+        <v>522214</v>
       </c>
       <c r="R51" t="n">
-        <v>6936430</v>
+        <v>6936414</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6055,7 +6055,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6092,32 +6092,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125600818</v>
+        <v>125646883</v>
       </c>
       <c r="B52" t="n">
-        <v>98248</v>
+        <v>98331</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6127,13 +6127,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>522217</v>
+        <v>522097</v>
       </c>
       <c r="R52" t="n">
-        <v>6936540</v>
+        <v>6936427</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6157,12 +6157,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6177,12 +6177,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -13780,32 +13780,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125632395</v>
+        <v>125632408</v>
       </c>
       <c r="B126" t="n">
-        <v>98331</v>
+        <v>98365</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13815,10 +13815,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>522113</v>
+        <v>522057</v>
       </c>
       <c r="R126" t="n">
-        <v>6936367</v>
+        <v>6936411</v>
       </c>
       <c r="S126" t="n">
         <v>4</v>
@@ -13850,7 +13850,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13860,7 +13860,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13887,7 +13887,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125632388</v>
+        <v>125632395</v>
       </c>
       <c r="B127" t="n">
         <v>98331</v>
@@ -13922,10 +13922,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>522190</v>
+        <v>522113</v>
       </c>
       <c r="R127" t="n">
-        <v>6936390</v>
+        <v>6936367</v>
       </c>
       <c r="S127" t="n">
         <v>4</v>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -13967,7 +13967,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13994,32 +13994,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125632326</v>
+        <v>125632388</v>
       </c>
       <c r="B128" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14029,10 +14029,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>522213</v>
+        <v>522190</v>
       </c>
       <c r="R128" t="n">
-        <v>6936615</v>
+        <v>6936390</v>
       </c>
       <c r="S128" t="n">
         <v>4</v>
@@ -14064,7 +14064,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14074,7 +14074,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14101,10 +14101,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125646878</v>
+        <v>125632326</v>
       </c>
       <c r="B129" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14112,21 +14112,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14136,13 +14136,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>522019</v>
+        <v>522213</v>
       </c>
       <c r="R129" t="n">
-        <v>6936608</v>
+        <v>6936615</v>
       </c>
       <c r="S129" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14166,12 +14166,22 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14186,22 +14196,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125632345</v>
+        <v>125646878</v>
       </c>
       <c r="B130" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14209,21 +14219,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14233,13 +14243,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>522244</v>
+        <v>522019</v>
       </c>
       <c r="R130" t="n">
-        <v>6936537</v>
+        <v>6936608</v>
       </c>
       <c r="S130" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14263,22 +14273,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>13:34</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>13:34</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14293,22 +14293,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125632414</v>
+        <v>125632345</v>
       </c>
       <c r="B131" t="n">
-        <v>91227</v>
+        <v>78967</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14316,21 +14316,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14340,10 +14340,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>522109</v>
+        <v>522244</v>
       </c>
       <c r="R131" t="n">
-        <v>6936426</v>
+        <v>6936537</v>
       </c>
       <c r="S131" t="n">
         <v>4</v>
@@ -14375,7 +14375,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14412,10 +14412,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125601077</v>
+        <v>125632414</v>
       </c>
       <c r="B132" t="n">
-        <v>80071</v>
+        <v>91227</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14423,21 +14423,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14447,13 +14447,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>522217</v>
+        <v>522109</v>
       </c>
       <c r="R132" t="n">
-        <v>6936540</v>
+        <v>6936426</v>
       </c>
       <c r="S132" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14480,11 +14480,21 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
@@ -14493,41 +14503,26 @@
       </c>
       <c r="AG132" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ132" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK132" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO132" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125635162</v>
+        <v>125601077</v>
       </c>
       <c r="B133" t="n">
-        <v>79585</v>
+        <v>80071</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14535,37 +14530,37 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>522010</v>
+        <v>522217</v>
       </c>
       <c r="R133" t="n">
-        <v>6936407</v>
+        <v>6936540</v>
       </c>
       <c r="S133" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14589,12 +14584,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14605,64 +14600,79 @@
       </c>
       <c r="AG133" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125632408</v>
+        <v>125635162</v>
       </c>
       <c r="B134" t="n">
-        <v>98365</v>
+        <v>79585</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>219874</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>522057</v>
+        <v>522010</v>
       </c>
       <c r="R134" t="n">
-        <v>6936411</v>
+        <v>6936407</v>
       </c>
       <c r="S134" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14686,22 +14696,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>15:18</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>15:18</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14716,12 +14716,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>

--- a/artfynd/A 26476-2025 artfynd.xlsx
+++ b/artfynd/A 26476-2025 artfynd.xlsx
@@ -2215,7 +2215,7 @@
         <v>125621452</v>
       </c>
       <c r="B14" t="n">
-        <v>91387</v>
+        <v>91389</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>125620054</v>
       </c>
       <c r="B15" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>125619969</v>
       </c>
       <c r="B16" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>125619776</v>
       </c>
       <c r="B17" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>125619796</v>
       </c>
       <c r="B18" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>125619751</v>
       </c>
       <c r="B19" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>125599631</v>
       </c>
       <c r="B20" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,32 +2925,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125632425</v>
+        <v>125602968</v>
       </c>
       <c r="B21" t="n">
-        <v>78967</v>
+        <v>98355</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2960,13 +2960,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>522345</v>
+        <v>522217</v>
       </c>
       <c r="R21" t="n">
-        <v>6936464</v>
+        <v>6936540</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2993,19 +2993,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3020,44 +3010,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125646902</v>
+        <v>125632425</v>
       </c>
       <c r="B22" t="n">
-        <v>4869</v>
+        <v>78968</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101675</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3067,13 +3057,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>522019</v>
+        <v>522345</v>
       </c>
       <c r="R22" t="n">
-        <v>6936608</v>
+        <v>6936464</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3097,17 +3087,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Kläckhål på asp</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3122,12 +3117,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3137,7 +3132,7 @@
         <v>125646874</v>
       </c>
       <c r="B23" t="n">
-        <v>80098</v>
+        <v>80099</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3231,32 +3226,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125601310</v>
+        <v>125646902</v>
       </c>
       <c r="B24" t="n">
-        <v>98331</v>
+        <v>4869</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>101675</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3266,13 +3261,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>522217</v>
+        <v>522019</v>
       </c>
       <c r="R24" t="n">
-        <v>6936540</v>
+        <v>6936608</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3296,12 +3291,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Kläckhål på asp</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3316,22 +3316,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125632569</v>
+        <v>125632421</v>
       </c>
       <c r="B25" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3359,17 +3359,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>522108</v>
+        <v>522260</v>
       </c>
       <c r="R25" t="n">
-        <v>6936467</v>
+        <v>6936447</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3393,12 +3393,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3413,22 +3423,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125632421</v>
+        <v>125601310</v>
       </c>
       <c r="B26" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3460,13 +3470,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>522260</v>
+        <v>522217</v>
       </c>
       <c r="R26" t="n">
-        <v>6936447</v>
+        <v>6936540</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3493,19 +3503,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3520,60 +3520,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125602968</v>
+        <v>125632569</v>
       </c>
       <c r="B27" t="n">
-        <v>98352</v>
+        <v>98334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>522217</v>
+        <v>522108</v>
       </c>
       <c r="R27" t="n">
-        <v>6936540</v>
+        <v>6936467</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3597,12 +3597,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3617,12 +3617,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3632,7 +3632,7 @@
         <v>125646875</v>
       </c>
       <c r="B28" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3726,10 +3726,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125632349</v>
+        <v>125601890</v>
       </c>
       <c r="B29" t="n">
-        <v>98331</v>
+        <v>91682</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3737,21 +3737,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3761,13 +3761,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>522259</v>
+        <v>522217</v>
       </c>
       <c r="R29" t="n">
-        <v>6936489</v>
+        <v>6936540</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3794,19 +3794,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3821,60 +3811,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125636837</v>
+        <v>125603562</v>
       </c>
       <c r="B30" t="n">
-        <v>98331</v>
+        <v>80031</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>522164</v>
+        <v>522217</v>
       </c>
       <c r="R30" t="n">
-        <v>6936587</v>
+        <v>6936540</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3898,12 +3888,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3918,22 +3908,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125603562</v>
+        <v>125600280</v>
       </c>
       <c r="B31" t="n">
-        <v>80030</v>
+        <v>92518</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3941,21 +3931,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4027,32 +4017,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125600280</v>
+        <v>125632332</v>
       </c>
       <c r="B32" t="n">
-        <v>92509</v>
+        <v>78968</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4062,13 +4052,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>522217</v>
+        <v>522239</v>
       </c>
       <c r="R32" t="n">
-        <v>6936540</v>
+        <v>6936598</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4095,9 +4085,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4112,22 +4112,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125632332</v>
+        <v>125600959</v>
       </c>
       <c r="B33" t="n">
-        <v>78967</v>
+        <v>80071</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4135,21 +4135,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4159,13 +4159,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>522239</v>
+        <v>522217</v>
       </c>
       <c r="R33" t="n">
-        <v>6936598</v>
+        <v>6936540</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4192,21 +4192,11 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4215,26 +4205,41 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125601890</v>
+        <v>125632349</v>
       </c>
       <c r="B34" t="n">
-        <v>91678</v>
+        <v>98334</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4242,21 +4247,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4266,13 +4271,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>522217</v>
+        <v>522259</v>
       </c>
       <c r="R34" t="n">
-        <v>6936540</v>
+        <v>6936489</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4299,9 +4304,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4316,60 +4331,60 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125600959</v>
+        <v>125636837</v>
       </c>
       <c r="B35" t="n">
-        <v>80070</v>
+        <v>98334</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>522217</v>
+        <v>522164</v>
       </c>
       <c r="R35" t="n">
-        <v>6936540</v>
+        <v>6936587</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4393,12 +4408,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4409,31 +4424,16 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4443,7 +4443,7 @@
         <v>125632367</v>
       </c>
       <c r="B36" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>125634580</v>
       </c>
       <c r="B37" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>125632337</v>
       </c>
       <c r="B38" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>125632362</v>
       </c>
       <c r="B39" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>125632338</v>
       </c>
       <c r="B40" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>125636088</v>
       </c>
       <c r="B41" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>125632329</v>
       </c>
       <c r="B42" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5169,32 +5169,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125632353</v>
+        <v>125632401</v>
       </c>
       <c r="B43" t="n">
-        <v>98331</v>
+        <v>100516</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>522241</v>
+        <v>522046</v>
       </c>
       <c r="R43" t="n">
-        <v>6936509</v>
+        <v>6936397</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5276,10 +5276,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125646892</v>
+        <v>125646893</v>
       </c>
       <c r="B44" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>522130</v>
+        <v>522204</v>
       </c>
       <c r="R44" t="n">
-        <v>6936481</v>
+        <v>6936495</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5373,10 +5373,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125646893</v>
+        <v>125632353</v>
       </c>
       <c r="B45" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5408,13 +5408,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>522204</v>
+        <v>522241</v>
       </c>
       <c r="R45" t="n">
-        <v>6936495</v>
+        <v>6936509</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5438,12 +5438,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5458,44 +5468,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125632368</v>
+        <v>125646892</v>
       </c>
       <c r="B46" t="n">
-        <v>98352</v>
+        <v>98334</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5505,13 +5515,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>522245</v>
+        <v>522130</v>
       </c>
       <c r="R46" t="n">
-        <v>6936456</v>
+        <v>6936481</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5535,22 +5545,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>14:17</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>14:17</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5565,22 +5565,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125632401</v>
+        <v>125632368</v>
       </c>
       <c r="B47" t="n">
-        <v>100513</v>
+        <v>98355</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5588,21 +5588,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5612,10 +5612,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>522046</v>
+        <v>522245</v>
       </c>
       <c r="R47" t="n">
-        <v>6936397</v>
+        <v>6936456</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5684,32 +5684,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125632416</v>
+        <v>125600818</v>
       </c>
       <c r="B48" t="n">
-        <v>91245</v>
+        <v>98251</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5719,13 +5719,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>522125</v>
+        <v>522217</v>
       </c>
       <c r="R48" t="n">
-        <v>6936430</v>
+        <v>6936540</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5752,19 +5752,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>15:27</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5779,60 +5769,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125600818</v>
+        <v>125638972</v>
       </c>
       <c r="B49" t="n">
-        <v>98248</v>
+        <v>98334</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>522217</v>
+        <v>522318</v>
       </c>
       <c r="R49" t="n">
-        <v>6936540</v>
+        <v>6936398</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5856,12 +5846,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5876,22 +5866,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125638972</v>
+        <v>125632382</v>
       </c>
       <c r="B50" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5919,17 +5909,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>522318</v>
+        <v>522214</v>
       </c>
       <c r="R50" t="n">
-        <v>6936398</v>
+        <v>6936414</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5953,12 +5943,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5973,22 +5973,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125632382</v>
+        <v>125646883</v>
       </c>
       <c r="B51" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6020,13 +6020,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>522214</v>
+        <v>522097</v>
       </c>
       <c r="R51" t="n">
-        <v>6936414</v>
+        <v>6936427</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6050,22 +6050,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:29</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:29</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6080,44 +6070,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125646883</v>
+        <v>125632416</v>
       </c>
       <c r="B52" t="n">
-        <v>98331</v>
+        <v>91246</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6127,13 +6117,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>522097</v>
+        <v>522125</v>
       </c>
       <c r="R52" t="n">
-        <v>6936427</v>
+        <v>6936430</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6157,12 +6147,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6177,44 +6177,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125632397</v>
+        <v>125632400</v>
       </c>
       <c r="B53" t="n">
-        <v>98331</v>
+        <v>91228</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6224,10 +6224,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>522077</v>
+        <v>522048</v>
       </c>
       <c r="R53" t="n">
-        <v>6936379</v>
+        <v>6936403</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6296,32 +6296,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125636925</v>
+        <v>125637287</v>
       </c>
       <c r="B54" t="n">
-        <v>98331</v>
+        <v>79586</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6331,13 +6331,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>522220</v>
+        <v>522356</v>
       </c>
       <c r="R54" t="n">
-        <v>6936601</v>
+        <v>6936466</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6393,48 +6393,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125632815</v>
+        <v>125632336</v>
       </c>
       <c r="B55" t="n">
-        <v>98352</v>
+        <v>78726</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>522129</v>
+        <v>522224</v>
       </c>
       <c r="R55" t="n">
-        <v>6936436</v>
+        <v>6936572</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6458,12 +6458,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6478,44 +6488,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125637287</v>
+        <v>125636925</v>
       </c>
       <c r="B56" t="n">
-        <v>79585</v>
+        <v>98334</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6525,13 +6535,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>522356</v>
+        <v>522220</v>
       </c>
       <c r="R56" t="n">
-        <v>6936466</v>
+        <v>6936601</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6587,32 +6597,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125632336</v>
+        <v>125632397</v>
       </c>
       <c r="B57" t="n">
-        <v>78725</v>
+        <v>98334</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6622,10 +6632,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>522224</v>
+        <v>522077</v>
       </c>
       <c r="R57" t="n">
-        <v>6936572</v>
+        <v>6936379</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6657,7 +6667,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6667,7 +6677,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6694,10 +6704,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125632400</v>
+        <v>125637245</v>
       </c>
       <c r="B58" t="n">
-        <v>91227</v>
+        <v>80071</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6705,37 +6715,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>522048</v>
+        <v>522360</v>
       </c>
       <c r="R58" t="n">
-        <v>6936403</v>
+        <v>6936453</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6759,22 +6769,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>15:08</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>15:08</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6789,44 +6789,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125637245</v>
+        <v>125632815</v>
       </c>
       <c r="B59" t="n">
-        <v>80070</v>
+        <v>98355</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6836,13 +6836,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>522360</v>
+        <v>522129</v>
       </c>
       <c r="R59" t="n">
-        <v>6936453</v>
+        <v>6936436</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6898,10 +6898,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125646891</v>
+        <v>125632354</v>
       </c>
       <c r="B60" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6933,13 +6933,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>522159</v>
+        <v>522234</v>
       </c>
       <c r="R60" t="n">
-        <v>6936408</v>
+        <v>6936499</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6963,12 +6963,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6983,22 +6993,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125632392</v>
+        <v>125646887</v>
       </c>
       <c r="B61" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7030,13 +7040,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>522181</v>
+        <v>522185</v>
       </c>
       <c r="R61" t="n">
-        <v>6936381</v>
+        <v>6936414</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7060,22 +7070,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7090,22 +7090,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125632398</v>
+        <v>125646891</v>
       </c>
       <c r="B62" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7137,13 +7137,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>522059</v>
+        <v>522159</v>
       </c>
       <c r="R62" t="n">
-        <v>6936399</v>
+        <v>6936408</v>
       </c>
       <c r="S62" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7167,22 +7167,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>15:05</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>15:05</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7197,22 +7187,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125632354</v>
+        <v>125632392</v>
       </c>
       <c r="B63" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7244,10 +7234,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>522234</v>
+        <v>522181</v>
       </c>
       <c r="R63" t="n">
-        <v>6936499</v>
+        <v>6936381</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -7279,7 +7269,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7289,7 +7279,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7316,10 +7306,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125646887</v>
+        <v>125632398</v>
       </c>
       <c r="B64" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7351,13 +7341,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>522185</v>
+        <v>522059</v>
       </c>
       <c r="R64" t="n">
-        <v>6936414</v>
+        <v>6936399</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7381,12 +7371,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7401,44 +7401,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125632356</v>
+        <v>125632410</v>
       </c>
       <c r="B65" t="n">
-        <v>78967</v>
+        <v>92518</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>522233</v>
+        <v>522063</v>
       </c>
       <c r="R65" t="n">
-        <v>6936499</v>
+        <v>6936423</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7520,10 +7520,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125632410</v>
+        <v>125632324</v>
       </c>
       <c r="B66" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7555,10 +7555,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>522063</v>
+        <v>522198</v>
       </c>
       <c r="R66" t="n">
-        <v>6936423</v>
+        <v>6936634</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7627,32 +7627,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125632324</v>
+        <v>125632356</v>
       </c>
       <c r="B67" t="n">
-        <v>92509</v>
+        <v>78968</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7662,10 +7662,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>522198</v>
+        <v>522233</v>
       </c>
       <c r="R67" t="n">
-        <v>6936634</v>
+        <v>6936499</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -7697,7 +7697,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7737,7 +7737,7 @@
         <v>125632422</v>
       </c>
       <c r="B68" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>125632396</v>
       </c>
       <c r="B69" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>125632361</v>
       </c>
       <c r="B70" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8055,10 +8055,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125632357</v>
+        <v>125646879</v>
       </c>
       <c r="B71" t="n">
-        <v>91227</v>
+        <v>80071</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8066,21 +8066,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>522221</v>
+        <v>522202</v>
       </c>
       <c r="R71" t="n">
-        <v>6936489</v>
+        <v>6936502</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8120,22 +8120,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8150,44 +8140,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125646872</v>
+        <v>125632350</v>
       </c>
       <c r="B72" t="n">
-        <v>91192</v>
+        <v>80071</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8197,13 +8187,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>522064</v>
+        <v>522254</v>
       </c>
       <c r="R72" t="n">
-        <v>6936505</v>
+        <v>6936496</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8227,12 +8217,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8247,44 +8247,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125646879</v>
+        <v>125646872</v>
       </c>
       <c r="B73" t="n">
-        <v>80070</v>
+        <v>91193</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8294,10 +8294,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>522202</v>
+        <v>522064</v>
       </c>
       <c r="R73" t="n">
-        <v>6936502</v>
+        <v>6936505</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8356,10 +8356,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125632350</v>
+        <v>125632357</v>
       </c>
       <c r="B74" t="n">
-        <v>80070</v>
+        <v>91228</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8367,21 +8367,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8391,10 +8391,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>522254</v>
+        <v>522221</v>
       </c>
       <c r="R74" t="n">
-        <v>6936496</v>
+        <v>6936489</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8466,7 +8466,7 @@
         <v>125632370</v>
       </c>
       <c r="B75" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>125632381</v>
       </c>
       <c r="B76" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>125632418</v>
       </c>
       <c r="B77" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>125632372</v>
       </c>
       <c r="B78" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8891,10 +8891,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125632406</v>
+        <v>125632387</v>
       </c>
       <c r="B79" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8926,10 +8926,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>522052</v>
+        <v>522191</v>
       </c>
       <c r="R79" t="n">
-        <v>6936412</v>
+        <v>6936398</v>
       </c>
       <c r="S79" t="n">
         <v>4</v>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8998,10 +8998,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125632377</v>
+        <v>125632423</v>
       </c>
       <c r="B80" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9033,10 +9033,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>522237</v>
+        <v>522332</v>
       </c>
       <c r="R80" t="n">
-        <v>6936417</v>
+        <v>6936449</v>
       </c>
       <c r="S80" t="n">
         <v>4</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9105,10 +9105,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125632387</v>
+        <v>125632593</v>
       </c>
       <c r="B81" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9136,17 +9136,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>522191</v>
+        <v>522125</v>
       </c>
       <c r="R81" t="n">
-        <v>6936398</v>
+        <v>6936475</v>
       </c>
       <c r="S81" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9170,22 +9170,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9200,44 +9190,44 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125632423</v>
+        <v>125632420</v>
       </c>
       <c r="B82" t="n">
-        <v>98331</v>
+        <v>98355</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9247,10 +9237,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>522332</v>
+        <v>522236</v>
       </c>
       <c r="R82" t="n">
-        <v>6936449</v>
+        <v>6936446</v>
       </c>
       <c r="S82" t="n">
         <v>4</v>
@@ -9282,7 +9272,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9292,7 +9282,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9319,10 +9309,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125632365</v>
+        <v>125632406</v>
       </c>
       <c r="B83" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9354,10 +9344,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>522249</v>
+        <v>522052</v>
       </c>
       <c r="R83" t="n">
-        <v>6936473</v>
+        <v>6936412</v>
       </c>
       <c r="S83" t="n">
         <v>4</v>
@@ -9389,7 +9379,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9399,7 +9389,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9426,10 +9416,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125632554</v>
+        <v>125632377</v>
       </c>
       <c r="B84" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9457,17 +9447,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>522125</v>
+        <v>522237</v>
       </c>
       <c r="R84" t="n">
-        <v>6936477</v>
+        <v>6936417</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9491,12 +9481,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9511,22 +9511,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125632593</v>
+        <v>125632365</v>
       </c>
       <c r="B85" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9554,17 +9554,17 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>522125</v>
+        <v>522249</v>
       </c>
       <c r="R85" t="n">
-        <v>6936475</v>
+        <v>6936473</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9588,12 +9588,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9608,60 +9618,60 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125632420</v>
+        <v>125632554</v>
       </c>
       <c r="B86" t="n">
-        <v>98352</v>
+        <v>98334</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>522236</v>
+        <v>522125</v>
       </c>
       <c r="R86" t="n">
-        <v>6936446</v>
+        <v>6936477</v>
       </c>
       <c r="S86" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9685,22 +9695,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9715,60 +9715,60 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125646882</v>
+        <v>125635192</v>
       </c>
       <c r="B87" t="n">
-        <v>98331</v>
+        <v>92518</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>522029</v>
+        <v>522003</v>
       </c>
       <c r="R87" t="n">
-        <v>6936561</v>
+        <v>6936451</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9824,48 +9824,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125632417</v>
+        <v>125637200</v>
       </c>
       <c r="B88" t="n">
-        <v>98331</v>
+        <v>78968</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>522163</v>
+        <v>522362</v>
       </c>
       <c r="R88" t="n">
-        <v>6936406</v>
+        <v>6936466</v>
       </c>
       <c r="S88" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9889,22 +9889,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9919,60 +9909,60 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125637200</v>
+        <v>125646882</v>
       </c>
       <c r="B89" t="n">
-        <v>78967</v>
+        <v>98334</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>522362</v>
+        <v>522029</v>
       </c>
       <c r="R89" t="n">
-        <v>6936466</v>
+        <v>6936561</v>
       </c>
       <c r="S89" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10028,48 +10018,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125635192</v>
+        <v>125632417</v>
       </c>
       <c r="B90" t="n">
-        <v>92509</v>
+        <v>98334</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>522003</v>
+        <v>522163</v>
       </c>
       <c r="R90" t="n">
-        <v>6936451</v>
+        <v>6936406</v>
       </c>
       <c r="S90" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10093,12 +10083,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10113,60 +10113,60 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125632341</v>
+        <v>125635666</v>
       </c>
       <c r="B91" t="n">
-        <v>92509</v>
+        <v>80071</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>522236</v>
+        <v>522038</v>
       </c>
       <c r="R91" t="n">
-        <v>6936562</v>
+        <v>6936535</v>
       </c>
       <c r="S91" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10190,22 +10190,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10220,22 +10215,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125635666</v>
+        <v>125633268</v>
       </c>
       <c r="B92" t="n">
-        <v>80070</v>
+        <v>57811</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10243,37 +10238,42 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>522038</v>
+        <v>522121</v>
       </c>
       <c r="R92" t="n">
-        <v>6936535</v>
+        <v>6936402</v>
       </c>
       <c r="S92" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10303,11 +10303,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10334,53 +10329,48 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125633268</v>
+        <v>125632409</v>
       </c>
       <c r="B93" t="n">
-        <v>57811</v>
+        <v>98334</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>522121</v>
+        <v>522062</v>
       </c>
       <c r="R93" t="n">
-        <v>6936402</v>
+        <v>6936422</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10404,12 +10394,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10424,44 +10424,44 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125632409</v>
+        <v>125632341</v>
       </c>
       <c r="B94" t="n">
-        <v>98331</v>
+        <v>92518</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10471,10 +10471,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>522062</v>
+        <v>522236</v>
       </c>
       <c r="R94" t="n">
-        <v>6936422</v>
+        <v>6936562</v>
       </c>
       <c r="S94" t="n">
         <v>4</v>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10546,7 +10546,7 @@
         <v>125632415</v>
       </c>
       <c r="B95" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>125632358</v>
       </c>
       <c r="B96" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10757,32 +10757,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125646900</v>
+        <v>125646886</v>
       </c>
       <c r="B97" t="n">
-        <v>78967</v>
+        <v>98334</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10792,10 +10792,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>521975</v>
+        <v>522109</v>
       </c>
       <c r="R97" t="n">
-        <v>6936372</v>
+        <v>6936414</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10828,11 +10828,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10859,32 +10854,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125632348</v>
+        <v>125646894</v>
       </c>
       <c r="B98" t="n">
-        <v>78967</v>
+        <v>98334</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10894,13 +10889,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>522241</v>
+        <v>522227</v>
       </c>
       <c r="R98" t="n">
-        <v>6936518</v>
+        <v>6936562</v>
       </c>
       <c r="S98" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10924,22 +10919,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>13:44</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>13:44</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10954,44 +10939,44 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125632333</v>
+        <v>125632344</v>
       </c>
       <c r="B99" t="n">
-        <v>80070</v>
+        <v>98334</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11001,10 +10986,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>522235</v>
+        <v>522268</v>
       </c>
       <c r="R99" t="n">
-        <v>6936598</v>
+        <v>6936556</v>
       </c>
       <c r="S99" t="n">
         <v>4</v>
@@ -11036,7 +11021,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11046,7 +11031,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11073,32 +11058,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125646894</v>
+        <v>125632333</v>
       </c>
       <c r="B100" t="n">
-        <v>98331</v>
+        <v>80071</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11108,13 +11093,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>522227</v>
+        <v>522235</v>
       </c>
       <c r="R100" t="n">
-        <v>6936562</v>
+        <v>6936598</v>
       </c>
       <c r="S100" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11138,12 +11123,22 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11158,44 +11153,44 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125632344</v>
+        <v>125646900</v>
       </c>
       <c r="B101" t="n">
-        <v>98331</v>
+        <v>78968</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11205,13 +11200,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>522268</v>
+        <v>521975</v>
       </c>
       <c r="R101" t="n">
-        <v>6936556</v>
+        <v>6936372</v>
       </c>
       <c r="S101" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11235,22 +11230,17 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11265,44 +11255,44 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125646886</v>
+        <v>125632348</v>
       </c>
       <c r="B102" t="n">
-        <v>98331</v>
+        <v>78968</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11312,13 +11302,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>522109</v>
+        <v>522241</v>
       </c>
       <c r="R102" t="n">
-        <v>6936414</v>
+        <v>6936518</v>
       </c>
       <c r="S102" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11342,12 +11332,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11362,22 +11362,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125632323</v>
+        <v>125632390</v>
       </c>
       <c r="B103" t="n">
-        <v>78967</v>
+        <v>91228</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11385,21 +11385,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11409,10 +11409,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>522189</v>
+        <v>522187</v>
       </c>
       <c r="R103" t="n">
-        <v>6936648</v>
+        <v>6936377</v>
       </c>
       <c r="S103" t="n">
         <v>4</v>
@@ -11444,7 +11444,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11454,7 +11454,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11481,10 +11481,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125635476</v>
+        <v>125632323</v>
       </c>
       <c r="B104" t="n">
-        <v>80070</v>
+        <v>78968</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11492,37 +11492,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>522057</v>
+        <v>522189</v>
       </c>
       <c r="R104" t="n">
-        <v>6936487</v>
+        <v>6936648</v>
       </c>
       <c r="S104" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11546,17 +11546,22 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11571,22 +11576,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125632325</v>
+        <v>125635476</v>
       </c>
       <c r="B105" t="n">
-        <v>78725</v>
+        <v>80071</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11594,37 +11599,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>522198</v>
+        <v>522057</v>
       </c>
       <c r="R105" t="n">
-        <v>6936620</v>
+        <v>6936487</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11648,22 +11653,17 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>12:57</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>12:57</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11678,22 +11678,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125632390</v>
+        <v>125632325</v>
       </c>
       <c r="B106" t="n">
-        <v>91227</v>
+        <v>78726</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11701,21 +11701,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11725,13 +11725,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>522187</v>
+        <v>522198</v>
       </c>
       <c r="R106" t="n">
-        <v>6936377</v>
+        <v>6936620</v>
       </c>
       <c r="S106" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11800,7 +11800,7 @@
         <v>125632330</v>
       </c>
       <c r="B107" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>125646880</v>
       </c>
       <c r="B108" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11991,10 +11991,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125632412</v>
+        <v>125632340</v>
       </c>
       <c r="B109" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12026,10 +12026,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>522101</v>
+        <v>522232</v>
       </c>
       <c r="R109" t="n">
-        <v>6936425</v>
+        <v>6936562</v>
       </c>
       <c r="S109" t="n">
         <v>4</v>
@@ -12061,7 +12061,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12071,7 +12071,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12098,10 +12098,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125632379</v>
+        <v>125632351</v>
       </c>
       <c r="B110" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12133,10 +12133,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>522237</v>
+        <v>522250</v>
       </c>
       <c r="R110" t="n">
-        <v>6936415</v>
+        <v>6936497</v>
       </c>
       <c r="S110" t="n">
         <v>4</v>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12178,7 +12178,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12205,10 +12205,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125632340</v>
+        <v>125632412</v>
       </c>
       <c r="B111" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12240,10 +12240,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>522232</v>
+        <v>522101</v>
       </c>
       <c r="R111" t="n">
-        <v>6936562</v>
+        <v>6936425</v>
       </c>
       <c r="S111" t="n">
         <v>4</v>
@@ -12275,7 +12275,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12312,10 +12312,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125632351</v>
+        <v>125632379</v>
       </c>
       <c r="B112" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12347,10 +12347,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>522250</v>
+        <v>522237</v>
       </c>
       <c r="R112" t="n">
-        <v>6936497</v>
+        <v>6936415</v>
       </c>
       <c r="S112" t="n">
         <v>4</v>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12392,7 +12392,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12422,7 +12422,7 @@
         <v>125646884</v>
       </c>
       <c r="B113" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>125632347</v>
       </c>
       <c r="B114" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>125632346</v>
       </c>
       <c r="B115" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12730,32 +12730,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125632399</v>
+        <v>125632394</v>
       </c>
       <c r="B116" t="n">
-        <v>56843</v>
+        <v>98334</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12765,10 +12765,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>522053</v>
+        <v>522136</v>
       </c>
       <c r="R116" t="n">
-        <v>6936400</v>
+        <v>6936370</v>
       </c>
       <c r="S116" t="n">
         <v>4</v>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12810,12 +12810,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>15:07</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>spillning</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12842,10 +12837,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125632371</v>
+        <v>125635820</v>
       </c>
       <c r="B117" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12873,17 +12868,17 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>522243</v>
+        <v>522040</v>
       </c>
       <c r="R117" t="n">
-        <v>6936460</v>
+        <v>6936582</v>
       </c>
       <c r="S117" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12907,22 +12902,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>14:17</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>14:17</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12937,44 +12922,44 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125632385</v>
+        <v>125632399</v>
       </c>
       <c r="B118" t="n">
-        <v>98331</v>
+        <v>56843</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12984,10 +12969,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>522197</v>
+        <v>522053</v>
       </c>
       <c r="R118" t="n">
-        <v>6936406</v>
+        <v>6936400</v>
       </c>
       <c r="S118" t="n">
         <v>4</v>
@@ -13019,7 +13004,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13029,7 +13014,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13056,10 +13046,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125632394</v>
+        <v>125632371</v>
       </c>
       <c r="B119" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13091,10 +13081,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>522136</v>
+        <v>522243</v>
       </c>
       <c r="R119" t="n">
-        <v>6936370</v>
+        <v>6936460</v>
       </c>
       <c r="S119" t="n">
         <v>4</v>
@@ -13126,7 +13116,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13136,7 +13126,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13163,10 +13153,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125635820</v>
+        <v>125632385</v>
       </c>
       <c r="B120" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13194,17 +13184,17 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>522040</v>
+        <v>522197</v>
       </c>
       <c r="R120" t="n">
-        <v>6936582</v>
+        <v>6936406</v>
       </c>
       <c r="S120" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13228,12 +13218,22 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13248,22 +13248,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125632360</v>
+        <v>125632405</v>
       </c>
       <c r="B121" t="n">
-        <v>57648</v>
+        <v>91524</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13271,21 +13271,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13295,10 +13295,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>522247</v>
+        <v>522044</v>
       </c>
       <c r="R121" t="n">
-        <v>6936482</v>
+        <v>6936401</v>
       </c>
       <c r="S121" t="n">
         <v>4</v>
@@ -13330,7 +13330,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13340,12 +13340,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>födosök död stående tall</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13372,10 +13367,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125632405</v>
+        <v>125601877</v>
       </c>
       <c r="B122" t="n">
-        <v>91520</v>
+        <v>91228</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13383,21 +13378,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13407,13 +13402,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>522044</v>
+        <v>522217</v>
       </c>
       <c r="R122" t="n">
-        <v>6936401</v>
+        <v>6936540</v>
       </c>
       <c r="S122" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13440,19 +13435,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>15:15</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13467,22 +13452,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125601877</v>
+        <v>125632383</v>
       </c>
       <c r="B123" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13514,13 +13499,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>522217</v>
+        <v>522219</v>
       </c>
       <c r="R123" t="n">
-        <v>6936540</v>
+        <v>6936411</v>
       </c>
       <c r="S123" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13547,9 +13532,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13564,12 +13559,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
@@ -13579,7 +13574,7 @@
         <v>125637290</v>
       </c>
       <c r="B124" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13673,10 +13668,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125632383</v>
+        <v>125632360</v>
       </c>
       <c r="B125" t="n">
-        <v>91227</v>
+        <v>57648</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13684,21 +13679,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13708,10 +13703,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>522219</v>
+        <v>522247</v>
       </c>
       <c r="R125" t="n">
-        <v>6936411</v>
+        <v>6936482</v>
       </c>
       <c r="S125" t="n">
         <v>4</v>
@@ -13743,7 +13738,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13753,7 +13748,12 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>födosök död stående tall</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13780,32 +13780,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125632408</v>
+        <v>125632414</v>
       </c>
       <c r="B126" t="n">
-        <v>98365</v>
+        <v>91228</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13815,10 +13815,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>522057</v>
+        <v>522109</v>
       </c>
       <c r="R126" t="n">
-        <v>6936411</v>
+        <v>6936426</v>
       </c>
       <c r="S126" t="n">
         <v>4</v>
@@ -13850,7 +13850,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13860,7 +13860,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13887,32 +13887,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125632395</v>
+        <v>125632326</v>
       </c>
       <c r="B127" t="n">
-        <v>98331</v>
+        <v>78968</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13922,10 +13922,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>522113</v>
+        <v>522213</v>
       </c>
       <c r="R127" t="n">
-        <v>6936367</v>
+        <v>6936615</v>
       </c>
       <c r="S127" t="n">
         <v>4</v>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -13967,7 +13967,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13994,32 +13994,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125632388</v>
+        <v>125646878</v>
       </c>
       <c r="B128" t="n">
-        <v>98331</v>
+        <v>80071</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14029,13 +14029,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>522190</v>
+        <v>522019</v>
       </c>
       <c r="R128" t="n">
-        <v>6936390</v>
+        <v>6936608</v>
       </c>
       <c r="S128" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14059,22 +14059,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14089,22 +14079,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125632326</v>
+        <v>125632345</v>
       </c>
       <c r="B129" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14136,10 +14126,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>522213</v>
+        <v>522244</v>
       </c>
       <c r="R129" t="n">
-        <v>6936615</v>
+        <v>6936537</v>
       </c>
       <c r="S129" t="n">
         <v>4</v>
@@ -14171,7 +14161,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14181,7 +14171,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14208,10 +14198,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125646878</v>
+        <v>125635162</v>
       </c>
       <c r="B130" t="n">
-        <v>80070</v>
+        <v>79586</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14219,37 +14209,37 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>522019</v>
+        <v>522010</v>
       </c>
       <c r="R130" t="n">
-        <v>6936608</v>
+        <v>6936407</v>
       </c>
       <c r="S130" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14305,32 +14295,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125632345</v>
+        <v>125632408</v>
       </c>
       <c r="B131" t="n">
-        <v>78967</v>
+        <v>98368</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14340,10 +14330,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>522244</v>
+        <v>522057</v>
       </c>
       <c r="R131" t="n">
-        <v>6936537</v>
+        <v>6936411</v>
       </c>
       <c r="S131" t="n">
         <v>4</v>
@@ -14375,7 +14365,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14385,7 +14375,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14412,32 +14402,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125632414</v>
+        <v>125632395</v>
       </c>
       <c r="B132" t="n">
-        <v>91227</v>
+        <v>98334</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14447,10 +14437,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>522109</v>
+        <v>522113</v>
       </c>
       <c r="R132" t="n">
-        <v>6936426</v>
+        <v>6936367</v>
       </c>
       <c r="S132" t="n">
         <v>4</v>
@@ -14482,7 +14472,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14492,7 +14482,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14519,32 +14509,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125601077</v>
+        <v>125632388</v>
       </c>
       <c r="B133" t="n">
-        <v>80071</v>
+        <v>98334</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14554,13 +14544,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>522217</v>
+        <v>522190</v>
       </c>
       <c r="R133" t="n">
-        <v>6936540</v>
+        <v>6936390</v>
       </c>
       <c r="S133" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14587,11 +14577,21 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
@@ -14600,41 +14600,26 @@
       </c>
       <c r="AG133" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ133" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK133" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO133" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125635162</v>
+        <v>125601077</v>
       </c>
       <c r="B134" t="n">
-        <v>79585</v>
+        <v>80072</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14642,37 +14627,37 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>522010</v>
+        <v>522217</v>
       </c>
       <c r="R134" t="n">
-        <v>6936407</v>
+        <v>6936540</v>
       </c>
       <c r="S134" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14696,12 +14681,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14712,48 +14697,63 @@
       </c>
       <c r="AG134" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125632373</v>
+        <v>125632407</v>
       </c>
       <c r="B135" t="n">
-        <v>98331</v>
+        <v>91228</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14763,10 +14763,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>522236</v>
+        <v>522052</v>
       </c>
       <c r="R135" t="n">
-        <v>6936449</v>
+        <v>6936413</v>
       </c>
       <c r="S135" t="n">
         <v>4</v>
@@ -14798,7 +14798,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14808,7 +14808,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14835,32 +14835,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125632352</v>
+        <v>125632334</v>
       </c>
       <c r="B136" t="n">
-        <v>98331</v>
+        <v>80100</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14870,10 +14870,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>522245</v>
+        <v>522239</v>
       </c>
       <c r="R136" t="n">
-        <v>6936497</v>
+        <v>6936600</v>
       </c>
       <c r="S136" t="n">
         <v>4</v>
@@ -14905,7 +14905,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14942,10 +14942,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125632359</v>
+        <v>125633219</v>
       </c>
       <c r="B137" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14973,17 +14973,17 @@
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>MD0:Ånge, SE-VN, SE, Mpd</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>522236</v>
+        <v>522237</v>
       </c>
       <c r="R137" t="n">
-        <v>6936482</v>
+        <v>6936437</v>
       </c>
       <c r="S137" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15049,10 +15049,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125633219</v>
+        <v>125632352</v>
       </c>
       <c r="B138" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15080,17 +15080,17 @@
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>MD0:Ånge, SE-VN, SE, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>522237</v>
+        <v>522245</v>
       </c>
       <c r="R138" t="n">
-        <v>6936437</v>
+        <v>6936497</v>
       </c>
       <c r="S138" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15156,32 +15156,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125632407</v>
+        <v>125632359</v>
       </c>
       <c r="B139" t="n">
-        <v>91227</v>
+        <v>98334</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15191,10 +15191,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>522052</v>
+        <v>522236</v>
       </c>
       <c r="R139" t="n">
-        <v>6936413</v>
+        <v>6936482</v>
       </c>
       <c r="S139" t="n">
         <v>4</v>
@@ -15226,7 +15226,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15236,7 +15236,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15263,32 +15263,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125632334</v>
+        <v>125632373</v>
       </c>
       <c r="B140" t="n">
-        <v>80099</v>
+        <v>98334</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15298,10 +15298,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>522239</v>
+        <v>522236</v>
       </c>
       <c r="R140" t="n">
-        <v>6936600</v>
+        <v>6936449</v>
       </c>
       <c r="S140" t="n">
         <v>4</v>
@@ -15333,7 +15333,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15343,7 +15343,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15370,32 +15370,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125632375</v>
+        <v>125646901</v>
       </c>
       <c r="B141" t="n">
-        <v>98331</v>
+        <v>92518</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15405,13 +15405,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>522243</v>
+        <v>522030</v>
       </c>
       <c r="R141" t="n">
-        <v>6936427</v>
+        <v>6936634</v>
       </c>
       <c r="S141" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15435,22 +15435,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15465,22 +15455,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125633218</v>
+        <v>125632375</v>
       </c>
       <c r="B142" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15508,17 +15498,17 @@
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>MD1:Ånge, SE-VN, SE, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>522221</v>
+        <v>522243</v>
       </c>
       <c r="R142" t="n">
-        <v>6936591</v>
+        <v>6936427</v>
       </c>
       <c r="S142" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15547,7 +15537,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15557,7 +15547,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15584,10 +15574,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125632364</v>
+        <v>125633218</v>
       </c>
       <c r="B143" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15615,17 +15605,17 @@
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>MD1:Ånge, SE-VN, SE, Mpd</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>522260</v>
+        <v>522221</v>
       </c>
       <c r="R143" t="n">
-        <v>6936473</v>
+        <v>6936591</v>
       </c>
       <c r="S143" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15654,7 +15644,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15664,7 +15654,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15691,32 +15681,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125646901</v>
+        <v>125632364</v>
       </c>
       <c r="B144" t="n">
-        <v>92509</v>
+        <v>98334</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15726,13 +15716,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>522030</v>
+        <v>522260</v>
       </c>
       <c r="R144" t="n">
-        <v>6936634</v>
+        <v>6936473</v>
       </c>
       <c r="S144" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15756,12 +15746,22 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15776,12 +15776,12 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
@@ -15791,7 +15791,7 @@
         <v>125632389</v>
       </c>
       <c r="B145" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>125636452</v>
       </c>
       <c r="B146" t="n">
-        <v>91387</v>
+        <v>91389</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15992,10 +15992,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125632366</v>
+        <v>125632331</v>
       </c>
       <c r="B147" t="n">
-        <v>98352</v>
+        <v>92518</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16003,21 +16003,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>221952</v>
+        <v>4364</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>522249</v>
+        <v>522221</v>
       </c>
       <c r="R147" t="n">
-        <v>6936460</v>
+        <v>6936608</v>
       </c>
       <c r="S147" t="n">
         <v>4</v>
@@ -16062,7 +16062,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16072,7 +16072,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16099,10 +16099,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125632384</v>
+        <v>125632386</v>
       </c>
       <c r="B148" t="n">
-        <v>98352</v>
+        <v>56843</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16110,21 +16110,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16134,10 +16134,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>522207</v>
+        <v>522200</v>
       </c>
       <c r="R148" t="n">
-        <v>6936406</v>
+        <v>6936398</v>
       </c>
       <c r="S148" t="n">
         <v>4</v>
@@ -16169,7 +16169,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16179,7 +16179,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16209,7 +16209,7 @@
         <v>125632419</v>
       </c>
       <c r="B149" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16313,10 +16313,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125646888</v>
+        <v>125632411</v>
       </c>
       <c r="B150" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16348,13 +16348,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>522159</v>
+        <v>522063</v>
       </c>
       <c r="R150" t="n">
-        <v>6936405</v>
+        <v>6936424</v>
       </c>
       <c r="S150" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16378,12 +16378,22 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16398,22 +16408,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125632411</v>
+        <v>125646888</v>
       </c>
       <c r="B151" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16445,13 +16455,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>522063</v>
+        <v>522159</v>
       </c>
       <c r="R151" t="n">
-        <v>6936424</v>
+        <v>6936405</v>
       </c>
       <c r="S151" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16475,22 +16485,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16505,22 +16505,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125632331</v>
+        <v>125632366</v>
       </c>
       <c r="B152" t="n">
-        <v>92509</v>
+        <v>98355</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16528,21 +16528,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>4364</v>
+        <v>221952</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16552,10 +16552,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>522221</v>
+        <v>522249</v>
       </c>
       <c r="R152" t="n">
-        <v>6936608</v>
+        <v>6936460</v>
       </c>
       <c r="S152" t="n">
         <v>4</v>
@@ -16587,7 +16587,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16597,7 +16597,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16624,10 +16624,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125632386</v>
+        <v>125632384</v>
       </c>
       <c r="B153" t="n">
-        <v>56843</v>
+        <v>98355</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16635,21 +16635,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16659,10 +16659,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>522200</v>
+        <v>522207</v>
       </c>
       <c r="R153" t="n">
-        <v>6936398</v>
+        <v>6936406</v>
       </c>
       <c r="S153" t="n">
         <v>4</v>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16704,7 +16704,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16731,48 +16731,48 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125635540</v>
+        <v>125632376</v>
       </c>
       <c r="B154" t="n">
-        <v>98331</v>
+        <v>56843</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>522055</v>
+        <v>522237</v>
       </c>
       <c r="R154" t="n">
-        <v>6936516</v>
+        <v>6936423</v>
       </c>
       <c r="S154" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16796,12 +16796,22 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16816,22 +16826,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125632393</v>
+        <v>125635540</v>
       </c>
       <c r="B155" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16859,17 +16869,17 @@
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>522160</v>
+        <v>522055</v>
       </c>
       <c r="R155" t="n">
-        <v>6936368</v>
+        <v>6936516</v>
       </c>
       <c r="S155" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16893,22 +16903,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16923,44 +16923,44 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125632343</v>
+        <v>125632393</v>
       </c>
       <c r="B156" t="n">
-        <v>78967</v>
+        <v>98334</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16970,10 +16970,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>522269</v>
+        <v>522160</v>
       </c>
       <c r="R156" t="n">
-        <v>6936560</v>
+        <v>6936368</v>
       </c>
       <c r="S156" t="n">
         <v>4</v>
@@ -17005,7 +17005,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17015,7 +17015,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17042,10 +17042,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125632327</v>
+        <v>125632343</v>
       </c>
       <c r="B157" t="n">
-        <v>80070</v>
+        <v>78968</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17053,21 +17053,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17077,10 +17077,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>522218</v>
+        <v>522269</v>
       </c>
       <c r="R157" t="n">
-        <v>6936625</v>
+        <v>6936560</v>
       </c>
       <c r="S157" t="n">
         <v>4</v>
@@ -17112,7 +17112,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17122,7 +17122,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17152,7 +17152,7 @@
         <v>125646899</v>
       </c>
       <c r="B158" t="n">
-        <v>91387</v>
+        <v>91389</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17246,32 +17246,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125632376</v>
+        <v>125632327</v>
       </c>
       <c r="B159" t="n">
-        <v>56843</v>
+        <v>80071</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17281,10 +17281,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>522237</v>
+        <v>522218</v>
       </c>
       <c r="R159" t="n">
-        <v>6936423</v>
+        <v>6936625</v>
       </c>
       <c r="S159" t="n">
         <v>4</v>
@@ -17316,7 +17316,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17326,7 +17326,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD159" t="b">

--- a/artfynd/A 26476-2025 artfynd.xlsx
+++ b/artfynd/A 26476-2025 artfynd.xlsx
@@ -2925,32 +2925,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125602968</v>
+        <v>125632425</v>
       </c>
       <c r="B21" t="n">
-        <v>98355</v>
+        <v>78968</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2960,13 +2960,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>522217</v>
+        <v>522345</v>
       </c>
       <c r="R21" t="n">
-        <v>6936540</v>
+        <v>6936464</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2993,9 +2993,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3010,44 +3020,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125632425</v>
+        <v>125646874</v>
       </c>
       <c r="B22" t="n">
-        <v>78968</v>
+        <v>80099</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3057,13 +3067,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>522345</v>
+        <v>522022</v>
       </c>
       <c r="R22" t="n">
-        <v>6936464</v>
+        <v>6936611</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3087,22 +3097,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3117,22 +3117,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125646874</v>
+        <v>125646902</v>
       </c>
       <c r="B23" t="n">
-        <v>80099</v>
+        <v>4869</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3140,21 +3140,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6461</v>
+        <v>101675</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>522022</v>
+        <v>522019</v>
       </c>
       <c r="R23" t="n">
-        <v>6936611</v>
+        <v>6936608</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3200,6 +3200,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Kläckhål på asp</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3226,32 +3231,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125646902</v>
+        <v>125632421</v>
       </c>
       <c r="B24" t="n">
-        <v>4869</v>
+        <v>98334</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>101675</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3261,13 +3266,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>522019</v>
+        <v>522260</v>
       </c>
       <c r="R24" t="n">
-        <v>6936608</v>
+        <v>6936447</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3291,17 +3296,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Kläckhål på asp</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3316,19 +3326,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125632421</v>
+        <v>125601310</v>
       </c>
       <c r="B25" t="n">
         <v>98334</v>
@@ -3363,13 +3373,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>522260</v>
+        <v>522217</v>
       </c>
       <c r="R25" t="n">
-        <v>6936447</v>
+        <v>6936540</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3396,19 +3406,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3423,19 +3423,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125601310</v>
+        <v>125632569</v>
       </c>
       <c r="B26" t="n">
         <v>98334</v>
@@ -3466,17 +3466,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>522217</v>
+        <v>522108</v>
       </c>
       <c r="R26" t="n">
-        <v>6936540</v>
+        <v>6936467</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3500,12 +3500,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3520,60 +3520,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125632569</v>
+        <v>125602968</v>
       </c>
       <c r="B27" t="n">
-        <v>98334</v>
+        <v>98355</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>522108</v>
+        <v>522217</v>
       </c>
       <c r="R27" t="n">
-        <v>6936467</v>
+        <v>6936540</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3597,12 +3597,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3617,12 +3617,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3726,32 +3726,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125601890</v>
+        <v>125600280</v>
       </c>
       <c r="B29" t="n">
-        <v>91682</v>
+        <v>92518</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3823,32 +3823,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125603562</v>
+        <v>125601890</v>
       </c>
       <c r="B30" t="n">
-        <v>80031</v>
+        <v>91682</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229497</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3920,32 +3920,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125600280</v>
+        <v>125632349</v>
       </c>
       <c r="B31" t="n">
-        <v>92518</v>
+        <v>98334</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3955,13 +3955,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>522217</v>
+        <v>522259</v>
       </c>
       <c r="R31" t="n">
-        <v>6936540</v>
+        <v>6936489</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3988,9 +3988,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4005,60 +4015,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125632332</v>
+        <v>125636837</v>
       </c>
       <c r="B32" t="n">
-        <v>78968</v>
+        <v>98334</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>522239</v>
+        <v>522164</v>
       </c>
       <c r="R32" t="n">
-        <v>6936598</v>
+        <v>6936587</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4082,22 +4092,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4112,22 +4112,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125600959</v>
+        <v>125632332</v>
       </c>
       <c r="B33" t="n">
-        <v>80071</v>
+        <v>78968</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4135,21 +4135,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4159,13 +4159,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>522217</v>
+        <v>522239</v>
       </c>
       <c r="R33" t="n">
-        <v>6936540</v>
+        <v>6936598</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4192,11 +4192,21 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4205,63 +4215,48 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125632349</v>
+        <v>125600959</v>
       </c>
       <c r="B34" t="n">
-        <v>98334</v>
+        <v>80071</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4271,13 +4266,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>522259</v>
+        <v>522217</v>
       </c>
       <c r="R34" t="n">
-        <v>6936489</v>
+        <v>6936540</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4304,21 +4299,11 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4327,64 +4312,79 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125636837</v>
+        <v>125632367</v>
       </c>
       <c r="B35" t="n">
-        <v>98334</v>
+        <v>98355</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>522164</v>
+        <v>522247</v>
       </c>
       <c r="R35" t="n">
-        <v>6936587</v>
+        <v>6936458</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4408,12 +4408,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4428,19 +4438,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125632367</v>
+        <v>125634580</v>
       </c>
       <c r="B36" t="n">
         <v>98355</v>
@@ -4471,17 +4481,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>522247</v>
+        <v>522044</v>
       </c>
       <c r="R36" t="n">
-        <v>6936458</v>
+        <v>6936401</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4505,22 +4515,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14:16</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>14:16</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4535,22 +4535,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125634580</v>
+        <v>125603562</v>
       </c>
       <c r="B37" t="n">
-        <v>98355</v>
+        <v>80031</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4558,37 +4558,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221952</v>
+        <v>229497</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>522044</v>
+        <v>522217</v>
       </c>
       <c r="R37" t="n">
-        <v>6936401</v>
+        <v>6936540</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4632,12 +4632,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4858,10 +4858,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125632338</v>
+        <v>125632329</v>
       </c>
       <c r="B40" t="n">
-        <v>92518</v>
+        <v>80100</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4869,21 +4869,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>522221</v>
+        <v>522215</v>
       </c>
       <c r="R40" t="n">
-        <v>6936572</v>
+        <v>6936627</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4965,48 +4965,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125636088</v>
+        <v>125646893</v>
       </c>
       <c r="B41" t="n">
-        <v>92518</v>
+        <v>98334</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>522049</v>
+        <v>522204</v>
       </c>
       <c r="R41" t="n">
-        <v>6936650</v>
+        <v>6936495</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5062,32 +5062,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125632329</v>
+        <v>125632353</v>
       </c>
       <c r="B42" t="n">
-        <v>80100</v>
+        <v>98334</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>522215</v>
+        <v>522241</v>
       </c>
       <c r="R42" t="n">
-        <v>6936627</v>
+        <v>6936509</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5169,32 +5169,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125632401</v>
+        <v>125646892</v>
       </c>
       <c r="B43" t="n">
-        <v>100516</v>
+        <v>98334</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5204,13 +5204,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>522046</v>
+        <v>522130</v>
       </c>
       <c r="R43" t="n">
-        <v>6936397</v>
+        <v>6936481</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5234,22 +5234,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:09</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:09</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5264,44 +5254,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125646893</v>
+        <v>125632368</v>
       </c>
       <c r="B44" t="n">
-        <v>98334</v>
+        <v>98355</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5311,13 +5301,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>522204</v>
+        <v>522245</v>
       </c>
       <c r="R44" t="n">
-        <v>6936495</v>
+        <v>6936456</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5341,12 +5331,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5361,44 +5361,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125632353</v>
+        <v>125632401</v>
       </c>
       <c r="B45" t="n">
-        <v>98334</v>
+        <v>100516</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>522241</v>
+        <v>522046</v>
       </c>
       <c r="R45" t="n">
-        <v>6936509</v>
+        <v>6936397</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5480,32 +5480,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125646892</v>
+        <v>125632338</v>
       </c>
       <c r="B46" t="n">
-        <v>98334</v>
+        <v>92518</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5515,13 +5515,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>522130</v>
+        <v>522221</v>
       </c>
       <c r="R46" t="n">
-        <v>6936481</v>
+        <v>6936572</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5545,12 +5545,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5565,22 +5575,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125632368</v>
+        <v>125636088</v>
       </c>
       <c r="B47" t="n">
-        <v>98355</v>
+        <v>92518</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5588,37 +5598,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>522245</v>
+        <v>522049</v>
       </c>
       <c r="R47" t="n">
-        <v>6936456</v>
+        <v>6936650</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5642,22 +5652,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:17</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:17</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5672,12 +5672,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -10125,48 +10125,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125635666</v>
+        <v>125632341</v>
       </c>
       <c r="B91" t="n">
-        <v>80071</v>
+        <v>92518</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>522038</v>
+        <v>522236</v>
       </c>
       <c r="R91" t="n">
-        <v>6936535</v>
+        <v>6936562</v>
       </c>
       <c r="S91" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10190,17 +10190,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10215,22 +10220,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125633268</v>
+        <v>125635666</v>
       </c>
       <c r="B92" t="n">
-        <v>57811</v>
+        <v>80071</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10238,42 +10243,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>522121</v>
+        <v>522038</v>
       </c>
       <c r="R92" t="n">
-        <v>6936402</v>
+        <v>6936535</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10303,6 +10303,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10329,48 +10334,53 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125632409</v>
+        <v>125633268</v>
       </c>
       <c r="B93" t="n">
-        <v>98334</v>
+        <v>57811</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>522062</v>
+        <v>522121</v>
       </c>
       <c r="R93" t="n">
-        <v>6936422</v>
+        <v>6936402</v>
       </c>
       <c r="S93" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10394,22 +10404,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10424,44 +10424,44 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125632341</v>
+        <v>125632409</v>
       </c>
       <c r="B94" t="n">
-        <v>92518</v>
+        <v>98334</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10471,10 +10471,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>522236</v>
+        <v>522062</v>
       </c>
       <c r="R94" t="n">
-        <v>6936562</v>
+        <v>6936422</v>
       </c>
       <c r="S94" t="n">
         <v>4</v>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10543,32 +10543,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125632415</v>
+        <v>125632358</v>
       </c>
       <c r="B95" t="n">
-        <v>98334</v>
+        <v>98355</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10578,10 +10578,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>522124</v>
+        <v>522231</v>
       </c>
       <c r="R95" t="n">
-        <v>6936410</v>
+        <v>6936488</v>
       </c>
       <c r="S95" t="n">
         <v>4</v>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10650,32 +10650,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125632358</v>
+        <v>125632415</v>
       </c>
       <c r="B96" t="n">
-        <v>98355</v>
+        <v>98334</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10685,10 +10685,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>522231</v>
+        <v>522124</v>
       </c>
       <c r="R96" t="n">
-        <v>6936488</v>
+        <v>6936410</v>
       </c>
       <c r="S96" t="n">
         <v>4</v>
@@ -10720,7 +10720,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10757,7 +10757,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125646886</v>
+        <v>125646894</v>
       </c>
       <c r="B97" t="n">
         <v>98334</v>
@@ -10792,10 +10792,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>522109</v>
+        <v>522227</v>
       </c>
       <c r="R97" t="n">
-        <v>6936414</v>
+        <v>6936562</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10854,7 +10854,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125646894</v>
+        <v>125632344</v>
       </c>
       <c r="B98" t="n">
         <v>98334</v>
@@ -10889,13 +10889,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>522227</v>
+        <v>522268</v>
       </c>
       <c r="R98" t="n">
-        <v>6936562</v>
+        <v>6936556</v>
       </c>
       <c r="S98" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10919,12 +10919,22 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10939,19 +10949,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125632344</v>
+        <v>125646886</v>
       </c>
       <c r="B99" t="n">
         <v>98334</v>
@@ -10986,13 +10996,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>522268</v>
+        <v>522109</v>
       </c>
       <c r="R99" t="n">
-        <v>6936556</v>
+        <v>6936414</v>
       </c>
       <c r="S99" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11016,22 +11026,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11046,12 +11046,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -11374,32 +11374,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125632390</v>
+        <v>125632412</v>
       </c>
       <c r="B103" t="n">
-        <v>91228</v>
+        <v>98334</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11409,10 +11409,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>522187</v>
+        <v>522101</v>
       </c>
       <c r="R103" t="n">
-        <v>6936377</v>
+        <v>6936425</v>
       </c>
       <c r="S103" t="n">
         <v>4</v>
@@ -11444,7 +11444,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11454,7 +11454,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11481,32 +11481,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125632323</v>
+        <v>125632379</v>
       </c>
       <c r="B104" t="n">
-        <v>78968</v>
+        <v>98334</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11516,10 +11516,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>522189</v>
+        <v>522237</v>
       </c>
       <c r="R104" t="n">
-        <v>6936648</v>
+        <v>6936415</v>
       </c>
       <c r="S104" t="n">
         <v>4</v>
@@ -11551,7 +11551,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11588,48 +11588,48 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125635476</v>
+        <v>125646884</v>
       </c>
       <c r="B105" t="n">
-        <v>80071</v>
+        <v>98334</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>522057</v>
+        <v>522100</v>
       </c>
       <c r="R105" t="n">
-        <v>6936487</v>
+        <v>6936419</v>
       </c>
       <c r="S105" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11659,11 +11659,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11690,10 +11685,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125632325</v>
+        <v>125632390</v>
       </c>
       <c r="B106" t="n">
-        <v>78726</v>
+        <v>91228</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11701,21 +11696,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11725,13 +11720,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>522198</v>
+        <v>522187</v>
       </c>
       <c r="R106" t="n">
-        <v>6936620</v>
+        <v>6936377</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11760,7 +11755,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11770,7 +11765,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11797,7 +11792,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125632330</v>
+        <v>125632323</v>
       </c>
       <c r="B107" t="n">
         <v>78968</v>
@@ -11828,17 +11823,17 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>522172</v>
+        <v>522189</v>
       </c>
       <c r="R107" t="n">
-        <v>6936483</v>
+        <v>6936648</v>
       </c>
       <c r="S107" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11862,12 +11857,22 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11882,19 +11887,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125646880</v>
+        <v>125635476</v>
       </c>
       <c r="B108" t="n">
         <v>80071</v>
@@ -11925,17 +11930,17 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>522225</v>
+        <v>522057</v>
       </c>
       <c r="R108" t="n">
-        <v>6936564</v>
+        <v>6936487</v>
       </c>
       <c r="S108" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11965,6 +11970,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11991,32 +12001,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125632340</v>
+        <v>125632325</v>
       </c>
       <c r="B109" t="n">
-        <v>98334</v>
+        <v>78726</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12026,13 +12036,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>522232</v>
+        <v>522198</v>
       </c>
       <c r="R109" t="n">
-        <v>6936562</v>
+        <v>6936620</v>
       </c>
       <c r="S109" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12061,7 +12071,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12071,7 +12081,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12098,48 +12108,48 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125632351</v>
+        <v>125632330</v>
       </c>
       <c r="B110" t="n">
-        <v>98334</v>
+        <v>78968</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>522250</v>
+        <v>522172</v>
       </c>
       <c r="R110" t="n">
-        <v>6936497</v>
+        <v>6936483</v>
       </c>
       <c r="S110" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12163,22 +12173,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>13:48</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>13:48</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12193,44 +12193,44 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125632412</v>
+        <v>125646880</v>
       </c>
       <c r="B111" t="n">
-        <v>98334</v>
+        <v>80071</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12240,13 +12240,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>522101</v>
+        <v>522225</v>
       </c>
       <c r="R111" t="n">
-        <v>6936425</v>
+        <v>6936564</v>
       </c>
       <c r="S111" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12270,22 +12270,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>15:23</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>15:23</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12300,19 +12290,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125632379</v>
+        <v>125632340</v>
       </c>
       <c r="B112" t="n">
         <v>98334</v>
@@ -12347,10 +12337,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>522237</v>
+        <v>522232</v>
       </c>
       <c r="R112" t="n">
-        <v>6936415</v>
+        <v>6936562</v>
       </c>
       <c r="S112" t="n">
         <v>4</v>
@@ -12382,7 +12372,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12392,7 +12382,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12419,7 +12409,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125646884</v>
+        <v>125632351</v>
       </c>
       <c r="B113" t="n">
         <v>98334</v>
@@ -12454,13 +12444,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>522100</v>
+        <v>522250</v>
       </c>
       <c r="R113" t="n">
-        <v>6936419</v>
+        <v>6936497</v>
       </c>
       <c r="S113" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12484,12 +12474,22 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12504,12 +12504,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -15370,32 +15370,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125646901</v>
+        <v>125632375</v>
       </c>
       <c r="B141" t="n">
-        <v>92518</v>
+        <v>98334</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15405,13 +15405,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>522030</v>
+        <v>522243</v>
       </c>
       <c r="R141" t="n">
-        <v>6936634</v>
+        <v>6936427</v>
       </c>
       <c r="S141" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15435,12 +15435,22 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15455,19 +15465,19 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125632375</v>
+        <v>125633218</v>
       </c>
       <c r="B142" t="n">
         <v>98334</v>
@@ -15498,17 +15508,17 @@
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>MD1:Ånge, SE-VN, SE, Mpd</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>522243</v>
+        <v>522221</v>
       </c>
       <c r="R142" t="n">
-        <v>6936427</v>
+        <v>6936591</v>
       </c>
       <c r="S142" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15537,7 +15547,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15547,7 +15557,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15574,7 +15584,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125633218</v>
+        <v>125632364</v>
       </c>
       <c r="B143" t="n">
         <v>98334</v>
@@ -15605,17 +15615,17 @@
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>MD1:Ånge, SE-VN, SE, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>522221</v>
+        <v>522260</v>
       </c>
       <c r="R143" t="n">
-        <v>6936591</v>
+        <v>6936473</v>
       </c>
       <c r="S143" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15644,7 +15654,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15654,7 +15664,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15681,32 +15691,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125632364</v>
+        <v>125646901</v>
       </c>
       <c r="B144" t="n">
-        <v>98334</v>
+        <v>92518</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15716,13 +15726,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>522260</v>
+        <v>522030</v>
       </c>
       <c r="R144" t="n">
-        <v>6936473</v>
+        <v>6936634</v>
       </c>
       <c r="S144" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15746,22 +15756,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15776,12 +15776,12 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
@@ -15992,32 +15992,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125632331</v>
+        <v>125632419</v>
       </c>
       <c r="B147" t="n">
-        <v>92518</v>
+        <v>98334</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>522221</v>
+        <v>522202</v>
       </c>
       <c r="R147" t="n">
-        <v>6936608</v>
+        <v>6936414</v>
       </c>
       <c r="S147" t="n">
         <v>4</v>
@@ -16062,7 +16062,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16072,7 +16072,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16099,32 +16099,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125632386</v>
+        <v>125632411</v>
       </c>
       <c r="B148" t="n">
-        <v>56843</v>
+        <v>98334</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16134,10 +16134,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>522200</v>
+        <v>522063</v>
       </c>
       <c r="R148" t="n">
-        <v>6936398</v>
+        <v>6936424</v>
       </c>
       <c r="S148" t="n">
         <v>4</v>
@@ -16169,7 +16169,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16179,7 +16179,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16206,7 +16206,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125632419</v>
+        <v>125646888</v>
       </c>
       <c r="B149" t="n">
         <v>98334</v>
@@ -16241,13 +16241,13 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>522202</v>
+        <v>522159</v>
       </c>
       <c r="R149" t="n">
-        <v>6936414</v>
+        <v>6936405</v>
       </c>
       <c r="S149" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16271,22 +16271,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>15:37</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>15:37</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16301,44 +16291,44 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125632411</v>
+        <v>125632366</v>
       </c>
       <c r="B150" t="n">
-        <v>98334</v>
+        <v>98355</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16348,10 +16338,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>522063</v>
+        <v>522249</v>
       </c>
       <c r="R150" t="n">
-        <v>6936424</v>
+        <v>6936460</v>
       </c>
       <c r="S150" t="n">
         <v>4</v>
@@ -16383,7 +16373,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16393,7 +16383,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16420,32 +16410,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125646888</v>
+        <v>125632384</v>
       </c>
       <c r="B151" t="n">
-        <v>98334</v>
+        <v>98355</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16455,13 +16445,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>522159</v>
+        <v>522207</v>
       </c>
       <c r="R151" t="n">
-        <v>6936405</v>
+        <v>6936406</v>
       </c>
       <c r="S151" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16485,12 +16475,22 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16505,22 +16505,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125632366</v>
+        <v>125632331</v>
       </c>
       <c r="B152" t="n">
-        <v>98355</v>
+        <v>92518</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16528,21 +16528,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>221952</v>
+        <v>4364</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16552,10 +16552,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>522249</v>
+        <v>522221</v>
       </c>
       <c r="R152" t="n">
-        <v>6936460</v>
+        <v>6936608</v>
       </c>
       <c r="S152" t="n">
         <v>4</v>
@@ -16587,7 +16587,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16597,7 +16597,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16624,10 +16624,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125632384</v>
+        <v>125632386</v>
       </c>
       <c r="B153" t="n">
-        <v>98355</v>
+        <v>56843</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16635,21 +16635,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16659,10 +16659,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>522207</v>
+        <v>522200</v>
       </c>
       <c r="R153" t="n">
-        <v>6936406</v>
+        <v>6936398</v>
       </c>
       <c r="S153" t="n">
         <v>4</v>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16704,7 +16704,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD153" t="b">

--- a/artfynd/A 26476-2025 artfynd.xlsx
+++ b/artfynd/A 26476-2025 artfynd.xlsx
@@ -2215,7 +2215,7 @@
         <v>125621452</v>
       </c>
       <c r="B14" t="n">
-        <v>91389</v>
+        <v>91393</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>125620054</v>
       </c>
       <c r="B15" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125619969</v>
+        <v>125619776</v>
       </c>
       <c r="B16" t="n">
-        <v>80071</v>
+        <v>78731</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>522066</v>
+        <v>521964</v>
       </c>
       <c r="R16" t="n">
-        <v>6936575</v>
+        <v>6936664</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2515,10 +2515,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125619776</v>
+        <v>125619969</v>
       </c>
       <c r="B17" t="n">
-        <v>78727</v>
+        <v>80075</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2526,21 +2526,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>521964</v>
+        <v>522066</v>
       </c>
       <c r="R17" t="n">
-        <v>6936664</v>
+        <v>6936575</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2619,7 +2619,7 @@
         <v>125619796</v>
       </c>
       <c r="B18" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>125619751</v>
       </c>
       <c r="B19" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>125599631</v>
       </c>
       <c r="B20" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>125632425</v>
       </c>
       <c r="B21" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3032,32 +3032,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125646874</v>
+        <v>125601606</v>
       </c>
       <c r="B22" t="n">
-        <v>80099</v>
+        <v>98338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>522022</v>
+        <v>522217</v>
       </c>
       <c r="R22" t="n">
-        <v>6936611</v>
+        <v>6936540</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3097,12 +3097,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3117,44 +3117,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125646902</v>
+        <v>125632421</v>
       </c>
       <c r="B23" t="n">
-        <v>4869</v>
+        <v>98338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101675</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3164,13 +3164,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>522019</v>
+        <v>522260</v>
       </c>
       <c r="R23" t="n">
-        <v>6936608</v>
+        <v>6936447</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3194,17 +3194,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Kläckhål på asp</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3219,22 +3224,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125632421</v>
+        <v>125632569</v>
       </c>
       <c r="B24" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3262,17 +3267,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>522260</v>
+        <v>522108</v>
       </c>
       <c r="R24" t="n">
-        <v>6936447</v>
+        <v>6936467</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3296,22 +3301,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3326,44 +3321,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125601310</v>
+        <v>125646874</v>
       </c>
       <c r="B25" t="n">
-        <v>98334</v>
+        <v>80103</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3373,13 +3368,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>522217</v>
+        <v>522022</v>
       </c>
       <c r="R25" t="n">
-        <v>6936540</v>
+        <v>6936611</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3403,12 +3398,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3423,60 +3418,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125632569</v>
+        <v>125646902</v>
       </c>
       <c r="B26" t="n">
-        <v>98334</v>
+        <v>4869</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>101675</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>522108</v>
+        <v>522019</v>
       </c>
       <c r="R26" t="n">
-        <v>6936467</v>
+        <v>6936608</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3506,6 +3501,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Kläckhål på asp</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3535,7 +3535,7 @@
         <v>125602968</v>
       </c>
       <c r="B27" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>125646875</v>
       </c>
       <c r="B28" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3726,32 +3726,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125600280</v>
+        <v>125632349</v>
       </c>
       <c r="B29" t="n">
-        <v>92518</v>
+        <v>98338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3761,13 +3761,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>522217</v>
+        <v>522259</v>
       </c>
       <c r="R29" t="n">
-        <v>6936540</v>
+        <v>6936489</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3794,9 +3794,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3811,22 +3821,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125601890</v>
+        <v>125636837</v>
       </c>
       <c r="B30" t="n">
-        <v>91682</v>
+        <v>98338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3834,37 +3844,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>522217</v>
+        <v>522164</v>
       </c>
       <c r="R30" t="n">
-        <v>6936540</v>
+        <v>6936587</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3888,12 +3898,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3908,44 +3918,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125632349</v>
+        <v>125603562</v>
       </c>
       <c r="B31" t="n">
-        <v>98334</v>
+        <v>80035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3955,13 +3965,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>522259</v>
+        <v>522217</v>
       </c>
       <c r="R31" t="n">
-        <v>6936489</v>
+        <v>6936540</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3988,19 +3998,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4015,60 +4015,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125636837</v>
+        <v>125632367</v>
       </c>
       <c r="B32" t="n">
-        <v>98334</v>
+        <v>98359</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>522164</v>
+        <v>522247</v>
       </c>
       <c r="R32" t="n">
-        <v>6936587</v>
+        <v>6936458</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4092,12 +4092,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4112,60 +4122,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125632332</v>
+        <v>125634580</v>
       </c>
       <c r="B33" t="n">
-        <v>78968</v>
+        <v>98359</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>522239</v>
+        <v>522044</v>
       </c>
       <c r="R33" t="n">
-        <v>6936598</v>
+        <v>6936401</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4189,22 +4199,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4219,44 +4219,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125600959</v>
+        <v>125600280</v>
       </c>
       <c r="B34" t="n">
-        <v>80071</v>
+        <v>92522</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4312,21 +4312,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4343,32 +4328,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125632367</v>
+        <v>125600959</v>
       </c>
       <c r="B35" t="n">
-        <v>98355</v>
+        <v>80075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4378,13 +4363,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>522247</v>
+        <v>522217</v>
       </c>
       <c r="R35" t="n">
-        <v>6936458</v>
+        <v>6936540</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4411,21 +4396,11 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4434,64 +4409,79 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125634580</v>
+        <v>125601890</v>
       </c>
       <c r="B36" t="n">
-        <v>98355</v>
+        <v>91686</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>522044</v>
+        <v>522217</v>
       </c>
       <c r="R36" t="n">
-        <v>6936401</v>
+        <v>6936540</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4515,12 +4505,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4535,44 +4525,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125603562</v>
+        <v>125632332</v>
       </c>
       <c r="B37" t="n">
-        <v>80031</v>
+        <v>78972</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4582,13 +4572,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>522217</v>
+        <v>522239</v>
       </c>
       <c r="R37" t="n">
-        <v>6936540</v>
+        <v>6936598</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4615,9 +4605,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4632,44 +4632,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125632337</v>
+        <v>125632353</v>
       </c>
       <c r="B38" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4679,10 +4679,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>522224</v>
+        <v>522241</v>
       </c>
       <c r="R38" t="n">
-        <v>6936572</v>
+        <v>6936509</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4751,32 +4751,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125632362</v>
+        <v>125646892</v>
       </c>
       <c r="B39" t="n">
-        <v>78726</v>
+        <v>98338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4786,13 +4786,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>522249</v>
+        <v>522130</v>
       </c>
       <c r="R39" t="n">
-        <v>6936486</v>
+        <v>6936481</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4816,22 +4816,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4846,44 +4836,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125632329</v>
+        <v>125646893</v>
       </c>
       <c r="B40" t="n">
-        <v>80100</v>
+        <v>98338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4893,13 +4883,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>522215</v>
+        <v>522204</v>
       </c>
       <c r="R40" t="n">
-        <v>6936627</v>
+        <v>6936495</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4923,22 +4913,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:04</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:04</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4953,44 +4933,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125646893</v>
+        <v>125632401</v>
       </c>
       <c r="B41" t="n">
-        <v>98334</v>
+        <v>100520</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5000,13 +4980,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>522204</v>
+        <v>522046</v>
       </c>
       <c r="R41" t="n">
-        <v>6936495</v>
+        <v>6936397</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5030,12 +5010,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5050,44 +5040,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125632353</v>
+        <v>125632338</v>
       </c>
       <c r="B42" t="n">
-        <v>98334</v>
+        <v>92522</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5097,10 +5087,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>522241</v>
+        <v>522221</v>
       </c>
       <c r="R42" t="n">
-        <v>6936509</v>
+        <v>6936572</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5132,7 +5122,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5142,7 +5132,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5169,48 +5159,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125646892</v>
+        <v>125636088</v>
       </c>
       <c r="B43" t="n">
-        <v>98334</v>
+        <v>92522</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>522130</v>
+        <v>522049</v>
       </c>
       <c r="R43" t="n">
-        <v>6936481</v>
+        <v>6936650</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5266,32 +5256,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125632368</v>
+        <v>125632337</v>
       </c>
       <c r="B44" t="n">
-        <v>98355</v>
+        <v>78972</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5301,10 +5291,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>522245</v>
+        <v>522224</v>
       </c>
       <c r="R44" t="n">
-        <v>6936456</v>
+        <v>6936572</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5336,7 +5326,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5346,7 +5336,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5373,32 +5363,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125632401</v>
+        <v>125632362</v>
       </c>
       <c r="B45" t="n">
-        <v>100516</v>
+        <v>78730</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5408,10 +5398,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>522046</v>
+        <v>522249</v>
       </c>
       <c r="R45" t="n">
-        <v>6936397</v>
+        <v>6936486</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5443,7 +5433,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5453,7 +5443,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5480,10 +5470,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125632338</v>
+        <v>125632329</v>
       </c>
       <c r="B46" t="n">
-        <v>92518</v>
+        <v>80104</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5491,21 +5481,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5515,10 +5505,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>522221</v>
+        <v>522215</v>
       </c>
       <c r="R46" t="n">
-        <v>6936572</v>
+        <v>6936627</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -5550,7 +5540,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5560,7 +5550,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5587,10 +5577,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125636088</v>
+        <v>125632368</v>
       </c>
       <c r="B47" t="n">
-        <v>92518</v>
+        <v>98359</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5598,37 +5588,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>522049</v>
+        <v>522245</v>
       </c>
       <c r="R47" t="n">
-        <v>6936650</v>
+        <v>6936456</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5652,12 +5642,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5672,44 +5672,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125600818</v>
+        <v>125632382</v>
       </c>
       <c r="B48" t="n">
-        <v>98251</v>
+        <v>98338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5719,13 +5719,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>522217</v>
+        <v>522214</v>
       </c>
       <c r="R48" t="n">
-        <v>6936540</v>
+        <v>6936414</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5752,9 +5752,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5769,22 +5779,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125638972</v>
+        <v>125646883</v>
       </c>
       <c r="B49" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5812,17 +5822,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>522318</v>
+        <v>522097</v>
       </c>
       <c r="R49" t="n">
-        <v>6936398</v>
+        <v>6936427</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5878,10 +5888,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125632382</v>
+        <v>125638972</v>
       </c>
       <c r="B50" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5909,17 +5919,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>522214</v>
+        <v>522318</v>
       </c>
       <c r="R50" t="n">
-        <v>6936414</v>
+        <v>6936398</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5943,22 +5953,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>14:29</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>14:29</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5973,44 +5973,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125646883</v>
+        <v>125632416</v>
       </c>
       <c r="B51" t="n">
-        <v>98334</v>
+        <v>91250</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6020,13 +6020,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>522097</v>
+        <v>522125</v>
       </c>
       <c r="R51" t="n">
-        <v>6936427</v>
+        <v>6936430</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6050,12 +6050,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6070,44 +6080,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125632416</v>
+        <v>125600818</v>
       </c>
       <c r="B52" t="n">
-        <v>91246</v>
+        <v>98255</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>219790</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6117,13 +6127,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>522125</v>
+        <v>522217</v>
       </c>
       <c r="R52" t="n">
-        <v>6936430</v>
+        <v>6936540</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6150,19 +6160,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:27</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6177,60 +6177,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125632400</v>
+        <v>125632815</v>
       </c>
       <c r="B53" t="n">
-        <v>91228</v>
+        <v>98359</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>522048</v>
+        <v>522129</v>
       </c>
       <c r="R53" t="n">
-        <v>6936403</v>
+        <v>6936436</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6254,22 +6254,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:08</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:08</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6284,60 +6274,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125637287</v>
+        <v>125632397</v>
       </c>
       <c r="B54" t="n">
-        <v>79586</v>
+        <v>98338</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>522356</v>
+        <v>522077</v>
       </c>
       <c r="R54" t="n">
-        <v>6936466</v>
+        <v>6936379</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6361,12 +6351,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6381,60 +6381,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125632336</v>
+        <v>125636925</v>
       </c>
       <c r="B55" t="n">
-        <v>78726</v>
+        <v>98338</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>522224</v>
+        <v>522220</v>
       </c>
       <c r="R55" t="n">
-        <v>6936572</v>
+        <v>6936601</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6458,22 +6458,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>13:25</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>13:25</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6488,44 +6478,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125636925</v>
+        <v>125637245</v>
       </c>
       <c r="B56" t="n">
-        <v>98334</v>
+        <v>80075</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6535,10 +6525,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>522220</v>
+        <v>522360</v>
       </c>
       <c r="R56" t="n">
-        <v>6936601</v>
+        <v>6936453</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6597,32 +6587,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125632397</v>
+        <v>125632400</v>
       </c>
       <c r="B57" t="n">
-        <v>98334</v>
+        <v>91232</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6632,10 +6622,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>522077</v>
+        <v>522048</v>
       </c>
       <c r="R57" t="n">
-        <v>6936379</v>
+        <v>6936403</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6667,7 +6657,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6677,7 +6667,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6704,10 +6694,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125637245</v>
+        <v>125637287</v>
       </c>
       <c r="B58" t="n">
-        <v>80071</v>
+        <v>79590</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6715,21 +6705,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6739,13 +6729,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>522360</v>
+        <v>522356</v>
       </c>
       <c r="R58" t="n">
-        <v>6936453</v>
+        <v>6936466</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6801,48 +6791,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125632815</v>
+        <v>125632336</v>
       </c>
       <c r="B59" t="n">
-        <v>98355</v>
+        <v>78730</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221952</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>522129</v>
+        <v>522224</v>
       </c>
       <c r="R59" t="n">
-        <v>6936436</v>
+        <v>6936572</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6866,12 +6856,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6886,22 +6886,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125632354</v>
+        <v>125646891</v>
       </c>
       <c r="B60" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6933,13 +6933,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>522234</v>
+        <v>522159</v>
       </c>
       <c r="R60" t="n">
-        <v>6936499</v>
+        <v>6936408</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6963,22 +6963,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6993,22 +6983,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125646887</v>
+        <v>125632392</v>
       </c>
       <c r="B61" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7040,13 +7030,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>522185</v>
+        <v>522181</v>
       </c>
       <c r="R61" t="n">
-        <v>6936414</v>
+        <v>6936381</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7070,12 +7060,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7090,22 +7090,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125646891</v>
+        <v>125632398</v>
       </c>
       <c r="B62" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7137,13 +7137,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>522159</v>
+        <v>522059</v>
       </c>
       <c r="R62" t="n">
-        <v>6936408</v>
+        <v>6936399</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7167,12 +7167,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7187,22 +7197,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125632392</v>
+        <v>125632354</v>
       </c>
       <c r="B63" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7234,10 +7244,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>522181</v>
+        <v>522234</v>
       </c>
       <c r="R63" t="n">
-        <v>6936381</v>
+        <v>6936499</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -7269,7 +7279,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7279,7 +7289,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7306,10 +7316,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125632398</v>
+        <v>125646887</v>
       </c>
       <c r="B64" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7341,13 +7351,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>522059</v>
+        <v>522185</v>
       </c>
       <c r="R64" t="n">
-        <v>6936399</v>
+        <v>6936414</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7371,22 +7381,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:05</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:05</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7401,12 +7401,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7416,7 +7416,7 @@
         <v>125632410</v>
       </c>
       <c r="B65" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>125632324</v>
       </c>
       <c r="B66" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>125632356</v>
       </c>
       <c r="B67" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>125632422</v>
       </c>
       <c r="B68" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7841,10 +7841,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125632396</v>
+        <v>125632361</v>
       </c>
       <c r="B69" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7876,10 +7876,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>522109</v>
+        <v>522249</v>
       </c>
       <c r="R69" t="n">
-        <v>6936384</v>
+        <v>6936484</v>
       </c>
       <c r="S69" t="n">
         <v>4</v>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7948,10 +7948,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125632361</v>
+        <v>125632396</v>
       </c>
       <c r="B70" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7983,10 +7983,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>522249</v>
+        <v>522109</v>
       </c>
       <c r="R70" t="n">
-        <v>6936484</v>
+        <v>6936384</v>
       </c>
       <c r="S70" t="n">
         <v>4</v>
@@ -8018,7 +8018,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8055,10 +8055,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125646879</v>
+        <v>125632350</v>
       </c>
       <c r="B71" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>522202</v>
+        <v>522254</v>
       </c>
       <c r="R71" t="n">
-        <v>6936502</v>
+        <v>6936496</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8120,12 +8120,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8140,22 +8150,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125632350</v>
+        <v>125646879</v>
       </c>
       <c r="B72" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8187,13 +8197,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>522254</v>
+        <v>522202</v>
       </c>
       <c r="R72" t="n">
-        <v>6936496</v>
+        <v>6936502</v>
       </c>
       <c r="S72" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8217,22 +8227,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>13:47</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>13:47</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8247,44 +8247,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125646872</v>
+        <v>125632357</v>
       </c>
       <c r="B73" t="n">
-        <v>91193</v>
+        <v>91232</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8294,13 +8294,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>522064</v>
+        <v>522221</v>
       </c>
       <c r="R73" t="n">
-        <v>6936505</v>
+        <v>6936489</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8324,12 +8324,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8344,44 +8354,44 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125632357</v>
+        <v>125646872</v>
       </c>
       <c r="B74" t="n">
-        <v>91228</v>
+        <v>91197</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8391,13 +8401,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>522221</v>
+        <v>522064</v>
       </c>
       <c r="R74" t="n">
-        <v>6936489</v>
+        <v>6936505</v>
       </c>
       <c r="S74" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8421,22 +8431,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8451,22 +8451,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125632370</v>
+        <v>125632381</v>
       </c>
       <c r="B75" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8498,10 +8498,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>522243</v>
+        <v>522240</v>
       </c>
       <c r="R75" t="n">
-        <v>6936456</v>
+        <v>6936412</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -8533,7 +8533,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8570,10 +8570,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125632381</v>
+        <v>125632418</v>
       </c>
       <c r="B76" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>522240</v>
+        <v>522162</v>
       </c>
       <c r="R76" t="n">
-        <v>6936412</v>
+        <v>6936404</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8677,32 +8677,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125632418</v>
+        <v>125632372</v>
       </c>
       <c r="B77" t="n">
-        <v>98334</v>
+        <v>98359</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8712,10 +8712,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>522162</v>
+        <v>522236</v>
       </c>
       <c r="R77" t="n">
-        <v>6936404</v>
+        <v>6936448</v>
       </c>
       <c r="S77" t="n">
         <v>4</v>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8784,32 +8784,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125632372</v>
+        <v>125632370</v>
       </c>
       <c r="B78" t="n">
-        <v>98355</v>
+        <v>98338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8819,10 +8819,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>522236</v>
+        <v>522243</v>
       </c>
       <c r="R78" t="n">
-        <v>6936448</v>
+        <v>6936456</v>
       </c>
       <c r="S78" t="n">
         <v>4</v>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8891,10 +8891,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125632387</v>
+        <v>125632406</v>
       </c>
       <c r="B79" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8926,10 +8926,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>522191</v>
+        <v>522052</v>
       </c>
       <c r="R79" t="n">
-        <v>6936398</v>
+        <v>6936412</v>
       </c>
       <c r="S79" t="n">
         <v>4</v>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8998,10 +8998,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125632423</v>
+        <v>125632377</v>
       </c>
       <c r="B80" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9033,10 +9033,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>522332</v>
+        <v>522237</v>
       </c>
       <c r="R80" t="n">
-        <v>6936449</v>
+        <v>6936417</v>
       </c>
       <c r="S80" t="n">
         <v>4</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9105,10 +9105,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125632593</v>
+        <v>125632387</v>
       </c>
       <c r="B81" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9136,17 +9136,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>522125</v>
+        <v>522191</v>
       </c>
       <c r="R81" t="n">
-        <v>6936475</v>
+        <v>6936398</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9170,12 +9170,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9190,44 +9200,44 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125632420</v>
+        <v>125632365</v>
       </c>
       <c r="B82" t="n">
-        <v>98355</v>
+        <v>98338</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9237,10 +9247,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>522236</v>
+        <v>522249</v>
       </c>
       <c r="R82" t="n">
-        <v>6936446</v>
+        <v>6936473</v>
       </c>
       <c r="S82" t="n">
         <v>4</v>
@@ -9272,7 +9282,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9282,7 +9292,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9309,10 +9319,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125632406</v>
+        <v>125632554</v>
       </c>
       <c r="B83" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9340,17 +9350,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>522052</v>
+        <v>522125</v>
       </c>
       <c r="R83" t="n">
-        <v>6936412</v>
+        <v>6936477</v>
       </c>
       <c r="S83" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9374,22 +9384,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>15:17</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>15:17</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9404,22 +9404,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125632377</v>
+        <v>125632593</v>
       </c>
       <c r="B84" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9447,17 +9447,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>522237</v>
+        <v>522125</v>
       </c>
       <c r="R84" t="n">
-        <v>6936417</v>
+        <v>6936475</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9481,22 +9481,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9511,22 +9501,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125632365</v>
+        <v>125632423</v>
       </c>
       <c r="B85" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9558,10 +9548,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>522249</v>
+        <v>522332</v>
       </c>
       <c r="R85" t="n">
-        <v>6936473</v>
+        <v>6936449</v>
       </c>
       <c r="S85" t="n">
         <v>4</v>
@@ -9593,7 +9583,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9603,7 +9593,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9630,48 +9620,48 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125632554</v>
+        <v>125632420</v>
       </c>
       <c r="B86" t="n">
-        <v>98334</v>
+        <v>98359</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>522125</v>
+        <v>522236</v>
       </c>
       <c r="R86" t="n">
-        <v>6936477</v>
+        <v>6936446</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9695,12 +9685,22 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9715,60 +9715,60 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125635192</v>
+        <v>125632417</v>
       </c>
       <c r="B87" t="n">
-        <v>92518</v>
+        <v>98338</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>522003</v>
+        <v>522163</v>
       </c>
       <c r="R87" t="n">
-        <v>6936451</v>
+        <v>6936406</v>
       </c>
       <c r="S87" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9792,12 +9792,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9812,60 +9822,60 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125637200</v>
+        <v>125646882</v>
       </c>
       <c r="B88" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>522362</v>
+        <v>522029</v>
       </c>
       <c r="R88" t="n">
-        <v>6936466</v>
+        <v>6936561</v>
       </c>
       <c r="S88" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9921,48 +9931,48 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125646882</v>
+        <v>125635192</v>
       </c>
       <c r="B89" t="n">
-        <v>98334</v>
+        <v>92522</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>522029</v>
+        <v>522003</v>
       </c>
       <c r="R89" t="n">
-        <v>6936561</v>
+        <v>6936451</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10018,48 +10028,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125632417</v>
+        <v>125637200</v>
       </c>
       <c r="B90" t="n">
-        <v>98334</v>
+        <v>78972</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>522163</v>
+        <v>522362</v>
       </c>
       <c r="R90" t="n">
-        <v>6936406</v>
+        <v>6936466</v>
       </c>
       <c r="S90" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10083,22 +10093,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10113,12 +10113,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -10128,7 +10128,7 @@
         <v>125632341</v>
       </c>
       <c r="B91" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         <v>125635666</v>
       </c>
       <c r="B92" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10334,53 +10334,48 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125633268</v>
+        <v>125632409</v>
       </c>
       <c r="B93" t="n">
-        <v>57811</v>
+        <v>98338</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>522121</v>
+        <v>522062</v>
       </c>
       <c r="R93" t="n">
-        <v>6936402</v>
+        <v>6936422</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10404,12 +10399,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10424,22 +10429,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125632409</v>
+        <v>125632415</v>
       </c>
       <c r="B94" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10471,10 +10476,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>522062</v>
+        <v>522124</v>
       </c>
       <c r="R94" t="n">
-        <v>6936422</v>
+        <v>6936410</v>
       </c>
       <c r="S94" t="n">
         <v>4</v>
@@ -10506,7 +10511,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10516,7 +10521,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10546,7 +10551,7 @@
         <v>125632358</v>
       </c>
       <c r="B95" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10650,48 +10655,53 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125632415</v>
+        <v>125633268</v>
       </c>
       <c r="B96" t="n">
-        <v>98334</v>
+        <v>57811</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>522124</v>
+        <v>522121</v>
       </c>
       <c r="R96" t="n">
-        <v>6936410</v>
+        <v>6936402</v>
       </c>
       <c r="S96" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10715,22 +10725,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>15:26</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>15:26</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10745,12 +10745,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -10760,7 +10760,7 @@
         <v>125646894</v>
       </c>
       <c r="B97" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10857,7 +10857,7 @@
         <v>125632344</v>
       </c>
       <c r="B98" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>125646886</v>
       </c>
       <c r="B99" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>125632333</v>
       </c>
       <c r="B100" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
         <v>125646900</v>
       </c>
       <c r="B101" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>125632348</v>
       </c>
       <c r="B102" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11374,32 +11374,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125632412</v>
+        <v>125646880</v>
       </c>
       <c r="B103" t="n">
-        <v>98334</v>
+        <v>80075</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11409,13 +11409,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>522101</v>
+        <v>522225</v>
       </c>
       <c r="R103" t="n">
-        <v>6936425</v>
+        <v>6936564</v>
       </c>
       <c r="S103" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11439,22 +11439,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>15:23</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>15:23</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11469,60 +11459,60 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125632379</v>
+        <v>125635476</v>
       </c>
       <c r="B104" t="n">
-        <v>98334</v>
+        <v>80075</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>522237</v>
+        <v>522057</v>
       </c>
       <c r="R104" t="n">
-        <v>6936415</v>
+        <v>6936487</v>
       </c>
       <c r="S104" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11546,22 +11536,17 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>14:26</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>14:26</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11576,44 +11561,44 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125646884</v>
+        <v>125632323</v>
       </c>
       <c r="B105" t="n">
-        <v>98334</v>
+        <v>78972</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11623,13 +11608,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>522100</v>
+        <v>522189</v>
       </c>
       <c r="R105" t="n">
-        <v>6936419</v>
+        <v>6936648</v>
       </c>
       <c r="S105" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11653,12 +11638,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11673,22 +11668,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125632390</v>
+        <v>125632325</v>
       </c>
       <c r="B106" t="n">
-        <v>91228</v>
+        <v>78730</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11696,21 +11691,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11720,13 +11715,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>522187</v>
+        <v>522198</v>
       </c>
       <c r="R106" t="n">
-        <v>6936377</v>
+        <v>6936620</v>
       </c>
       <c r="S106" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11755,7 +11750,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11765,7 +11760,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11792,10 +11787,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125632323</v>
+        <v>125632330</v>
       </c>
       <c r="B107" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11823,17 +11818,17 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>522189</v>
+        <v>522172</v>
       </c>
       <c r="R107" t="n">
-        <v>6936648</v>
+        <v>6936483</v>
       </c>
       <c r="S107" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11857,22 +11852,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>12:51</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>12:51</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11887,60 +11872,60 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125635476</v>
+        <v>125632379</v>
       </c>
       <c r="B108" t="n">
-        <v>80071</v>
+        <v>98338</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>522057</v>
+        <v>522237</v>
       </c>
       <c r="R108" t="n">
-        <v>6936487</v>
+        <v>6936415</v>
       </c>
       <c r="S108" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11964,17 +11949,22 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11989,44 +11979,44 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125632325</v>
+        <v>125632412</v>
       </c>
       <c r="B109" t="n">
-        <v>78726</v>
+        <v>98338</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12036,13 +12026,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>522198</v>
+        <v>522101</v>
       </c>
       <c r="R109" t="n">
-        <v>6936620</v>
+        <v>6936425</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12071,7 +12061,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12081,7 +12071,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12108,48 +12098,48 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125632330</v>
+        <v>125632340</v>
       </c>
       <c r="B110" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>522172</v>
+        <v>522232</v>
       </c>
       <c r="R110" t="n">
-        <v>6936483</v>
+        <v>6936562</v>
       </c>
       <c r="S110" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12173,12 +12163,22 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12193,44 +12193,44 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125646880</v>
+        <v>125632351</v>
       </c>
       <c r="B111" t="n">
-        <v>80071</v>
+        <v>98338</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12240,13 +12240,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>522225</v>
+        <v>522250</v>
       </c>
       <c r="R111" t="n">
-        <v>6936564</v>
+        <v>6936497</v>
       </c>
       <c r="S111" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12270,12 +12270,22 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12290,22 +12300,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125632340</v>
+        <v>125646884</v>
       </c>
       <c r="B112" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12337,13 +12347,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>522232</v>
+        <v>522100</v>
       </c>
       <c r="R112" t="n">
-        <v>6936562</v>
+        <v>6936419</v>
       </c>
       <c r="S112" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12367,22 +12377,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12397,44 +12397,44 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125632351</v>
+        <v>125632390</v>
       </c>
       <c r="B113" t="n">
-        <v>98334</v>
+        <v>91232</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12444,10 +12444,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>522250</v>
+        <v>522187</v>
       </c>
       <c r="R113" t="n">
-        <v>6936497</v>
+        <v>6936377</v>
       </c>
       <c r="S113" t="n">
         <v>4</v>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12516,32 +12516,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125632347</v>
+        <v>125632371</v>
       </c>
       <c r="B114" t="n">
-        <v>78726</v>
+        <v>98338</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12551,10 +12551,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>522239</v>
+        <v>522243</v>
       </c>
       <c r="R114" t="n">
-        <v>6936527</v>
+        <v>6936460</v>
       </c>
       <c r="S114" t="n">
         <v>4</v>
@@ -12586,7 +12586,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12623,48 +12623,48 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125632346</v>
+        <v>125635820</v>
       </c>
       <c r="B115" t="n">
-        <v>80071</v>
+        <v>98338</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>522239</v>
+        <v>522040</v>
       </c>
       <c r="R115" t="n">
-        <v>6936527</v>
+        <v>6936582</v>
       </c>
       <c r="S115" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12688,22 +12688,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>13:38</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>13:38</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12718,22 +12708,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125632394</v>
+        <v>125632385</v>
       </c>
       <c r="B116" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12765,10 +12755,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>522136</v>
+        <v>522197</v>
       </c>
       <c r="R116" t="n">
-        <v>6936370</v>
+        <v>6936406</v>
       </c>
       <c r="S116" t="n">
         <v>4</v>
@@ -12800,7 +12790,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12810,7 +12800,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12837,10 +12827,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125635820</v>
+        <v>125632394</v>
       </c>
       <c r="B117" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12868,17 +12858,17 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>522040</v>
+        <v>522136</v>
       </c>
       <c r="R117" t="n">
-        <v>6936582</v>
+        <v>6936370</v>
       </c>
       <c r="S117" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12902,12 +12892,22 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12922,44 +12922,44 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125632399</v>
+        <v>125632346</v>
       </c>
       <c r="B118" t="n">
-        <v>56843</v>
+        <v>80075</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12969,10 +12969,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>522053</v>
+        <v>522239</v>
       </c>
       <c r="R118" t="n">
-        <v>6936400</v>
+        <v>6936527</v>
       </c>
       <c r="S118" t="n">
         <v>4</v>
@@ -13004,7 +13004,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13014,12 +13014,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>15:07</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>spillning</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13046,32 +13041,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125632371</v>
+        <v>125632399</v>
       </c>
       <c r="B119" t="n">
-        <v>98334</v>
+        <v>56843</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13081,10 +13076,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>522243</v>
+        <v>522053</v>
       </c>
       <c r="R119" t="n">
-        <v>6936460</v>
+        <v>6936400</v>
       </c>
       <c r="S119" t="n">
         <v>4</v>
@@ -13116,7 +13111,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13126,7 +13121,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13153,32 +13153,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125632385</v>
+        <v>125632347</v>
       </c>
       <c r="B120" t="n">
-        <v>98334</v>
+        <v>78730</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13188,10 +13188,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>522197</v>
+        <v>522239</v>
       </c>
       <c r="R120" t="n">
-        <v>6936406</v>
+        <v>6936527</v>
       </c>
       <c r="S120" t="n">
         <v>4</v>
@@ -13223,7 +13223,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13233,7 +13233,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13260,10 +13260,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125632405</v>
+        <v>125637290</v>
       </c>
       <c r="B121" t="n">
-        <v>91524</v>
+        <v>78730</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13271,37 +13271,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>522044</v>
+        <v>522366</v>
       </c>
       <c r="R121" t="n">
-        <v>6936401</v>
+        <v>6936463</v>
       </c>
       <c r="S121" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13325,22 +13325,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13355,22 +13345,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125601877</v>
+        <v>125632360</v>
       </c>
       <c r="B122" t="n">
-        <v>91228</v>
+        <v>57648</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13378,21 +13368,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13402,13 +13392,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>522217</v>
+        <v>522247</v>
       </c>
       <c r="R122" t="n">
-        <v>6936540</v>
+        <v>6936482</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13435,9 +13425,24 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>födosök död stående tall</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13452,22 +13457,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125632383</v>
+        <v>125632405</v>
       </c>
       <c r="B123" t="n">
-        <v>91228</v>
+        <v>91528</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13475,21 +13480,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13499,10 +13504,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>522219</v>
+        <v>522044</v>
       </c>
       <c r="R123" t="n">
-        <v>6936411</v>
+        <v>6936401</v>
       </c>
       <c r="S123" t="n">
         <v>4</v>
@@ -13534,7 +13539,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13544,7 +13549,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13571,10 +13576,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125637290</v>
+        <v>125601877</v>
       </c>
       <c r="B124" t="n">
-        <v>78726</v>
+        <v>91232</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13582,37 +13587,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>522366</v>
+        <v>522217</v>
       </c>
       <c r="R124" t="n">
-        <v>6936463</v>
+        <v>6936540</v>
       </c>
       <c r="S124" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13636,12 +13641,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13656,22 +13661,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125632360</v>
+        <v>125632383</v>
       </c>
       <c r="B125" t="n">
-        <v>57648</v>
+        <v>91232</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13679,21 +13684,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13703,10 +13708,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>522247</v>
+        <v>522219</v>
       </c>
       <c r="R125" t="n">
-        <v>6936482</v>
+        <v>6936411</v>
       </c>
       <c r="S125" t="n">
         <v>4</v>
@@ -13738,7 +13743,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13748,12 +13753,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>födosök död stående tall</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13780,10 +13780,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125632414</v>
+        <v>125601077</v>
       </c>
       <c r="B126" t="n">
-        <v>91228</v>
+        <v>80076</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13791,21 +13791,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13815,13 +13815,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>522109</v>
+        <v>522217</v>
       </c>
       <c r="R126" t="n">
-        <v>6936426</v>
+        <v>6936540</v>
       </c>
       <c r="S126" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13848,21 +13848,11 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
@@ -13871,26 +13861,41 @@
       </c>
       <c r="AG126" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125632326</v>
+        <v>125646878</v>
       </c>
       <c r="B127" t="n">
-        <v>78968</v>
+        <v>80075</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13898,21 +13903,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13922,13 +13927,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>522213</v>
+        <v>522019</v>
       </c>
       <c r="R127" t="n">
-        <v>6936615</v>
+        <v>6936608</v>
       </c>
       <c r="S127" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13952,22 +13957,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>13:02</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>13:02</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13982,22 +13977,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125646878</v>
+        <v>125632414</v>
       </c>
       <c r="B128" t="n">
-        <v>80071</v>
+        <v>91232</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14005,21 +14000,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14029,13 +14024,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>522019</v>
+        <v>522109</v>
       </c>
       <c r="R128" t="n">
-        <v>6936608</v>
+        <v>6936426</v>
       </c>
       <c r="S128" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14059,12 +14054,22 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14079,22 +14084,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125632345</v>
+        <v>125632326</v>
       </c>
       <c r="B129" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14126,10 +14131,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>522244</v>
+        <v>522213</v>
       </c>
       <c r="R129" t="n">
-        <v>6936537</v>
+        <v>6936615</v>
       </c>
       <c r="S129" t="n">
         <v>4</v>
@@ -14161,7 +14166,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14171,7 +14176,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14198,10 +14203,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125635162</v>
+        <v>125632345</v>
       </c>
       <c r="B130" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14209,37 +14214,37 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>522010</v>
+        <v>522244</v>
       </c>
       <c r="R130" t="n">
-        <v>6936407</v>
+        <v>6936537</v>
       </c>
       <c r="S130" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14263,12 +14268,22 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14283,60 +14298,60 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125632408</v>
+        <v>125635162</v>
       </c>
       <c r="B131" t="n">
-        <v>98368</v>
+        <v>79590</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219874</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>522057</v>
+        <v>522010</v>
       </c>
       <c r="R131" t="n">
-        <v>6936411</v>
+        <v>6936407</v>
       </c>
       <c r="S131" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14360,22 +14375,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>15:18</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>15:18</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14390,44 +14395,44 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125632395</v>
+        <v>125632408</v>
       </c>
       <c r="B132" t="n">
-        <v>98334</v>
+        <v>98372</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14437,10 +14442,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>522113</v>
+        <v>522057</v>
       </c>
       <c r="R132" t="n">
-        <v>6936367</v>
+        <v>6936411</v>
       </c>
       <c r="S132" t="n">
         <v>4</v>
@@ -14472,7 +14477,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14482,7 +14487,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14509,10 +14514,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125632388</v>
+        <v>125632395</v>
       </c>
       <c r="B133" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14544,10 +14549,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>522190</v>
+        <v>522113</v>
       </c>
       <c r="R133" t="n">
-        <v>6936390</v>
+        <v>6936367</v>
       </c>
       <c r="S133" t="n">
         <v>4</v>
@@ -14579,7 +14584,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14589,7 +14594,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14616,32 +14621,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125601077</v>
+        <v>125632388</v>
       </c>
       <c r="B134" t="n">
-        <v>80072</v>
+        <v>98338</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14651,13 +14656,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>522217</v>
+        <v>522190</v>
       </c>
       <c r="R134" t="n">
-        <v>6936540</v>
+        <v>6936390</v>
       </c>
       <c r="S134" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14684,11 +14689,21 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
@@ -14697,63 +14712,48 @@
       </c>
       <c r="AG134" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ134" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125632407</v>
+        <v>125632334</v>
       </c>
       <c r="B135" t="n">
-        <v>91228</v>
+        <v>80104</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14763,10 +14763,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>522052</v>
+        <v>522239</v>
       </c>
       <c r="R135" t="n">
-        <v>6936413</v>
+        <v>6936600</v>
       </c>
       <c r="S135" t="n">
         <v>4</v>
@@ -14798,7 +14798,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14808,7 +14808,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14835,32 +14835,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125632334</v>
+        <v>125632407</v>
       </c>
       <c r="B136" t="n">
-        <v>80100</v>
+        <v>91232</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14870,10 +14870,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>522239</v>
+        <v>522052</v>
       </c>
       <c r="R136" t="n">
-        <v>6936600</v>
+        <v>6936413</v>
       </c>
       <c r="S136" t="n">
         <v>4</v>
@@ -14905,7 +14905,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14945,7 +14945,7 @@
         <v>125633219</v>
       </c>
       <c r="B137" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125632352</v>
+        <v>125632373</v>
       </c>
       <c r="B138" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15084,10 +15084,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>522245</v>
+        <v>522236</v>
       </c>
       <c r="R138" t="n">
-        <v>6936497</v>
+        <v>6936449</v>
       </c>
       <c r="S138" t="n">
         <v>4</v>
@@ -15119,7 +15119,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15156,10 +15156,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125632359</v>
+        <v>125632352</v>
       </c>
       <c r="B139" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15191,10 +15191,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>522236</v>
+        <v>522245</v>
       </c>
       <c r="R139" t="n">
-        <v>6936482</v>
+        <v>6936497</v>
       </c>
       <c r="S139" t="n">
         <v>4</v>
@@ -15226,7 +15226,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15236,7 +15236,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15263,10 +15263,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125632373</v>
+        <v>125632359</v>
       </c>
       <c r="B140" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15301,7 +15301,7 @@
         <v>522236</v>
       </c>
       <c r="R140" t="n">
-        <v>6936449</v>
+        <v>6936482</v>
       </c>
       <c r="S140" t="n">
         <v>4</v>
@@ -15333,7 +15333,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15343,7 +15343,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15373,7 +15373,7 @@
         <v>125632375</v>
       </c>
       <c r="B141" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>125633218</v>
       </c>
       <c r="B142" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>125632364</v>
       </c>
       <c r="B143" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15694,7 +15694,7 @@
         <v>125646901</v>
       </c>
       <c r="B144" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15788,48 +15788,48 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125632389</v>
+        <v>125636452</v>
       </c>
       <c r="B145" t="n">
-        <v>78968</v>
+        <v>91393</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>522188</v>
+        <v>522141</v>
       </c>
       <c r="R145" t="n">
-        <v>6936385</v>
+        <v>6936548</v>
       </c>
       <c r="S145" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15853,22 +15853,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15883,60 +15873,60 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125636452</v>
+        <v>125632389</v>
       </c>
       <c r="B146" t="n">
-        <v>91389</v>
+        <v>78972</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>522141</v>
+        <v>522188</v>
       </c>
       <c r="R146" t="n">
-        <v>6936548</v>
+        <v>6936385</v>
       </c>
       <c r="S146" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15960,12 +15950,22 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15980,44 +15980,44 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125632419</v>
+        <v>125632331</v>
       </c>
       <c r="B147" t="n">
-        <v>98334</v>
+        <v>92522</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>522202</v>
+        <v>522221</v>
       </c>
       <c r="R147" t="n">
-        <v>6936414</v>
+        <v>6936608</v>
       </c>
       <c r="S147" t="n">
         <v>4</v>
@@ -16062,7 +16062,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16072,7 +16072,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16099,32 +16099,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125632411</v>
+        <v>125632386</v>
       </c>
       <c r="B148" t="n">
-        <v>98334</v>
+        <v>56843</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16134,10 +16134,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>522063</v>
+        <v>522200</v>
       </c>
       <c r="R148" t="n">
-        <v>6936424</v>
+        <v>6936398</v>
       </c>
       <c r="S148" t="n">
         <v>4</v>
@@ -16169,7 +16169,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16179,7 +16179,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16206,10 +16206,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125646888</v>
+        <v>125632411</v>
       </c>
       <c r="B149" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16241,13 +16241,13 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>522159</v>
+        <v>522063</v>
       </c>
       <c r="R149" t="n">
-        <v>6936405</v>
+        <v>6936424</v>
       </c>
       <c r="S149" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16271,12 +16271,22 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16291,44 +16301,44 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125632366</v>
+        <v>125632419</v>
       </c>
       <c r="B150" t="n">
-        <v>98355</v>
+        <v>98338</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16338,10 +16348,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>522249</v>
+        <v>522202</v>
       </c>
       <c r="R150" t="n">
-        <v>6936460</v>
+        <v>6936414</v>
       </c>
       <c r="S150" t="n">
         <v>4</v>
@@ -16373,7 +16383,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16383,7 +16393,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16410,32 +16420,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125632384</v>
+        <v>125646888</v>
       </c>
       <c r="B151" t="n">
-        <v>98355</v>
+        <v>98338</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16445,13 +16455,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>522207</v>
+        <v>522159</v>
       </c>
       <c r="R151" t="n">
-        <v>6936406</v>
+        <v>6936405</v>
       </c>
       <c r="S151" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16475,22 +16485,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>14:32</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>14:32</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16505,22 +16505,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125632331</v>
+        <v>125632366</v>
       </c>
       <c r="B152" t="n">
-        <v>92518</v>
+        <v>98359</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16528,21 +16528,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>4364</v>
+        <v>221952</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16552,10 +16552,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>522221</v>
+        <v>522249</v>
       </c>
       <c r="R152" t="n">
-        <v>6936608</v>
+        <v>6936460</v>
       </c>
       <c r="S152" t="n">
         <v>4</v>
@@ -16587,7 +16587,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16597,7 +16597,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16624,10 +16624,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125632386</v>
+        <v>125632384</v>
       </c>
       <c r="B153" t="n">
-        <v>56843</v>
+        <v>98359</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16635,21 +16635,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16659,10 +16659,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>522200</v>
+        <v>522207</v>
       </c>
       <c r="R153" t="n">
-        <v>6936398</v>
+        <v>6936406</v>
       </c>
       <c r="S153" t="n">
         <v>4</v>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16704,7 +16704,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16841,7 +16841,7 @@
         <v>125635540</v>
       </c>
       <c r="B155" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         <v>125632393</v>
       </c>
       <c r="B156" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17042,32 +17042,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125632343</v>
+        <v>125646899</v>
       </c>
       <c r="B157" t="n">
-        <v>78968</v>
+        <v>91393</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17077,13 +17077,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>522269</v>
+        <v>522143</v>
       </c>
       <c r="R157" t="n">
-        <v>6936560</v>
+        <v>6936554</v>
       </c>
       <c r="S157" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17107,22 +17107,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>13:32</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>13:32</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17137,44 +17127,44 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125646899</v>
+        <v>125632343</v>
       </c>
       <c r="B158" t="n">
-        <v>91389</v>
+        <v>78972</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17184,13 +17174,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>522143</v>
+        <v>522269</v>
       </c>
       <c r="R158" t="n">
-        <v>6936554</v>
+        <v>6936560</v>
       </c>
       <c r="S158" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17214,12 +17204,22 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17234,12 +17234,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
@@ -17249,7 +17249,7 @@
         <v>125632327</v>
       </c>
       <c r="B159" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>

--- a/artfynd/A 26476-2025 artfynd.xlsx
+++ b/artfynd/A 26476-2025 artfynd.xlsx
@@ -2414,10 +2414,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125619776</v>
+        <v>125619969</v>
       </c>
       <c r="B16" t="n">
-        <v>78731</v>
+        <v>80075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>521964</v>
+        <v>522066</v>
       </c>
       <c r="R16" t="n">
-        <v>6936664</v>
+        <v>6936575</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2515,10 +2515,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125619969</v>
+        <v>125619776</v>
       </c>
       <c r="B17" t="n">
-        <v>80075</v>
+        <v>78731</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2526,21 +2526,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>522066</v>
+        <v>521964</v>
       </c>
       <c r="R17" t="n">
-        <v>6936575</v>
+        <v>6936664</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2925,32 +2925,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125632425</v>
+        <v>125601606</v>
       </c>
       <c r="B21" t="n">
-        <v>78972</v>
+        <v>98338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2960,13 +2960,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>522345</v>
+        <v>522217</v>
       </c>
       <c r="R21" t="n">
-        <v>6936464</v>
+        <v>6936540</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2993,19 +2993,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3020,19 +3010,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125601606</v>
+        <v>125632421</v>
       </c>
       <c r="B22" t="n">
         <v>98338</v>
@@ -3067,13 +3057,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>522217</v>
+        <v>522260</v>
       </c>
       <c r="R22" t="n">
-        <v>6936540</v>
+        <v>6936447</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3100,9 +3090,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3117,19 +3117,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125632421</v>
+        <v>125632569</v>
       </c>
       <c r="B23" t="n">
         <v>98338</v>
@@ -3160,17 +3160,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>522260</v>
+        <v>522108</v>
       </c>
       <c r="R23" t="n">
-        <v>6936447</v>
+        <v>6936467</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3194,22 +3194,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3224,60 +3214,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125632569</v>
+        <v>125646875</v>
       </c>
       <c r="B24" t="n">
-        <v>98338</v>
+        <v>78731</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>522108</v>
+        <v>522035</v>
       </c>
       <c r="R24" t="n">
-        <v>6936467</v>
+        <v>6936550</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3333,10 +3323,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125646874</v>
+        <v>125646902</v>
       </c>
       <c r="B25" t="n">
-        <v>80103</v>
+        <v>4869</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3344,21 +3334,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6461</v>
+        <v>101675</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3368,10 +3358,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>522022</v>
+        <v>522019</v>
       </c>
       <c r="R25" t="n">
-        <v>6936611</v>
+        <v>6936608</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3404,6 +3394,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Kläckhål på asp</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3430,10 +3425,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125646902</v>
+        <v>125602968</v>
       </c>
       <c r="B26" t="n">
-        <v>4869</v>
+        <v>98359</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3441,21 +3436,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>101675</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3465,13 +3460,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>522019</v>
+        <v>522217</v>
       </c>
       <c r="R26" t="n">
-        <v>6936608</v>
+        <v>6936540</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3495,17 +3490,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Kläckhål på asp</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3520,22 +3510,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125602968</v>
+        <v>125646874</v>
       </c>
       <c r="B27" t="n">
-        <v>98359</v>
+        <v>80103</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3543,21 +3533,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3567,13 +3557,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>522217</v>
+        <v>522022</v>
       </c>
       <c r="R27" t="n">
-        <v>6936540</v>
+        <v>6936611</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3597,12 +3587,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3617,22 +3607,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125646875</v>
+        <v>125632425</v>
       </c>
       <c r="B28" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,21 +3630,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3664,13 +3654,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>522035</v>
+        <v>522345</v>
       </c>
       <c r="R28" t="n">
-        <v>6936550</v>
+        <v>6936464</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3694,12 +3684,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3714,12 +3714,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -5684,32 +5684,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125632382</v>
+        <v>125600818</v>
       </c>
       <c r="B48" t="n">
-        <v>98338</v>
+        <v>98255</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5719,13 +5719,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>522214</v>
+        <v>522217</v>
       </c>
       <c r="R48" t="n">
-        <v>6936414</v>
+        <v>6936540</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5752,19 +5752,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5779,19 +5769,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125646883</v>
+        <v>125632382</v>
       </c>
       <c r="B49" t="n">
         <v>98338</v>
@@ -5826,13 +5816,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>522097</v>
+        <v>522214</v>
       </c>
       <c r="R49" t="n">
-        <v>6936427</v>
+        <v>6936414</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5856,12 +5846,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5876,19 +5876,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125638972</v>
+        <v>125646883</v>
       </c>
       <c r="B50" t="n">
         <v>98338</v>
@@ -5919,17 +5919,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>522318</v>
+        <v>522097</v>
       </c>
       <c r="R50" t="n">
-        <v>6936398</v>
+        <v>6936427</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5985,48 +5985,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125632416</v>
+        <v>125638972</v>
       </c>
       <c r="B51" t="n">
-        <v>91250</v>
+        <v>98338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>522125</v>
+        <v>522318</v>
       </c>
       <c r="R51" t="n">
-        <v>6936430</v>
+        <v>6936398</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6050,22 +6050,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>15:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>15:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6080,44 +6070,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125600818</v>
+        <v>125632416</v>
       </c>
       <c r="B52" t="n">
-        <v>98255</v>
+        <v>91250</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219790</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6127,13 +6117,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>522217</v>
+        <v>522125</v>
       </c>
       <c r="R52" t="n">
-        <v>6936540</v>
+        <v>6936430</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6160,9 +6150,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6177,12 +6177,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -7734,32 +7734,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125632422</v>
+        <v>125632396</v>
       </c>
       <c r="B68" t="n">
-        <v>92522</v>
+        <v>98338</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7769,10 +7769,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>522263</v>
+        <v>522109</v>
       </c>
       <c r="R68" t="n">
-        <v>6936447</v>
+        <v>6936384</v>
       </c>
       <c r="S68" t="n">
         <v>4</v>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7948,32 +7948,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125632396</v>
+        <v>125632422</v>
       </c>
       <c r="B70" t="n">
-        <v>98338</v>
+        <v>92522</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7983,10 +7983,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>522109</v>
+        <v>522263</v>
       </c>
       <c r="R70" t="n">
-        <v>6936384</v>
+        <v>6936447</v>
       </c>
       <c r="S70" t="n">
         <v>4</v>
@@ -8018,7 +8018,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8055,32 +8055,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125632350</v>
+        <v>125632381</v>
       </c>
       <c r="B71" t="n">
-        <v>80075</v>
+        <v>98338</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8090,10 +8090,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>522254</v>
+        <v>522240</v>
       </c>
       <c r="R71" t="n">
-        <v>6936496</v>
+        <v>6936412</v>
       </c>
       <c r="S71" t="n">
         <v>4</v>
@@ -8125,7 +8125,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8162,32 +8162,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125646879</v>
+        <v>125632418</v>
       </c>
       <c r="B72" t="n">
-        <v>80075</v>
+        <v>98338</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8197,13 +8197,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>522202</v>
+        <v>522162</v>
       </c>
       <c r="R72" t="n">
-        <v>6936502</v>
+        <v>6936404</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8227,12 +8227,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8247,44 +8257,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125632357</v>
+        <v>125632370</v>
       </c>
       <c r="B73" t="n">
-        <v>91232</v>
+        <v>98338</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8294,10 +8304,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>522221</v>
+        <v>522243</v>
       </c>
       <c r="R73" t="n">
-        <v>6936489</v>
+        <v>6936456</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -8329,7 +8339,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8339,7 +8349,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8366,10 +8376,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125646872</v>
+        <v>125632372</v>
       </c>
       <c r="B74" t="n">
-        <v>91197</v>
+        <v>98359</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8377,21 +8387,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8401,13 +8411,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>522064</v>
+        <v>522236</v>
       </c>
       <c r="R74" t="n">
-        <v>6936505</v>
+        <v>6936448</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8431,12 +8441,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8451,44 +8471,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125632381</v>
+        <v>125632350</v>
       </c>
       <c r="B75" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8498,10 +8518,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>522240</v>
+        <v>522254</v>
       </c>
       <c r="R75" t="n">
-        <v>6936412</v>
+        <v>6936496</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -8533,7 +8553,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8543,7 +8563,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8570,32 +8590,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125632418</v>
+        <v>125646879</v>
       </c>
       <c r="B76" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8605,13 +8625,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>522162</v>
+        <v>522202</v>
       </c>
       <c r="R76" t="n">
-        <v>6936404</v>
+        <v>6936502</v>
       </c>
       <c r="S76" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8635,22 +8655,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>15:34</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>15:34</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8665,44 +8675,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125632372</v>
+        <v>125632357</v>
       </c>
       <c r="B77" t="n">
-        <v>98359</v>
+        <v>91232</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8712,10 +8722,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>522236</v>
+        <v>522221</v>
       </c>
       <c r="R77" t="n">
-        <v>6936448</v>
+        <v>6936489</v>
       </c>
       <c r="S77" t="n">
         <v>4</v>
@@ -8747,7 +8757,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8757,7 +8767,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8784,32 +8794,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125632370</v>
+        <v>125646872</v>
       </c>
       <c r="B78" t="n">
-        <v>98338</v>
+        <v>91197</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8819,13 +8829,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>522243</v>
+        <v>522064</v>
       </c>
       <c r="R78" t="n">
-        <v>6936456</v>
+        <v>6936505</v>
       </c>
       <c r="S78" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8849,22 +8859,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>14:17</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>14:17</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8879,12 +8879,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9834,48 +9834,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125646882</v>
+        <v>125635192</v>
       </c>
       <c r="B88" t="n">
-        <v>98338</v>
+        <v>92522</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>522029</v>
+        <v>522003</v>
       </c>
       <c r="R88" t="n">
-        <v>6936561</v>
+        <v>6936451</v>
       </c>
       <c r="S88" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9931,32 +9931,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125635192</v>
+        <v>125637200</v>
       </c>
       <c r="B89" t="n">
-        <v>92522</v>
+        <v>78972</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9966,10 +9966,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>522003</v>
+        <v>522362</v>
       </c>
       <c r="R89" t="n">
-        <v>6936451</v>
+        <v>6936466</v>
       </c>
       <c r="S89" t="n">
         <v>20</v>
@@ -10028,48 +10028,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125637200</v>
+        <v>125646882</v>
       </c>
       <c r="B90" t="n">
-        <v>78972</v>
+        <v>98338</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>522362</v>
+        <v>522029</v>
       </c>
       <c r="R90" t="n">
-        <v>6936466</v>
+        <v>6936561</v>
       </c>
       <c r="S90" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10334,48 +10334,53 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125632409</v>
+        <v>125633268</v>
       </c>
       <c r="B93" t="n">
-        <v>98338</v>
+        <v>57811</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>522062</v>
+        <v>522121</v>
       </c>
       <c r="R93" t="n">
-        <v>6936422</v>
+        <v>6936402</v>
       </c>
       <c r="S93" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10399,22 +10404,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10429,19 +10424,19 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125632415</v>
+        <v>125632409</v>
       </c>
       <c r="B94" t="n">
         <v>98338</v>
@@ -10476,10 +10471,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>522124</v>
+        <v>522062</v>
       </c>
       <c r="R94" t="n">
-        <v>6936410</v>
+        <v>6936422</v>
       </c>
       <c r="S94" t="n">
         <v>4</v>
@@ -10511,7 +10506,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10521,7 +10516,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10548,32 +10543,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125632358</v>
+        <v>125632415</v>
       </c>
       <c r="B95" t="n">
-        <v>98359</v>
+        <v>98338</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10583,10 +10578,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>522231</v>
+        <v>522124</v>
       </c>
       <c r="R95" t="n">
-        <v>6936488</v>
+        <v>6936410</v>
       </c>
       <c r="S95" t="n">
         <v>4</v>
@@ -10618,7 +10613,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10628,7 +10623,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10655,53 +10650,48 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125633268</v>
+        <v>125632358</v>
       </c>
       <c r="B96" t="n">
-        <v>57811</v>
+        <v>98359</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>522121</v>
+        <v>522231</v>
       </c>
       <c r="R96" t="n">
-        <v>6936402</v>
+        <v>6936488</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10725,12 +10715,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10745,12 +10745,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -11573,10 +11573,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125632323</v>
+        <v>125632390</v>
       </c>
       <c r="B105" t="n">
-        <v>78972</v>
+        <v>91232</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11584,21 +11584,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11608,10 +11608,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>522189</v>
+        <v>522187</v>
       </c>
       <c r="R105" t="n">
-        <v>6936648</v>
+        <v>6936377</v>
       </c>
       <c r="S105" t="n">
         <v>4</v>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11653,7 +11653,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11680,10 +11680,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125632325</v>
+        <v>125632323</v>
       </c>
       <c r="B106" t="n">
-        <v>78730</v>
+        <v>78972</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11691,21 +11691,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11715,13 +11715,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>522198</v>
+        <v>522189</v>
       </c>
       <c r="R106" t="n">
-        <v>6936620</v>
+        <v>6936648</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11787,10 +11787,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125632330</v>
+        <v>125632325</v>
       </c>
       <c r="B107" t="n">
-        <v>78972</v>
+        <v>78730</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11798,37 +11798,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>522172</v>
+        <v>522198</v>
       </c>
       <c r="R107" t="n">
-        <v>6936483</v>
+        <v>6936620</v>
       </c>
       <c r="S107" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11852,12 +11852,22 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11872,60 +11882,60 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125632379</v>
+        <v>125632330</v>
       </c>
       <c r="B108" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>522237</v>
+        <v>522172</v>
       </c>
       <c r="R108" t="n">
-        <v>6936415</v>
+        <v>6936483</v>
       </c>
       <c r="S108" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11949,22 +11959,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>14:26</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>14:26</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11979,12 +11979,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -12409,32 +12409,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125632390</v>
+        <v>125632379</v>
       </c>
       <c r="B113" t="n">
-        <v>91232</v>
+        <v>98338</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12444,10 +12444,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>522187</v>
+        <v>522237</v>
       </c>
       <c r="R113" t="n">
-        <v>6936377</v>
+        <v>6936415</v>
       </c>
       <c r="S113" t="n">
         <v>4</v>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14407,32 +14407,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125632408</v>
+        <v>125632395</v>
       </c>
       <c r="B132" t="n">
-        <v>98372</v>
+        <v>98338</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14442,10 +14442,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>522057</v>
+        <v>522113</v>
       </c>
       <c r="R132" t="n">
-        <v>6936411</v>
+        <v>6936367</v>
       </c>
       <c r="S132" t="n">
         <v>4</v>
@@ -14477,7 +14477,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14514,7 +14514,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125632395</v>
+        <v>125632388</v>
       </c>
       <c r="B133" t="n">
         <v>98338</v>
@@ -14549,10 +14549,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>522113</v>
+        <v>522190</v>
       </c>
       <c r="R133" t="n">
-        <v>6936367</v>
+        <v>6936390</v>
       </c>
       <c r="S133" t="n">
         <v>4</v>
@@ -14584,7 +14584,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14621,32 +14621,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125632388</v>
+        <v>125632408</v>
       </c>
       <c r="B134" t="n">
-        <v>98338</v>
+        <v>98372</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14656,10 +14656,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>522190</v>
+        <v>522057</v>
       </c>
       <c r="R134" t="n">
-        <v>6936390</v>
+        <v>6936411</v>
       </c>
       <c r="S134" t="n">
         <v>4</v>
@@ -14691,7 +14691,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14701,7 +14701,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16731,32 +16731,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125632376</v>
+        <v>125646899</v>
       </c>
       <c r="B154" t="n">
-        <v>56843</v>
+        <v>91393</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100138</v>
+        <v>1503</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16766,13 +16766,13 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>522237</v>
+        <v>522143</v>
       </c>
       <c r="R154" t="n">
-        <v>6936423</v>
+        <v>6936554</v>
       </c>
       <c r="S154" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16796,22 +16796,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16826,60 +16816,60 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125635540</v>
+        <v>125632376</v>
       </c>
       <c r="B155" t="n">
-        <v>98338</v>
+        <v>56843</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>522055</v>
+        <v>522237</v>
       </c>
       <c r="R155" t="n">
-        <v>6936516</v>
+        <v>6936423</v>
       </c>
       <c r="S155" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16903,12 +16893,22 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16923,44 +16923,44 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125632393</v>
+        <v>125632327</v>
       </c>
       <c r="B156" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16970,10 +16970,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>522160</v>
+        <v>522218</v>
       </c>
       <c r="R156" t="n">
-        <v>6936368</v>
+        <v>6936625</v>
       </c>
       <c r="S156" t="n">
         <v>4</v>
@@ -17005,7 +17005,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17015,7 +17015,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17042,32 +17042,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125646899</v>
+        <v>125632343</v>
       </c>
       <c r="B157" t="n">
-        <v>91393</v>
+        <v>78972</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17077,13 +17077,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>522143</v>
+        <v>522269</v>
       </c>
       <c r="R157" t="n">
-        <v>6936554</v>
+        <v>6936560</v>
       </c>
       <c r="S157" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17107,12 +17107,22 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17127,44 +17137,44 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125632343</v>
+        <v>125632393</v>
       </c>
       <c r="B158" t="n">
-        <v>78972</v>
+        <v>98338</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17174,10 +17184,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>522269</v>
+        <v>522160</v>
       </c>
       <c r="R158" t="n">
-        <v>6936560</v>
+        <v>6936368</v>
       </c>
       <c r="S158" t="n">
         <v>4</v>
@@ -17209,7 +17219,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17219,7 +17229,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17246,48 +17256,48 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125632327</v>
+        <v>125635540</v>
       </c>
       <c r="B159" t="n">
-        <v>80075</v>
+        <v>98338</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>522218</v>
+        <v>522055</v>
       </c>
       <c r="R159" t="n">
-        <v>6936625</v>
+        <v>6936516</v>
       </c>
       <c r="S159" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17311,22 +17321,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>13:03</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>13:03</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17341,12 +17341,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>

--- a/artfynd/A 26476-2025 artfynd.xlsx
+++ b/artfynd/A 26476-2025 artfynd.xlsx
@@ -2925,32 +2925,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125601606</v>
+        <v>125646874</v>
       </c>
       <c r="B21" t="n">
-        <v>98338</v>
+        <v>80103</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2960,13 +2960,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>522217</v>
+        <v>522022</v>
       </c>
       <c r="R21" t="n">
-        <v>6936540</v>
+        <v>6936611</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2990,12 +2990,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3010,44 +3010,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125632421</v>
+        <v>125632425</v>
       </c>
       <c r="B22" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>522260</v>
+        <v>522345</v>
       </c>
       <c r="R22" t="n">
-        <v>6936447</v>
+        <v>6936464</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3129,48 +3129,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125632569</v>
+        <v>125602968</v>
       </c>
       <c r="B23" t="n">
-        <v>98338</v>
+        <v>98360</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>522108</v>
+        <v>522217</v>
       </c>
       <c r="R23" t="n">
-        <v>6936467</v>
+        <v>6936540</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3194,12 +3194,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3214,44 +3214,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125646875</v>
+        <v>125646902</v>
       </c>
       <c r="B24" t="n">
-        <v>78731</v>
+        <v>4869</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>101675</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>522035</v>
+        <v>522019</v>
       </c>
       <c r="R24" t="n">
-        <v>6936550</v>
+        <v>6936608</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3297,6 +3297,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Kläckhål på asp</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3323,32 +3328,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125646902</v>
+        <v>125601310</v>
       </c>
       <c r="B25" t="n">
-        <v>4869</v>
+        <v>98339</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>101675</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3358,13 +3363,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>522019</v>
+        <v>522217</v>
       </c>
       <c r="R25" t="n">
-        <v>6936608</v>
+        <v>6936540</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3388,17 +3393,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Kläckhål på asp</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3413,44 +3413,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125602968</v>
+        <v>125632421</v>
       </c>
       <c r="B26" t="n">
-        <v>98359</v>
+        <v>98339</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3460,13 +3460,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>522217</v>
+        <v>522260</v>
       </c>
       <c r="R26" t="n">
-        <v>6936540</v>
+        <v>6936447</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3493,9 +3493,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3510,60 +3520,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125646874</v>
+        <v>125632569</v>
       </c>
       <c r="B27" t="n">
-        <v>80103</v>
+        <v>98339</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>522022</v>
+        <v>522108</v>
       </c>
       <c r="R27" t="n">
-        <v>6936611</v>
+        <v>6936467</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3619,10 +3629,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125632425</v>
+        <v>125646875</v>
       </c>
       <c r="B28" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3630,21 +3640,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3654,13 +3664,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>522345</v>
+        <v>522035</v>
       </c>
       <c r="R28" t="n">
-        <v>6936464</v>
+        <v>6936550</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3684,22 +3694,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3714,44 +3714,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125632349</v>
+        <v>125632332</v>
       </c>
       <c r="B29" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3761,13 +3761,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>522259</v>
+        <v>522239</v>
       </c>
       <c r="R29" t="n">
-        <v>6936489</v>
+        <v>6936598</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3833,48 +3833,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125636837</v>
+        <v>125600959</v>
       </c>
       <c r="B30" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>522164</v>
+        <v>522217</v>
       </c>
       <c r="R30" t="n">
-        <v>6936587</v>
+        <v>6936540</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3898,12 +3898,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3914,26 +3914,41 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125603562</v>
+        <v>125600280</v>
       </c>
       <c r="B31" t="n">
-        <v>80035</v>
+        <v>92522</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3941,21 +3956,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4027,32 +4042,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125632367</v>
+        <v>125601890</v>
       </c>
       <c r="B32" t="n">
-        <v>98359</v>
+        <v>91686</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4062,13 +4077,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>522247</v>
+        <v>522217</v>
       </c>
       <c r="R32" t="n">
-        <v>6936458</v>
+        <v>6936540</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4095,19 +4110,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4122,44 +4127,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125634580</v>
+        <v>125636837</v>
       </c>
       <c r="B33" t="n">
-        <v>98359</v>
+        <v>98339</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4169,10 +4174,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>522044</v>
+        <v>522164</v>
       </c>
       <c r="R33" t="n">
-        <v>6936401</v>
+        <v>6936587</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4231,32 +4236,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125600280</v>
+        <v>125632349</v>
       </c>
       <c r="B34" t="n">
-        <v>92522</v>
+        <v>98339</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4266,13 +4271,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>522217</v>
+        <v>522259</v>
       </c>
       <c r="R34" t="n">
-        <v>6936540</v>
+        <v>6936489</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4299,9 +4304,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4316,44 +4331,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125600959</v>
+        <v>125603562</v>
       </c>
       <c r="B35" t="n">
-        <v>80075</v>
+        <v>80035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4409,21 +4424,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4440,48 +4440,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125601890</v>
+        <v>125634580</v>
       </c>
       <c r="B36" t="n">
-        <v>91686</v>
+        <v>98360</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>221952</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>522217</v>
+        <v>522044</v>
       </c>
       <c r="R36" t="n">
-        <v>6936540</v>
+        <v>6936401</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4505,12 +4505,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4525,44 +4525,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125632332</v>
+        <v>125632367</v>
       </c>
       <c r="B37" t="n">
-        <v>78972</v>
+        <v>98360</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4572,13 +4572,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>522239</v>
+        <v>522247</v>
       </c>
       <c r="R37" t="n">
-        <v>6936598</v>
+        <v>6936458</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4644,32 +4644,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125632353</v>
+        <v>125632337</v>
       </c>
       <c r="B38" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4679,10 +4679,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>522241</v>
+        <v>522224</v>
       </c>
       <c r="R38" t="n">
-        <v>6936509</v>
+        <v>6936572</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4751,32 +4751,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125646892</v>
+        <v>125632329</v>
       </c>
       <c r="B39" t="n">
-        <v>98338</v>
+        <v>80104</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4786,13 +4786,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>522130</v>
+        <v>522215</v>
       </c>
       <c r="R39" t="n">
-        <v>6936481</v>
+        <v>6936627</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4816,12 +4816,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4836,44 +4846,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125646893</v>
+        <v>125632362</v>
       </c>
       <c r="B40" t="n">
-        <v>98338</v>
+        <v>78730</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4883,13 +4893,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>522204</v>
+        <v>522249</v>
       </c>
       <c r="R40" t="n">
-        <v>6936495</v>
+        <v>6936486</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4913,12 +4923,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4933,22 +4953,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125632401</v>
+        <v>125632338</v>
       </c>
       <c r="B41" t="n">
-        <v>100520</v>
+        <v>92522</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4956,21 +4976,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4980,10 +5000,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>522046</v>
+        <v>522221</v>
       </c>
       <c r="R41" t="n">
-        <v>6936397</v>
+        <v>6936572</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5015,7 +5035,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5025,7 +5045,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5052,7 +5072,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125632338</v>
+        <v>125636088</v>
       </c>
       <c r="B42" t="n">
         <v>92522</v>
@@ -5083,17 +5103,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>522221</v>
+        <v>522049</v>
       </c>
       <c r="R42" t="n">
-        <v>6936572</v>
+        <v>6936650</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5117,22 +5137,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5147,22 +5157,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125636088</v>
+        <v>125632401</v>
       </c>
       <c r="B43" t="n">
-        <v>92522</v>
+        <v>100521</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5170,37 +5180,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>522049</v>
+        <v>522046</v>
       </c>
       <c r="R43" t="n">
-        <v>6936650</v>
+        <v>6936397</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5224,12 +5234,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5244,44 +5264,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125632337</v>
+        <v>125632353</v>
       </c>
       <c r="B44" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5291,10 +5311,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>522224</v>
+        <v>522241</v>
       </c>
       <c r="R44" t="n">
-        <v>6936572</v>
+        <v>6936509</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5326,7 +5346,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5336,7 +5356,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5363,32 +5383,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125632362</v>
+        <v>125646893</v>
       </c>
       <c r="B45" t="n">
-        <v>78730</v>
+        <v>98339</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5398,13 +5418,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>522249</v>
+        <v>522204</v>
       </c>
       <c r="R45" t="n">
-        <v>6936486</v>
+        <v>6936495</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5428,22 +5448,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5458,44 +5468,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125632329</v>
+        <v>125646892</v>
       </c>
       <c r="B46" t="n">
-        <v>80104</v>
+        <v>98339</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5505,13 +5515,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>522215</v>
+        <v>522130</v>
       </c>
       <c r="R46" t="n">
-        <v>6936627</v>
+        <v>6936481</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5535,22 +5545,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:04</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:04</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5565,12 +5565,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5580,7 +5580,7 @@
         <v>125632368</v>
       </c>
       <c r="B47" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5684,32 +5684,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125600818</v>
+        <v>125632416</v>
       </c>
       <c r="B48" t="n">
-        <v>98255</v>
+        <v>91250</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5719,13 +5719,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>522217</v>
+        <v>522125</v>
       </c>
       <c r="R48" t="n">
-        <v>6936540</v>
+        <v>6936430</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5752,9 +5752,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5769,44 +5779,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125632382</v>
+        <v>125600818</v>
       </c>
       <c r="B49" t="n">
-        <v>98338</v>
+        <v>98256</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5816,13 +5826,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>522214</v>
+        <v>522217</v>
       </c>
       <c r="R49" t="n">
-        <v>6936414</v>
+        <v>6936540</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5849,19 +5859,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5876,22 +5876,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125646883</v>
+        <v>125632382</v>
       </c>
       <c r="B50" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>522097</v>
+        <v>522214</v>
       </c>
       <c r="R50" t="n">
-        <v>6936427</v>
+        <v>6936414</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5953,12 +5953,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5973,22 +5983,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125638972</v>
+        <v>125646883</v>
       </c>
       <c r="B51" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6016,17 +6026,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>522318</v>
+        <v>522097</v>
       </c>
       <c r="R51" t="n">
-        <v>6936398</v>
+        <v>6936427</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6082,48 +6092,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125632416</v>
+        <v>125638972</v>
       </c>
       <c r="B52" t="n">
-        <v>91250</v>
+        <v>98339</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>522125</v>
+        <v>522318</v>
       </c>
       <c r="R52" t="n">
-        <v>6936430</v>
+        <v>6936398</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6147,22 +6157,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6177,44 +6177,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125632815</v>
+        <v>125637287</v>
       </c>
       <c r="B53" t="n">
-        <v>98359</v>
+        <v>79590</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6224,10 +6224,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>522129</v>
+        <v>522356</v>
       </c>
       <c r="R53" t="n">
-        <v>6936436</v>
+        <v>6936466</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6286,48 +6286,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125632397</v>
+        <v>125637245</v>
       </c>
       <c r="B54" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>522077</v>
+        <v>522360</v>
       </c>
       <c r="R54" t="n">
-        <v>6936379</v>
+        <v>6936453</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6351,22 +6351,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6381,60 +6371,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125636925</v>
+        <v>125632336</v>
       </c>
       <c r="B55" t="n">
-        <v>98338</v>
+        <v>78730</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>522220</v>
+        <v>522224</v>
       </c>
       <c r="R55" t="n">
-        <v>6936601</v>
+        <v>6936572</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6458,12 +6448,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6478,22 +6478,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125637245</v>
+        <v>125632400</v>
       </c>
       <c r="B56" t="n">
-        <v>80075</v>
+        <v>91232</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6501,37 +6501,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>522360</v>
+        <v>522048</v>
       </c>
       <c r="R56" t="n">
-        <v>6936453</v>
+        <v>6936403</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6555,12 +6555,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6575,44 +6585,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125632400</v>
+        <v>125632397</v>
       </c>
       <c r="B57" t="n">
-        <v>91232</v>
+        <v>98339</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6622,10 +6632,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>522048</v>
+        <v>522077</v>
       </c>
       <c r="R57" t="n">
-        <v>6936403</v>
+        <v>6936379</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6657,7 +6667,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6667,7 +6677,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6694,32 +6704,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125637287</v>
+        <v>125636925</v>
       </c>
       <c r="B58" t="n">
-        <v>79590</v>
+        <v>98339</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6729,13 +6739,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>522356</v>
+        <v>522220</v>
       </c>
       <c r="R58" t="n">
-        <v>6936466</v>
+        <v>6936601</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6791,48 +6801,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125632336</v>
+        <v>125632815</v>
       </c>
       <c r="B59" t="n">
-        <v>78730</v>
+        <v>98360</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>522224</v>
+        <v>522129</v>
       </c>
       <c r="R59" t="n">
-        <v>6936572</v>
+        <v>6936436</v>
       </c>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6856,22 +6866,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>13:25</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>13:25</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6886,22 +6886,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125646891</v>
+        <v>125632392</v>
       </c>
       <c r="B60" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6933,13 +6933,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>522159</v>
+        <v>522181</v>
       </c>
       <c r="R60" t="n">
-        <v>6936408</v>
+        <v>6936381</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6963,12 +6963,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6983,22 +6993,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125632392</v>
+        <v>125632354</v>
       </c>
       <c r="B61" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7030,10 +7040,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>522181</v>
+        <v>522234</v>
       </c>
       <c r="R61" t="n">
-        <v>6936381</v>
+        <v>6936499</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -7065,7 +7075,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7075,7 +7085,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7102,10 +7112,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125632398</v>
+        <v>125646887</v>
       </c>
       <c r="B62" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7137,13 +7147,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>522059</v>
+        <v>522185</v>
       </c>
       <c r="R62" t="n">
-        <v>6936399</v>
+        <v>6936414</v>
       </c>
       <c r="S62" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7167,22 +7177,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>15:05</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>15:05</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7197,22 +7197,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125632354</v>
+        <v>125632398</v>
       </c>
       <c r="B63" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>522234</v>
+        <v>522059</v>
       </c>
       <c r="R63" t="n">
-        <v>6936499</v>
+        <v>6936399</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7316,10 +7316,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125646887</v>
+        <v>125646891</v>
       </c>
       <c r="B64" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7351,10 +7351,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>522185</v>
+        <v>522159</v>
       </c>
       <c r="R64" t="n">
-        <v>6936414</v>
+        <v>6936408</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7413,32 +7413,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125632410</v>
+        <v>125632356</v>
       </c>
       <c r="B65" t="n">
-        <v>92522</v>
+        <v>78972</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>522063</v>
+        <v>522233</v>
       </c>
       <c r="R65" t="n">
-        <v>6936423</v>
+        <v>6936499</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7520,7 +7520,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125632324</v>
+        <v>125632410</v>
       </c>
       <c r="B66" t="n">
         <v>92522</v>
@@ -7555,10 +7555,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>522198</v>
+        <v>522063</v>
       </c>
       <c r="R66" t="n">
-        <v>6936634</v>
+        <v>6936423</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7627,32 +7627,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125632356</v>
+        <v>125632324</v>
       </c>
       <c r="B67" t="n">
-        <v>78972</v>
+        <v>92522</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7662,10 +7662,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>522233</v>
+        <v>522198</v>
       </c>
       <c r="R67" t="n">
-        <v>6936499</v>
+        <v>6936634</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -7697,7 +7697,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7737,7 +7737,7 @@
         <v>125632396</v>
       </c>
       <c r="B68" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>125632361</v>
       </c>
       <c r="B69" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8055,32 +8055,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125632381</v>
+        <v>125646879</v>
       </c>
       <c r="B71" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>522240</v>
+        <v>522202</v>
       </c>
       <c r="R71" t="n">
-        <v>6936412</v>
+        <v>6936502</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8120,22 +8120,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>14:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>14:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8150,44 +8140,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125632418</v>
+        <v>125632350</v>
       </c>
       <c r="B72" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8197,10 +8187,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>522162</v>
+        <v>522254</v>
       </c>
       <c r="R72" t="n">
-        <v>6936404</v>
+        <v>6936496</v>
       </c>
       <c r="S72" t="n">
         <v>4</v>
@@ -8232,7 +8222,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8242,7 +8232,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8269,32 +8259,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125632370</v>
+        <v>125632357</v>
       </c>
       <c r="B73" t="n">
-        <v>98338</v>
+        <v>91232</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8304,10 +8294,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>522243</v>
+        <v>522221</v>
       </c>
       <c r="R73" t="n">
-        <v>6936456</v>
+        <v>6936489</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -8339,7 +8329,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8349,7 +8339,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8376,10 +8366,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125632372</v>
+        <v>125646872</v>
       </c>
       <c r="B74" t="n">
-        <v>98359</v>
+        <v>91197</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8387,21 +8377,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8411,13 +8401,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>522236</v>
+        <v>522064</v>
       </c>
       <c r="R74" t="n">
-        <v>6936448</v>
+        <v>6936505</v>
       </c>
       <c r="S74" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8441,22 +8431,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>14:19</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>14:19</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8471,44 +8451,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125632350</v>
+        <v>125632381</v>
       </c>
       <c r="B75" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8518,10 +8498,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>522254</v>
+        <v>522240</v>
       </c>
       <c r="R75" t="n">
-        <v>6936496</v>
+        <v>6936412</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -8553,7 +8533,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8563,7 +8543,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8590,32 +8570,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125646879</v>
+        <v>125632370</v>
       </c>
       <c r="B76" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8625,13 +8605,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>522202</v>
+        <v>522243</v>
       </c>
       <c r="R76" t="n">
-        <v>6936502</v>
+        <v>6936456</v>
       </c>
       <c r="S76" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8655,12 +8635,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8675,44 +8665,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125632357</v>
+        <v>125632418</v>
       </c>
       <c r="B77" t="n">
-        <v>91232</v>
+        <v>98339</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8722,10 +8712,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>522221</v>
+        <v>522162</v>
       </c>
       <c r="R77" t="n">
-        <v>6936489</v>
+        <v>6936404</v>
       </c>
       <c r="S77" t="n">
         <v>4</v>
@@ -8757,7 +8747,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8767,7 +8757,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8794,10 +8784,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125646872</v>
+        <v>125632372</v>
       </c>
       <c r="B78" t="n">
-        <v>91197</v>
+        <v>98360</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8805,21 +8795,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8829,13 +8819,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>522064</v>
+        <v>522236</v>
       </c>
       <c r="R78" t="n">
-        <v>6936505</v>
+        <v>6936448</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8859,12 +8849,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8879,12 +8879,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8894,7 +8894,7 @@
         <v>125632406</v>
       </c>
       <c r="B79" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8998,10 +8998,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125632377</v>
+        <v>125632365</v>
       </c>
       <c r="B80" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9033,10 +9033,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>522237</v>
+        <v>522249</v>
       </c>
       <c r="R80" t="n">
-        <v>6936417</v>
+        <v>6936473</v>
       </c>
       <c r="S80" t="n">
         <v>4</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9108,7 +9108,7 @@
         <v>125632387</v>
       </c>
       <c r="B81" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9212,10 +9212,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125632365</v>
+        <v>125632423</v>
       </c>
       <c r="B82" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9247,10 +9247,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>522249</v>
+        <v>522332</v>
       </c>
       <c r="R82" t="n">
-        <v>6936473</v>
+        <v>6936449</v>
       </c>
       <c r="S82" t="n">
         <v>4</v>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9322,7 +9322,7 @@
         <v>125632554</v>
       </c>
       <c r="B83" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9416,10 +9416,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125632593</v>
+        <v>125632377</v>
       </c>
       <c r="B84" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9447,17 +9447,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>522125</v>
+        <v>522237</v>
       </c>
       <c r="R84" t="n">
-        <v>6936475</v>
+        <v>6936417</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9481,12 +9481,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9501,22 +9511,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125632423</v>
+        <v>125632593</v>
       </c>
       <c r="B85" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9544,17 +9554,17 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>522332</v>
+        <v>522125</v>
       </c>
       <c r="R85" t="n">
-        <v>6936449</v>
+        <v>6936475</v>
       </c>
       <c r="S85" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9578,22 +9588,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>15:44</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>15:44</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9608,12 +9608,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9623,7 +9623,7 @@
         <v>125632420</v>
       </c>
       <c r="B86" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>125632417</v>
       </c>
       <c r="B87" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9834,48 +9834,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125635192</v>
+        <v>125646882</v>
       </c>
       <c r="B88" t="n">
-        <v>92522</v>
+        <v>98339</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>522003</v>
+        <v>522029</v>
       </c>
       <c r="R88" t="n">
-        <v>6936451</v>
+        <v>6936561</v>
       </c>
       <c r="S88" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9931,32 +9931,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125637200</v>
+        <v>125635192</v>
       </c>
       <c r="B89" t="n">
-        <v>78972</v>
+        <v>92522</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9966,10 +9966,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>522362</v>
+        <v>522003</v>
       </c>
       <c r="R89" t="n">
-        <v>6936466</v>
+        <v>6936451</v>
       </c>
       <c r="S89" t="n">
         <v>20</v>
@@ -10028,48 +10028,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125646882</v>
+        <v>125637200</v>
       </c>
       <c r="B90" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>522029</v>
+        <v>522362</v>
       </c>
       <c r="R90" t="n">
-        <v>6936561</v>
+        <v>6936466</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10125,48 +10125,53 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125632341</v>
+        <v>125633268</v>
       </c>
       <c r="B91" t="n">
-        <v>92522</v>
+        <v>57811</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>522236</v>
+        <v>522121</v>
       </c>
       <c r="R91" t="n">
-        <v>6936562</v>
+        <v>6936402</v>
       </c>
       <c r="S91" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10190,22 +10195,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10220,60 +10215,60 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125635666</v>
+        <v>125632415</v>
       </c>
       <c r="B92" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>522038</v>
+        <v>522124</v>
       </c>
       <c r="R92" t="n">
-        <v>6936535</v>
+        <v>6936410</v>
       </c>
       <c r="S92" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10297,17 +10292,22 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10322,65 +10322,60 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125633268</v>
+        <v>125632409</v>
       </c>
       <c r="B93" t="n">
-        <v>57811</v>
+        <v>98339</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>522121</v>
+        <v>522062</v>
       </c>
       <c r="R93" t="n">
-        <v>6936402</v>
+        <v>6936422</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10404,12 +10399,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10424,44 +10429,44 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125632409</v>
+        <v>125632358</v>
       </c>
       <c r="B94" t="n">
-        <v>98338</v>
+        <v>98360</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10471,10 +10476,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>522062</v>
+        <v>522231</v>
       </c>
       <c r="R94" t="n">
-        <v>6936422</v>
+        <v>6936488</v>
       </c>
       <c r="S94" t="n">
         <v>4</v>
@@ -10506,7 +10511,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10516,7 +10521,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10543,48 +10548,48 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125632415</v>
+        <v>125635666</v>
       </c>
       <c r="B95" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>522124</v>
+        <v>522038</v>
       </c>
       <c r="R95" t="n">
-        <v>6936410</v>
+        <v>6936535</v>
       </c>
       <c r="S95" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10608,22 +10613,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>15:26</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>15:26</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10638,22 +10638,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125632358</v>
+        <v>125632341</v>
       </c>
       <c r="B96" t="n">
-        <v>98359</v>
+        <v>92522</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10661,21 +10661,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221952</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10685,10 +10685,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>522231</v>
+        <v>522236</v>
       </c>
       <c r="R96" t="n">
-        <v>6936488</v>
+        <v>6936562</v>
       </c>
       <c r="S96" t="n">
         <v>4</v>
@@ -10720,7 +10720,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10757,32 +10757,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125646894</v>
+        <v>125632333</v>
       </c>
       <c r="B97" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10792,13 +10792,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>522227</v>
+        <v>522235</v>
       </c>
       <c r="R97" t="n">
-        <v>6936562</v>
+        <v>6936598</v>
       </c>
       <c r="S97" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10822,12 +10822,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10842,44 +10852,44 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125632344</v>
+        <v>125646900</v>
       </c>
       <c r="B98" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10889,13 +10899,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>522268</v>
+        <v>521975</v>
       </c>
       <c r="R98" t="n">
-        <v>6936556</v>
+        <v>6936372</v>
       </c>
       <c r="S98" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10919,22 +10929,17 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10949,44 +10954,44 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125646886</v>
+        <v>125632348</v>
       </c>
       <c r="B99" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10996,13 +11001,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>522109</v>
+        <v>522241</v>
       </c>
       <c r="R99" t="n">
-        <v>6936414</v>
+        <v>6936518</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11026,12 +11031,22 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11046,44 +11061,44 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125632333</v>
+        <v>125646894</v>
       </c>
       <c r="B100" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11093,13 +11108,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>522235</v>
+        <v>522227</v>
       </c>
       <c r="R100" t="n">
-        <v>6936598</v>
+        <v>6936562</v>
       </c>
       <c r="S100" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11123,22 +11138,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11153,44 +11158,44 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125646900</v>
+        <v>125632344</v>
       </c>
       <c r="B101" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11200,13 +11205,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>521975</v>
+        <v>522268</v>
       </c>
       <c r="R101" t="n">
-        <v>6936372</v>
+        <v>6936556</v>
       </c>
       <c r="S101" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11230,17 +11235,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11255,44 +11265,44 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125632348</v>
+        <v>125646886</v>
       </c>
       <c r="B102" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11302,13 +11312,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>522241</v>
+        <v>522109</v>
       </c>
       <c r="R102" t="n">
-        <v>6936518</v>
+        <v>6936414</v>
       </c>
       <c r="S102" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11332,22 +11342,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>13:44</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>13:44</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11362,12 +11362,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -11471,10 +11471,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125635476</v>
+        <v>125632323</v>
       </c>
       <c r="B104" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11482,37 +11482,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>522057</v>
+        <v>522189</v>
       </c>
       <c r="R104" t="n">
-        <v>6936487</v>
+        <v>6936648</v>
       </c>
       <c r="S104" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11536,17 +11536,22 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11561,22 +11566,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125632390</v>
+        <v>125635476</v>
       </c>
       <c r="B105" t="n">
-        <v>91232</v>
+        <v>80075</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11584,37 +11589,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>522187</v>
+        <v>522057</v>
       </c>
       <c r="R105" t="n">
-        <v>6936377</v>
+        <v>6936487</v>
       </c>
       <c r="S105" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11638,22 +11643,17 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>14:52</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>14:52</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11668,22 +11668,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125632323</v>
+        <v>125632325</v>
       </c>
       <c r="B106" t="n">
-        <v>78972</v>
+        <v>78730</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11691,21 +11691,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11715,13 +11715,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>522189</v>
+        <v>522198</v>
       </c>
       <c r="R106" t="n">
-        <v>6936648</v>
+        <v>6936620</v>
       </c>
       <c r="S106" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11787,10 +11787,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125632325</v>
+        <v>125632330</v>
       </c>
       <c r="B107" t="n">
-        <v>78730</v>
+        <v>78972</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11798,37 +11798,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>522198</v>
+        <v>522172</v>
       </c>
       <c r="R107" t="n">
-        <v>6936620</v>
+        <v>6936483</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11852,22 +11852,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>12:57</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>12:57</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11882,22 +11872,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125632330</v>
+        <v>125632390</v>
       </c>
       <c r="B108" t="n">
-        <v>78972</v>
+        <v>91232</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11905,37 +11895,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>522172</v>
+        <v>522187</v>
       </c>
       <c r="R108" t="n">
-        <v>6936483</v>
+        <v>6936377</v>
       </c>
       <c r="S108" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11959,12 +11949,22 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11979,12 +11979,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -11994,7 +11994,7 @@
         <v>125632412</v>
       </c>
       <c r="B109" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12098,10 +12098,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125632340</v>
+        <v>125646884</v>
       </c>
       <c r="B110" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12133,13 +12133,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>522232</v>
+        <v>522100</v>
       </c>
       <c r="R110" t="n">
-        <v>6936562</v>
+        <v>6936419</v>
       </c>
       <c r="S110" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12163,22 +12163,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12193,22 +12183,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125632351</v>
+        <v>125632379</v>
       </c>
       <c r="B111" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12240,10 +12230,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>522250</v>
+        <v>522237</v>
       </c>
       <c r="R111" t="n">
-        <v>6936497</v>
+        <v>6936415</v>
       </c>
       <c r="S111" t="n">
         <v>4</v>
@@ -12275,7 +12265,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12285,7 +12275,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12312,10 +12302,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125646884</v>
+        <v>125632351</v>
       </c>
       <c r="B112" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12347,13 +12337,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>522100</v>
+        <v>522250</v>
       </c>
       <c r="R112" t="n">
-        <v>6936419</v>
+        <v>6936497</v>
       </c>
       <c r="S112" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12377,12 +12367,22 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12397,22 +12397,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125632379</v>
+        <v>125632340</v>
       </c>
       <c r="B113" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12444,10 +12444,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>522237</v>
+        <v>522232</v>
       </c>
       <c r="R113" t="n">
-        <v>6936415</v>
+        <v>6936562</v>
       </c>
       <c r="S113" t="n">
         <v>4</v>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12516,10 +12516,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125632371</v>
+        <v>125632385</v>
       </c>
       <c r="B114" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12551,10 +12551,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>522243</v>
+        <v>522197</v>
       </c>
       <c r="R114" t="n">
-        <v>6936460</v>
+        <v>6936406</v>
       </c>
       <c r="S114" t="n">
         <v>4</v>
@@ -12586,7 +12586,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12626,7 +12626,7 @@
         <v>125635820</v>
       </c>
       <c r="B115" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12720,10 +12720,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125632385</v>
+        <v>125632371</v>
       </c>
       <c r="B116" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12755,10 +12755,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>522197</v>
+        <v>522243</v>
       </c>
       <c r="R116" t="n">
-        <v>6936406</v>
+        <v>6936460</v>
       </c>
       <c r="S116" t="n">
         <v>4</v>
@@ -12790,7 +12790,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12830,7 +12830,7 @@
         <v>125632394</v>
       </c>
       <c r="B117" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12934,10 +12934,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125632346</v>
+        <v>125632347</v>
       </c>
       <c r="B118" t="n">
-        <v>80075</v>
+        <v>78730</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12945,21 +12945,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13041,32 +13041,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125632399</v>
+        <v>125632346</v>
       </c>
       <c r="B119" t="n">
-        <v>56843</v>
+        <v>80075</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13076,10 +13076,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>522053</v>
+        <v>522239</v>
       </c>
       <c r="R119" t="n">
-        <v>6936400</v>
+        <v>6936527</v>
       </c>
       <c r="S119" t="n">
         <v>4</v>
@@ -13111,7 +13111,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13121,12 +13121,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>15:07</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>spillning</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13153,32 +13148,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125632347</v>
+        <v>125632399</v>
       </c>
       <c r="B120" t="n">
-        <v>78730</v>
+        <v>56843</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13188,10 +13183,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>522239</v>
+        <v>522053</v>
       </c>
       <c r="R120" t="n">
-        <v>6936527</v>
+        <v>6936400</v>
       </c>
       <c r="S120" t="n">
         <v>4</v>
@@ -13223,7 +13218,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13233,7 +13228,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13780,32 +13780,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125601077</v>
+        <v>125632408</v>
       </c>
       <c r="B126" t="n">
-        <v>80076</v>
+        <v>98373</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2081</v>
+        <v>219874</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13815,13 +13815,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>522217</v>
+        <v>522057</v>
       </c>
       <c r="R126" t="n">
-        <v>6936540</v>
+        <v>6936411</v>
       </c>
       <c r="S126" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13848,11 +13848,21 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
@@ -13861,41 +13871,26 @@
       </c>
       <c r="AG126" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK126" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO126" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125646878</v>
+        <v>125632326</v>
       </c>
       <c r="B127" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13903,21 +13898,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13927,13 +13922,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>522019</v>
+        <v>522213</v>
       </c>
       <c r="R127" t="n">
-        <v>6936608</v>
+        <v>6936615</v>
       </c>
       <c r="S127" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13957,12 +13952,22 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13977,22 +13982,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125632414</v>
+        <v>125646878</v>
       </c>
       <c r="B128" t="n">
-        <v>91232</v>
+        <v>80075</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14000,21 +14005,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14024,13 +14029,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>522109</v>
+        <v>522019</v>
       </c>
       <c r="R128" t="n">
-        <v>6936426</v>
+        <v>6936608</v>
       </c>
       <c r="S128" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14054,22 +14059,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>15:24</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>15:24</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14084,19 +14079,19 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125632326</v>
+        <v>125632345</v>
       </c>
       <c r="B129" t="n">
         <v>78972</v>
@@ -14131,10 +14126,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>522213</v>
+        <v>522244</v>
       </c>
       <c r="R129" t="n">
-        <v>6936615</v>
+        <v>6936537</v>
       </c>
       <c r="S129" t="n">
         <v>4</v>
@@ -14166,7 +14161,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14176,7 +14171,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14203,10 +14198,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125632345</v>
+        <v>125635162</v>
       </c>
       <c r="B130" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14214,37 +14209,37 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>522244</v>
+        <v>522010</v>
       </c>
       <c r="R130" t="n">
-        <v>6936537</v>
+        <v>6936407</v>
       </c>
       <c r="S130" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14268,22 +14263,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>13:34</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>13:34</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14298,60 +14283,60 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125635162</v>
+        <v>125632388</v>
       </c>
       <c r="B131" t="n">
-        <v>79590</v>
+        <v>98339</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>522010</v>
+        <v>522190</v>
       </c>
       <c r="R131" t="n">
-        <v>6936407</v>
+        <v>6936390</v>
       </c>
       <c r="S131" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14375,12 +14360,22 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14395,12 +14390,12 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
@@ -14410,7 +14405,7 @@
         <v>125632395</v>
       </c>
       <c r="B132" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14514,32 +14509,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125632388</v>
+        <v>125632414</v>
       </c>
       <c r="B133" t="n">
-        <v>98338</v>
+        <v>91232</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14549,10 +14544,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>522190</v>
+        <v>522109</v>
       </c>
       <c r="R133" t="n">
-        <v>6936390</v>
+        <v>6936426</v>
       </c>
       <c r="S133" t="n">
         <v>4</v>
@@ -14584,7 +14579,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14594,7 +14589,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14621,32 +14616,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125632408</v>
+        <v>125601077</v>
       </c>
       <c r="B134" t="n">
-        <v>98372</v>
+        <v>80076</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>219874</v>
+        <v>2081</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14656,13 +14651,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>522057</v>
+        <v>522217</v>
       </c>
       <c r="R134" t="n">
-        <v>6936411</v>
+        <v>6936540</v>
       </c>
       <c r="S134" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14689,21 +14684,11 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
@@ -14712,16 +14697,31 @@
       </c>
       <c r="AG134" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
@@ -14945,7 +14945,7 @@
         <v>125633219</v>
       </c>
       <c r="B137" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125632373</v>
+        <v>125632359</v>
       </c>
       <c r="B138" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>522236</v>
       </c>
       <c r="R138" t="n">
-        <v>6936449</v>
+        <v>6936482</v>
       </c>
       <c r="S138" t="n">
         <v>4</v>
@@ -15119,7 +15119,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15156,10 +15156,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125632352</v>
+        <v>125632373</v>
       </c>
       <c r="B139" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15191,10 +15191,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>522245</v>
+        <v>522236</v>
       </c>
       <c r="R139" t="n">
-        <v>6936497</v>
+        <v>6936449</v>
       </c>
       <c r="S139" t="n">
         <v>4</v>
@@ -15226,7 +15226,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15236,7 +15236,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15263,10 +15263,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125632359</v>
+        <v>125632352</v>
       </c>
       <c r="B140" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15298,10 +15298,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>522236</v>
+        <v>522245</v>
       </c>
       <c r="R140" t="n">
-        <v>6936482</v>
+        <v>6936497</v>
       </c>
       <c r="S140" t="n">
         <v>4</v>
@@ -15333,7 +15333,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15343,7 +15343,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15370,10 +15370,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125632375</v>
+        <v>125636452</v>
       </c>
       <c r="B141" t="n">
-        <v>98338</v>
+        <v>91393</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15381,37 +15381,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>522243</v>
+        <v>522141</v>
       </c>
       <c r="R141" t="n">
-        <v>6936427</v>
+        <v>6936548</v>
       </c>
       <c r="S141" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15435,22 +15435,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15465,60 +15455,60 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125633218</v>
+        <v>125632389</v>
       </c>
       <c r="B142" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>MD1:Ånge, SE-VN, SE, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>522221</v>
+        <v>522188</v>
       </c>
       <c r="R142" t="n">
-        <v>6936591</v>
+        <v>6936385</v>
       </c>
       <c r="S142" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15547,7 +15537,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15557,7 +15547,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15584,32 +15574,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125632364</v>
+        <v>125646901</v>
       </c>
       <c r="B143" t="n">
-        <v>98338</v>
+        <v>92522</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15619,13 +15609,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>522260</v>
+        <v>522030</v>
       </c>
       <c r="R143" t="n">
-        <v>6936473</v>
+        <v>6936634</v>
       </c>
       <c r="S143" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15649,22 +15639,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15679,44 +15659,44 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125646901</v>
+        <v>125632364</v>
       </c>
       <c r="B144" t="n">
-        <v>92522</v>
+        <v>98339</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15726,13 +15706,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>522030</v>
+        <v>522260</v>
       </c>
       <c r="R144" t="n">
-        <v>6936634</v>
+        <v>6936473</v>
       </c>
       <c r="S144" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15756,12 +15736,22 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15776,22 +15766,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125636452</v>
+        <v>125632375</v>
       </c>
       <c r="B145" t="n">
-        <v>91393</v>
+        <v>98339</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15799,37 +15789,37 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>522141</v>
+        <v>522243</v>
       </c>
       <c r="R145" t="n">
-        <v>6936548</v>
+        <v>6936427</v>
       </c>
       <c r="S145" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15853,12 +15843,22 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15873,60 +15873,60 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125632389</v>
+        <v>125633218</v>
       </c>
       <c r="B146" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>MD1:Ånge, SE-VN, SE, Mpd</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>522188</v>
+        <v>522221</v>
       </c>
       <c r="R146" t="n">
-        <v>6936385</v>
+        <v>6936591</v>
       </c>
       <c r="S146" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15965,7 +15965,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15992,10 +15992,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125632331</v>
+        <v>125632386</v>
       </c>
       <c r="B147" t="n">
-        <v>92522</v>
+        <v>56843</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16003,21 +16003,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>522221</v>
+        <v>522200</v>
       </c>
       <c r="R147" t="n">
-        <v>6936608</v>
+        <v>6936398</v>
       </c>
       <c r="S147" t="n">
         <v>4</v>
@@ -16062,7 +16062,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16072,7 +16072,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16099,32 +16099,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125632386</v>
+        <v>125646888</v>
       </c>
       <c r="B148" t="n">
-        <v>56843</v>
+        <v>98339</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16134,13 +16134,13 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>522200</v>
+        <v>522159</v>
       </c>
       <c r="R148" t="n">
-        <v>6936398</v>
+        <v>6936405</v>
       </c>
       <c r="S148" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16164,22 +16164,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16194,22 +16184,22 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125632411</v>
+        <v>125632419</v>
       </c>
       <c r="B149" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16241,10 +16231,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>522063</v>
+        <v>522202</v>
       </c>
       <c r="R149" t="n">
-        <v>6936424</v>
+        <v>6936414</v>
       </c>
       <c r="S149" t="n">
         <v>4</v>
@@ -16276,7 +16266,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16286,7 +16276,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16313,10 +16303,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125632419</v>
+        <v>125632411</v>
       </c>
       <c r="B150" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16348,10 +16338,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>522202</v>
+        <v>522063</v>
       </c>
       <c r="R150" t="n">
-        <v>6936414</v>
+        <v>6936424</v>
       </c>
       <c r="S150" t="n">
         <v>4</v>
@@ -16383,7 +16373,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16393,7 +16383,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16420,32 +16410,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125646888</v>
+        <v>125632366</v>
       </c>
       <c r="B151" t="n">
-        <v>98338</v>
+        <v>98360</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16455,13 +16445,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>522159</v>
+        <v>522249</v>
       </c>
       <c r="R151" t="n">
-        <v>6936405</v>
+        <v>6936460</v>
       </c>
       <c r="S151" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16485,12 +16475,22 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16505,22 +16505,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125632366</v>
+        <v>125632384</v>
       </c>
       <c r="B152" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16552,10 +16552,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>522249</v>
+        <v>522207</v>
       </c>
       <c r="R152" t="n">
-        <v>6936460</v>
+        <v>6936406</v>
       </c>
       <c r="S152" t="n">
         <v>4</v>
@@ -16587,7 +16587,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16597,7 +16597,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16624,10 +16624,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125632384</v>
+        <v>125632331</v>
       </c>
       <c r="B153" t="n">
-        <v>98359</v>
+        <v>92522</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16635,21 +16635,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>221952</v>
+        <v>4364</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16659,10 +16659,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>522207</v>
+        <v>522221</v>
       </c>
       <c r="R153" t="n">
-        <v>6936406</v>
+        <v>6936608</v>
       </c>
       <c r="S153" t="n">
         <v>4</v>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16704,7 +16704,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16731,32 +16731,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125646899</v>
+        <v>125632343</v>
       </c>
       <c r="B154" t="n">
-        <v>91393</v>
+        <v>78972</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16766,13 +16766,13 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>522143</v>
+        <v>522269</v>
       </c>
       <c r="R154" t="n">
-        <v>6936554</v>
+        <v>6936560</v>
       </c>
       <c r="S154" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16796,12 +16796,22 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16816,44 +16826,44 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125632376</v>
+        <v>125632327</v>
       </c>
       <c r="B155" t="n">
-        <v>56843</v>
+        <v>80075</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16863,10 +16873,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>522237</v>
+        <v>522218</v>
       </c>
       <c r="R155" t="n">
-        <v>6936423</v>
+        <v>6936625</v>
       </c>
       <c r="S155" t="n">
         <v>4</v>
@@ -16898,7 +16908,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -16908,7 +16918,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16935,32 +16945,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125632327</v>
+        <v>125646899</v>
       </c>
       <c r="B156" t="n">
-        <v>80075</v>
+        <v>91393</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16970,13 +16980,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>522218</v>
+        <v>522143</v>
       </c>
       <c r="R156" t="n">
-        <v>6936625</v>
+        <v>6936554</v>
       </c>
       <c r="S156" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17000,22 +17010,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>13:03</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>13:03</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17030,44 +17030,44 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125632343</v>
+        <v>125632376</v>
       </c>
       <c r="B157" t="n">
-        <v>78972</v>
+        <v>56843</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17077,10 +17077,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>522269</v>
+        <v>522237</v>
       </c>
       <c r="R157" t="n">
-        <v>6936560</v>
+        <v>6936423</v>
       </c>
       <c r="S157" t="n">
         <v>4</v>
@@ -17112,7 +17112,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17122,7 +17122,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17149,10 +17149,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125632393</v>
+        <v>125635540</v>
       </c>
       <c r="B158" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17180,17 +17180,17 @@
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>522160</v>
+        <v>522055</v>
       </c>
       <c r="R158" t="n">
-        <v>6936368</v>
+        <v>6936516</v>
       </c>
       <c r="S158" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17214,22 +17214,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17244,22 +17234,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125635540</v>
+        <v>125632393</v>
       </c>
       <c r="B159" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17287,17 +17277,17 @@
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>522055</v>
+        <v>522160</v>
       </c>
       <c r="R159" t="n">
-        <v>6936516</v>
+        <v>6936368</v>
       </c>
       <c r="S159" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17321,12 +17311,22 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17341,12 +17341,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>

--- a/artfynd/A 26476-2025 artfynd.xlsx
+++ b/artfynd/A 26476-2025 artfynd.xlsx
@@ -2925,32 +2925,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125646874</v>
+        <v>125646875</v>
       </c>
       <c r="B21" t="n">
-        <v>80103</v>
+        <v>78731</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>522022</v>
+        <v>522035</v>
       </c>
       <c r="R21" t="n">
-        <v>6936611</v>
+        <v>6936550</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3022,32 +3022,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125632425</v>
+        <v>125602968</v>
       </c>
       <c r="B22" t="n">
-        <v>78972</v>
+        <v>98360</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3057,13 +3057,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>522345</v>
+        <v>522217</v>
       </c>
       <c r="R22" t="n">
-        <v>6936464</v>
+        <v>6936540</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3090,19 +3090,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3117,22 +3107,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125602968</v>
+        <v>125646874</v>
       </c>
       <c r="B23" t="n">
-        <v>98360</v>
+        <v>80103</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3140,21 +3130,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3164,13 +3154,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>522217</v>
+        <v>522022</v>
       </c>
       <c r="R23" t="n">
-        <v>6936540</v>
+        <v>6936611</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3194,12 +3184,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3214,44 +3204,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125646902</v>
+        <v>125632425</v>
       </c>
       <c r="B24" t="n">
-        <v>4869</v>
+        <v>78972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>101675</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3261,13 +3251,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>522019</v>
+        <v>522345</v>
       </c>
       <c r="R24" t="n">
-        <v>6936608</v>
+        <v>6936464</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3291,17 +3281,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Kläckhål på asp</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3316,44 +3311,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125601310</v>
+        <v>125646902</v>
       </c>
       <c r="B25" t="n">
-        <v>98339</v>
+        <v>4869</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>101675</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3363,13 +3358,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>522217</v>
+        <v>522019</v>
       </c>
       <c r="R25" t="n">
-        <v>6936540</v>
+        <v>6936608</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3393,12 +3388,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Kläckhål på asp</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3413,19 +3413,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125632421</v>
+        <v>125601310</v>
       </c>
       <c r="B26" t="n">
         <v>98339</v>
@@ -3460,13 +3460,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>522260</v>
+        <v>522217</v>
       </c>
       <c r="R26" t="n">
-        <v>6936447</v>
+        <v>6936540</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3493,19 +3493,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3520,19 +3510,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125632569</v>
+        <v>125632421</v>
       </c>
       <c r="B27" t="n">
         <v>98339</v>
@@ -3563,17 +3553,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>522108</v>
+        <v>522260</v>
       </c>
       <c r="R27" t="n">
-        <v>6936467</v>
+        <v>6936447</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3597,12 +3587,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3617,60 +3617,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125646875</v>
+        <v>125632569</v>
       </c>
       <c r="B28" t="n">
-        <v>78731</v>
+        <v>98339</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>522035</v>
+        <v>522108</v>
       </c>
       <c r="R28" t="n">
-        <v>6936550</v>
+        <v>6936467</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -5684,32 +5684,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125632416</v>
+        <v>125632382</v>
       </c>
       <c r="B48" t="n">
-        <v>91250</v>
+        <v>98339</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>522125</v>
+        <v>522214</v>
       </c>
       <c r="R48" t="n">
-        <v>6936430</v>
+        <v>6936414</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5791,32 +5791,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125600818</v>
+        <v>125646883</v>
       </c>
       <c r="B49" t="n">
-        <v>98256</v>
+        <v>98339</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5826,13 +5826,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>522217</v>
+        <v>522097</v>
       </c>
       <c r="R49" t="n">
-        <v>6936540</v>
+        <v>6936427</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5876,19 +5876,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125632382</v>
+        <v>125638972</v>
       </c>
       <c r="B50" t="n">
         <v>98339</v>
@@ -5919,17 +5919,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>522214</v>
+        <v>522318</v>
       </c>
       <c r="R50" t="n">
-        <v>6936414</v>
+        <v>6936398</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5953,22 +5953,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>14:29</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>14:29</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5983,44 +5973,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125646883</v>
+        <v>125600818</v>
       </c>
       <c r="B51" t="n">
-        <v>98339</v>
+        <v>98256</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6030,13 +6020,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>522097</v>
+        <v>522217</v>
       </c>
       <c r="R51" t="n">
-        <v>6936427</v>
+        <v>6936540</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6060,12 +6050,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6080,60 +6070,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125638972</v>
+        <v>125632416</v>
       </c>
       <c r="B52" t="n">
-        <v>98339</v>
+        <v>91250</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>522318</v>
+        <v>522125</v>
       </c>
       <c r="R52" t="n">
-        <v>6936398</v>
+        <v>6936430</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6157,12 +6147,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6177,12 +6177,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6898,32 +6898,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125632392</v>
+        <v>125632356</v>
       </c>
       <c r="B60" t="n">
-        <v>98339</v>
+        <v>78972</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6933,10 +6933,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>522181</v>
+        <v>522233</v>
       </c>
       <c r="R60" t="n">
-        <v>6936381</v>
+        <v>6936499</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7005,32 +7005,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125632354</v>
+        <v>125632410</v>
       </c>
       <c r="B61" t="n">
-        <v>98339</v>
+        <v>92522</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7040,10 +7040,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>522234</v>
+        <v>522063</v>
       </c>
       <c r="R61" t="n">
-        <v>6936499</v>
+        <v>6936423</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7112,32 +7112,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125646887</v>
+        <v>125632324</v>
       </c>
       <c r="B62" t="n">
-        <v>98339</v>
+        <v>92522</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7147,13 +7147,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>522185</v>
+        <v>522198</v>
       </c>
       <c r="R62" t="n">
-        <v>6936414</v>
+        <v>6936634</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7177,12 +7177,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7197,19 +7207,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125632398</v>
+        <v>125632392</v>
       </c>
       <c r="B63" t="n">
         <v>98339</v>
@@ -7244,10 +7254,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>522059</v>
+        <v>522181</v>
       </c>
       <c r="R63" t="n">
-        <v>6936399</v>
+        <v>6936381</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -7279,7 +7289,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7289,7 +7299,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7316,7 +7326,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125646891</v>
+        <v>125632354</v>
       </c>
       <c r="B64" t="n">
         <v>98339</v>
@@ -7351,13 +7361,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>522159</v>
+        <v>522234</v>
       </c>
       <c r="R64" t="n">
-        <v>6936408</v>
+        <v>6936499</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7381,12 +7391,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7401,44 +7421,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125632356</v>
+        <v>125646887</v>
       </c>
       <c r="B65" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7448,13 +7468,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>522233</v>
+        <v>522185</v>
       </c>
       <c r="R65" t="n">
-        <v>6936499</v>
+        <v>6936414</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7478,22 +7498,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>13:52</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>13:52</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7508,44 +7518,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125632410</v>
+        <v>125632398</v>
       </c>
       <c r="B66" t="n">
-        <v>92522</v>
+        <v>98339</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7555,10 +7565,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>522063</v>
+        <v>522059</v>
       </c>
       <c r="R66" t="n">
-        <v>6936423</v>
+        <v>6936399</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -7590,7 +7600,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7600,7 +7610,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7627,32 +7637,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125632324</v>
+        <v>125646891</v>
       </c>
       <c r="B67" t="n">
-        <v>92522</v>
+        <v>98339</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7662,13 +7672,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>522198</v>
+        <v>522159</v>
       </c>
       <c r="R67" t="n">
-        <v>6936634</v>
+        <v>6936408</v>
       </c>
       <c r="S67" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7692,22 +7702,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7722,12 +7722,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8055,32 +8055,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125646879</v>
+        <v>125632381</v>
       </c>
       <c r="B71" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>522202</v>
+        <v>522240</v>
       </c>
       <c r="R71" t="n">
-        <v>6936502</v>
+        <v>6936412</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8120,12 +8120,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8140,44 +8150,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125632350</v>
+        <v>125632370</v>
       </c>
       <c r="B72" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8187,10 +8197,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>522254</v>
+        <v>522243</v>
       </c>
       <c r="R72" t="n">
-        <v>6936496</v>
+        <v>6936456</v>
       </c>
       <c r="S72" t="n">
         <v>4</v>
@@ -8222,7 +8232,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8232,7 +8242,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8259,32 +8269,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125632357</v>
+        <v>125632418</v>
       </c>
       <c r="B73" t="n">
-        <v>91232</v>
+        <v>98339</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8294,10 +8304,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>522221</v>
+        <v>522162</v>
       </c>
       <c r="R73" t="n">
-        <v>6936489</v>
+        <v>6936404</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -8329,7 +8339,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8339,7 +8349,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8366,10 +8376,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125646872</v>
+        <v>125632372</v>
       </c>
       <c r="B74" t="n">
-        <v>91197</v>
+        <v>98360</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8377,21 +8387,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8401,13 +8411,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>522064</v>
+        <v>522236</v>
       </c>
       <c r="R74" t="n">
-        <v>6936505</v>
+        <v>6936448</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8431,12 +8441,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8451,44 +8471,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125632381</v>
+        <v>125646879</v>
       </c>
       <c r="B75" t="n">
-        <v>98339</v>
+        <v>80075</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8498,13 +8518,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>522240</v>
+        <v>522202</v>
       </c>
       <c r="R75" t="n">
-        <v>6936412</v>
+        <v>6936502</v>
       </c>
       <c r="S75" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8528,22 +8548,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>14:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>14:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8558,44 +8568,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125632370</v>
+        <v>125632350</v>
       </c>
       <c r="B76" t="n">
-        <v>98339</v>
+        <v>80075</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8605,10 +8615,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>522243</v>
+        <v>522254</v>
       </c>
       <c r="R76" t="n">
-        <v>6936456</v>
+        <v>6936496</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -8640,7 +8650,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8650,7 +8660,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8677,32 +8687,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125632418</v>
+        <v>125632357</v>
       </c>
       <c r="B77" t="n">
-        <v>98339</v>
+        <v>91232</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8712,10 +8722,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>522162</v>
+        <v>522221</v>
       </c>
       <c r="R77" t="n">
-        <v>6936404</v>
+        <v>6936489</v>
       </c>
       <c r="S77" t="n">
         <v>4</v>
@@ -8747,7 +8757,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8757,7 +8767,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8784,10 +8794,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125632372</v>
+        <v>125646872</v>
       </c>
       <c r="B78" t="n">
-        <v>98360</v>
+        <v>91197</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8795,21 +8805,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8819,13 +8829,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>522236</v>
+        <v>522064</v>
       </c>
       <c r="R78" t="n">
-        <v>6936448</v>
+        <v>6936505</v>
       </c>
       <c r="S78" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8849,22 +8859,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>14:19</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>14:19</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8879,44 +8879,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125632406</v>
+        <v>125632420</v>
       </c>
       <c r="B79" t="n">
-        <v>98339</v>
+        <v>98360</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8926,10 +8926,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>522052</v>
+        <v>522236</v>
       </c>
       <c r="R79" t="n">
-        <v>6936412</v>
+        <v>6936446</v>
       </c>
       <c r="S79" t="n">
         <v>4</v>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8998,7 +8998,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125632365</v>
+        <v>125632406</v>
       </c>
       <c r="B80" t="n">
         <v>98339</v>
@@ -9033,10 +9033,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>522249</v>
+        <v>522052</v>
       </c>
       <c r="R80" t="n">
-        <v>6936473</v>
+        <v>6936412</v>
       </c>
       <c r="S80" t="n">
         <v>4</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9105,7 +9105,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125632387</v>
+        <v>125632365</v>
       </c>
       <c r="B81" t="n">
         <v>98339</v>
@@ -9140,10 +9140,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>522191</v>
+        <v>522249</v>
       </c>
       <c r="R81" t="n">
-        <v>6936398</v>
+        <v>6936473</v>
       </c>
       <c r="S81" t="n">
         <v>4</v>
@@ -9175,7 +9175,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9185,7 +9185,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9212,7 +9212,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125632423</v>
+        <v>125632387</v>
       </c>
       <c r="B82" t="n">
         <v>98339</v>
@@ -9247,10 +9247,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>522332</v>
+        <v>522191</v>
       </c>
       <c r="R82" t="n">
-        <v>6936449</v>
+        <v>6936398</v>
       </c>
       <c r="S82" t="n">
         <v>4</v>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9319,7 +9319,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125632554</v>
+        <v>125632423</v>
       </c>
       <c r="B83" t="n">
         <v>98339</v>
@@ -9350,17 +9350,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>522125</v>
+        <v>522332</v>
       </c>
       <c r="R83" t="n">
-        <v>6936477</v>
+        <v>6936449</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9384,12 +9384,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9404,19 +9414,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125632377</v>
+        <v>125632554</v>
       </c>
       <c r="B84" t="n">
         <v>98339</v>
@@ -9447,17 +9457,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>522237</v>
+        <v>522125</v>
       </c>
       <c r="R84" t="n">
-        <v>6936417</v>
+        <v>6936477</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9481,22 +9491,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9511,19 +9511,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125632593</v>
+        <v>125632377</v>
       </c>
       <c r="B85" t="n">
         <v>98339</v>
@@ -9554,17 +9554,17 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>522125</v>
+        <v>522237</v>
       </c>
       <c r="R85" t="n">
-        <v>6936475</v>
+        <v>6936417</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9588,12 +9588,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9608,60 +9618,60 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125632420</v>
+        <v>125632593</v>
       </c>
       <c r="B86" t="n">
-        <v>98360</v>
+        <v>98339</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>522236</v>
+        <v>522125</v>
       </c>
       <c r="R86" t="n">
-        <v>6936446</v>
+        <v>6936475</v>
       </c>
       <c r="S86" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9685,22 +9695,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9715,12 +9715,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -13780,32 +13780,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125632408</v>
+        <v>125632414</v>
       </c>
       <c r="B126" t="n">
-        <v>98373</v>
+        <v>91232</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13815,10 +13815,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>522057</v>
+        <v>522109</v>
       </c>
       <c r="R126" t="n">
-        <v>6936411</v>
+        <v>6936426</v>
       </c>
       <c r="S126" t="n">
         <v>4</v>
@@ -13850,7 +13850,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13860,7 +13860,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13887,10 +13887,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125632326</v>
+        <v>125601077</v>
       </c>
       <c r="B127" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13898,21 +13898,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>522213</v>
+        <v>522217</v>
       </c>
       <c r="R127" t="n">
-        <v>6936615</v>
+        <v>6936540</v>
       </c>
       <c r="S127" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13955,21 +13955,11 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
@@ -13978,48 +13968,63 @@
       </c>
       <c r="AG127" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125646878</v>
+        <v>125632388</v>
       </c>
       <c r="B128" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14029,13 +14034,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>522019</v>
+        <v>522190</v>
       </c>
       <c r="R128" t="n">
-        <v>6936608</v>
+        <v>6936390</v>
       </c>
       <c r="S128" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14059,12 +14064,22 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14079,44 +14094,44 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125632345</v>
+        <v>125632395</v>
       </c>
       <c r="B129" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14126,10 +14141,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>522244</v>
+        <v>522113</v>
       </c>
       <c r="R129" t="n">
-        <v>6936537</v>
+        <v>6936367</v>
       </c>
       <c r="S129" t="n">
         <v>4</v>
@@ -14161,7 +14176,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14171,7 +14186,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14198,48 +14213,48 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125635162</v>
+        <v>125632408</v>
       </c>
       <c r="B130" t="n">
-        <v>79590</v>
+        <v>98373</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>219874</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>522010</v>
+        <v>522057</v>
       </c>
       <c r="R130" t="n">
-        <v>6936407</v>
+        <v>6936411</v>
       </c>
       <c r="S130" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14263,12 +14278,22 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14283,44 +14308,44 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125632388</v>
+        <v>125632326</v>
       </c>
       <c r="B131" t="n">
-        <v>98339</v>
+        <v>78972</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14330,10 +14355,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>522190</v>
+        <v>522213</v>
       </c>
       <c r="R131" t="n">
-        <v>6936390</v>
+        <v>6936615</v>
       </c>
       <c r="S131" t="n">
         <v>4</v>
@@ -14365,7 +14390,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14375,7 +14400,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14402,32 +14427,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125632395</v>
+        <v>125646878</v>
       </c>
       <c r="B132" t="n">
-        <v>98339</v>
+        <v>80075</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14437,13 +14462,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>522113</v>
+        <v>522019</v>
       </c>
       <c r="R132" t="n">
-        <v>6936367</v>
+        <v>6936608</v>
       </c>
       <c r="S132" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14467,22 +14492,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14497,22 +14512,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125632414</v>
+        <v>125632345</v>
       </c>
       <c r="B133" t="n">
-        <v>91232</v>
+        <v>78972</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14520,21 +14535,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14544,10 +14559,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>522109</v>
+        <v>522244</v>
       </c>
       <c r="R133" t="n">
-        <v>6936426</v>
+        <v>6936537</v>
       </c>
       <c r="S133" t="n">
         <v>4</v>
@@ -14579,7 +14594,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14589,7 +14604,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14616,10 +14631,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125601077</v>
+        <v>125635162</v>
       </c>
       <c r="B134" t="n">
-        <v>80076</v>
+        <v>79590</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14627,37 +14642,37 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>522217</v>
+        <v>522010</v>
       </c>
       <c r="R134" t="n">
-        <v>6936540</v>
+        <v>6936407</v>
       </c>
       <c r="S134" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14681,12 +14696,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14697,63 +14712,48 @@
       </c>
       <c r="AG134" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ134" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125632334</v>
+        <v>125632407</v>
       </c>
       <c r="B135" t="n">
-        <v>80104</v>
+        <v>91232</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14763,10 +14763,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>522239</v>
+        <v>522052</v>
       </c>
       <c r="R135" t="n">
-        <v>6936600</v>
+        <v>6936413</v>
       </c>
       <c r="S135" t="n">
         <v>4</v>
@@ -14798,7 +14798,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14808,7 +14808,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14835,32 +14835,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125632407</v>
+        <v>125632334</v>
       </c>
       <c r="B136" t="n">
-        <v>91232</v>
+        <v>80104</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14870,10 +14870,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>522052</v>
+        <v>522239</v>
       </c>
       <c r="R136" t="n">
-        <v>6936413</v>
+        <v>6936600</v>
       </c>
       <c r="S136" t="n">
         <v>4</v>
@@ -14905,7 +14905,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15992,32 +15992,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125632386</v>
+        <v>125646888</v>
       </c>
       <c r="B147" t="n">
-        <v>56843</v>
+        <v>98339</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16027,13 +16027,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>522200</v>
+        <v>522159</v>
       </c>
       <c r="R147" t="n">
-        <v>6936398</v>
+        <v>6936405</v>
       </c>
       <c r="S147" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16057,22 +16057,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16087,19 +16077,19 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125646888</v>
+        <v>125632419</v>
       </c>
       <c r="B148" t="n">
         <v>98339</v>
@@ -16134,13 +16124,13 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>522159</v>
+        <v>522202</v>
       </c>
       <c r="R148" t="n">
-        <v>6936405</v>
+        <v>6936414</v>
       </c>
       <c r="S148" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16164,12 +16154,22 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16184,19 +16184,19 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125632419</v>
+        <v>125632411</v>
       </c>
       <c r="B149" t="n">
         <v>98339</v>
@@ -16231,10 +16231,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>522202</v>
+        <v>522063</v>
       </c>
       <c r="R149" t="n">
-        <v>6936414</v>
+        <v>6936424</v>
       </c>
       <c r="S149" t="n">
         <v>4</v>
@@ -16266,7 +16266,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16276,7 +16276,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16303,32 +16303,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125632411</v>
+        <v>125632366</v>
       </c>
       <c r="B150" t="n">
-        <v>98339</v>
+        <v>98360</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16338,10 +16338,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>522063</v>
+        <v>522249</v>
       </c>
       <c r="R150" t="n">
-        <v>6936424</v>
+        <v>6936460</v>
       </c>
       <c r="S150" t="n">
         <v>4</v>
@@ -16373,7 +16373,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16383,7 +16383,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16410,7 +16410,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125632366</v>
+        <v>125632384</v>
       </c>
       <c r="B151" t="n">
         <v>98360</v>
@@ -16445,10 +16445,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>522249</v>
+        <v>522207</v>
       </c>
       <c r="R151" t="n">
-        <v>6936460</v>
+        <v>6936406</v>
       </c>
       <c r="S151" t="n">
         <v>4</v>
@@ -16480,7 +16480,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16490,7 +16490,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16517,10 +16517,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125632384</v>
+        <v>125632331</v>
       </c>
       <c r="B152" t="n">
-        <v>98360</v>
+        <v>92522</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16528,21 +16528,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>221952</v>
+        <v>4364</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16552,10 +16552,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>522207</v>
+        <v>522221</v>
       </c>
       <c r="R152" t="n">
-        <v>6936406</v>
+        <v>6936608</v>
       </c>
       <c r="S152" t="n">
         <v>4</v>
@@ -16587,7 +16587,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16597,7 +16597,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16624,10 +16624,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125632331</v>
+        <v>125632386</v>
       </c>
       <c r="B153" t="n">
-        <v>92522</v>
+        <v>56843</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16635,21 +16635,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16659,10 +16659,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>522221</v>
+        <v>522200</v>
       </c>
       <c r="R153" t="n">
-        <v>6936608</v>
+        <v>6936398</v>
       </c>
       <c r="S153" t="n">
         <v>4</v>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16704,7 +16704,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD153" t="b">

--- a/artfynd/A 26476-2025 artfynd.xlsx
+++ b/artfynd/A 26476-2025 artfynd.xlsx
@@ -2925,32 +2925,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125646875</v>
+        <v>125646874</v>
       </c>
       <c r="B21" t="n">
-        <v>78731</v>
+        <v>80103</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>522035</v>
+        <v>522022</v>
       </c>
       <c r="R21" t="n">
-        <v>6936550</v>
+        <v>6936611</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3022,32 +3022,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125602968</v>
+        <v>125632425</v>
       </c>
       <c r="B22" t="n">
-        <v>98360</v>
+        <v>78972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3057,13 +3057,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>522217</v>
+        <v>522345</v>
       </c>
       <c r="R22" t="n">
-        <v>6936540</v>
+        <v>6936464</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3090,9 +3090,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3107,22 +3117,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125646874</v>
+        <v>125602968</v>
       </c>
       <c r="B23" t="n">
-        <v>80103</v>
+        <v>98360</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3130,21 +3140,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6461</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3154,13 +3164,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>522022</v>
+        <v>522217</v>
       </c>
       <c r="R23" t="n">
-        <v>6936611</v>
+        <v>6936540</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3184,12 +3194,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3204,44 +3214,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125632425</v>
+        <v>125646902</v>
       </c>
       <c r="B24" t="n">
-        <v>78972</v>
+        <v>4869</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>101675</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3251,13 +3261,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>522345</v>
+        <v>522019</v>
       </c>
       <c r="R24" t="n">
-        <v>6936464</v>
+        <v>6936608</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3281,22 +3291,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Kläckhål på asp</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3311,44 +3316,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125646902</v>
+        <v>125601310</v>
       </c>
       <c r="B25" t="n">
-        <v>4869</v>
+        <v>98339</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>101675</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3358,13 +3363,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>522019</v>
+        <v>522217</v>
       </c>
       <c r="R25" t="n">
-        <v>6936608</v>
+        <v>6936540</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3388,17 +3393,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Kläckhål på asp</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3413,19 +3413,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125601310</v>
+        <v>125632421</v>
       </c>
       <c r="B26" t="n">
         <v>98339</v>
@@ -3460,13 +3460,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>522217</v>
+        <v>522260</v>
       </c>
       <c r="R26" t="n">
-        <v>6936540</v>
+        <v>6936447</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3493,9 +3493,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3510,19 +3520,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125632421</v>
+        <v>125632569</v>
       </c>
       <c r="B27" t="n">
         <v>98339</v>
@@ -3553,17 +3563,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>522260</v>
+        <v>522108</v>
       </c>
       <c r="R27" t="n">
-        <v>6936447</v>
+        <v>6936467</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3587,22 +3597,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3617,60 +3617,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125632569</v>
+        <v>125646875</v>
       </c>
       <c r="B28" t="n">
-        <v>98339</v>
+        <v>78731</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>522108</v>
+        <v>522035</v>
       </c>
       <c r="R28" t="n">
-        <v>6936467</v>
+        <v>6936550</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4644,32 +4644,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125632337</v>
+        <v>125632338</v>
       </c>
       <c r="B38" t="n">
-        <v>78972</v>
+        <v>92522</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4679,7 +4679,7 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>522224</v>
+        <v>522221</v>
       </c>
       <c r="R38" t="n">
         <v>6936572</v>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4751,10 +4751,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125632329</v>
+        <v>125636088</v>
       </c>
       <c r="B39" t="n">
-        <v>80104</v>
+        <v>92522</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4762,37 +4762,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>522215</v>
+        <v>522049</v>
       </c>
       <c r="R39" t="n">
-        <v>6936627</v>
+        <v>6936650</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4816,22 +4816,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:04</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:04</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4846,22 +4836,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125632362</v>
+        <v>125632337</v>
       </c>
       <c r="B40" t="n">
-        <v>78730</v>
+        <v>78972</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4869,21 +4859,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4893,10 +4883,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>522249</v>
+        <v>522224</v>
       </c>
       <c r="R40" t="n">
-        <v>6936486</v>
+        <v>6936572</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -4928,7 +4918,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4938,7 +4928,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4965,10 +4955,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125632338</v>
+        <v>125632329</v>
       </c>
       <c r="B41" t="n">
-        <v>92522</v>
+        <v>80104</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4976,21 +4966,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5000,10 +4990,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>522221</v>
+        <v>522215</v>
       </c>
       <c r="R41" t="n">
-        <v>6936572</v>
+        <v>6936627</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5035,7 +5025,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5045,7 +5035,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5072,48 +5062,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125636088</v>
+        <v>125632362</v>
       </c>
       <c r="B42" t="n">
-        <v>92522</v>
+        <v>78730</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>522049</v>
+        <v>522249</v>
       </c>
       <c r="R42" t="n">
-        <v>6936650</v>
+        <v>6936486</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5137,12 +5127,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5157,44 +5157,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125632401</v>
+        <v>125632353</v>
       </c>
       <c r="B43" t="n">
-        <v>100521</v>
+        <v>98339</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>522046</v>
+        <v>522241</v>
       </c>
       <c r="R43" t="n">
-        <v>6936397</v>
+        <v>6936509</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5276,7 +5276,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125632353</v>
+        <v>125646893</v>
       </c>
       <c r="B44" t="n">
         <v>98339</v>
@@ -5311,13 +5311,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>522241</v>
+        <v>522204</v>
       </c>
       <c r="R44" t="n">
-        <v>6936509</v>
+        <v>6936495</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5341,22 +5341,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5371,19 +5361,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125646893</v>
+        <v>125646892</v>
       </c>
       <c r="B45" t="n">
         <v>98339</v>
@@ -5418,10 +5408,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>522204</v>
+        <v>522130</v>
       </c>
       <c r="R45" t="n">
-        <v>6936495</v>
+        <v>6936481</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5480,32 +5470,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125646892</v>
+        <v>125632368</v>
       </c>
       <c r="B46" t="n">
-        <v>98339</v>
+        <v>98360</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5515,13 +5505,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>522130</v>
+        <v>522245</v>
       </c>
       <c r="R46" t="n">
-        <v>6936481</v>
+        <v>6936456</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5545,12 +5535,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5565,22 +5565,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125632368</v>
+        <v>125632401</v>
       </c>
       <c r="B47" t="n">
-        <v>98360</v>
+        <v>100521</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5588,21 +5588,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5612,10 +5612,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>522245</v>
+        <v>522046</v>
       </c>
       <c r="R47" t="n">
-        <v>6936456</v>
+        <v>6936397</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -8055,32 +8055,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125632381</v>
+        <v>125646879</v>
       </c>
       <c r="B71" t="n">
-        <v>98339</v>
+        <v>80075</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>522240</v>
+        <v>522202</v>
       </c>
       <c r="R71" t="n">
-        <v>6936412</v>
+        <v>6936502</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8120,22 +8120,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>14:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>14:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8150,44 +8140,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125632370</v>
+        <v>125632350</v>
       </c>
       <c r="B72" t="n">
-        <v>98339</v>
+        <v>80075</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8197,10 +8187,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>522243</v>
+        <v>522254</v>
       </c>
       <c r="R72" t="n">
-        <v>6936456</v>
+        <v>6936496</v>
       </c>
       <c r="S72" t="n">
         <v>4</v>
@@ -8232,7 +8222,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8242,7 +8232,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8269,32 +8259,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125632418</v>
+        <v>125632357</v>
       </c>
       <c r="B73" t="n">
-        <v>98339</v>
+        <v>91232</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8304,10 +8294,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>522162</v>
+        <v>522221</v>
       </c>
       <c r="R73" t="n">
-        <v>6936404</v>
+        <v>6936489</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -8339,7 +8329,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8349,7 +8339,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8376,10 +8366,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125632372</v>
+        <v>125646872</v>
       </c>
       <c r="B74" t="n">
-        <v>98360</v>
+        <v>91197</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8387,21 +8377,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8411,13 +8401,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>522236</v>
+        <v>522064</v>
       </c>
       <c r="R74" t="n">
-        <v>6936448</v>
+        <v>6936505</v>
       </c>
       <c r="S74" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8441,22 +8431,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>14:19</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>14:19</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8471,44 +8451,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125646879</v>
+        <v>125632381</v>
       </c>
       <c r="B75" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8518,13 +8498,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>522202</v>
+        <v>522240</v>
       </c>
       <c r="R75" t="n">
-        <v>6936502</v>
+        <v>6936412</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8548,12 +8528,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8568,44 +8558,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125632350</v>
+        <v>125632370</v>
       </c>
       <c r="B76" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8615,10 +8605,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>522254</v>
+        <v>522243</v>
       </c>
       <c r="R76" t="n">
-        <v>6936496</v>
+        <v>6936456</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -8650,7 +8640,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8660,7 +8650,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8687,32 +8677,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125632357</v>
+        <v>125632418</v>
       </c>
       <c r="B77" t="n">
-        <v>91232</v>
+        <v>98339</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8722,10 +8712,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>522221</v>
+        <v>522162</v>
       </c>
       <c r="R77" t="n">
-        <v>6936489</v>
+        <v>6936404</v>
       </c>
       <c r="S77" t="n">
         <v>4</v>
@@ -8757,7 +8747,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8767,7 +8757,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8794,10 +8784,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125646872</v>
+        <v>125632372</v>
       </c>
       <c r="B78" t="n">
-        <v>91197</v>
+        <v>98360</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8805,21 +8795,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8829,13 +8819,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>522064</v>
+        <v>522236</v>
       </c>
       <c r="R78" t="n">
-        <v>6936505</v>
+        <v>6936448</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8859,12 +8849,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8879,44 +8879,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125632420</v>
+        <v>125632406</v>
       </c>
       <c r="B79" t="n">
-        <v>98360</v>
+        <v>98339</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8926,10 +8926,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>522236</v>
+        <v>522052</v>
       </c>
       <c r="R79" t="n">
-        <v>6936446</v>
+        <v>6936412</v>
       </c>
       <c r="S79" t="n">
         <v>4</v>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8998,7 +8998,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125632406</v>
+        <v>125632365</v>
       </c>
       <c r="B80" t="n">
         <v>98339</v>
@@ -9033,10 +9033,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>522052</v>
+        <v>522249</v>
       </c>
       <c r="R80" t="n">
-        <v>6936412</v>
+        <v>6936473</v>
       </c>
       <c r="S80" t="n">
         <v>4</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9105,7 +9105,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125632365</v>
+        <v>125632387</v>
       </c>
       <c r="B81" t="n">
         <v>98339</v>
@@ -9140,10 +9140,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>522249</v>
+        <v>522191</v>
       </c>
       <c r="R81" t="n">
-        <v>6936473</v>
+        <v>6936398</v>
       </c>
       <c r="S81" t="n">
         <v>4</v>
@@ -9175,7 +9175,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9185,7 +9185,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9212,7 +9212,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125632387</v>
+        <v>125632423</v>
       </c>
       <c r="B82" t="n">
         <v>98339</v>
@@ -9247,10 +9247,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>522191</v>
+        <v>522332</v>
       </c>
       <c r="R82" t="n">
-        <v>6936398</v>
+        <v>6936449</v>
       </c>
       <c r="S82" t="n">
         <v>4</v>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9319,7 +9319,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125632423</v>
+        <v>125632554</v>
       </c>
       <c r="B83" t="n">
         <v>98339</v>
@@ -9350,17 +9350,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>522332</v>
+        <v>522125</v>
       </c>
       <c r="R83" t="n">
-        <v>6936449</v>
+        <v>6936477</v>
       </c>
       <c r="S83" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9384,22 +9384,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>15:44</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>15:44</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9414,19 +9404,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125632554</v>
+        <v>125632377</v>
       </c>
       <c r="B84" t="n">
         <v>98339</v>
@@ -9457,17 +9447,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>522125</v>
+        <v>522237</v>
       </c>
       <c r="R84" t="n">
-        <v>6936477</v>
+        <v>6936417</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9491,12 +9481,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9511,19 +9511,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125632377</v>
+        <v>125632593</v>
       </c>
       <c r="B85" t="n">
         <v>98339</v>
@@ -9554,17 +9554,17 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>522237</v>
+        <v>522125</v>
       </c>
       <c r="R85" t="n">
-        <v>6936417</v>
+        <v>6936475</v>
       </c>
       <c r="S85" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9588,22 +9588,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9618,60 +9608,60 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125632593</v>
+        <v>125632420</v>
       </c>
       <c r="B86" t="n">
-        <v>98339</v>
+        <v>98360</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>522125</v>
+        <v>522236</v>
       </c>
       <c r="R86" t="n">
-        <v>6936475</v>
+        <v>6936446</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9695,12 +9685,22 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9715,60 +9715,60 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125632417</v>
+        <v>125637200</v>
       </c>
       <c r="B87" t="n">
-        <v>98339</v>
+        <v>78972</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>522163</v>
+        <v>522362</v>
       </c>
       <c r="R87" t="n">
-        <v>6936406</v>
+        <v>6936466</v>
       </c>
       <c r="S87" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9792,22 +9792,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9822,60 +9812,60 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125646882</v>
+        <v>125635192</v>
       </c>
       <c r="B88" t="n">
-        <v>98339</v>
+        <v>92522</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>522029</v>
+        <v>522003</v>
       </c>
       <c r="R88" t="n">
-        <v>6936561</v>
+        <v>6936451</v>
       </c>
       <c r="S88" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9931,48 +9921,48 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125635192</v>
+        <v>125632417</v>
       </c>
       <c r="B89" t="n">
-        <v>92522</v>
+        <v>98339</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>522003</v>
+        <v>522163</v>
       </c>
       <c r="R89" t="n">
-        <v>6936451</v>
+        <v>6936406</v>
       </c>
       <c r="S89" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9996,12 +9986,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10016,60 +10016,60 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125637200</v>
+        <v>125646882</v>
       </c>
       <c r="B90" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>522362</v>
+        <v>522029</v>
       </c>
       <c r="R90" t="n">
-        <v>6936466</v>
+        <v>6936561</v>
       </c>
       <c r="S90" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -13780,32 +13780,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125632414</v>
+        <v>125632408</v>
       </c>
       <c r="B126" t="n">
-        <v>91232</v>
+        <v>98373</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1202</v>
+        <v>219874</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13815,10 +13815,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>522109</v>
+        <v>522057</v>
       </c>
       <c r="R126" t="n">
-        <v>6936426</v>
+        <v>6936411</v>
       </c>
       <c r="S126" t="n">
         <v>4</v>
@@ -13850,7 +13850,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13860,7 +13860,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13887,10 +13887,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125601077</v>
+        <v>125632326</v>
       </c>
       <c r="B127" t="n">
-        <v>80076</v>
+        <v>78972</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13898,21 +13898,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>522217</v>
+        <v>522213</v>
       </c>
       <c r="R127" t="n">
-        <v>6936540</v>
+        <v>6936615</v>
       </c>
       <c r="S127" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13955,11 +13955,21 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
@@ -13968,63 +13978,48 @@
       </c>
       <c r="AG127" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ127" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK127" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125632388</v>
+        <v>125646878</v>
       </c>
       <c r="B128" t="n">
-        <v>98339</v>
+        <v>80075</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14034,13 +14029,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>522190</v>
+        <v>522019</v>
       </c>
       <c r="R128" t="n">
-        <v>6936390</v>
+        <v>6936608</v>
       </c>
       <c r="S128" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14064,22 +14059,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14094,44 +14079,44 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125632395</v>
+        <v>125632345</v>
       </c>
       <c r="B129" t="n">
-        <v>98339</v>
+        <v>78972</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14141,10 +14126,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>522113</v>
+        <v>522244</v>
       </c>
       <c r="R129" t="n">
-        <v>6936367</v>
+        <v>6936537</v>
       </c>
       <c r="S129" t="n">
         <v>4</v>
@@ -14176,7 +14161,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14186,7 +14171,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14213,48 +14198,48 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125632408</v>
+        <v>125635162</v>
       </c>
       <c r="B130" t="n">
-        <v>98373</v>
+        <v>79590</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>219874</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>522057</v>
+        <v>522010</v>
       </c>
       <c r="R130" t="n">
-        <v>6936411</v>
+        <v>6936407</v>
       </c>
       <c r="S130" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14278,22 +14263,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>15:18</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>15:18</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14308,44 +14283,44 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125632326</v>
+        <v>125632388</v>
       </c>
       <c r="B131" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14355,10 +14330,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>522213</v>
+        <v>522190</v>
       </c>
       <c r="R131" t="n">
-        <v>6936615</v>
+        <v>6936390</v>
       </c>
       <c r="S131" t="n">
         <v>4</v>
@@ -14390,7 +14365,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14400,7 +14375,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14427,32 +14402,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125646878</v>
+        <v>125632395</v>
       </c>
       <c r="B132" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14462,13 +14437,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>522019</v>
+        <v>522113</v>
       </c>
       <c r="R132" t="n">
-        <v>6936608</v>
+        <v>6936367</v>
       </c>
       <c r="S132" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14492,12 +14467,22 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14512,22 +14497,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125632345</v>
+        <v>125632414</v>
       </c>
       <c r="B133" t="n">
-        <v>78972</v>
+        <v>91232</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14535,21 +14520,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14559,10 +14544,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>522244</v>
+        <v>522109</v>
       </c>
       <c r="R133" t="n">
-        <v>6936537</v>
+        <v>6936426</v>
       </c>
       <c r="S133" t="n">
         <v>4</v>
@@ -14594,7 +14579,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14604,7 +14589,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14631,10 +14616,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125635162</v>
+        <v>125601077</v>
       </c>
       <c r="B134" t="n">
-        <v>79590</v>
+        <v>80076</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14642,37 +14627,37 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>522010</v>
+        <v>522217</v>
       </c>
       <c r="R134" t="n">
-        <v>6936407</v>
+        <v>6936540</v>
       </c>
       <c r="S134" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14696,12 +14681,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14712,64 +14697,79 @@
       </c>
       <c r="AG134" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125632407</v>
+        <v>125633219</v>
       </c>
       <c r="B135" t="n">
-        <v>91232</v>
+        <v>98339</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>MD0:Ånge, SE-VN, SE, Mpd</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>522052</v>
+        <v>522237</v>
       </c>
       <c r="R135" t="n">
-        <v>6936413</v>
+        <v>6936437</v>
       </c>
       <c r="S135" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14808,7 +14808,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14835,32 +14835,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125632334</v>
+        <v>125632359</v>
       </c>
       <c r="B136" t="n">
-        <v>80104</v>
+        <v>98339</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14870,10 +14870,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>522239</v>
+        <v>522236</v>
       </c>
       <c r="R136" t="n">
-        <v>6936600</v>
+        <v>6936482</v>
       </c>
       <c r="S136" t="n">
         <v>4</v>
@@ -14905,7 +14905,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14942,7 +14942,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125633219</v>
+        <v>125632373</v>
       </c>
       <c r="B137" t="n">
         <v>98339</v>
@@ -14973,17 +14973,17 @@
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>MD0:Ånge, SE-VN, SE, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>522237</v>
+        <v>522236</v>
       </c>
       <c r="R137" t="n">
-        <v>6936437</v>
+        <v>6936449</v>
       </c>
       <c r="S137" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15049,7 +15049,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125632359</v>
+        <v>125632352</v>
       </c>
       <c r="B138" t="n">
         <v>98339</v>
@@ -15084,10 +15084,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>522236</v>
+        <v>522245</v>
       </c>
       <c r="R138" t="n">
-        <v>6936482</v>
+        <v>6936497</v>
       </c>
       <c r="S138" t="n">
         <v>4</v>
@@ -15119,7 +15119,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15156,32 +15156,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125632373</v>
+        <v>125632334</v>
       </c>
       <c r="B139" t="n">
-        <v>98339</v>
+        <v>80104</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15191,10 +15191,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>522236</v>
+        <v>522239</v>
       </c>
       <c r="R139" t="n">
-        <v>6936449</v>
+        <v>6936600</v>
       </c>
       <c r="S139" t="n">
         <v>4</v>
@@ -15226,7 +15226,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15236,7 +15236,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15263,32 +15263,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125632352</v>
+        <v>125632407</v>
       </c>
       <c r="B140" t="n">
-        <v>98339</v>
+        <v>91232</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15298,10 +15298,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>522245</v>
+        <v>522052</v>
       </c>
       <c r="R140" t="n">
-        <v>6936497</v>
+        <v>6936413</v>
       </c>
       <c r="S140" t="n">
         <v>4</v>
@@ -15333,7 +15333,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15343,7 +15343,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD140" t="b">

--- a/artfynd/A 26476-2025 artfynd.xlsx
+++ b/artfynd/A 26476-2025 artfynd.xlsx
@@ -2215,7 +2215,7 @@
         <v>125621452</v>
       </c>
       <c r="B14" t="n">
-        <v>91393</v>
+        <v>91395</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>125620054</v>
       </c>
       <c r="B15" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>125619969</v>
       </c>
       <c r="B16" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>125619776</v>
       </c>
       <c r="B17" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>125619796</v>
       </c>
       <c r="B18" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>125619751</v>
       </c>
       <c r="B19" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>125599631</v>
       </c>
       <c r="B20" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,32 +2925,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125646874</v>
+        <v>125601310</v>
       </c>
       <c r="B21" t="n">
-        <v>80103</v>
+        <v>98341</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2960,13 +2960,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>522022</v>
+        <v>522217</v>
       </c>
       <c r="R21" t="n">
-        <v>6936611</v>
+        <v>6936540</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2990,12 +2990,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3010,60 +3010,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125632425</v>
+        <v>125632569</v>
       </c>
       <c r="B22" t="n">
-        <v>78972</v>
+        <v>98341</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>522345</v>
+        <v>522108</v>
       </c>
       <c r="R22" t="n">
-        <v>6936464</v>
+        <v>6936467</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3087,22 +3087,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3117,44 +3107,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125602968</v>
+        <v>125632421</v>
       </c>
       <c r="B23" t="n">
-        <v>98360</v>
+        <v>98341</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3164,13 +3154,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>522217</v>
+        <v>522260</v>
       </c>
       <c r="R23" t="n">
-        <v>6936540</v>
+        <v>6936447</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3197,9 +3187,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3214,12 +3214,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3328,32 +3328,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125601310</v>
+        <v>125632425</v>
       </c>
       <c r="B25" t="n">
-        <v>98339</v>
+        <v>78973</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3363,13 +3363,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>522217</v>
+        <v>522345</v>
       </c>
       <c r="R25" t="n">
-        <v>6936540</v>
+        <v>6936464</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3396,9 +3396,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3413,44 +3423,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125632421</v>
+        <v>125646874</v>
       </c>
       <c r="B26" t="n">
-        <v>98339</v>
+        <v>80104</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3460,13 +3470,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>522260</v>
+        <v>522022</v>
       </c>
       <c r="R26" t="n">
-        <v>6936447</v>
+        <v>6936611</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3490,22 +3500,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3520,60 +3520,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125632569</v>
+        <v>125602968</v>
       </c>
       <c r="B27" t="n">
-        <v>98339</v>
+        <v>98362</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>522108</v>
+        <v>522217</v>
       </c>
       <c r="R27" t="n">
-        <v>6936467</v>
+        <v>6936540</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3597,12 +3597,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3617,12 +3617,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3632,7 +3632,7 @@
         <v>125646875</v>
       </c>
       <c r="B28" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3726,32 +3726,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125632332</v>
+        <v>125601890</v>
       </c>
       <c r="B29" t="n">
-        <v>78972</v>
+        <v>91688</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3761,13 +3761,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>522239</v>
+        <v>522217</v>
       </c>
       <c r="R29" t="n">
-        <v>6936598</v>
+        <v>6936540</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3794,19 +3794,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3821,22 +3811,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125600959</v>
+        <v>125632332</v>
       </c>
       <c r="B30" t="n">
-        <v>80075</v>
+        <v>78973</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3844,21 +3834,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3868,13 +3858,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>522217</v>
+        <v>522239</v>
       </c>
       <c r="R30" t="n">
-        <v>6936540</v>
+        <v>6936598</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3901,11 +3891,21 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3914,63 +3914,48 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125600280</v>
+        <v>125600959</v>
       </c>
       <c r="B31" t="n">
-        <v>92522</v>
+        <v>80076</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4026,6 +4011,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4042,32 +4042,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125601890</v>
+        <v>125600280</v>
       </c>
       <c r="B32" t="n">
-        <v>91686</v>
+        <v>92524</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4139,48 +4139,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125636837</v>
+        <v>125632367</v>
       </c>
       <c r="B33" t="n">
-        <v>98339</v>
+        <v>98362</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>522164</v>
+        <v>522247</v>
       </c>
       <c r="R33" t="n">
-        <v>6936587</v>
+        <v>6936458</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4204,12 +4204,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4224,60 +4234,60 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125632349</v>
+        <v>125634580</v>
       </c>
       <c r="B34" t="n">
-        <v>98339</v>
+        <v>98362</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>522259</v>
+        <v>522044</v>
       </c>
       <c r="R34" t="n">
-        <v>6936489</v>
+        <v>6936401</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4301,22 +4311,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4331,44 +4331,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125603562</v>
+        <v>125632349</v>
       </c>
       <c r="B35" t="n">
-        <v>80035</v>
+        <v>98341</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4378,13 +4378,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>522217</v>
+        <v>522259</v>
       </c>
       <c r="R35" t="n">
-        <v>6936540</v>
+        <v>6936489</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4411,9 +4411,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4428,44 +4438,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125634580</v>
+        <v>125636837</v>
       </c>
       <c r="B36" t="n">
-        <v>98360</v>
+        <v>98341</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4475,10 +4485,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>522044</v>
+        <v>522164</v>
       </c>
       <c r="R36" t="n">
-        <v>6936401</v>
+        <v>6936587</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4537,10 +4547,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125632367</v>
+        <v>125603562</v>
       </c>
       <c r="B37" t="n">
-        <v>98360</v>
+        <v>80036</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4548,21 +4558,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221952</v>
+        <v>229497</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4572,13 +4582,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>522247</v>
+        <v>522217</v>
       </c>
       <c r="R37" t="n">
-        <v>6936458</v>
+        <v>6936540</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4605,19 +4615,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>14:16</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4632,22 +4632,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125632338</v>
+        <v>125632401</v>
       </c>
       <c r="B38" t="n">
-        <v>92522</v>
+        <v>100523</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4655,21 +4655,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4679,10 +4679,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>522221</v>
+        <v>522046</v>
       </c>
       <c r="R38" t="n">
-        <v>6936572</v>
+        <v>6936397</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4751,10 +4751,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125636088</v>
+        <v>125632329</v>
       </c>
       <c r="B39" t="n">
-        <v>92522</v>
+        <v>80105</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4762,37 +4762,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>522049</v>
+        <v>522215</v>
       </c>
       <c r="R39" t="n">
-        <v>6936650</v>
+        <v>6936627</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4816,12 +4816,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4836,12 +4846,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4851,7 +4861,7 @@
         <v>125632337</v>
       </c>
       <c r="B40" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4955,32 +4965,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125632329</v>
+        <v>125632362</v>
       </c>
       <c r="B41" t="n">
-        <v>80104</v>
+        <v>78731</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4990,10 +5000,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>522215</v>
+        <v>522249</v>
       </c>
       <c r="R41" t="n">
-        <v>6936627</v>
+        <v>6936486</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5025,7 +5035,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5035,7 +5045,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5062,32 +5072,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125632362</v>
+        <v>125632338</v>
       </c>
       <c r="B42" t="n">
-        <v>78730</v>
+        <v>92524</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5097,10 +5107,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>522249</v>
+        <v>522221</v>
       </c>
       <c r="R42" t="n">
-        <v>6936486</v>
+        <v>6936572</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5132,7 +5142,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5142,7 +5152,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5169,48 +5179,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125632353</v>
+        <v>125636088</v>
       </c>
       <c r="B43" t="n">
-        <v>98339</v>
+        <v>92524</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>522241</v>
+        <v>522049</v>
       </c>
       <c r="R43" t="n">
-        <v>6936509</v>
+        <v>6936650</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5234,22 +5244,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5264,44 +5264,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125646893</v>
+        <v>125632368</v>
       </c>
       <c r="B44" t="n">
-        <v>98339</v>
+        <v>98362</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5311,13 +5311,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>522204</v>
+        <v>522245</v>
       </c>
       <c r="R44" t="n">
-        <v>6936495</v>
+        <v>6936456</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5341,12 +5341,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5361,22 +5371,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125646892</v>
+        <v>125632353</v>
       </c>
       <c r="B45" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5408,13 +5418,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>522130</v>
+        <v>522241</v>
       </c>
       <c r="R45" t="n">
-        <v>6936481</v>
+        <v>6936509</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5438,12 +5448,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5458,44 +5478,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125632368</v>
+        <v>125646892</v>
       </c>
       <c r="B46" t="n">
-        <v>98360</v>
+        <v>98341</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5505,13 +5525,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>522245</v>
+        <v>522130</v>
       </c>
       <c r="R46" t="n">
-        <v>6936456</v>
+        <v>6936481</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5535,22 +5555,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>14:17</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>14:17</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5565,44 +5575,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125632401</v>
+        <v>125646893</v>
       </c>
       <c r="B47" t="n">
-        <v>100521</v>
+        <v>98341</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5612,13 +5622,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>522046</v>
+        <v>522204</v>
       </c>
       <c r="R47" t="n">
-        <v>6936397</v>
+        <v>6936495</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5642,22 +5652,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>15:09</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>15:09</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5672,44 +5672,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125632382</v>
+        <v>125632416</v>
       </c>
       <c r="B48" t="n">
-        <v>98339</v>
+        <v>91252</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>522214</v>
+        <v>522125</v>
       </c>
       <c r="R48" t="n">
-        <v>6936414</v>
+        <v>6936430</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5791,32 +5791,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125646883</v>
+        <v>125600818</v>
       </c>
       <c r="B49" t="n">
-        <v>98339</v>
+        <v>98258</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5826,13 +5826,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>522097</v>
+        <v>522217</v>
       </c>
       <c r="R49" t="n">
-        <v>6936427</v>
+        <v>6936540</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5876,12 +5876,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5891,7 +5891,7 @@
         <v>125638972</v>
       </c>
       <c r="B50" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5985,32 +5985,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125600818</v>
+        <v>125632382</v>
       </c>
       <c r="B51" t="n">
-        <v>98256</v>
+        <v>98341</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6020,13 +6020,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>522217</v>
+        <v>522214</v>
       </c>
       <c r="R51" t="n">
-        <v>6936540</v>
+        <v>6936414</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6053,9 +6053,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6070,44 +6080,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125632416</v>
+        <v>125646883</v>
       </c>
       <c r="B52" t="n">
-        <v>91250</v>
+        <v>98341</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6117,13 +6127,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>522125</v>
+        <v>522097</v>
       </c>
       <c r="R52" t="n">
-        <v>6936430</v>
+        <v>6936427</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6147,22 +6157,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6177,44 +6177,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125637287</v>
+        <v>125632815</v>
       </c>
       <c r="B53" t="n">
-        <v>79590</v>
+        <v>98362</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6224,10 +6224,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>522356</v>
+        <v>522129</v>
       </c>
       <c r="R53" t="n">
-        <v>6936466</v>
+        <v>6936436</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6286,48 +6286,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125637245</v>
+        <v>125632397</v>
       </c>
       <c r="B54" t="n">
-        <v>80075</v>
+        <v>98341</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>522360</v>
+        <v>522077</v>
       </c>
       <c r="R54" t="n">
-        <v>6936453</v>
+        <v>6936379</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6351,12 +6351,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6371,60 +6381,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125632336</v>
+        <v>125636925</v>
       </c>
       <c r="B55" t="n">
-        <v>78730</v>
+        <v>98341</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>522224</v>
+        <v>522220</v>
       </c>
       <c r="R55" t="n">
-        <v>6936572</v>
+        <v>6936601</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6448,22 +6458,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>13:25</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>13:25</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6478,12 +6478,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6493,7 +6493,7 @@
         <v>125632400</v>
       </c>
       <c r="B56" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6597,48 +6597,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125632397</v>
+        <v>125637287</v>
       </c>
       <c r="B57" t="n">
-        <v>98339</v>
+        <v>79591</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>522077</v>
+        <v>522356</v>
       </c>
       <c r="R57" t="n">
-        <v>6936379</v>
+        <v>6936466</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6662,22 +6662,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6692,60 +6682,60 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125636925</v>
+        <v>125632336</v>
       </c>
       <c r="B58" t="n">
-        <v>98339</v>
+        <v>78731</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>522220</v>
+        <v>522224</v>
       </c>
       <c r="R58" t="n">
-        <v>6936601</v>
+        <v>6936572</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6769,12 +6759,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6789,44 +6789,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125632815</v>
+        <v>125637245</v>
       </c>
       <c r="B59" t="n">
-        <v>98360</v>
+        <v>80076</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6836,13 +6836,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>522129</v>
+        <v>522360</v>
       </c>
       <c r="R59" t="n">
-        <v>6936436</v>
+        <v>6936453</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6898,32 +6898,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125632356</v>
+        <v>125632410</v>
       </c>
       <c r="B60" t="n">
-        <v>78972</v>
+        <v>92524</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6933,10 +6933,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>522233</v>
+        <v>522063</v>
       </c>
       <c r="R60" t="n">
-        <v>6936499</v>
+        <v>6936423</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7005,10 +7005,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125632410</v>
+        <v>125632324</v>
       </c>
       <c r="B61" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7040,10 +7040,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>522063</v>
+        <v>522198</v>
       </c>
       <c r="R61" t="n">
-        <v>6936423</v>
+        <v>6936634</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7112,32 +7112,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125632324</v>
+        <v>125632356</v>
       </c>
       <c r="B62" t="n">
-        <v>92522</v>
+        <v>78973</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7147,10 +7147,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>522198</v>
+        <v>522233</v>
       </c>
       <c r="R62" t="n">
-        <v>6936634</v>
+        <v>6936499</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7219,10 +7219,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125632392</v>
+        <v>125646891</v>
       </c>
       <c r="B63" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7254,13 +7254,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>522181</v>
+        <v>522159</v>
       </c>
       <c r="R63" t="n">
-        <v>6936381</v>
+        <v>6936408</v>
       </c>
       <c r="S63" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7284,22 +7284,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7314,22 +7304,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125632354</v>
+        <v>125632392</v>
       </c>
       <c r="B64" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7361,10 +7351,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>522234</v>
+        <v>522181</v>
       </c>
       <c r="R64" t="n">
-        <v>6936499</v>
+        <v>6936381</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -7396,7 +7386,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7406,7 +7396,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7433,10 +7423,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125646887</v>
+        <v>125632398</v>
       </c>
       <c r="B65" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7468,13 +7458,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>522185</v>
+        <v>522059</v>
       </c>
       <c r="R65" t="n">
-        <v>6936414</v>
+        <v>6936399</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7498,12 +7488,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7518,22 +7518,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125632398</v>
+        <v>125632354</v>
       </c>
       <c r="B66" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7565,10 +7565,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>522059</v>
+        <v>522234</v>
       </c>
       <c r="R66" t="n">
-        <v>6936399</v>
+        <v>6936499</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -7600,7 +7600,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7637,10 +7637,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125646891</v>
+        <v>125646887</v>
       </c>
       <c r="B67" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7672,10 +7672,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>522159</v>
+        <v>522185</v>
       </c>
       <c r="R67" t="n">
-        <v>6936408</v>
+        <v>6936414</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7734,32 +7734,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125632396</v>
+        <v>125632422</v>
       </c>
       <c r="B68" t="n">
-        <v>98339</v>
+        <v>92524</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7769,10 +7769,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>522109</v>
+        <v>522263</v>
       </c>
       <c r="R68" t="n">
-        <v>6936384</v>
+        <v>6936447</v>
       </c>
       <c r="S68" t="n">
         <v>4</v>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7841,10 +7841,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125632361</v>
+        <v>125632396</v>
       </c>
       <c r="B69" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7876,10 +7876,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>522249</v>
+        <v>522109</v>
       </c>
       <c r="R69" t="n">
-        <v>6936484</v>
+        <v>6936384</v>
       </c>
       <c r="S69" t="n">
         <v>4</v>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7948,32 +7948,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125632422</v>
+        <v>125632361</v>
       </c>
       <c r="B70" t="n">
-        <v>92522</v>
+        <v>98341</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7983,10 +7983,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>522263</v>
+        <v>522249</v>
       </c>
       <c r="R70" t="n">
-        <v>6936447</v>
+        <v>6936484</v>
       </c>
       <c r="S70" t="n">
         <v>4</v>
@@ -8018,7 +8018,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8055,10 +8055,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125646879</v>
+        <v>125632357</v>
       </c>
       <c r="B71" t="n">
-        <v>80075</v>
+        <v>91234</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8066,21 +8066,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>522202</v>
+        <v>522221</v>
       </c>
       <c r="R71" t="n">
-        <v>6936502</v>
+        <v>6936489</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8120,12 +8120,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8140,44 +8150,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125632350</v>
+        <v>125646872</v>
       </c>
       <c r="B72" t="n">
-        <v>80075</v>
+        <v>91199</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8187,13 +8197,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>522254</v>
+        <v>522064</v>
       </c>
       <c r="R72" t="n">
-        <v>6936496</v>
+        <v>6936505</v>
       </c>
       <c r="S72" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8217,22 +8227,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>13:47</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>13:47</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8247,22 +8247,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125632357</v>
+        <v>125632350</v>
       </c>
       <c r="B73" t="n">
-        <v>91232</v>
+        <v>80076</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8270,21 +8270,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8294,10 +8294,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>522221</v>
+        <v>522254</v>
       </c>
       <c r="R73" t="n">
-        <v>6936489</v>
+        <v>6936496</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -8329,7 +8329,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8366,32 +8366,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125646872</v>
+        <v>125646879</v>
       </c>
       <c r="B74" t="n">
-        <v>91197</v>
+        <v>80076</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8401,10 +8401,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>522064</v>
+        <v>522202</v>
       </c>
       <c r="R74" t="n">
-        <v>6936505</v>
+        <v>6936502</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8463,32 +8463,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125632381</v>
+        <v>125632372</v>
       </c>
       <c r="B75" t="n">
-        <v>98339</v>
+        <v>98362</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8498,10 +8498,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>522240</v>
+        <v>522236</v>
       </c>
       <c r="R75" t="n">
-        <v>6936412</v>
+        <v>6936448</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -8533,7 +8533,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8573,7 +8573,7 @@
         <v>125632370</v>
       </c>
       <c r="B76" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8677,10 +8677,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125632418</v>
+        <v>125632381</v>
       </c>
       <c r="B77" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8712,10 +8712,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>522162</v>
+        <v>522240</v>
       </c>
       <c r="R77" t="n">
-        <v>6936404</v>
+        <v>6936412</v>
       </c>
       <c r="S77" t="n">
         <v>4</v>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8784,32 +8784,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125632372</v>
+        <v>125632418</v>
       </c>
       <c r="B78" t="n">
-        <v>98360</v>
+        <v>98341</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8819,10 +8819,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>522236</v>
+        <v>522162</v>
       </c>
       <c r="R78" t="n">
-        <v>6936448</v>
+        <v>6936404</v>
       </c>
       <c r="S78" t="n">
         <v>4</v>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8891,32 +8891,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125632406</v>
+        <v>125632420</v>
       </c>
       <c r="B79" t="n">
-        <v>98339</v>
+        <v>98362</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8926,10 +8926,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>522052</v>
+        <v>522236</v>
       </c>
       <c r="R79" t="n">
-        <v>6936412</v>
+        <v>6936446</v>
       </c>
       <c r="S79" t="n">
         <v>4</v>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8998,10 +8998,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125632365</v>
+        <v>125632406</v>
       </c>
       <c r="B80" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9033,10 +9033,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>522249</v>
+        <v>522052</v>
       </c>
       <c r="R80" t="n">
-        <v>6936473</v>
+        <v>6936412</v>
       </c>
       <c r="S80" t="n">
         <v>4</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9105,10 +9105,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125632387</v>
+        <v>125632377</v>
       </c>
       <c r="B81" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9140,10 +9140,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>522191</v>
+        <v>522237</v>
       </c>
       <c r="R81" t="n">
-        <v>6936398</v>
+        <v>6936417</v>
       </c>
       <c r="S81" t="n">
         <v>4</v>
@@ -9175,7 +9175,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9185,7 +9185,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9212,10 +9212,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125632423</v>
+        <v>125632387</v>
       </c>
       <c r="B82" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9247,10 +9247,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>522332</v>
+        <v>522191</v>
       </c>
       <c r="R82" t="n">
-        <v>6936449</v>
+        <v>6936398</v>
       </c>
       <c r="S82" t="n">
         <v>4</v>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9319,10 +9319,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125632554</v>
+        <v>125632423</v>
       </c>
       <c r="B83" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9350,17 +9350,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>522125</v>
+        <v>522332</v>
       </c>
       <c r="R83" t="n">
-        <v>6936477</v>
+        <v>6936449</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9384,12 +9384,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9404,22 +9414,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125632377</v>
+        <v>125632365</v>
       </c>
       <c r="B84" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9451,10 +9461,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>522237</v>
+        <v>522249</v>
       </c>
       <c r="R84" t="n">
-        <v>6936417</v>
+        <v>6936473</v>
       </c>
       <c r="S84" t="n">
         <v>4</v>
@@ -9486,7 +9496,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9496,7 +9506,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9523,10 +9533,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125632593</v>
+        <v>125632554</v>
       </c>
       <c r="B85" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9561,7 +9571,7 @@
         <v>522125</v>
       </c>
       <c r="R85" t="n">
-        <v>6936475</v>
+        <v>6936477</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9620,48 +9630,48 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125632420</v>
+        <v>125632593</v>
       </c>
       <c r="B86" t="n">
-        <v>98360</v>
+        <v>98341</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>522236</v>
+        <v>522125</v>
       </c>
       <c r="R86" t="n">
-        <v>6936446</v>
+        <v>6936475</v>
       </c>
       <c r="S86" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9685,22 +9695,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9715,60 +9715,60 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125637200</v>
+        <v>125646882</v>
       </c>
       <c r="B87" t="n">
-        <v>78972</v>
+        <v>98341</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>522362</v>
+        <v>522029</v>
       </c>
       <c r="R87" t="n">
-        <v>6936466</v>
+        <v>6936561</v>
       </c>
       <c r="S87" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9824,48 +9824,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125635192</v>
+        <v>125632417</v>
       </c>
       <c r="B88" t="n">
-        <v>92522</v>
+        <v>98341</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>522003</v>
+        <v>522163</v>
       </c>
       <c r="R88" t="n">
-        <v>6936451</v>
+        <v>6936406</v>
       </c>
       <c r="S88" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9889,12 +9889,22 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9909,60 +9919,60 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125632417</v>
+        <v>125637200</v>
       </c>
       <c r="B89" t="n">
-        <v>98339</v>
+        <v>78973</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>522163</v>
+        <v>522362</v>
       </c>
       <c r="R89" t="n">
-        <v>6936406</v>
+        <v>6936466</v>
       </c>
       <c r="S89" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9986,22 +9996,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10016,60 +10016,60 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125646882</v>
+        <v>125635192</v>
       </c>
       <c r="B90" t="n">
-        <v>98339</v>
+        <v>92524</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>522029</v>
+        <v>522003</v>
       </c>
       <c r="R90" t="n">
-        <v>6936561</v>
+        <v>6936451</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>125633268</v>
       </c>
       <c r="B91" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10227,48 +10227,48 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125632415</v>
+        <v>125635666</v>
       </c>
       <c r="B92" t="n">
-        <v>98339</v>
+        <v>80076</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>522124</v>
+        <v>522038</v>
       </c>
       <c r="R92" t="n">
-        <v>6936410</v>
+        <v>6936535</v>
       </c>
       <c r="S92" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10292,22 +10292,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>15:26</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>15:26</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10322,44 +10317,44 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125632409</v>
+        <v>125632341</v>
       </c>
       <c r="B93" t="n">
-        <v>98339</v>
+        <v>92524</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10369,10 +10364,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>522062</v>
+        <v>522236</v>
       </c>
       <c r="R93" t="n">
-        <v>6936422</v>
+        <v>6936562</v>
       </c>
       <c r="S93" t="n">
         <v>4</v>
@@ -10404,7 +10399,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10414,7 +10409,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10444,7 +10439,7 @@
         <v>125632358</v>
       </c>
       <c r="B94" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10548,48 +10543,48 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125635666</v>
+        <v>125632409</v>
       </c>
       <c r="B95" t="n">
-        <v>80075</v>
+        <v>98341</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>522038</v>
+        <v>522062</v>
       </c>
       <c r="R95" t="n">
-        <v>6936535</v>
+        <v>6936422</v>
       </c>
       <c r="S95" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10613,17 +10608,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10638,44 +10638,44 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125632341</v>
+        <v>125632415</v>
       </c>
       <c r="B96" t="n">
-        <v>92522</v>
+        <v>98341</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10685,10 +10685,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>522236</v>
+        <v>522124</v>
       </c>
       <c r="R96" t="n">
-        <v>6936562</v>
+        <v>6936410</v>
       </c>
       <c r="S96" t="n">
         <v>4</v>
@@ -10720,7 +10720,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10757,32 +10757,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125632333</v>
+        <v>125646894</v>
       </c>
       <c r="B97" t="n">
-        <v>80075</v>
+        <v>98341</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10792,13 +10792,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>522235</v>
+        <v>522227</v>
       </c>
       <c r="R97" t="n">
-        <v>6936598</v>
+        <v>6936562</v>
       </c>
       <c r="S97" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10822,22 +10822,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10852,44 +10842,44 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125646900</v>
+        <v>125632344</v>
       </c>
       <c r="B98" t="n">
-        <v>78972</v>
+        <v>98341</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10899,13 +10889,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>521975</v>
+        <v>522268</v>
       </c>
       <c r="R98" t="n">
-        <v>6936372</v>
+        <v>6936556</v>
       </c>
       <c r="S98" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10929,17 +10919,22 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10954,44 +10949,44 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125632348</v>
+        <v>125646886</v>
       </c>
       <c r="B99" t="n">
-        <v>78972</v>
+        <v>98341</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11001,13 +10996,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>522241</v>
+        <v>522109</v>
       </c>
       <c r="R99" t="n">
-        <v>6936518</v>
+        <v>6936414</v>
       </c>
       <c r="S99" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11031,22 +11026,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>13:44</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>13:44</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11061,44 +11046,44 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125646894</v>
+        <v>125632333</v>
       </c>
       <c r="B100" t="n">
-        <v>98339</v>
+        <v>80076</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11108,13 +11093,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>522227</v>
+        <v>522235</v>
       </c>
       <c r="R100" t="n">
-        <v>6936562</v>
+        <v>6936598</v>
       </c>
       <c r="S100" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11138,12 +11123,22 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11158,44 +11153,44 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125632344</v>
+        <v>125632348</v>
       </c>
       <c r="B101" t="n">
-        <v>98339</v>
+        <v>78973</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11205,10 +11200,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>522268</v>
+        <v>522241</v>
       </c>
       <c r="R101" t="n">
-        <v>6936556</v>
+        <v>6936518</v>
       </c>
       <c r="S101" t="n">
         <v>4</v>
@@ -11240,7 +11235,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11250,7 +11245,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11277,32 +11272,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125646886</v>
+        <v>125646900</v>
       </c>
       <c r="B102" t="n">
-        <v>98339</v>
+        <v>78973</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11312,10 +11307,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>522109</v>
+        <v>521975</v>
       </c>
       <c r="R102" t="n">
-        <v>6936414</v>
+        <v>6936372</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11348,6 +11343,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11374,10 +11374,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125646880</v>
+        <v>125632390</v>
       </c>
       <c r="B103" t="n">
-        <v>80075</v>
+        <v>91234</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11385,21 +11385,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11409,13 +11409,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>522225</v>
+        <v>522187</v>
       </c>
       <c r="R103" t="n">
-        <v>6936564</v>
+        <v>6936377</v>
       </c>
       <c r="S103" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11439,12 +11439,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11459,22 +11469,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125632323</v>
+        <v>125632325</v>
       </c>
       <c r="B104" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11482,21 +11492,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11506,13 +11516,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>522189</v>
+        <v>522198</v>
       </c>
       <c r="R104" t="n">
-        <v>6936648</v>
+        <v>6936620</v>
       </c>
       <c r="S104" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11541,7 +11551,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11551,7 +11561,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11578,10 +11588,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125635476</v>
+        <v>125646880</v>
       </c>
       <c r="B105" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11609,17 +11619,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>522057</v>
+        <v>522225</v>
       </c>
       <c r="R105" t="n">
-        <v>6936487</v>
+        <v>6936564</v>
       </c>
       <c r="S105" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11649,11 +11659,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11680,10 +11685,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125632325</v>
+        <v>125635476</v>
       </c>
       <c r="B106" t="n">
-        <v>78730</v>
+        <v>80076</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11691,37 +11696,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>522198</v>
+        <v>522057</v>
       </c>
       <c r="R106" t="n">
-        <v>6936620</v>
+        <v>6936487</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11745,22 +11750,17 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>12:57</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>12:57</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11775,22 +11775,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125632330</v>
+        <v>125632323</v>
       </c>
       <c r="B107" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11818,17 +11818,17 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>522172</v>
+        <v>522189</v>
       </c>
       <c r="R107" t="n">
-        <v>6936483</v>
+        <v>6936648</v>
       </c>
       <c r="S107" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11852,12 +11852,22 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11872,22 +11882,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125632390</v>
+        <v>125632330</v>
       </c>
       <c r="B108" t="n">
-        <v>91232</v>
+        <v>78973</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11895,37 +11905,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>522187</v>
+        <v>522172</v>
       </c>
       <c r="R108" t="n">
-        <v>6936377</v>
+        <v>6936483</v>
       </c>
       <c r="S108" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11949,22 +11959,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>14:52</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>14:52</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11979,12 +11979,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -11994,7 +11994,7 @@
         <v>125632412</v>
       </c>
       <c r="B109" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12098,10 +12098,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125646884</v>
+        <v>125632379</v>
       </c>
       <c r="B110" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12133,13 +12133,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>522100</v>
+        <v>522237</v>
       </c>
       <c r="R110" t="n">
-        <v>6936419</v>
+        <v>6936415</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12163,12 +12163,22 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12183,22 +12193,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125632379</v>
+        <v>125632340</v>
       </c>
       <c r="B111" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12230,10 +12240,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>522237</v>
+        <v>522232</v>
       </c>
       <c r="R111" t="n">
-        <v>6936415</v>
+        <v>6936562</v>
       </c>
       <c r="S111" t="n">
         <v>4</v>
@@ -12265,7 +12275,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12275,7 +12285,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12305,7 +12315,7 @@
         <v>125632351</v>
       </c>
       <c r="B112" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12409,10 +12419,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125632340</v>
+        <v>125646884</v>
       </c>
       <c r="B113" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12444,13 +12454,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>522232</v>
+        <v>522100</v>
       </c>
       <c r="R113" t="n">
-        <v>6936562</v>
+        <v>6936419</v>
       </c>
       <c r="S113" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12474,22 +12484,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12504,44 +12504,44 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125632385</v>
+        <v>125632347</v>
       </c>
       <c r="B114" t="n">
-        <v>98339</v>
+        <v>78731</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12551,10 +12551,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>522197</v>
+        <v>522239</v>
       </c>
       <c r="R114" t="n">
-        <v>6936406</v>
+        <v>6936527</v>
       </c>
       <c r="S114" t="n">
         <v>4</v>
@@ -12586,7 +12586,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12623,48 +12623,48 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125635820</v>
+        <v>125632346</v>
       </c>
       <c r="B115" t="n">
-        <v>98339</v>
+        <v>80076</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>522040</v>
+        <v>522239</v>
       </c>
       <c r="R115" t="n">
-        <v>6936582</v>
+        <v>6936527</v>
       </c>
       <c r="S115" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12688,12 +12688,22 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12708,44 +12718,44 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125632371</v>
+        <v>125632399</v>
       </c>
       <c r="B116" t="n">
-        <v>98339</v>
+        <v>56844</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12755,10 +12765,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>522243</v>
+        <v>522053</v>
       </c>
       <c r="R116" t="n">
-        <v>6936460</v>
+        <v>6936400</v>
       </c>
       <c r="S116" t="n">
         <v>4</v>
@@ -12790,7 +12800,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12800,7 +12810,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12827,10 +12842,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125632394</v>
+        <v>125632371</v>
       </c>
       <c r="B117" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12862,10 +12877,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>522136</v>
+        <v>522243</v>
       </c>
       <c r="R117" t="n">
-        <v>6936370</v>
+        <v>6936460</v>
       </c>
       <c r="S117" t="n">
         <v>4</v>
@@ -12897,7 +12912,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12907,7 +12922,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12934,32 +12949,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125632347</v>
+        <v>125632385</v>
       </c>
       <c r="B118" t="n">
-        <v>78730</v>
+        <v>98341</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12969,10 +12984,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>522239</v>
+        <v>522197</v>
       </c>
       <c r="R118" t="n">
-        <v>6936527</v>
+        <v>6936406</v>
       </c>
       <c r="S118" t="n">
         <v>4</v>
@@ -13004,7 +13019,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13014,7 +13029,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13041,32 +13056,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125632346</v>
+        <v>125632394</v>
       </c>
       <c r="B119" t="n">
-        <v>80075</v>
+        <v>98341</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13076,10 +13091,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>522239</v>
+        <v>522136</v>
       </c>
       <c r="R119" t="n">
-        <v>6936527</v>
+        <v>6936370</v>
       </c>
       <c r="S119" t="n">
         <v>4</v>
@@ -13111,7 +13126,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13121,7 +13136,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13148,48 +13163,48 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125632399</v>
+        <v>125635820</v>
       </c>
       <c r="B120" t="n">
-        <v>56843</v>
+        <v>98341</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>522053</v>
+        <v>522040</v>
       </c>
       <c r="R120" t="n">
-        <v>6936400</v>
+        <v>6936582</v>
       </c>
       <c r="S120" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13213,27 +13228,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>15:07</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>15:07</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>spillning</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13248,22 +13248,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125637290</v>
+        <v>125632405</v>
       </c>
       <c r="B121" t="n">
-        <v>78730</v>
+        <v>91530</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13271,37 +13271,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>522366</v>
+        <v>522044</v>
       </c>
       <c r="R121" t="n">
-        <v>6936463</v>
+        <v>6936401</v>
       </c>
       <c r="S121" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13325,12 +13325,22 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13345,22 +13355,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125632360</v>
+        <v>125601877</v>
       </c>
       <c r="B122" t="n">
-        <v>57648</v>
+        <v>91234</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13368,21 +13378,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13392,13 +13402,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>522247</v>
+        <v>522217</v>
       </c>
       <c r="R122" t="n">
-        <v>6936482</v>
+        <v>6936540</v>
       </c>
       <c r="S122" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13425,24 +13435,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>födosök död stående tall</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13457,22 +13452,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125632405</v>
+        <v>125632383</v>
       </c>
       <c r="B123" t="n">
-        <v>91528</v>
+        <v>91234</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13480,21 +13475,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13504,10 +13499,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>522044</v>
+        <v>522219</v>
       </c>
       <c r="R123" t="n">
-        <v>6936401</v>
+        <v>6936411</v>
       </c>
       <c r="S123" t="n">
         <v>4</v>
@@ -13539,7 +13534,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13549,7 +13544,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13576,10 +13571,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125601877</v>
+        <v>125632360</v>
       </c>
       <c r="B124" t="n">
-        <v>91232</v>
+        <v>57649</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13587,21 +13582,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13611,13 +13606,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>522217</v>
+        <v>522247</v>
       </c>
       <c r="R124" t="n">
-        <v>6936540</v>
+        <v>6936482</v>
       </c>
       <c r="S124" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13644,9 +13639,24 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>födosök död stående tall</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13661,22 +13671,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125632383</v>
+        <v>125637290</v>
       </c>
       <c r="B125" t="n">
-        <v>91232</v>
+        <v>78731</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13684,37 +13694,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>522219</v>
+        <v>522366</v>
       </c>
       <c r="R125" t="n">
-        <v>6936411</v>
+        <v>6936463</v>
       </c>
       <c r="S125" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13738,22 +13748,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13768,44 +13768,44 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125632408</v>
+        <v>125632326</v>
       </c>
       <c r="B126" t="n">
-        <v>98373</v>
+        <v>78973</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13815,10 +13815,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>522057</v>
+        <v>522213</v>
       </c>
       <c r="R126" t="n">
-        <v>6936411</v>
+        <v>6936615</v>
       </c>
       <c r="S126" t="n">
         <v>4</v>
@@ -13850,7 +13850,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13860,7 +13860,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13887,10 +13887,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125632326</v>
+        <v>125635162</v>
       </c>
       <c r="B127" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13898,37 +13898,37 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>522213</v>
+        <v>522010</v>
       </c>
       <c r="R127" t="n">
-        <v>6936615</v>
+        <v>6936407</v>
       </c>
       <c r="S127" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13952,22 +13952,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>13:02</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>13:02</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13982,12 +13972,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
@@ -13997,7 +13987,7 @@
         <v>125646878</v>
       </c>
       <c r="B128" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14094,7 +14084,7 @@
         <v>125632345</v>
       </c>
       <c r="B129" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14198,48 +14188,48 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125635162</v>
+        <v>125632395</v>
       </c>
       <c r="B130" t="n">
-        <v>79590</v>
+        <v>98341</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>522010</v>
+        <v>522113</v>
       </c>
       <c r="R130" t="n">
-        <v>6936407</v>
+        <v>6936367</v>
       </c>
       <c r="S130" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14263,12 +14253,22 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14283,12 +14283,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
@@ -14298,7 +14298,7 @@
         <v>125632388</v>
       </c>
       <c r="B131" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14402,32 +14402,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125632395</v>
+        <v>125632408</v>
       </c>
       <c r="B132" t="n">
-        <v>98339</v>
+        <v>98375</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14437,10 +14437,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>522113</v>
+        <v>522057</v>
       </c>
       <c r="R132" t="n">
-        <v>6936367</v>
+        <v>6936411</v>
       </c>
       <c r="S132" t="n">
         <v>4</v>
@@ -14472,7 +14472,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14482,7 +14482,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14512,7 +14512,7 @@
         <v>125632414</v>
       </c>
       <c r="B133" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         <v>125601077</v>
       </c>
       <c r="B134" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14728,48 +14728,48 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125633219</v>
+        <v>125632334</v>
       </c>
       <c r="B135" t="n">
-        <v>98339</v>
+        <v>80105</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>MD0:Ånge, SE-VN, SE, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>522237</v>
+        <v>522239</v>
       </c>
       <c r="R135" t="n">
-        <v>6936437</v>
+        <v>6936600</v>
       </c>
       <c r="S135" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14808,7 +14808,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14835,32 +14835,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125632359</v>
+        <v>125632407</v>
       </c>
       <c r="B136" t="n">
-        <v>98339</v>
+        <v>91234</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14870,10 +14870,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>522236</v>
+        <v>522052</v>
       </c>
       <c r="R136" t="n">
-        <v>6936482</v>
+        <v>6936413</v>
       </c>
       <c r="S136" t="n">
         <v>4</v>
@@ -14905,7 +14905,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14942,10 +14942,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125632373</v>
+        <v>125633219</v>
       </c>
       <c r="B137" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14973,17 +14973,17 @@
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>MD0:Ånge, SE-VN, SE, Mpd</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>522236</v>
+        <v>522237</v>
       </c>
       <c r="R137" t="n">
-        <v>6936449</v>
+        <v>6936437</v>
       </c>
       <c r="S137" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15049,10 +15049,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125632352</v>
+        <v>125632373</v>
       </c>
       <c r="B138" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15084,10 +15084,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>522245</v>
+        <v>522236</v>
       </c>
       <c r="R138" t="n">
-        <v>6936497</v>
+        <v>6936449</v>
       </c>
       <c r="S138" t="n">
         <v>4</v>
@@ -15119,7 +15119,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15156,32 +15156,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125632334</v>
+        <v>125632352</v>
       </c>
       <c r="B139" t="n">
-        <v>80104</v>
+        <v>98341</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15191,10 +15191,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>522239</v>
+        <v>522245</v>
       </c>
       <c r="R139" t="n">
-        <v>6936600</v>
+        <v>6936497</v>
       </c>
       <c r="S139" t="n">
         <v>4</v>
@@ -15226,7 +15226,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15236,7 +15236,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15263,32 +15263,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125632407</v>
+        <v>125632359</v>
       </c>
       <c r="B140" t="n">
-        <v>91232</v>
+        <v>98341</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15298,10 +15298,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>522052</v>
+        <v>522236</v>
       </c>
       <c r="R140" t="n">
-        <v>6936413</v>
+        <v>6936482</v>
       </c>
       <c r="S140" t="n">
         <v>4</v>
@@ -15333,7 +15333,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15343,7 +15343,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15373,7 +15373,7 @@
         <v>125636452</v>
       </c>
       <c r="B141" t="n">
-        <v>91393</v>
+        <v>91395</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15467,32 +15467,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125632389</v>
+        <v>125646901</v>
       </c>
       <c r="B142" t="n">
-        <v>78972</v>
+        <v>92524</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15502,13 +15502,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>522188</v>
+        <v>522030</v>
       </c>
       <c r="R142" t="n">
-        <v>6936385</v>
+        <v>6936634</v>
       </c>
       <c r="S142" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15532,22 +15532,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15562,44 +15552,44 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125646901</v>
+        <v>125632389</v>
       </c>
       <c r="B143" t="n">
-        <v>92522</v>
+        <v>78973</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15609,13 +15599,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>522030</v>
+        <v>522188</v>
       </c>
       <c r="R143" t="n">
-        <v>6936634</v>
+        <v>6936385</v>
       </c>
       <c r="S143" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15639,12 +15629,22 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15659,22 +15659,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125632364</v>
+        <v>125632375</v>
       </c>
       <c r="B144" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15706,10 +15706,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>522260</v>
+        <v>522243</v>
       </c>
       <c r="R144" t="n">
-        <v>6936473</v>
+        <v>6936427</v>
       </c>
       <c r="S144" t="n">
         <v>4</v>
@@ -15741,7 +15741,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15751,7 +15751,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15778,10 +15778,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125632375</v>
+        <v>125633218</v>
       </c>
       <c r="B145" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15809,17 +15809,17 @@
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>MD1:Ånge, SE-VN, SE, Mpd</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>522243</v>
+        <v>522221</v>
       </c>
       <c r="R145" t="n">
-        <v>6936427</v>
+        <v>6936591</v>
       </c>
       <c r="S145" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -15858,7 +15858,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15885,10 +15885,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125633218</v>
+        <v>125632364</v>
       </c>
       <c r="B146" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15916,17 +15916,17 @@
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>MD1:Ånge, SE-VN, SE, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>522221</v>
+        <v>522260</v>
       </c>
       <c r="R146" t="n">
-        <v>6936591</v>
+        <v>6936473</v>
       </c>
       <c r="S146" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15965,7 +15965,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15992,32 +15992,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125646888</v>
+        <v>125632331</v>
       </c>
       <c r="B147" t="n">
-        <v>98339</v>
+        <v>92524</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16027,13 +16027,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>522159</v>
+        <v>522221</v>
       </c>
       <c r="R147" t="n">
-        <v>6936405</v>
+        <v>6936608</v>
       </c>
       <c r="S147" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16057,12 +16057,22 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16077,44 +16087,44 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125632419</v>
+        <v>125632386</v>
       </c>
       <c r="B148" t="n">
-        <v>98339</v>
+        <v>56844</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16124,10 +16134,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>522202</v>
+        <v>522200</v>
       </c>
       <c r="R148" t="n">
-        <v>6936414</v>
+        <v>6936398</v>
       </c>
       <c r="S148" t="n">
         <v>4</v>
@@ -16159,7 +16169,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16169,7 +16179,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16196,32 +16206,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125632411</v>
+        <v>125632366</v>
       </c>
       <c r="B149" t="n">
-        <v>98339</v>
+        <v>98362</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16231,10 +16241,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>522063</v>
+        <v>522249</v>
       </c>
       <c r="R149" t="n">
-        <v>6936424</v>
+        <v>6936460</v>
       </c>
       <c r="S149" t="n">
         <v>4</v>
@@ -16266,7 +16276,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16276,7 +16286,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16303,10 +16313,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125632366</v>
+        <v>125632384</v>
       </c>
       <c r="B150" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16338,10 +16348,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>522249</v>
+        <v>522207</v>
       </c>
       <c r="R150" t="n">
-        <v>6936460</v>
+        <v>6936406</v>
       </c>
       <c r="S150" t="n">
         <v>4</v>
@@ -16373,7 +16383,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16383,7 +16393,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16410,32 +16420,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125632384</v>
+        <v>125632419</v>
       </c>
       <c r="B151" t="n">
-        <v>98360</v>
+        <v>98341</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16445,10 +16455,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>522207</v>
+        <v>522202</v>
       </c>
       <c r="R151" t="n">
-        <v>6936406</v>
+        <v>6936414</v>
       </c>
       <c r="S151" t="n">
         <v>4</v>
@@ -16480,7 +16490,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16490,7 +16500,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16517,32 +16527,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125632331</v>
+        <v>125646888</v>
       </c>
       <c r="B152" t="n">
-        <v>92522</v>
+        <v>98341</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16552,13 +16562,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>522221</v>
+        <v>522159</v>
       </c>
       <c r="R152" t="n">
-        <v>6936608</v>
+        <v>6936405</v>
       </c>
       <c r="S152" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16582,22 +16592,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16612,44 +16612,44 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125632386</v>
+        <v>125632411</v>
       </c>
       <c r="B153" t="n">
-        <v>56843</v>
+        <v>98341</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16659,10 +16659,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>522200</v>
+        <v>522063</v>
       </c>
       <c r="R153" t="n">
-        <v>6936398</v>
+        <v>6936424</v>
       </c>
       <c r="S153" t="n">
         <v>4</v>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16704,7 +16704,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16731,32 +16731,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125632343</v>
+        <v>125632376</v>
       </c>
       <c r="B154" t="n">
-        <v>78972</v>
+        <v>56844</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16766,10 +16766,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>522269</v>
+        <v>522237</v>
       </c>
       <c r="R154" t="n">
-        <v>6936560</v>
+        <v>6936423</v>
       </c>
       <c r="S154" t="n">
         <v>4</v>
@@ -16801,7 +16801,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -16811,7 +16811,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16838,32 +16838,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125632327</v>
+        <v>125646899</v>
       </c>
       <c r="B155" t="n">
-        <v>80075</v>
+        <v>91395</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16873,13 +16873,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>522218</v>
+        <v>522143</v>
       </c>
       <c r="R155" t="n">
-        <v>6936625</v>
+        <v>6936554</v>
       </c>
       <c r="S155" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16903,22 +16903,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>13:03</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>13:03</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16933,44 +16923,44 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125646899</v>
+        <v>125632343</v>
       </c>
       <c r="B156" t="n">
-        <v>91393</v>
+        <v>78973</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16980,13 +16970,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>522143</v>
+        <v>522269</v>
       </c>
       <c r="R156" t="n">
-        <v>6936554</v>
+        <v>6936560</v>
       </c>
       <c r="S156" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17010,12 +17000,22 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17030,44 +17030,44 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125632376</v>
+        <v>125632327</v>
       </c>
       <c r="B157" t="n">
-        <v>56843</v>
+        <v>80076</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17077,10 +17077,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>522237</v>
+        <v>522218</v>
       </c>
       <c r="R157" t="n">
-        <v>6936423</v>
+        <v>6936625</v>
       </c>
       <c r="S157" t="n">
         <v>4</v>
@@ -17112,7 +17112,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17122,7 +17122,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17152,7 +17152,7 @@
         <v>125635540</v>
       </c>
       <c r="B158" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>125632393</v>
       </c>
       <c r="B159" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>

--- a/artfynd/A 26476-2025 artfynd.xlsx
+++ b/artfynd/A 26476-2025 artfynd.xlsx
@@ -4751,10 +4751,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125632329</v>
+        <v>125632368</v>
       </c>
       <c r="B39" t="n">
-        <v>80105</v>
+        <v>98362</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4762,21 +4762,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4786,10 +4786,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>522215</v>
+        <v>522245</v>
       </c>
       <c r="R39" t="n">
-        <v>6936627</v>
+        <v>6936456</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4858,32 +4858,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125632337</v>
+        <v>125632353</v>
       </c>
       <c r="B40" t="n">
-        <v>78973</v>
+        <v>98341</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>522224</v>
+        <v>522241</v>
       </c>
       <c r="R40" t="n">
-        <v>6936572</v>
+        <v>6936509</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4965,32 +4965,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125632362</v>
+        <v>125646892</v>
       </c>
       <c r="B41" t="n">
-        <v>78731</v>
+        <v>98341</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5000,13 +5000,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>522249</v>
+        <v>522130</v>
       </c>
       <c r="R41" t="n">
-        <v>6936486</v>
+        <v>6936481</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5030,22 +5030,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5060,44 +5050,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125632338</v>
+        <v>125646893</v>
       </c>
       <c r="B42" t="n">
-        <v>92524</v>
+        <v>98341</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5107,13 +5097,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>522221</v>
+        <v>522204</v>
       </c>
       <c r="R42" t="n">
-        <v>6936572</v>
+        <v>6936495</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5137,22 +5127,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5167,22 +5147,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125636088</v>
+        <v>125632329</v>
       </c>
       <c r="B43" t="n">
-        <v>92524</v>
+        <v>80105</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5190,37 +5170,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>522049</v>
+        <v>522215</v>
       </c>
       <c r="R43" t="n">
-        <v>6936650</v>
+        <v>6936627</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5244,12 +5224,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5264,44 +5254,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125632368</v>
+        <v>125632337</v>
       </c>
       <c r="B44" t="n">
-        <v>98362</v>
+        <v>78973</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5311,10 +5301,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>522245</v>
+        <v>522224</v>
       </c>
       <c r="R44" t="n">
-        <v>6936456</v>
+        <v>6936572</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5346,7 +5336,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5356,7 +5346,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5383,32 +5373,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125632353</v>
+        <v>125632362</v>
       </c>
       <c r="B45" t="n">
-        <v>98341</v>
+        <v>78731</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5418,10 +5408,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>522241</v>
+        <v>522249</v>
       </c>
       <c r="R45" t="n">
-        <v>6936509</v>
+        <v>6936486</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5453,7 +5443,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5463,7 +5453,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5490,32 +5480,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125646892</v>
+        <v>125632338</v>
       </c>
       <c r="B46" t="n">
-        <v>98341</v>
+        <v>92524</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5525,13 +5515,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>522130</v>
+        <v>522221</v>
       </c>
       <c r="R46" t="n">
-        <v>6936481</v>
+        <v>6936572</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5555,12 +5545,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5575,60 +5575,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125646893</v>
+        <v>125636088</v>
       </c>
       <c r="B47" t="n">
-        <v>98341</v>
+        <v>92524</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>522204</v>
+        <v>522049</v>
       </c>
       <c r="R47" t="n">
-        <v>6936495</v>
+        <v>6936650</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6490,10 +6490,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125632400</v>
+        <v>125637287</v>
       </c>
       <c r="B56" t="n">
-        <v>91234</v>
+        <v>79591</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6501,37 +6501,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>522048</v>
+        <v>522356</v>
       </c>
       <c r="R56" t="n">
-        <v>6936403</v>
+        <v>6936466</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6555,22 +6555,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:08</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:08</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6585,22 +6575,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125637287</v>
+        <v>125632336</v>
       </c>
       <c r="B57" t="n">
-        <v>79591</v>
+        <v>78731</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6608,37 +6598,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>522356</v>
+        <v>522224</v>
       </c>
       <c r="R57" t="n">
-        <v>6936466</v>
+        <v>6936572</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6662,12 +6652,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6682,22 +6682,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125632336</v>
+        <v>125637245</v>
       </c>
       <c r="B58" t="n">
-        <v>78731</v>
+        <v>80076</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6705,37 +6705,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>522224</v>
+        <v>522360</v>
       </c>
       <c r="R58" t="n">
-        <v>6936572</v>
+        <v>6936453</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6759,22 +6759,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>13:25</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>13:25</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6789,22 +6779,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125637245</v>
+        <v>125632400</v>
       </c>
       <c r="B59" t="n">
-        <v>80076</v>
+        <v>91234</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6812,37 +6802,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>522360</v>
+        <v>522048</v>
       </c>
       <c r="R59" t="n">
-        <v>6936453</v>
+        <v>6936403</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6866,12 +6856,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6886,44 +6886,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125632410</v>
+        <v>125646891</v>
       </c>
       <c r="B60" t="n">
-        <v>92524</v>
+        <v>98341</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6933,13 +6933,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>522063</v>
+        <v>522159</v>
       </c>
       <c r="R60" t="n">
-        <v>6936423</v>
+        <v>6936408</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6963,22 +6963,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6993,44 +6983,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125632324</v>
+        <v>125632392</v>
       </c>
       <c r="B61" t="n">
-        <v>92524</v>
+        <v>98341</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7040,10 +7030,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>522198</v>
+        <v>522181</v>
       </c>
       <c r="R61" t="n">
-        <v>6936634</v>
+        <v>6936381</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -7075,7 +7065,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7085,7 +7075,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7112,32 +7102,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125632356</v>
+        <v>125632398</v>
       </c>
       <c r="B62" t="n">
-        <v>78973</v>
+        <v>98341</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7147,10 +7137,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>522233</v>
+        <v>522059</v>
       </c>
       <c r="R62" t="n">
-        <v>6936499</v>
+        <v>6936399</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -7182,7 +7172,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7192,7 +7182,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7219,7 +7209,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125646891</v>
+        <v>125632354</v>
       </c>
       <c r="B63" t="n">
         <v>98341</v>
@@ -7254,13 +7244,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>522159</v>
+        <v>522234</v>
       </c>
       <c r="R63" t="n">
-        <v>6936408</v>
+        <v>6936499</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7284,12 +7274,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7304,19 +7304,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125632392</v>
+        <v>125646887</v>
       </c>
       <c r="B64" t="n">
         <v>98341</v>
@@ -7351,13 +7351,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>522181</v>
+        <v>522185</v>
       </c>
       <c r="R64" t="n">
-        <v>6936381</v>
+        <v>6936414</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7381,22 +7381,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7411,44 +7401,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125632398</v>
+        <v>125632410</v>
       </c>
       <c r="B65" t="n">
-        <v>98341</v>
+        <v>92524</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7458,10 +7448,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>522059</v>
+        <v>522063</v>
       </c>
       <c r="R65" t="n">
-        <v>6936399</v>
+        <v>6936423</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7493,7 +7483,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7503,7 +7493,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7530,32 +7520,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125632354</v>
+        <v>125632324</v>
       </c>
       <c r="B66" t="n">
-        <v>98341</v>
+        <v>92524</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7565,10 +7555,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>522234</v>
+        <v>522198</v>
       </c>
       <c r="R66" t="n">
-        <v>6936499</v>
+        <v>6936634</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -7600,7 +7590,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7610,7 +7600,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7637,32 +7627,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125646887</v>
+        <v>125632356</v>
       </c>
       <c r="B67" t="n">
-        <v>98341</v>
+        <v>78973</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7672,13 +7662,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>522185</v>
+        <v>522233</v>
       </c>
       <c r="R67" t="n">
-        <v>6936414</v>
+        <v>6936499</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7702,12 +7692,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7722,12 +7722,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -13780,32 +13780,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125632326</v>
+        <v>125632388</v>
       </c>
       <c r="B126" t="n">
-        <v>78973</v>
+        <v>98341</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13815,10 +13815,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>522213</v>
+        <v>522190</v>
       </c>
       <c r="R126" t="n">
-        <v>6936615</v>
+        <v>6936390</v>
       </c>
       <c r="S126" t="n">
         <v>4</v>
@@ -13850,7 +13850,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13860,7 +13860,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13887,10 +13887,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125635162</v>
+        <v>125632326</v>
       </c>
       <c r="B127" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13898,37 +13898,37 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>522010</v>
+        <v>522213</v>
       </c>
       <c r="R127" t="n">
-        <v>6936407</v>
+        <v>6936615</v>
       </c>
       <c r="S127" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13952,12 +13952,22 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13972,22 +13982,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125646878</v>
+        <v>125635162</v>
       </c>
       <c r="B128" t="n">
-        <v>80076</v>
+        <v>79591</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13995,37 +14005,37 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>522019</v>
+        <v>522010</v>
       </c>
       <c r="R128" t="n">
-        <v>6936608</v>
+        <v>6936407</v>
       </c>
       <c r="S128" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14081,10 +14091,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125632345</v>
+        <v>125646878</v>
       </c>
       <c r="B129" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14092,21 +14102,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14116,13 +14126,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>522244</v>
+        <v>522019</v>
       </c>
       <c r="R129" t="n">
-        <v>6936537</v>
+        <v>6936608</v>
       </c>
       <c r="S129" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14146,22 +14156,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>13:34</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>13:34</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14176,44 +14176,44 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125632395</v>
+        <v>125632345</v>
       </c>
       <c r="B130" t="n">
-        <v>98341</v>
+        <v>78973</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14223,10 +14223,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>522113</v>
+        <v>522244</v>
       </c>
       <c r="R130" t="n">
-        <v>6936367</v>
+        <v>6936537</v>
       </c>
       <c r="S130" t="n">
         <v>4</v>
@@ -14258,7 +14258,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14295,7 +14295,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125632388</v>
+        <v>125632395</v>
       </c>
       <c r="B131" t="n">
         <v>98341</v>
@@ -14330,10 +14330,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>522190</v>
+        <v>522113</v>
       </c>
       <c r="R131" t="n">
-        <v>6936390</v>
+        <v>6936367</v>
       </c>
       <c r="S131" t="n">
         <v>4</v>
@@ -14365,7 +14365,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14375,7 +14375,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14728,32 +14728,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125632334</v>
+        <v>125632407</v>
       </c>
       <c r="B135" t="n">
-        <v>80105</v>
+        <v>91234</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14763,10 +14763,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>522239</v>
+        <v>522052</v>
       </c>
       <c r="R135" t="n">
-        <v>6936600</v>
+        <v>6936413</v>
       </c>
       <c r="S135" t="n">
         <v>4</v>
@@ -14798,7 +14798,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14808,7 +14808,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14835,32 +14835,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125632407</v>
+        <v>125632334</v>
       </c>
       <c r="B136" t="n">
-        <v>91234</v>
+        <v>80105</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14870,10 +14870,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>522052</v>
+        <v>522239</v>
       </c>
       <c r="R136" t="n">
-        <v>6936413</v>
+        <v>6936600</v>
       </c>
       <c r="S136" t="n">
         <v>4</v>
@@ -14905,7 +14905,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15992,10 +15992,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125632331</v>
+        <v>125632386</v>
       </c>
       <c r="B147" t="n">
-        <v>92524</v>
+        <v>56844</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16003,21 +16003,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>522221</v>
+        <v>522200</v>
       </c>
       <c r="R147" t="n">
-        <v>6936608</v>
+        <v>6936398</v>
       </c>
       <c r="S147" t="n">
         <v>4</v>
@@ -16062,7 +16062,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16072,7 +16072,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16099,32 +16099,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125632386</v>
+        <v>125632419</v>
       </c>
       <c r="B148" t="n">
-        <v>56844</v>
+        <v>98341</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16134,10 +16134,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>522200</v>
+        <v>522202</v>
       </c>
       <c r="R148" t="n">
-        <v>6936398</v>
+        <v>6936414</v>
       </c>
       <c r="S148" t="n">
         <v>4</v>
@@ -16169,7 +16169,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16179,7 +16179,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16206,32 +16206,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125632366</v>
+        <v>125646888</v>
       </c>
       <c r="B149" t="n">
-        <v>98362</v>
+        <v>98341</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16241,13 +16241,13 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>522249</v>
+        <v>522159</v>
       </c>
       <c r="R149" t="n">
-        <v>6936460</v>
+        <v>6936405</v>
       </c>
       <c r="S149" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16271,22 +16271,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16301,44 +16291,44 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125632384</v>
+        <v>125632411</v>
       </c>
       <c r="B150" t="n">
-        <v>98362</v>
+        <v>98341</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16348,10 +16338,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>522207</v>
+        <v>522063</v>
       </c>
       <c r="R150" t="n">
-        <v>6936406</v>
+        <v>6936424</v>
       </c>
       <c r="S150" t="n">
         <v>4</v>
@@ -16383,7 +16373,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16393,7 +16383,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16420,32 +16410,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125632419</v>
+        <v>125632331</v>
       </c>
       <c r="B151" t="n">
-        <v>98341</v>
+        <v>92524</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16455,10 +16445,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>522202</v>
+        <v>522221</v>
       </c>
       <c r="R151" t="n">
-        <v>6936414</v>
+        <v>6936608</v>
       </c>
       <c r="S151" t="n">
         <v>4</v>
@@ -16490,7 +16480,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16500,7 +16490,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16527,32 +16517,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125646888</v>
+        <v>125632366</v>
       </c>
       <c r="B152" t="n">
-        <v>98341</v>
+        <v>98362</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16562,13 +16552,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>522159</v>
+        <v>522249</v>
       </c>
       <c r="R152" t="n">
-        <v>6936405</v>
+        <v>6936460</v>
       </c>
       <c r="S152" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16592,12 +16582,22 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16612,44 +16612,44 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125632411</v>
+        <v>125632384</v>
       </c>
       <c r="B153" t="n">
-        <v>98341</v>
+        <v>98362</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16659,10 +16659,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>522063</v>
+        <v>522207</v>
       </c>
       <c r="R153" t="n">
-        <v>6936424</v>
+        <v>6936406</v>
       </c>
       <c r="S153" t="n">
         <v>4</v>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16704,7 +16704,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD153" t="b">

--- a/artfynd/A 26476-2025 artfynd.xlsx
+++ b/artfynd/A 26476-2025 artfynd.xlsx
@@ -2215,7 +2215,7 @@
         <v>125621452</v>
       </c>
       <c r="B14" t="n">
-        <v>91395</v>
+        <v>91397</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>125620054</v>
       </c>
       <c r="B15" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>125619796</v>
       </c>
       <c r="B18" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>125619751</v>
       </c>
       <c r="B19" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2925,32 +2925,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125601310</v>
+        <v>125646874</v>
       </c>
       <c r="B21" t="n">
-        <v>98341</v>
+        <v>80104</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2960,13 +2960,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>522217</v>
+        <v>522022</v>
       </c>
       <c r="R21" t="n">
-        <v>6936540</v>
+        <v>6936611</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2990,12 +2990,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3010,60 +3010,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125632569</v>
+        <v>125632425</v>
       </c>
       <c r="B22" t="n">
-        <v>98341</v>
+        <v>78973</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>522108</v>
+        <v>522345</v>
       </c>
       <c r="R22" t="n">
-        <v>6936467</v>
+        <v>6936464</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3087,12 +3087,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3107,44 +3117,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125632421</v>
+        <v>125646902</v>
       </c>
       <c r="B23" t="n">
-        <v>98341</v>
+        <v>4869</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>101675</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3154,13 +3164,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>522260</v>
+        <v>522019</v>
       </c>
       <c r="R23" t="n">
-        <v>6936447</v>
+        <v>6936608</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3184,22 +3194,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Kläckhål på asp</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3214,44 +3219,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125646902</v>
+        <v>125601310</v>
       </c>
       <c r="B24" t="n">
-        <v>4869</v>
+        <v>98343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>101675</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3261,13 +3266,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>522019</v>
+        <v>522217</v>
       </c>
       <c r="R24" t="n">
-        <v>6936608</v>
+        <v>6936540</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3291,17 +3296,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Kläckhål på asp</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3316,60 +3316,60 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125632425</v>
+        <v>125632569</v>
       </c>
       <c r="B25" t="n">
-        <v>78973</v>
+        <v>98343</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>522345</v>
+        <v>522108</v>
       </c>
       <c r="R25" t="n">
-        <v>6936464</v>
+        <v>6936467</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3393,22 +3393,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3423,44 +3413,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125646874</v>
+        <v>125632421</v>
       </c>
       <c r="B26" t="n">
-        <v>80104</v>
+        <v>98343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3470,13 +3460,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>522022</v>
+        <v>522260</v>
       </c>
       <c r="R26" t="n">
-        <v>6936611</v>
+        <v>6936447</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3500,12 +3490,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3520,44 +3520,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125602968</v>
+        <v>125646875</v>
       </c>
       <c r="B27" t="n">
-        <v>98362</v>
+        <v>78732</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221952</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3567,13 +3567,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>522217</v>
+        <v>522035</v>
       </c>
       <c r="R27" t="n">
-        <v>6936540</v>
+        <v>6936550</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3597,12 +3597,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3617,44 +3617,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125646875</v>
+        <v>125602968</v>
       </c>
       <c r="B28" t="n">
-        <v>78732</v>
+        <v>98364</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3664,13 +3664,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>522035</v>
+        <v>522217</v>
       </c>
       <c r="R28" t="n">
-        <v>6936550</v>
+        <v>6936540</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3714,44 +3714,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125601890</v>
+        <v>125600280</v>
       </c>
       <c r="B29" t="n">
-        <v>91688</v>
+        <v>92526</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4042,32 +4042,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125600280</v>
+        <v>125632349</v>
       </c>
       <c r="B32" t="n">
-        <v>92524</v>
+        <v>98343</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4077,13 +4077,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>522217</v>
+        <v>522259</v>
       </c>
       <c r="R32" t="n">
-        <v>6936540</v>
+        <v>6936489</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4110,9 +4110,19 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4127,60 +4137,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125632367</v>
+        <v>125636837</v>
       </c>
       <c r="B33" t="n">
-        <v>98362</v>
+        <v>98343</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>522247</v>
+        <v>522164</v>
       </c>
       <c r="R33" t="n">
-        <v>6936458</v>
+        <v>6936587</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4204,22 +4214,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:16</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:16</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4234,22 +4234,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125634580</v>
+        <v>125603562</v>
       </c>
       <c r="B34" t="n">
-        <v>98362</v>
+        <v>80036</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4257,37 +4257,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>229497</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>522044</v>
+        <v>522217</v>
       </c>
       <c r="R34" t="n">
-        <v>6936401</v>
+        <v>6936540</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4311,12 +4311,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4331,44 +4331,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125632349</v>
+        <v>125632367</v>
       </c>
       <c r="B35" t="n">
-        <v>98341</v>
+        <v>98364</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>522259</v>
+        <v>522247</v>
       </c>
       <c r="R35" t="n">
-        <v>6936489</v>
+        <v>6936458</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4450,32 +4450,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125636837</v>
+        <v>125634580</v>
       </c>
       <c r="B36" t="n">
-        <v>98341</v>
+        <v>98364</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4485,10 +4485,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>522164</v>
+        <v>522044</v>
       </c>
       <c r="R36" t="n">
-        <v>6936587</v>
+        <v>6936401</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4547,32 +4547,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125603562</v>
+        <v>125601890</v>
       </c>
       <c r="B37" t="n">
-        <v>80036</v>
+        <v>91690</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229497</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4644,10 +4644,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125632401</v>
+        <v>125632368</v>
       </c>
       <c r="B38" t="n">
-        <v>100523</v>
+        <v>98364</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4655,21 +4655,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4679,10 +4679,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>522046</v>
+        <v>522245</v>
       </c>
       <c r="R38" t="n">
-        <v>6936397</v>
+        <v>6936456</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4751,10 +4751,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125632368</v>
+        <v>125632401</v>
       </c>
       <c r="B39" t="n">
-        <v>98362</v>
+        <v>100525</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4762,21 +4762,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221952</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4786,10 +4786,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>522245</v>
+        <v>522046</v>
       </c>
       <c r="R39" t="n">
-        <v>6936456</v>
+        <v>6936397</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4858,32 +4858,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125632353</v>
+        <v>125632337</v>
       </c>
       <c r="B40" t="n">
-        <v>98341</v>
+        <v>78973</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>522241</v>
+        <v>522224</v>
       </c>
       <c r="R40" t="n">
-        <v>6936509</v>
+        <v>6936572</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4965,32 +4965,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125646892</v>
+        <v>125632329</v>
       </c>
       <c r="B41" t="n">
-        <v>98341</v>
+        <v>80105</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5000,13 +5000,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>522130</v>
+        <v>522215</v>
       </c>
       <c r="R41" t="n">
-        <v>6936481</v>
+        <v>6936627</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5030,12 +5030,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5050,44 +5060,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125646893</v>
+        <v>125632362</v>
       </c>
       <c r="B42" t="n">
-        <v>98341</v>
+        <v>78731</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5097,13 +5107,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>522204</v>
+        <v>522249</v>
       </c>
       <c r="R42" t="n">
-        <v>6936495</v>
+        <v>6936486</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5127,12 +5137,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5147,22 +5167,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125632329</v>
+        <v>125632338</v>
       </c>
       <c r="B43" t="n">
-        <v>80105</v>
+        <v>92526</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5170,21 +5190,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5194,10 +5214,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>522215</v>
+        <v>522221</v>
       </c>
       <c r="R43" t="n">
-        <v>6936627</v>
+        <v>6936572</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5229,7 +5249,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5239,7 +5259,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5266,48 +5286,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125632337</v>
+        <v>125636088</v>
       </c>
       <c r="B44" t="n">
-        <v>78973</v>
+        <v>92526</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>522224</v>
+        <v>522049</v>
       </c>
       <c r="R44" t="n">
-        <v>6936572</v>
+        <v>6936650</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5331,22 +5351,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:25</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:25</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5361,44 +5371,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125632362</v>
+        <v>125632353</v>
       </c>
       <c r="B45" t="n">
-        <v>78731</v>
+        <v>98343</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5408,10 +5418,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>522249</v>
+        <v>522241</v>
       </c>
       <c r="R45" t="n">
-        <v>6936486</v>
+        <v>6936509</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5443,7 +5453,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5453,7 +5463,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5480,32 +5490,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125632338</v>
+        <v>125646893</v>
       </c>
       <c r="B46" t="n">
-        <v>92524</v>
+        <v>98343</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5515,13 +5525,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>522221</v>
+        <v>522204</v>
       </c>
       <c r="R46" t="n">
-        <v>6936572</v>
+        <v>6936495</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5545,22 +5555,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5575,60 +5575,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125636088</v>
+        <v>125646892</v>
       </c>
       <c r="B47" t="n">
-        <v>92524</v>
+        <v>98343</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>522049</v>
+        <v>522130</v>
       </c>
       <c r="R47" t="n">
-        <v>6936650</v>
+        <v>6936481</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>125632416</v>
       </c>
       <c r="B48" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5791,32 +5791,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125600818</v>
+        <v>125646883</v>
       </c>
       <c r="B49" t="n">
-        <v>98258</v>
+        <v>98343</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5826,13 +5826,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>522217</v>
+        <v>522097</v>
       </c>
       <c r="R49" t="n">
-        <v>6936540</v>
+        <v>6936427</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5876,12 +5876,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5891,7 +5891,7 @@
         <v>125638972</v>
       </c>
       <c r="B50" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>125632382</v>
       </c>
       <c r="B51" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6092,32 +6092,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125646883</v>
+        <v>125600818</v>
       </c>
       <c r="B52" t="n">
-        <v>98341</v>
+        <v>98260</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6127,13 +6127,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>522097</v>
+        <v>522217</v>
       </c>
       <c r="R52" t="n">
-        <v>6936427</v>
+        <v>6936540</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6157,12 +6157,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6177,44 +6177,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125632815</v>
+        <v>125637287</v>
       </c>
       <c r="B53" t="n">
-        <v>98362</v>
+        <v>79591</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6224,10 +6224,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>522129</v>
+        <v>522356</v>
       </c>
       <c r="R53" t="n">
-        <v>6936436</v>
+        <v>6936466</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6286,48 +6286,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125632397</v>
+        <v>125637245</v>
       </c>
       <c r="B54" t="n">
-        <v>98341</v>
+        <v>80076</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>522077</v>
+        <v>522360</v>
       </c>
       <c r="R54" t="n">
-        <v>6936379</v>
+        <v>6936453</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6351,22 +6351,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6381,60 +6371,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125636925</v>
+        <v>125632336</v>
       </c>
       <c r="B55" t="n">
-        <v>98341</v>
+        <v>78731</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>522220</v>
+        <v>522224</v>
       </c>
       <c r="R55" t="n">
-        <v>6936601</v>
+        <v>6936572</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6458,12 +6448,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6478,22 +6478,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125637287</v>
+        <v>125632400</v>
       </c>
       <c r="B56" t="n">
-        <v>79591</v>
+        <v>91236</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6501,37 +6501,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>522356</v>
+        <v>522048</v>
       </c>
       <c r="R56" t="n">
-        <v>6936466</v>
+        <v>6936403</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6555,12 +6555,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6575,44 +6585,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125632336</v>
+        <v>125632397</v>
       </c>
       <c r="B57" t="n">
-        <v>78731</v>
+        <v>98343</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6622,10 +6632,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>522224</v>
+        <v>522077</v>
       </c>
       <c r="R57" t="n">
-        <v>6936572</v>
+        <v>6936379</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6657,7 +6667,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6667,7 +6677,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6694,32 +6704,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125637245</v>
+        <v>125632815</v>
       </c>
       <c r="B58" t="n">
-        <v>80076</v>
+        <v>98364</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6729,13 +6739,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>522360</v>
+        <v>522129</v>
       </c>
       <c r="R58" t="n">
-        <v>6936453</v>
+        <v>6936436</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6791,48 +6801,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125632400</v>
+        <v>125636925</v>
       </c>
       <c r="B59" t="n">
-        <v>91234</v>
+        <v>98343</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>522048</v>
+        <v>522220</v>
       </c>
       <c r="R59" t="n">
-        <v>6936403</v>
+        <v>6936601</v>
       </c>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6856,22 +6866,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>15:08</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>15:08</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6886,44 +6886,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125646891</v>
+        <v>125632356</v>
       </c>
       <c r="B60" t="n">
-        <v>98341</v>
+        <v>78973</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6933,13 +6933,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>522159</v>
+        <v>522233</v>
       </c>
       <c r="R60" t="n">
-        <v>6936408</v>
+        <v>6936499</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6963,12 +6963,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6983,44 +6993,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125632392</v>
+        <v>125632410</v>
       </c>
       <c r="B61" t="n">
-        <v>98341</v>
+        <v>92526</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7030,10 +7040,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>522181</v>
+        <v>522063</v>
       </c>
       <c r="R61" t="n">
-        <v>6936381</v>
+        <v>6936423</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -7065,7 +7075,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7075,7 +7085,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7102,32 +7112,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125632398</v>
+        <v>125632324</v>
       </c>
       <c r="B62" t="n">
-        <v>98341</v>
+        <v>92526</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7137,10 +7147,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>522059</v>
+        <v>522198</v>
       </c>
       <c r="R62" t="n">
-        <v>6936399</v>
+        <v>6936634</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -7172,7 +7182,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7182,7 +7192,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7209,10 +7219,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125632354</v>
+        <v>125632398</v>
       </c>
       <c r="B63" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7244,10 +7254,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>522234</v>
+        <v>522059</v>
       </c>
       <c r="R63" t="n">
-        <v>6936499</v>
+        <v>6936399</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -7279,7 +7289,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7289,7 +7299,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7316,10 +7326,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125646887</v>
+        <v>125632354</v>
       </c>
       <c r="B64" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7351,13 +7361,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>522185</v>
+        <v>522234</v>
       </c>
       <c r="R64" t="n">
-        <v>6936414</v>
+        <v>6936499</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7381,12 +7391,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7401,44 +7421,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125632410</v>
+        <v>125646891</v>
       </c>
       <c r="B65" t="n">
-        <v>92524</v>
+        <v>98343</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7448,13 +7468,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>522063</v>
+        <v>522159</v>
       </c>
       <c r="R65" t="n">
-        <v>6936423</v>
+        <v>6936408</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7478,22 +7498,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7508,44 +7518,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125632324</v>
+        <v>125632392</v>
       </c>
       <c r="B66" t="n">
-        <v>92524</v>
+        <v>98343</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7555,10 +7565,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>522198</v>
+        <v>522181</v>
       </c>
       <c r="R66" t="n">
-        <v>6936634</v>
+        <v>6936381</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -7590,7 +7600,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7600,7 +7610,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7627,32 +7637,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125632356</v>
+        <v>125646887</v>
       </c>
       <c r="B67" t="n">
-        <v>78973</v>
+        <v>98343</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7662,13 +7672,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>522233</v>
+        <v>522185</v>
       </c>
       <c r="R67" t="n">
-        <v>6936499</v>
+        <v>6936414</v>
       </c>
       <c r="S67" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7692,22 +7702,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>13:52</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>13:52</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7722,12 +7722,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7737,7 +7737,7 @@
         <v>125632422</v>
       </c>
       <c r="B68" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>125632396</v>
       </c>
       <c r="B69" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>125632361</v>
       </c>
       <c r="B70" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8055,10 +8055,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125632357</v>
+        <v>125646879</v>
       </c>
       <c r="B71" t="n">
-        <v>91234</v>
+        <v>80076</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8066,21 +8066,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>522221</v>
+        <v>522202</v>
       </c>
       <c r="R71" t="n">
-        <v>6936489</v>
+        <v>6936502</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8120,22 +8120,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8150,44 +8140,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125646872</v>
+        <v>125632350</v>
       </c>
       <c r="B72" t="n">
-        <v>91199</v>
+        <v>80076</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8197,13 +8187,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>522064</v>
+        <v>522254</v>
       </c>
       <c r="R72" t="n">
-        <v>6936505</v>
+        <v>6936496</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8227,12 +8217,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8247,44 +8247,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125632350</v>
+        <v>125646872</v>
       </c>
       <c r="B73" t="n">
-        <v>80076</v>
+        <v>91201</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8294,13 +8294,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>522254</v>
+        <v>522064</v>
       </c>
       <c r="R73" t="n">
-        <v>6936496</v>
+        <v>6936505</v>
       </c>
       <c r="S73" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8324,22 +8324,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>13:47</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>13:47</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8354,22 +8344,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125646879</v>
+        <v>125632357</v>
       </c>
       <c r="B74" t="n">
-        <v>80076</v>
+        <v>91236</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8377,21 +8367,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8401,13 +8391,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>522202</v>
+        <v>522221</v>
       </c>
       <c r="R74" t="n">
-        <v>6936502</v>
+        <v>6936489</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8431,12 +8421,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8451,44 +8451,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125632372</v>
+        <v>125632370</v>
       </c>
       <c r="B75" t="n">
-        <v>98362</v>
+        <v>98343</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8498,10 +8498,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>522236</v>
+        <v>522243</v>
       </c>
       <c r="R75" t="n">
-        <v>6936448</v>
+        <v>6936456</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -8533,7 +8533,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8570,10 +8570,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125632370</v>
+        <v>125632381</v>
       </c>
       <c r="B76" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>522243</v>
+        <v>522240</v>
       </c>
       <c r="R76" t="n">
-        <v>6936456</v>
+        <v>6936412</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8677,10 +8677,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125632381</v>
+        <v>125632418</v>
       </c>
       <c r="B77" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8712,10 +8712,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>522240</v>
+        <v>522162</v>
       </c>
       <c r="R77" t="n">
-        <v>6936412</v>
+        <v>6936404</v>
       </c>
       <c r="S77" t="n">
         <v>4</v>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8784,32 +8784,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125632418</v>
+        <v>125632372</v>
       </c>
       <c r="B78" t="n">
-        <v>98341</v>
+        <v>98364</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8819,10 +8819,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>522162</v>
+        <v>522236</v>
       </c>
       <c r="R78" t="n">
-        <v>6936404</v>
+        <v>6936448</v>
       </c>
       <c r="S78" t="n">
         <v>4</v>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8891,32 +8891,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125632420</v>
+        <v>125632406</v>
       </c>
       <c r="B79" t="n">
-        <v>98362</v>
+        <v>98343</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8926,10 +8926,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>522236</v>
+        <v>522052</v>
       </c>
       <c r="R79" t="n">
-        <v>6936446</v>
+        <v>6936412</v>
       </c>
       <c r="S79" t="n">
         <v>4</v>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8998,10 +8998,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125632406</v>
+        <v>125632387</v>
       </c>
       <c r="B80" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9033,10 +9033,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>522052</v>
+        <v>522191</v>
       </c>
       <c r="R80" t="n">
-        <v>6936412</v>
+        <v>6936398</v>
       </c>
       <c r="S80" t="n">
         <v>4</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9105,10 +9105,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125632377</v>
+        <v>125632423</v>
       </c>
       <c r="B81" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9140,10 +9140,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>522237</v>
+        <v>522332</v>
       </c>
       <c r="R81" t="n">
-        <v>6936417</v>
+        <v>6936449</v>
       </c>
       <c r="S81" t="n">
         <v>4</v>
@@ -9175,7 +9175,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9185,7 +9185,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9212,10 +9212,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125632387</v>
+        <v>125632365</v>
       </c>
       <c r="B82" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9247,10 +9247,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>522191</v>
+        <v>522249</v>
       </c>
       <c r="R82" t="n">
-        <v>6936398</v>
+        <v>6936473</v>
       </c>
       <c r="S82" t="n">
         <v>4</v>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9319,10 +9319,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125632423</v>
+        <v>125632377</v>
       </c>
       <c r="B83" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9354,10 +9354,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>522332</v>
+        <v>522237</v>
       </c>
       <c r="R83" t="n">
-        <v>6936449</v>
+        <v>6936417</v>
       </c>
       <c r="S83" t="n">
         <v>4</v>
@@ -9389,7 +9389,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9426,10 +9426,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125632365</v>
+        <v>125632593</v>
       </c>
       <c r="B84" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9457,17 +9457,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>522249</v>
+        <v>522125</v>
       </c>
       <c r="R84" t="n">
-        <v>6936473</v>
+        <v>6936475</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9491,22 +9491,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>14:14</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>14:14</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9521,12 +9511,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9536,7 +9526,7 @@
         <v>125632554</v>
       </c>
       <c r="B85" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9630,48 +9620,48 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125632593</v>
+        <v>125632420</v>
       </c>
       <c r="B86" t="n">
-        <v>98341</v>
+        <v>98364</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>522125</v>
+        <v>522236</v>
       </c>
       <c r="R86" t="n">
-        <v>6936475</v>
+        <v>6936446</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9695,12 +9685,22 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9715,12 +9715,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9730,7 +9730,7 @@
         <v>125646882</v>
       </c>
       <c r="B87" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>125632417</v>
       </c>
       <c r="B88" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         <v>125635192</v>
       </c>
       <c r="B90" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10125,53 +10125,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125633268</v>
+        <v>125632341</v>
       </c>
       <c r="B91" t="n">
-        <v>57812</v>
+        <v>92526</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>522121</v>
+        <v>522236</v>
       </c>
       <c r="R91" t="n">
-        <v>6936402</v>
+        <v>6936562</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10195,12 +10190,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10215,12 +10220,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10329,48 +10334,53 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125632341</v>
+        <v>125633268</v>
       </c>
       <c r="B93" t="n">
-        <v>92524</v>
+        <v>57812</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>522236</v>
+        <v>522121</v>
       </c>
       <c r="R93" t="n">
-        <v>6936562</v>
+        <v>6936402</v>
       </c>
       <c r="S93" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10394,22 +10404,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10424,44 +10424,44 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125632358</v>
+        <v>125632409</v>
       </c>
       <c r="B94" t="n">
-        <v>98362</v>
+        <v>98343</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10471,10 +10471,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>522231</v>
+        <v>522062</v>
       </c>
       <c r="R94" t="n">
-        <v>6936488</v>
+        <v>6936422</v>
       </c>
       <c r="S94" t="n">
         <v>4</v>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10543,10 +10543,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125632409</v>
+        <v>125632415</v>
       </c>
       <c r="B95" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10578,10 +10578,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>522062</v>
+        <v>522124</v>
       </c>
       <c r="R95" t="n">
-        <v>6936422</v>
+        <v>6936410</v>
       </c>
       <c r="S95" t="n">
         <v>4</v>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10650,32 +10650,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125632415</v>
+        <v>125632358</v>
       </c>
       <c r="B96" t="n">
-        <v>98341</v>
+        <v>98364</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10685,10 +10685,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>522124</v>
+        <v>522231</v>
       </c>
       <c r="R96" t="n">
-        <v>6936410</v>
+        <v>6936488</v>
       </c>
       <c r="S96" t="n">
         <v>4</v>
@@ -10720,7 +10720,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10760,7 +10760,7 @@
         <v>125646894</v>
       </c>
       <c r="B97" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10857,7 +10857,7 @@
         <v>125632344</v>
       </c>
       <c r="B98" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>125646886</v>
       </c>
       <c r="B99" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125632348</v>
+        <v>125646900</v>
       </c>
       <c r="B101" t="n">
         <v>78973</v>
@@ -11200,13 +11200,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>522241</v>
+        <v>521975</v>
       </c>
       <c r="R101" t="n">
-        <v>6936518</v>
+        <v>6936372</v>
       </c>
       <c r="S101" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11230,22 +11230,17 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>13:44</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>13:44</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11260,19 +11255,19 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125646900</v>
+        <v>125632348</v>
       </c>
       <c r="B102" t="n">
         <v>78973</v>
@@ -11307,13 +11302,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>521975</v>
+        <v>522241</v>
       </c>
       <c r="R102" t="n">
-        <v>6936372</v>
+        <v>6936518</v>
       </c>
       <c r="S102" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11337,17 +11332,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11362,44 +11362,44 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125632390</v>
+        <v>125632351</v>
       </c>
       <c r="B103" t="n">
-        <v>91234</v>
+        <v>98343</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11409,10 +11409,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>522187</v>
+        <v>522250</v>
       </c>
       <c r="R103" t="n">
-        <v>6936377</v>
+        <v>6936497</v>
       </c>
       <c r="S103" t="n">
         <v>4</v>
@@ -11444,7 +11444,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11454,7 +11454,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11481,10 +11481,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125632325</v>
+        <v>125646880</v>
       </c>
       <c r="B104" t="n">
-        <v>78731</v>
+        <v>80076</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11492,21 +11492,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11516,13 +11516,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>522198</v>
+        <v>522225</v>
       </c>
       <c r="R104" t="n">
-        <v>6936620</v>
+        <v>6936564</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11546,22 +11546,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>12:57</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>12:57</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11576,22 +11566,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125646880</v>
+        <v>125632323</v>
       </c>
       <c r="B105" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11599,21 +11589,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11623,13 +11613,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>522225</v>
+        <v>522189</v>
       </c>
       <c r="R105" t="n">
-        <v>6936564</v>
+        <v>6936648</v>
       </c>
       <c r="S105" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11653,12 +11643,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11673,12 +11673,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -11787,10 +11787,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125632323</v>
+        <v>125632325</v>
       </c>
       <c r="B107" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11798,21 +11798,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11822,13 +11822,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>522189</v>
+        <v>522198</v>
       </c>
       <c r="R107" t="n">
-        <v>6936648</v>
+        <v>6936620</v>
       </c>
       <c r="S107" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11867,7 +11867,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11991,32 +11991,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125632412</v>
+        <v>125632390</v>
       </c>
       <c r="B109" t="n">
-        <v>98341</v>
+        <v>91236</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12026,10 +12026,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>522101</v>
+        <v>522187</v>
       </c>
       <c r="R109" t="n">
-        <v>6936425</v>
+        <v>6936377</v>
       </c>
       <c r="S109" t="n">
         <v>4</v>
@@ -12061,7 +12061,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12071,7 +12071,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12098,10 +12098,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125632379</v>
+        <v>125646884</v>
       </c>
       <c r="B110" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12133,13 +12133,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>522237</v>
+        <v>522100</v>
       </c>
       <c r="R110" t="n">
-        <v>6936415</v>
+        <v>6936419</v>
       </c>
       <c r="S110" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12163,22 +12163,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>14:26</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>14:26</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12193,22 +12183,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125632340</v>
+        <v>125632412</v>
       </c>
       <c r="B111" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12240,10 +12230,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>522232</v>
+        <v>522101</v>
       </c>
       <c r="R111" t="n">
-        <v>6936562</v>
+        <v>6936425</v>
       </c>
       <c r="S111" t="n">
         <v>4</v>
@@ -12275,7 +12265,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12285,7 +12275,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12312,10 +12302,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125632351</v>
+        <v>125632379</v>
       </c>
       <c r="B112" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12347,10 +12337,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>522250</v>
+        <v>522237</v>
       </c>
       <c r="R112" t="n">
-        <v>6936497</v>
+        <v>6936415</v>
       </c>
       <c r="S112" t="n">
         <v>4</v>
@@ -12382,7 +12372,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12392,7 +12382,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12419,10 +12409,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125646884</v>
+        <v>125632340</v>
       </c>
       <c r="B113" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12454,13 +12444,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>522100</v>
+        <v>522232</v>
       </c>
       <c r="R113" t="n">
-        <v>6936419</v>
+        <v>6936562</v>
       </c>
       <c r="S113" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12484,12 +12474,22 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12504,12 +12504,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -12730,32 +12730,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125632399</v>
+        <v>125632371</v>
       </c>
       <c r="B116" t="n">
-        <v>56844</v>
+        <v>98343</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12765,10 +12765,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>522053</v>
+        <v>522243</v>
       </c>
       <c r="R116" t="n">
-        <v>6936400</v>
+        <v>6936460</v>
       </c>
       <c r="S116" t="n">
         <v>4</v>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12810,12 +12810,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>15:07</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>spillning</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12842,10 +12837,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125632371</v>
+        <v>125632385</v>
       </c>
       <c r="B117" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12877,10 +12872,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>522243</v>
+        <v>522197</v>
       </c>
       <c r="R117" t="n">
-        <v>6936460</v>
+        <v>6936406</v>
       </c>
       <c r="S117" t="n">
         <v>4</v>
@@ -12912,7 +12907,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12922,7 +12917,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12949,10 +12944,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125632385</v>
+        <v>125632394</v>
       </c>
       <c r="B118" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12984,10 +12979,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>522197</v>
+        <v>522136</v>
       </c>
       <c r="R118" t="n">
-        <v>6936406</v>
+        <v>6936370</v>
       </c>
       <c r="S118" t="n">
         <v>4</v>
@@ -13019,7 +13014,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13029,7 +13024,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13056,10 +13051,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125632394</v>
+        <v>125635820</v>
       </c>
       <c r="B119" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13087,17 +13082,17 @@
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>522136</v>
+        <v>522040</v>
       </c>
       <c r="R119" t="n">
-        <v>6936370</v>
+        <v>6936582</v>
       </c>
       <c r="S119" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13121,22 +13116,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13151,60 +13136,60 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125635820</v>
+        <v>125632399</v>
       </c>
       <c r="B120" t="n">
-        <v>98341</v>
+        <v>56844</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>522040</v>
+        <v>522053</v>
       </c>
       <c r="R120" t="n">
-        <v>6936582</v>
+        <v>6936400</v>
       </c>
       <c r="S120" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13228,12 +13213,27 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13248,12 +13248,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -13263,7 +13263,7 @@
         <v>125632405</v>
       </c>
       <c r="B121" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>125601877</v>
       </c>
       <c r="B122" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>125632383</v>
       </c>
       <c r="B123" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13780,32 +13780,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125632388</v>
+        <v>125646878</v>
       </c>
       <c r="B126" t="n">
-        <v>98341</v>
+        <v>80076</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13815,13 +13815,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>522190</v>
+        <v>522019</v>
       </c>
       <c r="R126" t="n">
-        <v>6936390</v>
+        <v>6936608</v>
       </c>
       <c r="S126" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13845,22 +13845,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13875,19 +13865,19 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125632326</v>
+        <v>125632345</v>
       </c>
       <c r="B127" t="n">
         <v>78973</v>
@@ -13922,10 +13912,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>522213</v>
+        <v>522244</v>
       </c>
       <c r="R127" t="n">
-        <v>6936615</v>
+        <v>6936537</v>
       </c>
       <c r="S127" t="n">
         <v>4</v>
@@ -13957,7 +13947,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -13967,7 +13957,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14091,10 +14081,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125646878</v>
+        <v>125601077</v>
       </c>
       <c r="B129" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14102,21 +14092,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14126,13 +14116,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>522019</v>
+        <v>522217</v>
       </c>
       <c r="R129" t="n">
-        <v>6936608</v>
+        <v>6936540</v>
       </c>
       <c r="S129" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14156,12 +14146,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14172,48 +14162,63 @@
       </c>
       <c r="AG129" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125632345</v>
+        <v>125632395</v>
       </c>
       <c r="B130" t="n">
-        <v>78973</v>
+        <v>98343</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14223,10 +14228,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>522244</v>
+        <v>522113</v>
       </c>
       <c r="R130" t="n">
-        <v>6936537</v>
+        <v>6936367</v>
       </c>
       <c r="S130" t="n">
         <v>4</v>
@@ -14258,7 +14263,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14268,7 +14273,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14295,10 +14300,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125632395</v>
+        <v>125632388</v>
       </c>
       <c r="B131" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14330,10 +14335,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>522113</v>
+        <v>522190</v>
       </c>
       <c r="R131" t="n">
-        <v>6936367</v>
+        <v>6936390</v>
       </c>
       <c r="S131" t="n">
         <v>4</v>
@@ -14365,7 +14370,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14375,7 +14380,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14405,7 +14410,7 @@
         <v>125632408</v>
       </c>
       <c r="B132" t="n">
-        <v>98375</v>
+        <v>98377</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14509,10 +14514,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125632414</v>
+        <v>125632326</v>
       </c>
       <c r="B133" t="n">
-        <v>91234</v>
+        <v>78973</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14520,21 +14525,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14544,10 +14549,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>522109</v>
+        <v>522213</v>
       </c>
       <c r="R133" t="n">
-        <v>6936426</v>
+        <v>6936615</v>
       </c>
       <c r="S133" t="n">
         <v>4</v>
@@ -14579,7 +14584,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14589,7 +14594,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14616,10 +14621,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125601077</v>
+        <v>125632414</v>
       </c>
       <c r="B134" t="n">
-        <v>80077</v>
+        <v>91236</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14627,21 +14632,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14651,13 +14656,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>522217</v>
+        <v>522109</v>
       </c>
       <c r="R134" t="n">
-        <v>6936540</v>
+        <v>6936426</v>
       </c>
       <c r="S134" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14684,11 +14689,21 @@
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-06-01</t>
         </is>
       </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
@@ -14697,63 +14712,48 @@
       </c>
       <c r="AG134" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ134" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125632407</v>
+        <v>125632334</v>
       </c>
       <c r="B135" t="n">
-        <v>91234</v>
+        <v>80105</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14763,10 +14763,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>522052</v>
+        <v>522239</v>
       </c>
       <c r="R135" t="n">
-        <v>6936413</v>
+        <v>6936600</v>
       </c>
       <c r="S135" t="n">
         <v>4</v>
@@ -14798,7 +14798,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14808,7 +14808,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14835,32 +14835,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125632334</v>
+        <v>125632407</v>
       </c>
       <c r="B136" t="n">
-        <v>80105</v>
+        <v>91236</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14870,10 +14870,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>522239</v>
+        <v>522052</v>
       </c>
       <c r="R136" t="n">
-        <v>6936600</v>
+        <v>6936413</v>
       </c>
       <c r="S136" t="n">
         <v>4</v>
@@ -14905,7 +14905,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14945,7 +14945,7 @@
         <v>125633219</v>
       </c>
       <c r="B137" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>125632373</v>
       </c>
       <c r="B138" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15156,10 +15156,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125632352</v>
+        <v>125632359</v>
       </c>
       <c r="B139" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15191,10 +15191,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>522245</v>
+        <v>522236</v>
       </c>
       <c r="R139" t="n">
-        <v>6936497</v>
+        <v>6936482</v>
       </c>
       <c r="S139" t="n">
         <v>4</v>
@@ -15226,7 +15226,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15236,7 +15236,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15263,10 +15263,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125632359</v>
+        <v>125632352</v>
       </c>
       <c r="B140" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15298,10 +15298,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>522236</v>
+        <v>522245</v>
       </c>
       <c r="R140" t="n">
-        <v>6936482</v>
+        <v>6936497</v>
       </c>
       <c r="S140" t="n">
         <v>4</v>
@@ -15333,7 +15333,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15343,7 +15343,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15370,48 +15370,48 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125636452</v>
+        <v>125646901</v>
       </c>
       <c r="B141" t="n">
-        <v>91395</v>
+        <v>92526</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>522141</v>
+        <v>522030</v>
       </c>
       <c r="R141" t="n">
-        <v>6936548</v>
+        <v>6936634</v>
       </c>
       <c r="S141" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15467,32 +15467,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125646901</v>
+        <v>125632389</v>
       </c>
       <c r="B142" t="n">
-        <v>92524</v>
+        <v>78973</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15502,13 +15502,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>522030</v>
+        <v>522188</v>
       </c>
       <c r="R142" t="n">
-        <v>6936634</v>
+        <v>6936385</v>
       </c>
       <c r="S142" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15532,12 +15532,22 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15552,60 +15562,60 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125632389</v>
+        <v>125636452</v>
       </c>
       <c r="B143" t="n">
-        <v>78973</v>
+        <v>91397</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>522188</v>
+        <v>522141</v>
       </c>
       <c r="R143" t="n">
-        <v>6936385</v>
+        <v>6936548</v>
       </c>
       <c r="S143" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15629,22 +15639,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15659,12 +15659,12 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
@@ -15674,7 +15674,7 @@
         <v>125632375</v>
       </c>
       <c r="B144" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>125633218</v>
       </c>
       <c r="B145" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>125632364</v>
       </c>
       <c r="B146" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15992,10 +15992,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125632386</v>
+        <v>125632366</v>
       </c>
       <c r="B147" t="n">
-        <v>56844</v>
+        <v>98364</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16003,21 +16003,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>522200</v>
+        <v>522249</v>
       </c>
       <c r="R147" t="n">
-        <v>6936398</v>
+        <v>6936460</v>
       </c>
       <c r="S147" t="n">
         <v>4</v>
@@ -16062,7 +16062,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16072,7 +16072,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16099,32 +16099,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125632419</v>
+        <v>125632384</v>
       </c>
       <c r="B148" t="n">
-        <v>98341</v>
+        <v>98364</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16134,10 +16134,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>522202</v>
+        <v>522207</v>
       </c>
       <c r="R148" t="n">
-        <v>6936414</v>
+        <v>6936406</v>
       </c>
       <c r="S148" t="n">
         <v>4</v>
@@ -16169,7 +16169,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16179,7 +16179,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16206,32 +16206,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125646888</v>
+        <v>125632331</v>
       </c>
       <c r="B149" t="n">
-        <v>98341</v>
+        <v>92526</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16241,13 +16241,13 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>522159</v>
+        <v>522221</v>
       </c>
       <c r="R149" t="n">
-        <v>6936405</v>
+        <v>6936608</v>
       </c>
       <c r="S149" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16271,12 +16271,22 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16291,44 +16301,44 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125632411</v>
+        <v>125632386</v>
       </c>
       <c r="B150" t="n">
-        <v>98341</v>
+        <v>56844</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16338,10 +16348,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>522063</v>
+        <v>522200</v>
       </c>
       <c r="R150" t="n">
-        <v>6936424</v>
+        <v>6936398</v>
       </c>
       <c r="S150" t="n">
         <v>4</v>
@@ -16373,7 +16383,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16383,7 +16393,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16410,32 +16420,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125632331</v>
+        <v>125632419</v>
       </c>
       <c r="B151" t="n">
-        <v>92524</v>
+        <v>98343</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16445,10 +16455,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>522221</v>
+        <v>522202</v>
       </c>
       <c r="R151" t="n">
-        <v>6936608</v>
+        <v>6936414</v>
       </c>
       <c r="S151" t="n">
         <v>4</v>
@@ -16480,7 +16490,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16490,7 +16500,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16517,32 +16527,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125632366</v>
+        <v>125646888</v>
       </c>
       <c r="B152" t="n">
-        <v>98362</v>
+        <v>98343</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16552,13 +16562,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>522249</v>
+        <v>522159</v>
       </c>
       <c r="R152" t="n">
-        <v>6936460</v>
+        <v>6936405</v>
       </c>
       <c r="S152" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16582,22 +16592,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16612,44 +16612,44 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125632384</v>
+        <v>125632411</v>
       </c>
       <c r="B153" t="n">
-        <v>98362</v>
+        <v>98343</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16659,10 +16659,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>522207</v>
+        <v>522063</v>
       </c>
       <c r="R153" t="n">
-        <v>6936406</v>
+        <v>6936424</v>
       </c>
       <c r="S153" t="n">
         <v>4</v>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16704,7 +16704,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16731,32 +16731,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125632376</v>
+        <v>125646899</v>
       </c>
       <c r="B154" t="n">
-        <v>56844</v>
+        <v>91397</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100138</v>
+        <v>1503</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16766,13 +16766,13 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>522237</v>
+        <v>522143</v>
       </c>
       <c r="R154" t="n">
-        <v>6936423</v>
+        <v>6936554</v>
       </c>
       <c r="S154" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16796,22 +16796,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16826,44 +16816,44 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125646899</v>
+        <v>125632376</v>
       </c>
       <c r="B155" t="n">
-        <v>91395</v>
+        <v>56844</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1503</v>
+        <v>100138</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16873,13 +16863,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>522143</v>
+        <v>522237</v>
       </c>
       <c r="R155" t="n">
-        <v>6936554</v>
+        <v>6936423</v>
       </c>
       <c r="S155" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16903,12 +16893,22 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16923,12 +16923,12 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
@@ -17152,7 +17152,7 @@
         <v>125635540</v>
       </c>
       <c r="B158" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>125632393</v>
       </c>
       <c r="B159" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>

--- a/artfynd/A 26476-2025 artfynd.xlsx
+++ b/artfynd/A 26476-2025 artfynd.xlsx
@@ -4042,10 +4042,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125632349</v>
+        <v>125601890</v>
       </c>
       <c r="B32" t="n">
-        <v>98343</v>
+        <v>91690</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4053,21 +4053,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4077,13 +4077,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>522259</v>
+        <v>522217</v>
       </c>
       <c r="R32" t="n">
-        <v>6936489</v>
+        <v>6936540</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4110,19 +4110,9 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4137,19 +4127,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Henrik Ekvall</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125636837</v>
+        <v>125632349</v>
       </c>
       <c r="B33" t="n">
         <v>98343</v>
@@ -4180,17 +4170,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>522164</v>
+        <v>522259</v>
       </c>
       <c r="R33" t="n">
-        <v>6936587</v>
+        <v>6936489</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4214,12 +4204,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4234,12 +4234,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4547,10 +4547,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125601890</v>
+        <v>125636837</v>
       </c>
       <c r="B37" t="n">
-        <v>91690</v>
+        <v>98343</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4558,37 +4558,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>522217</v>
+        <v>522164</v>
       </c>
       <c r="R37" t="n">
-        <v>6936540</v>
+        <v>6936587</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4632,44 +4632,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Henrik Ekvall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125632368</v>
+        <v>125646893</v>
       </c>
       <c r="B38" t="n">
-        <v>98364</v>
+        <v>98343</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4679,13 +4679,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>522245</v>
+        <v>522204</v>
       </c>
       <c r="R38" t="n">
-        <v>6936456</v>
+        <v>6936495</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4709,22 +4709,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:17</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:17</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4739,44 +4729,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125632401</v>
+        <v>125646892</v>
       </c>
       <c r="B39" t="n">
-        <v>100525</v>
+        <v>98343</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4786,13 +4776,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>522046</v>
+        <v>522130</v>
       </c>
       <c r="R39" t="n">
-        <v>6936397</v>
+        <v>6936481</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4816,22 +4806,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:09</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:09</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4846,12 +4826,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5490,32 +5470,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125646893</v>
+        <v>125632368</v>
       </c>
       <c r="B46" t="n">
-        <v>98343</v>
+        <v>98364</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5525,13 +5505,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>522204</v>
+        <v>522245</v>
       </c>
       <c r="R46" t="n">
-        <v>6936495</v>
+        <v>6936456</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5555,12 +5535,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5575,44 +5565,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125646892</v>
+        <v>125632401</v>
       </c>
       <c r="B47" t="n">
-        <v>98343</v>
+        <v>100525</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5622,13 +5612,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>522130</v>
+        <v>522046</v>
       </c>
       <c r="R47" t="n">
-        <v>6936481</v>
+        <v>6936397</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5652,12 +5642,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5672,12 +5672,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -9319,7 +9319,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125632377</v>
+        <v>125632554</v>
       </c>
       <c r="B83" t="n">
         <v>98343</v>
@@ -9350,17 +9350,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>522237</v>
+        <v>522125</v>
       </c>
       <c r="R83" t="n">
-        <v>6936417</v>
+        <v>6936477</v>
       </c>
       <c r="S83" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9384,22 +9384,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9414,60 +9404,60 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125632593</v>
+        <v>125632420</v>
       </c>
       <c r="B84" t="n">
-        <v>98343</v>
+        <v>98364</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>522125</v>
+        <v>522236</v>
       </c>
       <c r="R84" t="n">
-        <v>6936475</v>
+        <v>6936446</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9491,12 +9481,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9511,19 +9511,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125632554</v>
+        <v>125632377</v>
       </c>
       <c r="B85" t="n">
         <v>98343</v>
@@ -9554,17 +9554,17 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
+          <t>Stor-Gravberget, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>522125</v>
+        <v>522237</v>
       </c>
       <c r="R85" t="n">
-        <v>6936477</v>
+        <v>6936417</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9588,12 +9588,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9608,60 +9618,60 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125632420</v>
+        <v>125632593</v>
       </c>
       <c r="B86" t="n">
-        <v>98364</v>
+        <v>98343</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Sundsvallstjärnen, Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>522236</v>
+        <v>522125</v>
       </c>
       <c r="R86" t="n">
-        <v>6936446</v>
+        <v>6936475</v>
       </c>
       <c r="S86" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9685,22 +9695,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9715,12 +9715,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -10757,32 +10757,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125646894</v>
+        <v>125632333</v>
       </c>
       <c r="B97" t="n">
-        <v>98343</v>
+        <v>80076</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10792,13 +10792,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>522227</v>
+        <v>522235</v>
       </c>
       <c r="R97" t="n">
-        <v>6936562</v>
+        <v>6936598</v>
       </c>
       <c r="S97" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10822,12 +10822,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10842,44 +10852,44 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125632344</v>
+        <v>125646900</v>
       </c>
       <c r="B98" t="n">
-        <v>98343</v>
+        <v>78973</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10889,13 +10899,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>522268</v>
+        <v>521975</v>
       </c>
       <c r="R98" t="n">
-        <v>6936556</v>
+        <v>6936372</v>
       </c>
       <c r="S98" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10919,22 +10929,17 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10949,44 +10954,44 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125646886</v>
+        <v>125632348</v>
       </c>
       <c r="B99" t="n">
-        <v>98343</v>
+        <v>78973</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10996,13 +11001,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>522109</v>
+        <v>522241</v>
       </c>
       <c r="R99" t="n">
-        <v>6936414</v>
+        <v>6936518</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11026,12 +11031,22 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11046,44 +11061,44 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125632333</v>
+        <v>125646894</v>
       </c>
       <c r="B100" t="n">
-        <v>80076</v>
+        <v>98343</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11093,13 +11108,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>522235</v>
+        <v>522227</v>
       </c>
       <c r="R100" t="n">
-        <v>6936598</v>
+        <v>6936562</v>
       </c>
       <c r="S100" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11123,22 +11138,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11153,44 +11158,44 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125646900</v>
+        <v>125632344</v>
       </c>
       <c r="B101" t="n">
-        <v>78973</v>
+        <v>98343</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R